--- a/dane/produkty/macierz_iMapServer.xlsx
+++ b/dane/produkty/macierz_iMapServer.xlsx
@@ -1705,7 +1705,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Serwer startuje w kilka minut na dowolnym srodowisku IT. Eliminuje tygodniowe wdrozenia reczne i ryzyko bledow konfiguracyjnych. Latwe przenoszenie miedzy srodowiskami (test -&gt; produkcja).</t>
+          <t>Serwer startuje w kilka minut na dowolnym środowisku IT. Eliminuje tygodniowe wdrożenia ręczne i ryzyko błędów konfiguracyjnych. Łatwe przenoszenie między środowiskami (test -&gt; produkcja).</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Wszystkie ustawienia systemu mozna zmienic w jednym pliku tekstowym - bez angazowania programistow. Upraszcza utrzymanie i przyspiesza reakcje na zmiany wymagan.</t>
+          <t>Wszystkie ustawienia systemu można zmienić w jednym pliku tekstowym — bez angażowania programistów. Upraszcza utrzymanie i przyspiesza reakcję na zmiany wymagań.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Analitycy i specjalisci GIS moga pisac wlasne skrypty analityczne korzystajac z gotowego, profesjonalnego srodowiska - bez instalowania narzedzi na swoich komputerach.</t>
+          <t>Analitycy i specjaliści GIS mogą pisać własne skrypty analityczne korzystając z gotowego, profesjonalnego środowiska — bez instalowania narzędzi na swoich komputerach.</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Koszt licencji jest przewidywalny i niezalezny od liczby uzytkownikow - firma placi za serwer, nie za kazdego pracownika. Ulatwia planowanie budzetu IT.</t>
+          <t>Koszt licencji jest przewidywalny i niezależny od liczby użytkowników — firma płaci za serwer, nie za każdego pracownika. Ułatwia planowanie budżetu IT.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Dane geograficzne organizacji pozostaja wylacznie na jej wlasnych serwerach. Kluczowe dla urzedow, sluzb i firm z wymogami bezpieczenstwa lub certyfikacja ISO 27001.</t>
+          <t>Dane geograficzne organizacji pozostają wyłącznie na jej własnych serwerach. Kluczowe dla urzędów, służb i firm z wymogami bezpieczeństwa lub certyfikacją ISO 27001.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Uzytkownicy widza mapy generowane dynamicznie - zawsze aktualne, bez koniecznosci recznego odswiezania. Kompatybilne z popularnymi przegladarkami mapowymi (QGIS, ArcGIS Pro).</t>
+          <t>Użytkownicy widzą mapy generowane dynamicznie — zawsze aktualne, bez konieczności ręcznego odświeżania. Kompatybilne z popularnymi przeglądarkami mapowymi (QGIS, ArcGIS Pro).</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Umozliwia edycje danych przestrzennych bezposrednio przez przegladarke lub aplikacje mobilna. Pracownicy terenowi moga aktualizowac dane z tabletu - zmiany od razu widoczne dla calej organizacji.</t>
+          <t>Umożliwia edycję danych przestrzennych bezpośrednio przez przeglądarkę lub aplikację mobilną. Pracownicy terenowi mogą aktualizować dane z tabletu — zmiany od razu widoczne dla całej organizacji.</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Mapy w postaci gotowych kafelkow laduja sie blyskawicznie nawet przy duzej liczbie uzytkownikow. Idealne dla portali publicznych z tysiarcami odwiedzajacych dziennie.</t>
+          <t>Mapy w postaci gotowych kafli ładują się błyskawicznie nawet przy dużej liczbie użytkowników. Idealne dla portali publicznych z tysiącami odwiedzających dziennie.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Zdjecia lotnicze i satelitarne dostepne jako usluga - uzytkownicy przegladaja je plynnie, bez pobierania gigabajtow danych na komputer.</t>
+          <t>Zdjęcia lotnicze i satelitarne dostępne jako usługa — użytkownicy przeglądają je płynnie, bez pobierania gigabajtów danych na komputer.</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Umozliwia prezentacje i analize danych 3D (budynki, rzezba terenu) bez specjalistycznego oprogramowania - wystarczy przegladarka lub prosta aplikacja.</t>
+          <t>Zdjęcia lotnicze, ortofotomapy i modele terenu przetwarzane na serwerze w chwili wyświetlania — użytkownik widzi obraz z nałożoną analizą (np. cieniowanie terenu, NDVI) bez generowania i przechowywania kopii danych.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Modele trojwymiarowe budynkow i infrastruktury dostepne on-line dla urbanistow, architektow i zarzadcow nieruchomosci.</t>
+          <t>Modele trójwymiarowe budynków i infrastruktury dostępne on-line dla urbanistów, architektów i zarządców nieruchomości.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Umozliwia wykonywanie obliczen geometrycznych (odleglosci, pola, przeciecia) przez zewnetrzne aplikacje - bez kupowania osobnych bibliotek matematycznych.</t>
+          <t>Umożliwia wykonywanie obliczeń geometrycznych (odległości, pola, przecięcia) przez zewnętrzne aplikacje — bez kupowania osobnych bibliotek matematycznych.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Automatyzacja powtarzalnych analiz przestrzennych (np. generowanie raportow, bufory, przeliczenia) bez recznej pracy. Skraca czas realizacji procesow z godzin do minut.</t>
+          <t>Automatyzacja powtarzalnych analiz przestrzennych (np. generowanie raportów, bufory, przeliczenia) bez ręcznej pracy. Skraca czas realizacji procesów z godzin do minut.</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Duze zbiory punktow (np. zgloszenia, wypadki, pomiary) automatycznie grupowane w klastry na mapie - czytelny obraz rozkladu zjawisk zamiast chaotycznej chmury punktow.</t>
+          <t>Duże zbiory punktów (np. zgłoszenia, wypadki, pomiary) automatycznie grupowane w klastry na mapie — czytelny obraz rozkładu zjawisk zamiast chaotycznej chmury punktów.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Dane z iMapServer sa dostepne w kazdej aplikacji GIS obslugujacej standard WMS. Brak uzaleznienia od jednego dostawcy oprogramowania.</t>
+          <t>Dane z iMapServer są dostępne w każdej aplikacji GIS obsługującej standard WMS. Brak uzależnienia od jednego dostawcy oprogramowania.</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr"/>
@@ -3079,7 +3079,11 @@
       <c r="AT17" s="6" t="inlineStr"/>
       <c r="AU17" s="6" t="inlineStr"/>
       <c r="AV17" s="6" t="inlineStr"/>
-      <c r="AW17" s="6" t="inlineStr"/>
+      <c r="AW17" s="6" t="inlineStr">
+        <is>
+          <t>Potwierdzona wyłącznie wersja 1.3.0 (pl.gispartner.imapserver.wms.version, domyślnie 1.3.0 — configuration/configuration/parameters.md:360). Wersja 1.1.1 nie ma potwierdzenia w bazie wiedzy; brak parametru typu acceptVersions. Plik services-type/wms.md jest pusty (0 B). Do potwierdzenia: czy 1.1.1 jest nadal serwowane.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -3114,7 +3118,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Dane wektorowe pobieralne do zewnetrznych systemow i narzedzi (QGIS, ETL) w standardowym formacie OGC. Integracja z rejestrowymi bazami danych.</t>
+          <t>Dane wektorowe pobieralne do zewnętrznych systemów i narzędzi (QGIS, ETL) w standardowym formacie OGC. Integracja z rejestrowymi bazami danych.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -3138,7 +3142,7 @@
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr"/>
@@ -3174,7 +3178,11 @@
       <c r="AT18" s="6" t="inlineStr"/>
       <c r="AU18" s="6" t="inlineStr"/>
       <c r="AV18" s="6" t="inlineStr"/>
-      <c r="AW18" s="6" t="inlineStr"/>
+      <c r="AW18" s="6" t="inlineStr">
+        <is>
+          <t>WFS jako usługa serwerowa jest w trakcie implementacji: changelog 5.1.2060 (2026-02-02) "pierwsza postać GetFeatures", 5.1.2098 "Początki generowania Capa", 5.1.2106 (2026-02-26) "GetFeature zamiast GetFeatures" — nazwa operacji zmieniona na ostatnim buildzie. Operacja Transaction i numer wersji protokołu nie mają potwierdzenia (brak parametru wfs.version; sekcja OGC w parameters.md zawiera tylko WMTS, WMS i WPS). WFS jako źródło danych (IMS-5.2.07) pozostaje potwierdzony. Do potwierdzenia: zakres operacji i wersja protokołu w wersji wydanej.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -3209,7 +3217,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Gotowe kafelki w standardzie WMTS - kompatybilne z QGIS, ArcGIS, OpenLayers i wszystkimi popularnymi narzedzami GIS bez zadnej konfiguracji.</t>
+          <t>Gotowe kafle w standardzie WMTS — kompatybilne z QGIS, ArcGIS, OpenLayers i wszystkimi popularnymi narzędziami GIS bez żadnej konfiguracji.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -3308,7 +3316,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Nowoczesne, RESTowe API do danych przestrzennych - kompatybilne z najnowszymi standardami europejskimi (INSPIRE) i wymaganiami srodowisk cloud-native.</t>
+          <t>Nowoczesne, RESTowe API do danych przestrzennych — kompatybilne z najnowszymi standardami europejskimi (INSPIRE) i wymaganiami środowisk cloud-native.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -3403,7 +3411,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Mozliwosc zadawania precyzyjnych pytan o dane (np. dzialki pow. &gt; 1 ha w gminie X) w zrozumialym jezyku. Nie wymaga pisania SQL przez uzytkownika koncowego.</t>
+          <t>Możliwość zadawania precyzyjnych pytań o dane (np. działki pow. &gt; 1 ha w gminie X) w zrozumiałym języku. Nie wymaga pisania SQL przez użytkownika końcowego.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -3498,7 +3506,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Zaawansowane filtrowanie danych: po geometrii, atrybutach, czasie, statystykach - w jednym zadaniu. Mniej zapytan do serwera = szybsze aplikacje.</t>
+          <t>Zaawansowane filtrowanie danych: po geometrii, atrybutach, czasie, statystykach — w jednym zadaniu. Mniej zapytań do serwera = szybsze aplikacje.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -3593,7 +3601,7 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Mozliwosc precyzyjnego okreslenia topologicznych relacji przestrzennych miedzy obiektami (np. czy granica dzialki A dotyka granicy dzialki B). Przydatne w kontrolach jakosci danych.</t>
+          <t>Możliwość precyzyjnego określenia topologicznych relacji przestrzennych między obiektami (np. czy granica działki A dotyka granicy działki B). Przydatne w kontrolach jakości danych.</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -3688,7 +3696,7 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Mozliwosc przegladania danych wedlug stanu na dowolna date w przeszlosci - bez duplikowania bazy danych. Kluczowe dla ewidencji, gdzie historia zmian jest wymagana prawnie.</t>
+          <t>Możliwość przeglądania danych według stanu na dowolną datę w przeszłości — bez duplikowania bazy danych. Kluczowe dla ewidencji, gdzie historia zmian jest wymagana prawnie.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -3783,7 +3791,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Tworzenie wyliczanych pol (np. wskaznik zabudowy, pelny adres z osobnych kolumn) bez modyfikowania struktury bazy danych. Oszczedza czas i eliminuje ryzyko bledow migracji.</t>
+          <t>Tworzenie wyliczanych pól (np. wskaźnik zabudowy, pełny adres z osobnych kolumn) bez modyfikowania struktury bazy danych. Oszczędza czas i eliminuje ryzyko błędów migracji.</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -3878,7 +3886,7 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Wyniki zapytan mozna zwrocic od razu ze stylem graficznym (kolor, grubosc linii) - aplikacje klienckie nie musza samodzielnie definiowac symboliki.</t>
+          <t>Wyniki zapytań można zwrócić od razu ze stylem graficznym (kolor, grubość linii) — aplikacje klienckie nie muszą samodzielnie definiować symboliki.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -3973,7 +3981,7 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Filtrowanie zagregowanych wynikow (np. tylko gminy, gdzie suma powierzchni &gt; 1000 ha) w jednym zapytaniu - zastepuje przetwarzanie po stronie klienta.</t>
+          <t>Filtrowanie zagregowanych wyników (np. tylko gminy, gdzie suma powierzchni &gt; 1000 ha) w jednym zapytaniu — zastępuje przetwarzanie po stronie klienta.</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -4068,7 +4076,7 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Operacje na zbiorach danych (suma, iloczyn, roznica) - np. obiekty wspolne dla dwoch warstw. Eliminuje reczne porownywanie w tabelkach.</t>
+          <t>Operacje na zbiorach danych (suma, iloczyn, różnica) — np. obiekty wspólne dla dwóch warstw. Eliminuje ręczne porównywanie w tabelkach.</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -4163,7 +4171,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Eksport widoku mapy jako obrazu rastrowego do dokumentow, prezentacji i raportow. Formatowanie gotowe do druku.</t>
+          <t>Eksport widoku mapy jako obrazu rastrowego do dokumentów, prezentacji i raportów. Formatowanie gotowe do druku.</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -4258,7 +4266,7 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Klikniecie punktu na mapie zwraca atrybuty wszystkich obiektow w tym miejscu - podstawa kazdej interaktywnej aplikacji mapowej.</t>
+          <t>Klikniecie punktu na mapie zwraca atrybuty wszystkich obiektów w tym miejscu — podstawa każdej interaktywnej aplikacji mapowej.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -4353,7 +4361,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Eksport danych do SQLite (offline dla aplikacji mobilnych), GeoPackage, modeli 3D (GLB/OBJ) bez koniecznosci korzystania z osobnych narzedzi konwersji.</t>
+          <t>Eksport danych do SQLite (offline dla aplikacji mobilnych), GeoPackage, modeli 3D (GLB/OBJ) bez konieczności korzystania z osobnych narzędzi konwersji.</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -4448,7 +4456,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Administratorzy moga tworzyc, modyfikowac i usuwac konfiguracje map przez API - automatyzacja zarzadzania bez logowania do panelu.</t>
+          <t>Administratorzy mogą tworzyć, modyfikować i usuwać konfiguracje map przez API — automatyzacja zarządzania bez logowania do panelu.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -4543,7 +4551,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Automatyczne generowanie kafelkow na zadanie - zawsze aktualne bez recznego odbudowywania cache.</t>
+          <t>Automatyczne generowanie kafli na zadanie — zawsze aktualne bez ręcznego odbudowywania cache.</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -4638,7 +4646,7 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Przejrzysty podzial na bazy, schematy i tabele - administratorzy widza cala strukture danych w jednym miejscu i moga zarzadzac uprawnieniami na kazdym poziomie.</t>
+          <t>Przejrzysty podział na bazy, schematy i tabele — administratorzy widzą cala strukturę danych w jednym miejscu i mogą zarządzać uprawnieniami na każdym poziomie.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -4733,7 +4741,7 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Bezposrednie odpytywanie tabel bazodanowych przez API - umozliwia budowanie raportow i integracji bez tworzenia osobnych widokow w uslugach mapowych.</t>
+          <t>Bezpośrednie odpytywanie tabel bazodanowych przez API — umożliwia budowanie raportów i integracji bez tworzenia osobnych widoków w usługach mapowych.</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -4828,7 +4836,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Pelna edycja danych (dodawanie, aktualizacja, usuwanie obiektow) przez bezpieczne API - bez bezposredniego dostepu do bazy danych przez uzytkownika.</t>
+          <t>Pełna edycja danych (dodawanie, aktualizacja, usuwanie obiektów) przez bezpieczne API — bez bezpośredniego dostępu do bazy danych przez użytkownika.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -4923,7 +4931,7 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Masowe przeliczenie wartosci atrybutow (np. aktualizacja pola status dla tysiecy rekordow) w jednej operacji - bez recznej edycji.</t>
+          <t>Masowe przeliczenie wartości atrybutów (np. aktualizacja pola status dla tysięcy rekordów) w jednej operacji — bez ręcznej edycji.</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
@@ -5018,7 +5026,7 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Dodawanie nowych pol do tabel przez API bez interwencji administratora bazy danych - przyspiesza rozwoj systemu.</t>
+          <t>Dodawanie nowych pol do tabel przez API bez interwencji administratora bazy danych — przyspiesza rozwój systemu.</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
@@ -5113,7 +5121,7 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Definiowanie powiazan miedzy tabelami (np. dzialka &lt;-&gt; wlasciciel) - dane powiazane dostepne w jednym zapytaniu.</t>
+          <t>Definiowanie powiązań między tabelami (np. działka &lt;-&gt; właściciel) — dane powiązane dostępne w jednym zapytaniu.</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
@@ -5208,7 +5216,7 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Tworzenie logicznych widokow na dane (np. tylko aktywne obiekty danego uzytkownika) bez tworzenia kopii fizycznych danych.</t>
+          <t>Tworzenie logicznych widoków na dane (np. tylko aktywne obiekty danego użytkownika) bez tworzenia kopii fizycznych danych.</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -5303,7 +5311,7 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Automatyczne sledzenie historii zmian w tabeli - kazda modyfikacja zapisywana z data. Spelnienie wymogan prawnych (ewidencje, audyty) bez dodatkowych rozwiazan.</t>
+          <t>Automatyczne śledzenie historii zmian w tabeli — każda modyfikacja zapisywana z data. Spełnienie wymogan prawnych (ewidencje, audyty) bez dodatkowych rozwiązań.</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -5398,7 +5406,7 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Przechowywanie i serwowanie plikow (zdjecia, dokumenty, skany) powiazanych z obiektami przestrzennymi - kompletna dokumentacja w jednym miejscu.</t>
+          <t>Przechowywanie i serwowanie plików (zdjęcia, dokumenty, skany) powiązanych z obiektami przestrzennymi — kompletna dokumentacja w jednym miejscu.</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -5493,7 +5501,7 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Listy dopuszczalnych wartosci dla pol (np. typy uzytkow gruntowych) zarzadzane centralnie - spojnosc i poprawnosc danych we wszystkich aplikacjach.</t>
+          <t>Listy dopuszczalnych wartości dla pol (np. typy użytków gruntowych) zarządzane centralnie — spójność i poprawność danych we wszystkich aplikacjach.</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
@@ -5588,7 +5596,7 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Przyspieszenie zapytan przestrzennych przez indeksy - uzytkownik otrzymuje wyniki w sekundy nawet dla milionow obiektow.</t>
+          <t>Przyspieszenie zapytań przestrzennych przez indeksy — użytkownik otrzymuje wyniki w sekundy nawet dla milionów obiektów.</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
@@ -5683,7 +5691,7 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Zabezpieczenie danych przed rownoczesna edycja przez wielu uzytkownikow - eliminacja nadpisywania zmian w srodowiskach wielouzytkownikowych.</t>
+          <t>Zabezpieczenie danych przed równoczesną edycją przez wielu użytkowników — eliminacja nadpisywania zmian w środowiskach wieloużytkownikowych.</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
@@ -5778,7 +5786,7 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Precyzyjne zarzadzanie kluczami glownymi i identyfikatorami - spojnosc danych przy integracji z zewnetrznymi systemami (GML, EGiB, EMUiA).</t>
+          <t>Precyzyjne zarządzanie kluczami głównymi i identyfikatorami — spójność danych przy integracji z zewnętrznymi systemami (GML, EGiB, EMUiA).</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
@@ -5873,7 +5881,7 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Mozliwosc definiowania wlasnych funkcji obliczeniowych (np. obliczenie klasy bonitacji, przeliczenie podatku) dostepnych we wszystkich zapytaniach.</t>
+          <t>Możliwość definiowania własnych funkcji obliczeniowych (np. obliczenie klasy bonitacji, przeliczenie podatku) dostępnych we wszystkich zapytaniach.</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
@@ -5968,7 +5976,7 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Utrzymanie porzadku w bazie danych przez usuwanie nieuzywanych tabel i schematow - bez bezposredniego dostepu do silnika bazy danych.</t>
+          <t>Utrzymanie porządku w bazie danych przez usuwanie nieużywanych tabel i schematów — bez bezpośredniego dostępu do silnika bazy danych.</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
@@ -6063,7 +6071,7 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Jedno, spojne API REST obsluguje wszystkie funkcje systemu - integracja z dowolnym systemem informatycznym (ERP, CRM, portale) przez standardowe wywolania HTTP.</t>
+          <t>Jedno, spojne API REST obsługuje wszystkie funkcje systemu — integracja z dowolnym systemem informatycznym (ERP, CRM, portale) przez standardowe wywołania HTTP.</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
@@ -6158,7 +6166,7 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Wyszukiwanie obiektow na mapie po atrybutach i lokalizacji - fundament kazdej aplikacji GIS dla uzytkownikow koncowych.</t>
+          <t>Wyszukiwanie obiektów na mapie po atrybutach i lokalizacji — fundament każdej aplikacji GIS dla użytkowników końcowych.</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
@@ -6253,7 +6261,7 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Pobieranie duzych zbiorow danych stronami - aplikacje laduja dane plynnie bez przeciazania serwera i klienta.</t>
+          <t>Pobieranie dużych zbiorów danych stronami — aplikacje ładują dane płynnie bez przeciążania serwera i klienta.</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
@@ -6348,7 +6356,7 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Wyliczanie wartosci na biezaco (np. pelny adres z osobnych pol, wskazniki finansowe) - bez koniecznosci modyfikowania struktury bazy.</t>
+          <t>Wyliczanie wartości na bieżąco (np. pełny adres z osobnych pól, wskaźniki finansowe) — bez konieczności modyfikowania struktury bazy.</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
@@ -6443,7 +6451,7 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Jeden klik na mapie moze pobrac dane powiazane z obiektem (np. klikniecie dzialki -&gt; lista wlascicieli, historia transakcji) - bez kolejnych recznych wyszukan.</t>
+          <t>Jeden klik na mapie może pobrać dane powiązane z obiektem (np. klikniecie działki -&gt; lista właścicieli, historia transakcji) — bez kolejnych ręcznych wyszukań.</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
@@ -6538,7 +6546,7 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Logiczne widoki na dane (np. tylko moje zadania, aktywne zgloszenia) bez tworzenia osobnych tabel - kazdy uzytkownik widzi to, czego potrzebuje.</t>
+          <t>Logiczne widoki na dane (np. tylko moje zadania, aktywne zgłoszenia) bez tworzenia osobnych tabel — każdy użytkownik widzi to, czego potrzebuje.</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
@@ -6633,7 +6641,7 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Kazdy uzytkownik automatycznie widzi tylko swoje dane lub dane swojej organizacji - bezpieczenstwo i prywatnosc bez rozbudowanej logiki w aplikacji klienckiej.</t>
+          <t>Każdy użytkownik automatycznie widzi tylko swoje dane lub dane swojej organizacji — bezpieczeństwo i prywatność bez rozbudowanej logiki w aplikacji klienckiej.</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -6728,7 +6736,7 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Automatyczne wypelnianie pol na podstawie wczesniej wprowadzonych danych - przyspiesza prace edytorow danych terenowych.</t>
+          <t>Automatyczne wypełnianie pol na podstawie wcześniej wprowadzonych danych — przyspiesza pracę edytorów danych terenowych.</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
@@ -6823,7 +6831,7 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Przechowywanie i udostepnianie obrazow, dokumentow i innych plikow binarnych bezposrednio w tabeli przestrzennej.</t>
+          <t>Przechowywanie i udostępnianie obrazów, dokumentów i innych plików binarnych bezpośrednio w tabeli przestrzennej.</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
@@ -6918,7 +6926,7 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Opisy pol i aliasy dostepne w kilku jezykach - system GIS obsluguje wielojezyczne organizacje bez duplikowania konfiguracji.</t>
+          <t>Opisy pol i aliasy dostępne w kilku językach — system GIS obsługuje wielojęzyczne organizacje bez duplikowania konfiguracji.</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
@@ -7013,7 +7021,7 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Slowniki wartosci dozwolonych (np. typy drog, klasy budynkow) zarzadzane centralnie - poprawiaja jakosc danych i ulatwiaja raportowanie.</t>
+          <t>Słowniki wartości dozwolonych (np. typy dróg, klasy budynków) zarządzane centralnie — poprawiają jakość danych i ułatwiają raportowanie.</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
@@ -7108,7 +7116,7 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Bezpieczna komunikacja HTTPS i uwierzytelnianie tokenami JWT - standard bezpieczenstwa dla aplikacji webowych i mobilnych.</t>
+          <t>Bezpieczna komunikacja HTTPS i uwierzytelnianie tokenami JWT (OAuth 2.0) na poziomie API — integracja z aplikacjami webowymi i mobilnymi bez przesyłania danych logowania przy każdym żądaniu.</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
@@ -7203,7 +7211,7 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Administratorzy moga publikowac, aktualizowac i wycofywac aplikacje webowe z jednego miejsca - bez angazowania dzialu IT do kazdej zmiany.</t>
+          <t>Administratorzy mogą publikować, aktualizować i wycofywać aplikacje webowe z jednego miejsca — bez angażowania działu IT do każdej zmiany.</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
@@ -7298,7 +7306,7 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Pelna edycja konfiguracji aplikacji webowych przez API - automatyzacja wdrozen i aktualizacji.</t>
+          <t>Pełna edycja konfiguracji aplikacji webowych przez API — automatyzacja wdrożeń i aktualizacji.</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
@@ -7393,7 +7401,7 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Kontrola kto moze korzystac z ktorych aplikacji - bezpieczne srodowisko wieloorganizacyjne (np. kilka wydzialow, kilka klientow).</t>
+          <t>Kontrola kto może korzystać z których aplikacji — bezpieczne środowisko wieloorganizacyjne (np. kilka wydziałów, kilka klientów).</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
@@ -7488,7 +7496,7 @@
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Miniatura podgladu aplikacji widoczna w katalogu zasobow - uzytkownicy latwo odnajduja wlasciwa aplikacje bez otwierania kazdej z osobna.</t>
+          <t>Miniatura podglądu aplikacji widoczna w katalogu zasobów — użytkownicy łatwo odnajdują właściwa aplikacje bez otwierania każdej z osobną.</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
@@ -7583,7 +7591,7 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Mozliwosc rozszerzenia systemu o niestandardowe operacje analityczne napisane przez dzial IT w Javie - system rosnie razem z potrzebami organizacji.</t>
+          <t>Możliwość rozszerzenia systemu o niestandardowe operacje analityczne napisane przez dział IT w Javie — system rośnie razem z potrzebami organizacji.</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
@@ -7678,7 +7686,7 @@
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Analitycy GIS moga pisac skrypty w Pythonie i uruchamiac je jako uslugi serwerowe - gotowe srodowisko, brak konfiguracji.</t>
+          <t>Analitycy GIS mogą pisać skrypty w Pythonie i uruchamiać je jako usługi serwerowe — gotowe środowisko, brak konfiguracji.</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
@@ -7773,7 +7781,7 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Zlozone analizy wieloetapowe (np. bufor -&gt; selekcja -&gt; statystyki -&gt; eksport) definiowane raz, uruchamiane automatycznie - eliminacja recznej pracy powtarzalnej.</t>
+          <t>Złożone analizy wieloetapowe (np. bufor -&gt; selekcja -&gt; statystyki -&gt; eksport) definiowane raz, uruchamiane automatycznie — eliminacja ręcznej pracy powtarzalnej.</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
@@ -7868,7 +7876,7 @@
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Analizy uruchamiane automatycznie o zadanej porze (np. codziennie o 6:00 generuje raport dla zarzadu) - bez recznego uruchamiania przez pracownika.</t>
+          <t>Analizy uruchamiane automatycznie o zadanej porze (np. codziennie o 6:00 generuje raport dla zarządu) — bez ręcznego uruchamiania przez pracownika.</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
@@ -7963,7 +7971,7 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Proste analizy dzialaja natychmiast (odpowiedz w sekundy). Zlozone obliczenia dzialaja w tle - uzytkownik nie czeka i moze wykonywac inne czynnosci.</t>
+          <t>Proste analizy działają natychmiast (odpowiedz w sekundy). Złożone obliczenia działają w tle — użytkownik nie czeka i może wykonywać inne czynności.</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
@@ -8058,7 +8066,7 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Tworzenie stref buforowych (zasieg oddzialywania), wyznaczanie srodkow ciezkosci obiektow, obliczanie dlugosci i powierzchni - podstawowe operacje analityczne.</t>
+          <t>Tworzenie stref buforowych (zasięg oddziaływania), wyznaczanie środków ciężkości obiektów, obliczanie długości i powierzchni — podstawowe operacje analityczne.</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
@@ -8153,7 +8161,7 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Upraszczanie ksztaltow obiektow, podzial linii na rowne odcinki, dzielenie duzych poligonow - operacje przygotowania danych.</t>
+          <t>Upraszczanie kształtów obiektów, podział linii na równe odcinki, dzielenie dużych poligonów — operacje przygotowania danych.</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
@@ -8248,7 +8256,7 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Rozbijanie obiektow wieloczesciowych na skladowe, ekstrakcja wierzcholkow, wyrownywanie do siatki - narzedzia kontroli jakosci geometrii.</t>
+          <t>Rozbijanie obiektów wieloczęściowych na składowe, ekstrakcja wierzchołków, wyrównywanie do siatki — narzędzia kontroli jakości geometrii.</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
@@ -8343,7 +8351,7 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Obroty, skalowanie, przesuniecia geometrii oraz transformacje miedzy ukladami wspolrzednych - przygotowanie danych do integracji i kartowania.</t>
+          <t>Obroty, skalowanie, przesunięcia geometrii oraz transformacje między układami współrzędnych — przygotowanie danych do integracji i kartowania.</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
@@ -8438,7 +8446,7 @@
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Minimalne okragi opisane, generowanie siatek punktow probkowania, importowanie punktow z list CSV - narzedzia planowania pomiarow i inwentaryzacji.</t>
+          <t>Minimalne okręgi opisane, generowanie siatek punktów próbkowania, importowanie punktów z list CSV — narzędzia planowania pomiarów i inwentaryzacji.</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
@@ -8533,7 +8541,7 @@
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Obliczanie przeciecia, roznicy i sumy zbiorow obiektow przestrzennych - np. ktore dzialki NIE leza w zadnej strefie ochronnej.</t>
+          <t>Obliczanie przecięcia, różnicy i sumy zbiorów obiektów przestrzennych — np. które działki NIE leżą w żadnej strefie ochronnej.</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
@@ -8628,7 +8636,7 @@
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Scalanie wielu obiektow w jeden (np. wszystkie odcinki drogi w jedna calosc), kopiowanie danych miedzy warstwami.</t>
+          <t>Scalanie wielu obiektów w jeden (np. wszystkie odcinki drogi w jedna całość), kopiowanie danych między warstwami.</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
@@ -8723,7 +8731,7 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Usuwanie zbednych obiektow wedlug atrybutow lub lokalizacji - czyszczenie i odchudzanie zbiorow danych.</t>
+          <t>Usuwanie zbędnych obiektów według atrybutów lub lokalizacji — czyszczenie i odchudzanie zbiorów danych.</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
@@ -8818,7 +8826,7 @@
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Automatyczne przypisywanie atrybutow z jednej warstwy do drugiej na podstawie lokalizacji (np. dodanie nazwy gminy do kazdego punktu adresowego).</t>
+          <t>Automatyczne przypisywanie atrybutów z jednej warstwy do drugiej na podstawie lokalizacji (np. dodanie nazwy gminy do każdego punktu adresowego).</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -8913,7 +8921,7 @@
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Obliczanie statystyk (suma, srednia, min, max) per obszar lub kategoria - np. laczna powierzchnia uzytkow rolnych per powiat.</t>
+          <t>Obliczanie statystyk (suma, średnia, min, max) per obszar lub kategoria — np. łączna powierzchnia użytków rolnych per powiat.</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
@@ -9008,7 +9016,7 @@
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>Analiza gestosci zjawisk, wykrywanie skupisk (hot-spots), wyznaczanie najblizszego sasiada, generowanie diagramow Woronoja.</t>
+          <t>Analiza gęstości zjawisk, wykrywanie skupisk (hot-spots), wyznaczanie najbliższego sąsiada, generowanie diagramów Woronoja.</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
@@ -9103,7 +9111,7 @@
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>Zamiana adresow na wspolrzedne geograficzne z uzyciem Nominatim/OpenStreetMap - lokalizowanie obiektow na mapie na podstawie adresu tekstowego.</t>
+          <t>Zamiana adresów na współrzędne geograficzne z użyciem Nominatim/OpenStreetMap — lokalizowanie obiektów na mapie na podstawie adresu tekstowego.</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
@@ -9198,7 +9206,7 @@
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>Generowanie map cieniowania (widocznosc uksztaltowania terenu), map nachylen zboczy, wycinanie obszarow z rastrow - podstawowe analizy terenowe.</t>
+          <t>Generowanie map cieniowania (widoczność ukształtowania terenu), map nachyleń zboczy, wycinanie obszarów z rastrów — podstawowe analizy terenowe.</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
@@ -9293,7 +9301,7 @@
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Konwersja danych rastrowych (np. ortofoto, NMT) na wektory i odwrotnie - przygotowanie danych do analiz lub wizualizacji.</t>
+          <t>Konwersja danych rastrowych (np. ortofoto, NMT) na wektory i odwrotnie — przygotowanie danych do analiz lub wizualizacji.</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
@@ -9388,7 +9396,7 @@
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>Laczenie wielu rastrow w jeden, obliczanie statystyk na rastrze (np. srednia wysokosc), analiza pokrycia terenu.</t>
+          <t>Łączenie wielu rastrów w jeden, obliczanie statystyk na rastrze (np. średnia wysokość), analiza pokrycia terenu.</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -9483,7 +9491,7 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Import danych z roznych formatow i eksport do wielu formatow - integracja z zewnetrznymi dostawcami danych (GUGiK, BDOT, OSM).</t>
+          <t>Import danych z różnych formatów i eksport do wielu formatów — integracja z zewnętrznymi dostawcami danych (GUGiK, BDOT, OSM).</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
@@ -9578,7 +9586,7 @@
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>Tworzenie, modyfikacja i usuwanie tabel i schematow bazodanowych przez API - pelne zarzadzanie struktura danych bez narzedzi bazodanowych.</t>
+          <t>Tworzenie, modyfikacja i usuwanie tabel i schematów bazodanowych przez API — pełne zarządzanie struktura danych bez narzędzi bazodanowych.</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
@@ -9673,7 +9681,7 @@
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Zarzadzanie kolekcjami zdiec lotniczych i satelitarnych (mozaiki) oraz trojwymiarowymi modelami terenu i budynkow.</t>
+          <t>Zarządzanie kolekcjami zdjęć lotniczych i satelitarnych (mozaiki) oraz trójwymiarowymi modelami terenu i budynków.</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
@@ -9768,7 +9776,7 @@
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>Wizualizacja danych rastrowych w roznych skalach kolorow (gradienty, klasyfikacje) - np. mapa temperatur, poziomow halasu, zagrozen powodziowych.</t>
+          <t>Wizualizacja danych rastrowych w różnych skalach kolorów (gradienty, klasyfikacje) — np. mapa temperatur, poziomów hałasu, zagrożeń powodziowych.</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
@@ -9859,7 +9867,7 @@
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Przetwarzanie rastrow w locie: zmiana kontrastu, wyostrzanie, NDVI, kompozyty - uzytkownik widzi przetworzone obrazy bez generowania kopii.</t>
+          <t>Przetwarzanie rastrów w locie: zmiana kontrastu, wyostrzanie, NDVI, kompozyty — użytkownik widzi przetworzone obrazy bez generowania kopii.</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
@@ -9950,7 +9958,7 @@
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>Pre-generowane kafelki rastrowe (zdjecia lotnicze, mapy topograficzne) serwowane blyskawicznie przy duzym obciazeniu.</t>
+          <t>Pre-generowane kafle rastrowe (zdjęcia lotnicze, mapy topograficzne) serwowane błyskawicznie przy dużym obciążeniu.</t>
         </is>
       </c>
       <c r="H90" s="6" t="inlineStr">
@@ -10041,7 +10049,7 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Obsluga ponad 200 formatow i ukladow danych rastrowych - czytanie danych z dowolnego zrodla bez konwersji wstepnej.</t>
+          <t>Obsługa ponad 200 formatów i układów danych rastrowych — czytanie danych z dowolnego źródła bez konwersji wstępnej.</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
@@ -10132,7 +10140,7 @@
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>Automatyczne upraszczanie i agregowanie danych rastrowych dla mniejszych skal - mapa wyglada czytelnie na kazdym poziomie przyblizenia.</t>
+          <t>Automatyczne upraszczanie i agregowanie danych rastrowych dla mniejszych skal — mapa wygląda czytelnie na każdym poziomie przybliżenia.</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr">
@@ -10223,7 +10231,7 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>Zarzadzanie cache rastrowym przez API: czyszczenie, odbudowa, monitorowanie - automatyzacja konserwacji bez recznej interwencji.</t>
+          <t>Zarządzanie cache rastrowym przez API: czyszczenie, odbudowa, monitorowanie — automatyzacja konserwacji bez ręcznej interwencji.</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
@@ -10314,7 +10322,7 @@
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>Dane przestrzenne przechowywane w wiodacej open-source bazie GIS. Pelna obsluga zaawansowanej geometrii, analiz i replikacji.</t>
+          <t>Dane przestrzenne przechowywane w wiodącej open-source bazie GIS. Pełna obsługa zaawansowanej geometrii, analiz i replikacji.</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
@@ -10405,7 +10413,7 @@
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>Integracja z Oracle - standardowa baza danych w duzych organizacjach korporacyjnych i administracji publicznej. Obie geometrie Oracle natywnie wspierane.</t>
+          <t>Integracja z Oracle — standardowa baza danych w dużych organizacjach korporacyjnych i administracji publicznej. Obie geometrie Oracle natywnie wspierane.</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
@@ -10496,7 +10504,7 @@
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>Automatyczne filtrowanie danych na poziomie bazy - rozni uzytkownicy widza rozne podzbiory tych samych tabel (np. dane tylko swojej gminy). Bezpieczenstwo bez logiki w aplikacji.</t>
+          <t>Automatyczne filtrowanie danych na poziomie bazy — różni użytkownicy widzą różne podzbiory tych samych tabel (np. dane tylko swojej gminy). Bezpieczeństwo bez logiki w aplikacji.</t>
         </is>
       </c>
       <c r="H96" s="6" t="inlineStr">
@@ -10587,7 +10595,7 @@
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Integracja z Microsoft SQL Server i Active Directory (NTLM) - uzytkownicy loguja sie do systemu GIS tymi samymi danymi co do komputera sluzbowego.</t>
+          <t>Integracja z Microsoft SQL Server i Active Directory (NTLM) — użytkownicy logują się do systemu GIS tymi samymi danymi co do komputera służbowego.</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
@@ -10678,7 +10686,7 @@
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>Lekka baza plikowa (jeden plik) - idealna do dystrybucji danych w terenie (inspektorzy, tablety) i jako format wymiany offline.</t>
+          <t>Lekka baza w jednym pliku jako źródło danych — wdrożenia bez serwera bazodanowego oraz praca w terenie bez łącza.</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
@@ -10769,7 +10777,7 @@
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>Analityczna baza danych DuckDB jako zrodlo - umozliwia analize bardzo duzych zbiorow tabelarycznych bez osobnej hurtowni danych.</t>
+          <t>Analityczna baza danych DuckDB jako źródło — umożliwia analizę bardzo dużych zbiorów tabelarycznych bez osobnej hurtowni danych.</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
@@ -10860,7 +10868,7 @@
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>Dane z zewnetrznych serwisow WFS (np. GUGIK, EMUiA, BDOT) dostepne jako warstwy mapy - aktualne dane bez kopiowania do lokalnej bazy.</t>
+          <t>Dane z zewnętrznych serwisów WFS (np. GUGIK, EMUiA, BDOT) dostępne jako warstwy mapy — aktualne dane bez kopiowania do lokalnej bazy.</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
@@ -10951,7 +10959,7 @@
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>Nowoczesne zewnetrzne API (np. europejskie rejestry INSPIRE) jako zywe zrodlo danych - zawsze aktualne dane bez lokalnej kopii.</t>
+          <t>Nowoczesne zewnętrzne API (np. europejskie rejestry INSPIRE) jako żywe źródło danych — zawsze aktualne dane bez lokalnej kopii.</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
@@ -11042,7 +11050,7 @@
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>Mozliwosc korzystania z plikow Geodatabase (format Esri) jako zrodla danych - ulatwia migracje z dotychczasowego srodowiska ArcGIS.</t>
+          <t>Możliwość korzystania z plików Geodatabase (format Esri) jako źródła danych — ułatwia migracje z dotychczasowego środowiska ArcGIS.</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
@@ -11133,7 +11141,7 @@
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>Zewnetrzne uslugi WMS (np. mapa zasadnicza, ortofoto z geoportal.gov.pl) jako warstwy tla w mapach - bez pobierania danych.</t>
+          <t>Zewnętrzne usługi WMS (np. mapa zasadnicza, ortofoto z geoportal.gov.pl) jako warstwy tła w mapach — bez pobierania danych.</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
@@ -11224,7 +11232,7 @@
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>Precyzyjna kontrola kto widzi co i co moze robic: administrator systemu -&gt; administrator bazy -&gt; edytor schematu -&gt; edytor tabeli -&gt; edytor pola. Bezpieczenstwo na kazdym poziomie.</t>
+          <t>Precyzyjna kontrola kto widzi co i co może robić: administrator systemu -&gt; administrator bazy -&gt; edytor schematu -&gt; edytor tabeli -&gt; edytor pola. Bezpieczeństwo na każdym poziomie.</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
@@ -11315,7 +11323,7 @@
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>Bezpieczne logowanie przez tokeny - sesja nie wygasa nieoczekiwanie, dane logowania nie sa przesylane przy kazdym zadaniu.</t>
+          <t>Bezpieczne logowanie przez tokeny — sesja nie wygasa nieoczekiwanie, dane logowania nie są przesyłane przy każdym zadaniu.</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
@@ -11406,7 +11414,7 @@
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>Dostep do systemu tylko z okreslonych adresow IP (np. siec wewnetrzna urzedu) - ochrona przed nieautoryzowanym dostepem z internetu.</t>
+          <t>Dostęp do systemu tylko z określonych adresów IP (np. siec wewnętrzna urzędu) — ochrona przed nieautoryzowanym dostępem z internetu.</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
@@ -11497,7 +11505,7 @@
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>Logowanie domenowe Active Directory - uzytkownicy uzywaja tych samych danych co do sieci firmowej, bez dodatkowych hasel GIS.</t>
+          <t>Logowanie domenowe Active Directory — użytkownicy używają tych samych danych co do sieci firmowej, bez dodatkowych haseł GIS.</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
@@ -11588,7 +11596,7 @@
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>Szyfrowanie komunikacji i tokenowe uwierzytelnianie - standard bezpieczenstwa dla aplikacji webowych. Spelnienie wymagan Krajowych Ram Interoperacyjnosci (KRI).</t>
+          <t>Szyfrowanie komunikacji i tokenowe uwierzytelnianie — standard bezpieczeństwa dla aplikacji webowych. Spełnienie wymagań Krajowych Ram Interoperacyjności (KRI).</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
@@ -11679,7 +11687,7 @@
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>Bezpieczenstwo danych realizowane na poziomie bazy Oracle - eliminuje ryzyko obejscia filtrow przez bezposredni dostep SQL.</t>
+          <t>Bezpieczeństwo danych realizowane na poziomie bazy Oracle — eliminuje ryzyko obejścia filtrów przez bezpośredni dostęp SQL.</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
@@ -11770,7 +11778,7 @@
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>Sledzenie kto, kiedy i co zmienil w danych. Raportowanie dostepu do danych osobowych - niezbedne dla compliance RODO.</t>
+          <t>Śledzenie kto, kiedy i co zmienił w danych. Raportowanie dostępu do danych osobowych — niezbedne dla compliance RODO.</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
@@ -11861,7 +11869,7 @@
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>Granularna kontrola dostepu do aplikacji webowych per uzytkownik lub rola - kazdy dzial/klient widzi tylko swoje aplikacje.</t>
+          <t>Granularna kontrola dostępu do aplikacji webowych per użytkownik lub rola — każdy dział/klient widzi tylko swoje aplikacje.</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
@@ -11952,7 +11960,7 @@
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>Mozliwosc ukrycia wrazliwych pol (np. PESEL, dane wlasciciela) dla okreslonych uzytkownikow - ochrona danych osobowych na poziomie API.</t>
+          <t>Możliwość ukrycia wrażliwych pol (np. PESEL, dane właściciela) dla określonych użytkowników — ochrona danych osobowych na poziomie API.</t>
         </is>
       </c>
       <c r="H112" s="6" t="inlineStr">
@@ -12043,7 +12051,7 @@
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>Graficzny panel do zarzadzania calym systemem - administratorzy nie musza edytowac plikow konfiguracyjnych ani pisac skryptow.</t>
+          <t>Graficzny panel do zarządzania całym systemem — administratorzy nie muszą edytować plików konfiguracyjnych ani pisać skryptów.</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
@@ -12134,7 +12142,7 @@
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>Uruchamianie, zatrzymywanie i konfigurowanie uslug mapowych przez prosty interfejs webowy - zarzadzanie bez dostepu SSH do serwera.</t>
+          <t>Uruchamianie, zatrzymywanie i konfigurowanie usług mapowych przez prosty interfejs webowy — zarządzanie bez dostępu SSH do serwera.</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
@@ -12225,7 +12233,7 @@
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>Dodawanie, testowanie i usuwanie polaczen z bazami danych - weryfikacja polaczenia w czasie rzeczywistym bez pisania kodu.</t>
+          <t>Dodawanie, testowanie i usuwanie połączeń z bazami danych — weryfikacja polaczenia w czasie rzeczywistym bez pisania kodu.</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
@@ -12316,7 +12324,7 @@
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>Tworzenie uzytkownikow, przypisywanie rol i uprawnien przez interfejs graficzny - bez SQL i skryptow.</t>
+          <t>Tworzenie użytkowników, przypisywanie rol i uprawnień przez interfejs graficzny — bez SQL i skryptów.</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
@@ -12407,7 +12415,7 @@
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>Podglad logow, statystyk uzycia i bledow w czasie rzeczywistym - szybka diagnostyka problemow bez analizowania plikow na serwerze.</t>
+          <t>Podgląd logów, statystyk użycia i błędów w czasie rzeczywistym — szybka diagnostyka problemów bez analizowania plików na serwerze.</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
@@ -12498,7 +12506,7 @@
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>Harmonogramowanie i zarzadzanie generowaniem kafelkow przez interfejs webowy - bez skryptow i linii polecen.</t>
+          <t>Harmonogramowanie i zarządzanie generowaniem kafli przez interfejs webowy — bez skryptów i linii poleceń.</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
@@ -12589,7 +12597,7 @@
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>Podglad warstwy lub uslugi bezposrednio w panelu admina - weryfikacja ze dane sa prawidlowe przed opublikowaniem dla uzytkownikow.</t>
+          <t>Podgląd warstwy lub usługi bezpośrednio w panelu admina — weryfikacja że dane są prawidłowe przed opublikowaniem dla użytkowników.</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
@@ -12680,7 +12688,7 @@
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>Uruchamianie, monitorowanie i zarzadzanie zadaniami geoprzetwarzania przez graficzny panel - bez CLI.</t>
+          <t>Uruchamianie, monitorowanie i zarządzanie zadaniami geoprzetwarzania przez graficzny panel — bez CLI.</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
@@ -12771,7 +12779,7 @@
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>Publikowanie i zarzadzanie aplikacjami webowymi przez panel admina - wdrazanie zmian bez dzialu IT.</t>
+          <t>Publikowanie i zarządzanie aplikacjami webowymi przez panel admina — wdrażanie zmian bez działu IT.</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
@@ -12862,7 +12870,7 @@
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>Topologiczna baza danych sieci (drogi, kanalizacja, sieci elektryczne) - podloze dla analiz sieciowych.</t>
+          <t>Topologiczna baza danych sieci (drogi, kanalizacja, sieci elektryczne) — podłoże dla analiz sieciowych.</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr">
@@ -12957,7 +12965,7 @@
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>Obliczanie obszarow dostepnych w X minut jazdy/marszu (izochory) - planowanie lokalizacji, analiza dostepnosci uslug, ewakuacja.</t>
+          <t>Obliczanie obszarów dostępnych w X minut jazdy/marszu (izochory) — planowanie lokalizacji, analiza dostępności usług, ewakuacja.</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
@@ -13052,7 +13060,7 @@
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>Wyznaczanie optymalnych tras (najkrotsza, najszybsza, z objazdem przeszkod) - logistyka, planowanie inspekcji terenowych, nawigacja.</t>
+          <t>Wyznaczanie optymalnych tras (najkrótsza, najszybsza, z objazdem przeszkód) — logistyka, planowanie inspekcji terenowych, nawigacja.</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
@@ -13147,7 +13155,7 @@
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>Automatyczna weryfikacja spojnosci sieci (wezly, polaczenia, kierunkowosc) - gwarancja poprawnosci analiz sieciowych.</t>
+          <t>Automatyczna weryfikacja spójności sieci (węzły, polaczenia, kierunkowość) — gwarancja poprawności analiz sieciowych.</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
@@ -13242,7 +13250,7 @@
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>Zaawansowane wizualizacje statystyczne: kartodiagramy (slupki per gmina na mapie) i kartogramy (mapa choropleth) - czytelna komunikacja danych dla decydentow.</t>
+          <t>Zaawansowane wizualizacje statystyczne: kartodiagramy (słupki per gmina na mapie) i kartogramy (mapa choropleth) — czytelna komunikacja danych dla decydentów.</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
@@ -13337,7 +13345,7 @@
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>Analiza skupisk i wzorow przestrzennych w danych (np. czy wypadki sa przypadkowe czy skupione w konkretnych miejscach) - wspomaganie decyzji opartych na danych.</t>
+          <t>Analiza skupisk i wzorów przestrzennych w danych (np. czy wypadki są przypadkowe czy skupione w konkretnych miejscach) — wspomaganie decyzji opartych na danych.</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
@@ -13432,7 +13440,7 @@
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>Dane dostepne przez API w standardowym formacie JSON/GeoJSON - integracja z dowolnym nowoczesnym systemem informatycznym i narzedzami open-source.</t>
+          <t>Dane dostępne przez API w standardowym formacie JSON/GeoJSON — integracja z dowolnym nowoczesnym systemem informatycznym i narzędziami open-source.</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
@@ -13523,7 +13531,7 @@
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>Mapy generowane jako obrazy PNG/JPG - gotowe do wklejenia w raporty, prezentacje PowerPoint, dokumenty Word.</t>
+          <t>Mapy generowane jako obrazy PNG/JPG — gotowe do wklejenia w raporty, prezentacje PowerPoint, dokumenty Word.</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
@@ -13614,7 +13622,7 @@
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>Eksport danych do KMZ/KML - otwieranie w Google Earth, Google My Maps, aplikacjach mobilnych.</t>
+          <t>Eksport danych do KMZ/KML — otwieranie w Google Earth, Google My Maps, aplikacjach mobilnych.</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
@@ -13705,7 +13713,7 @@
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>Eksport atrybutow do pliku CSV - analiza w Excelu, importowanie do systemow ERP/CRM, przetwarzanie w Pythonie/R.</t>
+          <t>Eksport atrybutów do pliku CSV — analiza w Excelu, importowanie do systemów ERP/CRM, przetwarzanie w Pythonie/R.</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
@@ -13796,7 +13804,7 @@
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>Format GeoPackage (jeden plik z wieloma warstwami) - standard do pracy offline w terenie i wymiany danych z QGIS.</t>
+          <t>Format GeoPackage (jeden plik z wieloma warstwami) — standard do pracy offline w terenie i wymiany danych z QGIS.</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
@@ -13887,7 +13895,7 @@
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>Kafelki wektorowe (PBF/MVT) - najszybszy format dla nowoczesnych aplikacji webowych renderujacych mapy po stronie klienta.</t>
+          <t>Kafle wektorowe (PBF/MVT) — najszybszy format dla nowoczesnych aplikacji webowych renderujacych mapy po stronie klienta.</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -13978,7 +13986,7 @@
       </c>
       <c r="G134" s="6" t="inlineStr">
         <is>
-          <t>Eksport do SQLite/SpatiaLite - lekka baza plikowa idealna dla aplikacji mobilnych i dystrybucji danych bez serwera.</t>
+          <t>Eksport do SQLite/SpatiaLite — lekka baza plikowa idealna dla aplikacji mobilnych i dystrybucji danych bez serwera.</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -14069,7 +14077,7 @@
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>Shapefile - klasyczny format wymiany z innymi systemami GIS, CAD i zewnetrznymi partnerami.</t>
+          <t>Shapefile — klasyczny format wymiany z innymi systemami GIS, CAD i zewnętrznymi partnerami.</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -14160,7 +14168,7 @@
       </c>
       <c r="G136" s="6" t="inlineStr">
         <is>
-          <t>Eksport modeli 3D (GLB/OBJ) - wizualizacja budynkow i infrastruktury w narzedzach 3D (Blender, Unity, przegladarka WebGL).</t>
+          <t>Eksport modeli 3D (GLB/OBJ) — wizualizacja budynków i infrastruktury w narzedzach 3D (Blender, Unity, przeglądarka WebGL).</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
@@ -14249,11 +14257,7 @@
           <t>Action Message Format – binarny format dla starszych klientów Flash/Flex.</t>
         </is>
       </c>
-      <c r="G137" s="6" t="inlineStr">
-        <is>
-          <t>Format AMF do specjalistycznych zastosowan 3D i druku przestrzennego.</t>
-        </is>
-      </c>
+      <c r="G137" s="6" t="n"/>
       <c r="H137" s="6" t="inlineStr">
         <is>
           <t>format</t>
@@ -14271,7 +14275,7 @@
       </c>
       <c r="O137" s="6" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P137" s="6" t="inlineStr"/>
@@ -14307,7 +14311,11 @@
       <c r="AT137" s="6" t="inlineStr"/>
       <c r="AU137" s="6" t="inlineStr"/>
       <c r="AV137" s="6" t="inlineStr"/>
-      <c r="AW137" s="6" t="inlineStr"/>
+      <c r="AW137" s="6" t="inlineStr">
+        <is>
+          <t>Brak potwierdzenia w bazie wiedzy: zero wzmianek o AMF / Action Message Format w gp-knowledgebase (stan 2026-07-28). Udokumentowane wartości parametru f: html, json, pjson; dodatkowo PBF (pl.gispartner.imapserver.ags.pbf). Plik api/getstarted/output_formats.md jest pusty (0 B). Do potwierdzenia w kodzie: czy format jest nadal obsługiwany, czy wycofany.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -14342,7 +14350,7 @@
       </c>
       <c r="G138" s="6" t="inlineStr">
         <is>
-          <t>Podglad wynikow zapytan bezposrednio w przegladarce - szybkie testowanie i demonstracja danych bez instalowania klienta GIS.</t>
+          <t>Podgląd wyników zapytań bezpośrednio w przeglądarce — szybkie testowanie i demonstracja danych bez instalowania klienta GIS.</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -14431,7 +14439,11 @@
           <t>Bufory wokół obiektów.</t>
         </is>
       </c>
-      <c r="G139" s="6" t="inlineStr"/>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>Tworzenie stref ochronnych wokół obiektów (np. 100 m od drogi, 500 m od rzeki). Fundament analiz oddziaływania i planowania przestrzennego.</t>
+        </is>
+      </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -14526,7 +14538,11 @@
           <t>Centroidy poligonów.</t>
         </is>
       </c>
-      <c r="G140" s="6" t="inlineStr"/>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>Wyznaczanie środków ciężkości poligonów — do etykiet na mapie, analiz położenia, markery zamiast pełnych poligonów.</t>
+        </is>
+      </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -14621,7 +14637,11 @@
           <t>Długość, pole, wierzchołki, poprawność.</t>
         </is>
       </c>
-      <c r="G141" s="6" t="inlineStr"/>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>Automatyczne obliczanie długości, powierzchni, liczby wierzchołków i poprawności geometrii — podstawa kontroli jakości danych.</t>
+        </is>
+      </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -14716,7 +14736,11 @@
           <t>Uproszczenie geometrii.</t>
         </is>
       </c>
-      <c r="G142" s="6" t="inlineStr"/>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>Upraszczanie skomplikowanych granic do prostszych kształtów — szybsze mapy przeglądowe, mniejsze pliki, lepsza czytelność.</t>
+        </is>
+      </c>
       <c r="H142" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -14811,7 +14835,11 @@
           <t>Podział linii wg max długości.</t>
         </is>
       </c>
-      <c r="G143" s="6" t="inlineStr"/>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>Podział długich linii na równe odcinki — przygotowanie sieci do analiz liniowych i interpolacji atrybutów.</t>
+        </is>
+      </c>
       <c r="H143" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -14906,7 +14934,11 @@
           <t>Podział poligonów wg liczby wierzchołków.</t>
         </is>
       </c>
-      <c r="G144" s="6" t="inlineStr"/>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>Dzielenie dużych poligonów na mniejsze części — optymalizacja zbiorów dla analiz przestrzennych i wydajności bazy.</t>
+        </is>
+      </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -15001,7 +15033,11 @@
           <t>Rozbicie multigeometrii na części.</t>
         </is>
       </c>
-      <c r="G145" s="6" t="inlineStr"/>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>Rozbijanie obiektów wieloczęściowych na pojedyncze — uporządkowanie danych przed analizą, eliminacja multigeometrii.</t>
+        </is>
+      </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -15096,7 +15132,11 @@
           <t>Punkt per wierzchołek geometrii.</t>
         </is>
       </c>
-      <c r="G146" s="6" t="inlineStr"/>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>Ekstrakcja wierzchołków geometrii jako osobnych punktów — analiza dokładności digitalizacji, generowanie siatek próbkowania.</t>
+        </is>
+      </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -15191,7 +15231,11 @@
           <t>Zaokrąglenie do siatki.</t>
         </is>
       </c>
-      <c r="G147" s="6" t="inlineStr"/>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>Wyrównywanie współrzędnych do siatki — normalizacja danych z różnych źródeł, eliminacja mikrobłędów topologicznych.</t>
+        </is>
+      </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -15286,7 +15330,11 @@
           <t>Przekształcenie przez macierz afiniczną.</t>
         </is>
       </c>
-      <c r="G148" s="6" t="inlineStr"/>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>Geometryczne przekształcenia obiektów (rotacja, skalowanie, przesunięcie) — dostosowanie danych do docelowego układu przestrzennego.</t>
+        </is>
+      </c>
       <c r="H148" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -15381,7 +15429,11 @@
           <t>Przeliczenie do nowego CRS.</t>
         </is>
       </c>
-      <c r="G149" s="6" t="inlineStr"/>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>Zmiana układu współrzędnych całych zbiorów danych — migracja między PUWG 92, 2000, WGS84, web Mercator.</t>
+        </is>
+      </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -15476,7 +15528,11 @@
           <t>X↔Y w geometrii.</t>
         </is>
       </c>
-      <c r="G150" s="6" t="inlineStr"/>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>Zamiana kolejności X/Y — naprawa danych z błędną kolejnością współrzędnych bez ręcznej edycji.</t>
+        </is>
+      </c>
       <c r="H150" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -15571,7 +15627,11 @@
           <t>Najmniejsze koło otaczające zbiór.</t>
         </is>
       </c>
-      <c r="G151" s="6" t="inlineStr"/>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>Generowanie najmniejszego okręgu otaczającego obiekt — analiza zasięgu, kompaktowości kształtów.</t>
+        </is>
+      </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -15666,7 +15726,11 @@
           <t>Generowanie punktów wewnątrz geometrii.</t>
         </is>
       </c>
-      <c r="G152" s="6" t="inlineStr"/>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>Tworzenie siatki punktów próbkowania wewnątrz poligonów — planowanie inwentaryzacji terenowej, rozmieszczenie pomiarów.</t>
+        </is>
+      </c>
       <c r="H152" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -15761,7 +15825,11 @@
           <t>Punkty z listy współrzędnych (x,y,CRS).</t>
         </is>
       </c>
-      <c r="G153" s="6" t="inlineStr"/>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>Import lokalizacji z tabeli (x, y, CRS) jako warstwa punktowa — geokodowanie współrzędnymi zamiast adresami.</t>
+        </is>
+      </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -15856,7 +15924,11 @@
           <t>Iloczyn przestrzenny zbiorów.</t>
         </is>
       </c>
-      <c r="G154" s="6" t="inlineStr"/>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>Obliczanie części wspólnej dwóch warstw — np. działki w strefie zalewowej, tereny w zasięgu planowanej inwestycji.</t>
+        </is>
+      </c>
       <c r="H154" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -15951,7 +16023,11 @@
           <t>Zbiór 1 minus część wspólna z 2.</t>
         </is>
       </c>
-      <c r="G155" s="6" t="inlineStr"/>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>Odejmowanie geometrii — co pozostaje po wyjęciu jednego zbioru (np. tereny niezabudowane = gmina minus zabudowa).</t>
+        </is>
+      </c>
       <c r="H155" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -16046,7 +16122,11 @@
           <t>Obiekty wyłącznie z jednego ze zbiorów.</t>
         </is>
       </c>
-      <c r="G156" s="6" t="inlineStr"/>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>Obiekty które są tylko w jednym ze zbiorów — wykrywanie zmian między dwoma wersjami danych ewidencyjnych.</t>
+        </is>
+      </c>
       <c r="H156" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -16141,7 +16221,11 @@
           <t>Pocięcie zbioru 1 geometrią zbioru 2.</t>
         </is>
       </c>
-      <c r="G157" s="6" t="inlineStr"/>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>Przecinanie obiektów przez inną linię lub granice — podział działek przez planowaną drogę lub granicę administracyjną.</t>
+        </is>
+      </c>
       <c r="H157" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -16236,7 +16320,11 @@
           <t>Clip do zasięgu zbioru 2.</t>
         </is>
       </c>
-      <c r="G158" s="6" t="inlineStr"/>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>Przycinanie warstwy do obszaru zainteresowania — ograniczenie danych do granic gminy, powiatu lub projektu.</t>
+        </is>
+      </c>
       <c r="H158" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -16331,7 +16419,11 @@
           <t>Połączenie wielu zbiorów w jeden.</t>
         </is>
       </c>
-      <c r="G159" s="6" t="inlineStr"/>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>Łączenie wielu zbiorów danych w jeden — integracja danych z różnych gmin lub źródeł w jeden zbiór roboczy.</t>
+        </is>
+      </c>
       <c r="H159" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -16426,7 +16518,11 @@
           <t>Dissolve z opcjonalnymi statystykami.</t>
         </is>
       </c>
-      <c r="G160" s="6" t="inlineStr"/>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>Scalanie obiektów o tych samych atrybutach w jeden — np. granice gmin scalane do powiatów, odcinki drogi w jeden przebieg.</t>
+        </is>
+      </c>
       <c r="H160" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -16521,7 +16617,11 @@
           <t>Kopia zbioru (z filtracją).</t>
         </is>
       </c>
-      <c r="G161" s="6" t="inlineStr"/>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>Tworzenie kopii warstwy lub wybranego podzbioru — archiwizacja stanu danych przed edycją lub eksportem.</t>
+        </is>
+      </c>
       <c r="H161" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -16616,7 +16716,11 @@
           <t>Filtr wg warunków atrybutowych.</t>
         </is>
       </c>
-      <c r="G162" s="6" t="inlineStr"/>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>Wybór obiektów spełniających warunek atrybutowy — filtrowanie zbioru do analizy bez usuwania pozostałych danych.</t>
+        </is>
+      </c>
       <c r="H162" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -16711,7 +16815,11 @@
           <t>Obiekty bez części wspólnej z zbiorem 2.</t>
         </is>
       </c>
-      <c r="G163" s="6" t="inlineStr"/>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>Obiekty które NIE mają części wspólnej z innym zbiorem — np. budynki poza strefami ochronnymi.</t>
+        </is>
+      </c>
       <c r="H163" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -16806,7 +16914,11 @@
           <t>Obiekty z częścią wspólną z zbiorem 2.</t>
         </is>
       </c>
-      <c r="G164" s="6" t="inlineStr"/>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>Obiekty mające część wspólną z innym zbiorem — np. budynki na terenach zagrożeń powodziowych.</t>
+        </is>
+      </c>
       <c r="H164" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -16901,7 +17013,11 @@
           <t>Usunięcie zduplikowanych punktów.</t>
         </is>
       </c>
-      <c r="G165" s="6" t="inlineStr"/>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>Eliminacja zduplikowanych wierzchołków geometrii — czyszczenie danych z powtarzającymi się punktami.</t>
+        </is>
+      </c>
       <c r="H165" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -16996,7 +17112,11 @@
           <t>Usunięcie wg kryterium atrybutowego.</t>
         </is>
       </c>
-      <c r="G166" s="6" t="inlineStr"/>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>Usuwanie wybranych obiektów z warstwy na podstawie warunku atrybutowego — czyszczenie danych niespełniających kryterium jakości.</t>
+        </is>
+      </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -17091,7 +17211,11 @@
           <t>Usunięcie obiektów z częścią wspólną z 2.</t>
         </is>
       </c>
-      <c r="G167" s="6" t="inlineStr"/>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>Usuwanie obiektów nakładających się z inną warstwą — eliminacja obiektów w strefach wykluczenia.</t>
+        </is>
+      </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -17186,7 +17310,11 @@
           <t>Join przez relację przestrzenną.</t>
         </is>
       </c>
-      <c r="G168" s="6" t="inlineStr"/>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>Automatyczne przypisanie atrybutów z jednej warstwy do drugiej na podstawie położenia — np. nazwa gminy do każdego budynku, numer działki do adresu.</t>
+        </is>
+      </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -17281,7 +17409,11 @@
           <t>Join przez wspólny klucz.</t>
         </is>
       </c>
-      <c r="G169" s="6" t="inlineStr"/>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>Łączenie danych tabelarycznych (CSV, XLS) z warstwa przestrzenna przez wspólny klucz — wzbogacenie geometrii o dane statystyczne.</t>
+        </is>
+      </c>
       <c r="H169" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -17376,7 +17508,11 @@
           <t>Sum/avg/min/max pkt/lin w poligonach.</t>
         </is>
       </c>
-      <c r="G170" s="6" t="inlineStr"/>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>Obliczanie statystyk (suma, średnia, min, max) dla obiektów wewnątrz poligonów — np. średnia wysokość budynków per działka.</t>
+        </is>
+      </c>
       <c r="H170" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -17471,7 +17607,11 @@
           <t>Wyrażenia matematyczne na atrybutach.</t>
         </is>
       </c>
-      <c r="G171" s="6" t="inlineStr"/>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>Masowe wyliczanie i aktualizacja wartości pól na podstawie wyrażeń matematycznych — przeliczenia, kategorie, wskaźniki dla całego zbioru naraz.</t>
+        </is>
+      </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -17566,7 +17706,11 @@
           <t>Gęstość pkt w poligonach referencyjnych.</t>
         </is>
       </c>
-      <c r="G172" s="6" t="inlineStr"/>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>Wizualizacja gęstości zjawisk punktowych w poligonach referencyjnych — identyfikacja hot spotów incydentów, zgłoszeń, inwestycji.</t>
+        </is>
+      </c>
       <c r="H172" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -17661,7 +17805,11 @@
           <t>Najbliższy obiekt z odległością.</t>
         </is>
       </c>
-      <c r="G173" s="6" t="inlineStr"/>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>Wyznaczanie najbliższego obiektu i odległości do niego dla każdego elementu — analiza sąsiedztwa, dostępność usług.</t>
+        </is>
+      </c>
       <c r="H173" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -17756,7 +17904,11 @@
           <t>Tesselacja Woronoja z wierzchołków.</t>
         </is>
       </c>
-      <c r="G174" s="6" t="inlineStr"/>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>Generowanie obszarów wpływu wokół punktów — strefy obsługi placówek, zasięg stacji, obszary Thiessena.</t>
+        </is>
+      </c>
       <c r="H174" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -17851,7 +18003,11 @@
           <t>Punkt = mediana współrzędnych.</t>
         </is>
       </c>
-      <c r="G175" s="6" t="inlineStr"/>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>Wyznaczanie optymalnego punktu centralnego minimalizującego odległości — optymalna lokalizacja magazynu, centrum zdarzeń.</t>
+        </is>
+      </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -17946,7 +18102,11 @@
           <t>Identyfikacja skupisk przestrzennych.</t>
         </is>
       </c>
-      <c r="G176" s="6" t="inlineStr"/>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>Automatyczne wykrywanie skupisk przestrzennych w danych punktowych — identyfikacja hot spotów wypadków, ognisk chorob, koncentracji inwestycji.</t>
+        </is>
+      </c>
       <c r="H176" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -18041,7 +18201,11 @@
           <t>Liczba obiektów pkt/lin wewnątrz poligonów.</t>
         </is>
       </c>
-      <c r="G177" s="6" t="inlineStr"/>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>Zliczanie punktów i linii wewnątrz poligonów — liczba budynków per działka, incydenty per rejon, klienci per obszar sprzedaży.</t>
+        </is>
+      </c>
       <c r="H177" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -18136,7 +18300,11 @@
           <t>Cieniowanie reliefu z DEM.</t>
         </is>
       </c>
-      <c r="G178" s="6" t="inlineStr"/>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>Cieniowanie rzeźby terenu z modelu wysokościowego (DEM) — czytelna wizualizacja ukształtowania terenu na mapie.</t>
+        </is>
+      </c>
       <c r="H178" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -18231,7 +18399,11 @@
           <t>Mapa spadków z DEM.</t>
         </is>
       </c>
-      <c r="G179" s="6" t="inlineStr"/>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>Mapa nachyleń stoku z DEM — analiza zagrożenia osuwiskowego, dobór użytków rolnych, planowanie infrastruktury.</t>
+        </is>
+      </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -18326,7 +18498,11 @@
           <t>Przeliczenie CRS rastra.</t>
         </is>
       </c>
-      <c r="G180" s="6" t="inlineStr"/>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>Zmiana układu współrzędnych rastra — dostosowanie zdjęć lotniczych lub NMT do układu mapy projektowej.</t>
+        </is>
+      </c>
       <c r="H180" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -18421,7 +18597,11 @@
           <t>Zmiana rozdzielczości przestrzennej.</t>
         </is>
       </c>
-      <c r="G181" s="6" t="inlineStr"/>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>Zmiana rozdzielczości piksela rastra — optymalizacja dla wydajności przy dużych zbiorach lub dokładności przy analizach precyzyjnych.</t>
+        </is>
+      </c>
       <c r="H181" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -18516,7 +18696,11 @@
           <t>Przycięcie do poligonu/bbox.</t>
         </is>
       </c>
-      <c r="G182" s="6" t="inlineStr"/>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>Wycinanie fragmentu rastra do obszaru zainteresowania — ograniczenie dużego NMT lub ortofoto do obszaru projektu.</t>
+        </is>
+      </c>
       <c r="H182" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -18611,7 +18795,11 @@
           <t>Mozaikowanie wielu rastrów.</t>
         </is>
       </c>
-      <c r="G183" s="6" t="inlineStr"/>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>Łączenie wielu rastrów w mozaikę — jednolity NMT lub ortofoto z kilku arkuszy lub lotów.</t>
+        </is>
+      </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -18706,7 +18894,11 @@
           <t>Poligon/linia → raster.</t>
         </is>
       </c>
-      <c r="G184" s="6" t="inlineStr"/>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>Konwersja poligonów i linii na raster — przygotowanie danych wektorowych do analiz rastrowych.</t>
+        </is>
+      </c>
       <c r="H184" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -18801,7 +18993,11 @@
           <t>Warstwa wektorowa → raster.</t>
         </is>
       </c>
-      <c r="G185" s="6" t="inlineStr"/>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>Tworzenie rastra na podstawie wartości atrybutów warstwy wektorowej — np. mapa bonitacji gleb jako raster z wartości atrybutu.</t>
+        </is>
+      </c>
       <c r="H185" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -18896,7 +19092,11 @@
           <t>Raster → poligony.</t>
         </is>
       </c>
-      <c r="G186" s="6" t="inlineStr"/>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>Konwersja rastra klasyfikowanego na warstwę wektorową — ekstrakcja obszarów z satelitarnej klasyfikacji pokrycia terenu.</t>
+        </is>
+      </c>
       <c r="H186" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -18991,7 +19191,11 @@
           <t>Punkt per piksel z wartością.</t>
         </is>
       </c>
-      <c r="G187" s="6" t="inlineStr"/>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>Konwersja każdego piksela rastra na punkt z wartością — próbkowanie wartości wysokościowych lub spektralnych.</t>
+        </is>
+      </c>
       <c r="H187" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -19086,7 +19290,11 @@
           <t>Kontury/izolinie z rastra.</t>
         </is>
       </c>
-      <c r="G188" s="6" t="inlineStr"/>
+      <c r="G188" s="6" t="inlineStr">
+        <is>
+          <t>Generowanie poziomic i izolinii z rastra — poziomice z NMT, izobary z modelu meteorologicznego, izolinie hałasu.</t>
+        </is>
+      </c>
       <c r="H188" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -19181,7 +19389,11 @@
           <t>Min, max, mean, std, histogram.</t>
         </is>
       </c>
-      <c r="G189" s="6" t="inlineStr"/>
+      <c r="G189" s="6" t="inlineStr">
+        <is>
+          <t>Obliczanie statystyk pikselowych (min, max, średnia, odch. std.) — analiza zakresu wartości NMT lub danych pomiarowych.</t>
+        </is>
+      </c>
       <c r="H189" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -19276,7 +19488,11 @@
           <t>Zasięg danych i obszary NoData.</t>
         </is>
       </c>
-      <c r="G190" s="6" t="inlineStr"/>
+      <c r="G190" s="6" t="inlineStr">
+        <is>
+          <t>Analiza zasięgu danych rastrowych i obszarów bez danych — kontrola kompletności pokrycia przed analizą.</t>
+        </is>
+      </c>
       <c r="H190" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -19371,7 +19587,11 @@
           <t>SHP/GeoJSON/GPKG/CSV/GDB → baza.</t>
         </is>
       </c>
-      <c r="G191" s="6" t="inlineStr"/>
+      <c r="G191" s="6" t="inlineStr">
+        <is>
+          <t>Automatyczny import danych z plików (SHP, GeoJSON, GPKG, CSV, GDB) do bazy — bez ręcznego ładowania przez narzędzia bazodanowe.</t>
+        </is>
+      </c>
       <c r="H191" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -19466,7 +19686,11 @@
           <t>Inspekcja struktury przed importem.</t>
         </is>
       </c>
-      <c r="G192" s="6" t="inlineStr"/>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>Inspekcja struktury i zawartość pliku przed importem — weryfikacja pol, typów i układu bez otwierania pliku w GIS.</t>
+        </is>
+      </c>
       <c r="H192" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -19561,7 +19785,11 @@
           <t>Nowa tabela w bazie danych.</t>
         </is>
       </c>
-      <c r="G193" s="6" t="inlineStr"/>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>Programowe tworzenie nowej tabeli w bazie danych — automatyzacja tworzenia struktur w procesach ETL.</t>
+        </is>
+      </c>
       <c r="H193" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -19656,7 +19884,11 @@
           <t>Usunięcie schematu z tabelami.</t>
         </is>
       </c>
-      <c r="G194" s="6" t="inlineStr"/>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>Usuniecie schematu z wszystkimi tabelami — czyszczenie środowisk testowych i tymczasowych zbiorów roboczych.</t>
+        </is>
+      </c>
       <c r="H194" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -19751,7 +19983,11 @@
           <t>Usunięcie wybranej tabeli.</t>
         </is>
       </c>
-      <c r="G195" s="6" t="inlineStr"/>
+      <c r="G195" s="6" t="inlineStr">
+        <is>
+          <t>Usuniecie wybranej tabeli z bazy — porządkowanie po zakończeniu projektu lub po zastąpieniu nowszymi danymi.</t>
+        </is>
+      </c>
       <c r="H195" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -19846,7 +20082,11 @@
           <t>Zapytanie jako zadanie GP.</t>
         </is>
       </c>
-      <c r="G196" s="6" t="inlineStr"/>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>Wykonanie zapytania do danych jako zadanie GP — użycie pełnej logiki query (WHERE, statystyki, joins) w kontekście geoprzetwarzania.</t>
+        </is>
+      </c>
       <c r="H196" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -19941,7 +20181,11 @@
           <t>Mozaika z zestawu rastrów.</t>
         </is>
       </c>
-      <c r="G197" s="6" t="inlineStr"/>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>Tworzenie katalogu mozaiki rastrowej z zestawu plików — organizacja dużych kolekcji zdjęć do efektywnego serwowania.</t>
+        </is>
+      </c>
       <c r="H197" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -20036,7 +20280,11 @@
           <t>Import gotowej mozaiki.</t>
         </is>
       </c>
-      <c r="G198" s="6" t="inlineStr"/>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>Import gotowej mozaiki rastrowej do systemu iMapServer — szybkie udostępnianie dużych zbiorów zdjęć bez ponownego przetwarzania.</t>
+        </is>
+      </c>
       <c r="H198" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -20131,7 +20379,11 @@
           <t>Wsadowe ładowanie przez kursory DB.</t>
         </is>
       </c>
-      <c r="G199" s="6" t="inlineStr"/>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>Wsadowe ładowanie danych przez kursory bazodanowe — wysokowydajny import dużych zbiorów bez overhead'u REST API.</t>
+        </is>
+      </c>
       <c r="H199" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -20226,7 +20478,11 @@
           <t>Konwersja przez kursory DB.</t>
         </is>
       </c>
-      <c r="G200" s="6" t="inlineStr"/>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>Konwersja danych przez kursory bazodanowe — transformacja i przepisywanie dużych zbiorów między strukturami.</t>
+        </is>
+      </c>
       <c r="H200" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -20321,7 +20577,11 @@
           <t>Pakiet kafli wektorowych (.vtpk).</t>
         </is>
       </c>
-      <c r="G201" s="6" t="inlineStr"/>
+      <c r="G201" s="6" t="inlineStr">
+        <is>
+          <t>Tworzenie pakietu kafli wektorowych (.vtpk) — offline lub CDN-ready kafle dla aplikacji mobilnych i portal'i bez serwera.</t>
+        </is>
+      </c>
       <c r="H201" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -20416,7 +20676,11 @@
           <t>Pakiet scen 3D (.slpk).</t>
         </is>
       </c>
-      <c r="G202" s="6" t="inlineStr"/>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>Tworzenie pakietu scen 3D (.slpk) — offline-capable modele 3D miast i terenu dla SceneViewer.</t>
+        </is>
+      </c>
       <c r="H202" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>
@@ -20511,7 +20775,11 @@
           <t>Linear Referencing System: kalibracja, pomiar, zdarzenia na sieci.</t>
         </is>
       </c>
-      <c r="G203" s="6" t="inlineStr"/>
+      <c r="G203" s="6" t="inlineStr">
+        <is>
+          <t>Kalibracja tras, pomiar odległości na sieci, lokalizacja zdarzeń po kilometrażu (Linear Referencing) — obowiązek w systemach zarządzania drogami i sieciami.</t>
+        </is>
+      </c>
       <c r="H203" s="6" t="inlineStr">
         <is>
           <t>zadanie GP</t>

--- a/dane/produkty/macierz_iMapServer.xlsx
+++ b/dane/produkty/macierz_iMapServer.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Załącznik techniczny" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$2:$AW$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Macierz'!$A$2:$AW$236</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Załącznik techniczny'!$A$2:$M$45</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1435,7 +1435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW222"/>
+  <dimension ref="A1:AW236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="15" min="1" max="1"/>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P3" s="5" t="n"/>
@@ -1793,7 +1793,11 @@
       <c r="AT3" s="5" t="n"/>
       <c r="AU3" s="5" t="n"/>
       <c r="AV3" s="5" t="n"/>
-      <c r="AW3" s="5" t="n"/>
+      <c r="AW3" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: niepotwierdzone. Niepotwierdzone w kodzie: Obraz Docker na Ubuntu 20.04; OpenJDK 11; GDAL 3.3.2 (kod wspomina 3.4.3); Gotowe srodowisko on-premise bez dodatkowych zalezności. Sprawdzone frazy: docker, Dockerfile, ubuntu, openjdk, gdal 3. Nie znalazlem != nie istnieje: obraz zapewne budowany w osobnym repo (np. CI/DevOps). Rozbieznosc: komentarz w kodzie GDAL 3.4.3 vs opis 3.3.2. gradle.properties: java_sources_version=1.8 (zrodla Java 1.8, bez wskazania JDK 11). GDAL w iMS wymaga recznego dostarczenia natywnych bibliotek (gdal.jar w gp-imapserver-gdb/lib, libgdalalljni.so) - sugeruje, ze 'bez dodatkowych zaleznosci' dotyczy obrazu, nie kodu. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/raster/FileRaster.java; gradle.properties Dowód: W repo brak Dockerfile, docker-compose i obrazu (Glob **/Dockerfile* pusty, Grep docker/ubuntu/openjdk w yml/dockerfile bez trafien). Jedyne slady GDAL to komentarze w FileRaster.java (linie 37-53) mowiace o GDAL 3.4.3 (Windows C:\GDAL_3_4_3, Linux libgdalalljni.so/libgdal.so w /usr/local/lib64).</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55.2" customHeight="1" s="15">
       <c r="A4" s="5" t="n">
@@ -1846,7 +1850,7 @@
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P4" s="5" t="n"/>
@@ -1882,7 +1886,11 @@
       <c r="AT4" s="5" t="n"/>
       <c r="AU4" s="5" t="n"/>
       <c r="AV4" s="5" t="n"/>
-      <c r="AW4" s="5" t="n"/>
+      <c r="AW4" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Limity sesji (brak klucza o sesjach; jest tylko waznosc tokenu security.token.expiration w minutach); Wszystkie ustawienia w jednym pliku (konfiguracja jest rozproszona: application.properties + config/&lt;profil&gt;/application.properties + pliki .gdb/.map/.jgp). Wzorzec polaczen bazodanowych definiowany tez w plikach *.gdb (np. gp-imapserver-app/config/default/*.gdb) - nie tylko w application.properties. Grep 'session' w application.properties bez trafien. Przy okazji: w repo sa jawne hasla (gradle.properties smtp_password, config/gugik/gugikogcapi.gdb) - ryzyko bezpieczenstwa. Pliki: gp-imapserver-app/src/main/resources/application.properties; gp-imapserver-app/config/default/application.properties Dowód: application.properties zawiera pule polaczen (default.datasource.maximumPoolSize=10, db.ora/db.postgre/... .datasource.*), parametry bezpieczenstwa (pl.gispartner.imapserver.security.*), port (server.port=8080, server.servlet.contextPath=/ims), timeouty (spring.mvc.async.request-timeout=300000, db.ora.datasource.connectionTimeout=2500, security.token.expiration=720).</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55.2" customHeight="1" s="15">
       <c r="A5" s="5" t="n">
@@ -1935,7 +1943,7 @@
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P5" s="5" t="n"/>
@@ -1971,7 +1979,11 @@
       <c r="AT5" s="5" t="n"/>
       <c r="AU5" s="5" t="n"/>
       <c r="AV5" s="5" t="n"/>
-      <c r="AW5" s="5" t="n"/>
+      <c r="AW5" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: niepotwierdzone. Niepotwierdzone w kodzie: GeoPandas; Shapely; Rasterio; NumPy; Pandas; scikit-learn; networkx; psycopg2; cx-Oracle; Fiona; Pillow; Preinstalowanie bibliotek. Grep geopandas|rasterio|cx_Oracle|scikit|networkx|fiona (bez js) - trafienie tylko w ai/docs/agp/analiza-custom-sr-wkt.md (dokument, nie dowod). Biblioteki zapewne instalowane w obrazie Docker poza repo (requirements.txt/Dockerfile nie znalezione). Domyslne exe 'py' to launcher Windows - na Linuksie trzeba ustawic parametr exe. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/cmd/Python.java; gp-imapserver-app/config/default/python.jgp Dowód: Kod zawiera tylko zadanie GP Python (klasa Python rozszerza Cmd, domyslny exe 'py', uruchamia skrypt jako polecenie systemowe) zarejestrowane w python.jgp. Nie ma w repo listy bibliotek Pythona.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55.2" customHeight="1" s="15">
       <c r="A6" s="5" t="n">
@@ -2024,7 +2036,7 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P6" s="5" t="n"/>
@@ -2060,7 +2072,11 @@
       <c r="AT6" s="5" t="n"/>
       <c r="AU6" s="5" t="n"/>
       <c r="AV6" s="5" t="n"/>
-      <c r="AW6" s="5" t="n"/>
+      <c r="AW6" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: niepotwierdzone. Niepotwierdzone w kodzie: Model licencji per serwer / per CPU; Rok 2026. Grep licen[cs]e w java: tylko licencje bibliotek Aspose (gdb/xls/XlsUtil.java, DocUtils.java) i metadane licencji mapy (licenseName/licenseUrl). public_key.pem sluzy do weryfikacji JWT (security/jwtUserFactory.kt), nie licencji. Model licencyjny jest handlowy - nie do potwierdzenia w kodzie. Pliki: gradle.properties; gp-imapserver-app/src/main/resources/application.properties Dowód: Potwierdzona tylko wersja: gradle.properties iMapServer_version=5.1, wstrzykiwana do application.properties (pl.gispartner.imapserver.version=@iMapServer_version@). Brak mechanizmu licencjonowania per serwer/CPU.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55.2" customHeight="1" s="15">
       <c r="A7" s="5" t="n">
@@ -2113,7 +2129,7 @@
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P7" s="5" t="n"/>
@@ -2149,7 +2165,11 @@
       <c r="AT7" s="5" t="n"/>
       <c r="AU7" s="5" t="n"/>
       <c r="AV7" s="5" t="n"/>
-      <c r="AW7" s="5" t="n"/>
+      <c r="AW7" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Praca w sieciach izolowanych (nieweryfikowalne w kodzie); Certyfikacja ISO 27001 (tresc biznesowa). Opcjonalne zaleznosci zewnetrzne istnieja: Kafka (cluster.host, domyslnie zakomentowane), S3 (gdb/s3), Loki/ELK, domyslny pl.gispartner.imapserver.wizard.search.url=https://capap.gugik.gov.pl/. To ocena architektoniczna, nie pojedyncza funkcja. Pliki: gp-imapserver-app/src/main/resources/application.properties; gradle.properties Dowód: Aplikacja to samodzielny Spring Boot z osadzonym Tomcatem (server.port, tomcatVersion=9.0.105, spring_boot_version=2.7.18) bez obowiazkowych uslug chmurowych w konfiguracji domyslnej.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="69" customHeight="1" s="15">
       <c r="A8" s="5" t="n">
@@ -2206,7 +2226,7 @@
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P8" s="5" t="n"/>
@@ -2242,7 +2262,11 @@
       <c r="AT8" s="5" t="n"/>
       <c r="AU8" s="5" t="n"/>
       <c r="AV8" s="5" t="n"/>
-      <c r="AW8" s="5" t="n"/>
+      <c r="AW8" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Operacja find (brak mapowania ani stringu "find" w rest-carto). Sprawdzone: grep '"find"', '/find', findAddress w rest-carto. Poza opisem: info/metadata, setOperation, tile. Kompatybilnosc z QGIS/ArcGIS Pro nie weryfikowana w kodzie. Serwis aktywny, bez @Conditional. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/MapServer.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java Dowód: MapServer.java (/{map}/MapServer) mapuje: export (l.334-408), identify (509,544), {layer}/query (578,632), {layer}/generateRenderer (744,786), legend (213,220), layers, tile/{level}/{row}/{col}.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="69" customHeight="1" s="15">
       <c r="A9" s="5" t="n">
@@ -2335,7 +2359,11 @@
       <c r="AT9" s="5" t="n"/>
       <c r="AU9" s="5" t="n"/>
       <c r="AV9" s="5" t="n"/>
-      <c r="AW9" s="5" t="n"/>
+      <c r="AW9" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wszystkie 5 wymienionych operacji ma mapowania w kodzie (GET html/JSON i POST). Realne uprawnienia edycji zalezne od rol (properties.*.addRoles itd. domyslnie admin). Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/FeatureServer.java Dowód: FeatureServer.java (/{map}/FeatureServer) ma {layer}/query (478,533), {layer}/addFeatures (264-294), {layer}/updateFeatures (311-342), {layer}/deleteFeatures (357-394), applyEdits (154-183 oraz {layer}/applyEdits 428-461), plus zalaczniki.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55.2" customHeight="1" s="15">
       <c r="A10" s="5" t="n">
@@ -2428,7 +2456,11 @@
       <c r="AT10" s="5" t="n"/>
       <c r="AU10" s="5" t="n"/>
       <c r="AV10" s="5" t="n"/>
-      <c r="AW10" s="5" t="n"/>
+      <c r="AW10" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: Serwowanie bezposrednio z pakietu .vtpk (kod importuje/rozpakowuje vtpk do storage kafli, nie czyta paczki w locie). Sprawdzenie 'pelna kontrola symbologii' client-side: serwowane sa style (resources/styles root.json), ale ocena po stronie klienta. Nazwa 'wejscie .vtpk' tylko w GP, nie w VectorTileServer. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/VectorTileServer.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/vectorTiles/MapCreatorFromVtpk.java; gp-imapserver-app/config/default/vectorTiles.jgp Dowód: VectorTileServer.java serwuje tile/{level}/{row}/{col}.pbf, tilemap, resources/styles, sprites i fonts; zadanie GP MapCreatorFromVtpk (TILE_VALUE='vtpk', wejscie File 'file') tworzy mape z pakietu .vtpk, zarejestrowane w vectorTiles.jgp.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="41.4" customHeight="1" s="15">
       <c r="A11" s="5" t="n">
@@ -2521,7 +2553,11 @@
       <c r="AT11" s="5" t="n"/>
       <c r="AU11" s="5" t="n"/>
       <c r="AV11" s="5" t="n"/>
-      <c r="AW11" s="5" t="n"/>
+      <c r="AW11" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Brak osobnego endpointu 'RasterTileServer' - to nazwa pojeciowa; kafle rastrowe to tile w MapServer/ImageServer. LERC to osobny generator, nie wartosc enum Format. getContentType() zwraca 'image/jpg' (niestandardowy MIME) dla jpg. Pliki: gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/tile/RasterGenerator.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/tile/LercGenerator.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/MapServer.java Dowód: RasterGenerator.Format = {unknown, png32, jpg, mix}; LercGenerator (getName 'lerc') generuje kafle LERC dla float; kafle serwowane przez MapServer tile/{level}/{row}/{col} i ImageServer tile/{level}/{row}/{col}; tworzenie/bufor: createTile w MapsController.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="69" customHeight="1" s="15">
       <c r="A12" s="5" t="n">
@@ -2614,7 +2650,11 @@
       <c r="AT12" s="5" t="n"/>
       <c r="AU12" s="5" t="n"/>
       <c r="AV12" s="5" t="n"/>
-      <c r="AW12" s="5" t="n"/>
+      <c r="AW12" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Opis biznesowy mowi o analizie danych 3D (budynki) - to odpowiada SceneServer, nie ImageServer (rozbieznosc opisu biznesowego). 'Analizy' to funkcje rastrowe, nie osobne operacje analityczne. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/ImageServer.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/raster/functions/HillshadeFunction.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/raster/functions/NDVIFunction.java Dowód: ImageServer.java: exportImage, identify, tile; drawMosaic uzywa RenderingRule i RasterFunction. Pakiet carto/raster/functions: Hillshade, NDVI, Colormap, Stretch, BandArithmetic, Convolution, Grayscale, Resample i in.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="41.4" customHeight="1" s="15">
       <c r="A13" s="5" t="n">
@@ -2707,7 +2747,11 @@
       <c r="AT13" s="5" t="n"/>
       <c r="AU13" s="5" t="n"/>
       <c r="AV13" s="5" t="n"/>
-      <c r="AW13" s="5" t="n"/>
+      <c r="AW13" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Fragment mapowania geometries/{geometry} w l.268 jest zakomentowany, ale aktywny jest drugi wariant (l.349). Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/SceneServer.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/storage/scene/SlpkZipStorage.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ScenesController.java Dowód: SceneServer.java wystawia layers/{layer}, nodes, nodepages, geometries, textures, attributes; SlpkZipStorage czyta paczki .slpk (indeks .inx, EOCD); ScenesController zarzadza storage scen (reload/remove).</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55.2" customHeight="1" s="15">
       <c r="A14" s="5" t="n">
@@ -2764,7 +2808,7 @@
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P14" s="5" t="n"/>
@@ -2800,7 +2844,11 @@
       <c r="AT14" s="5" t="n"/>
       <c r="AU14" s="5" t="n"/>
       <c r="AV14" s="5" t="n"/>
-      <c r="AW14" s="5" t="n"/>
+      <c r="AW14" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: labelPoints (brak); areas jako osobna operacja (jest tylko areasAndLengths); densify jako operacja REST (densify tylko wewnetrznie w lenghtsDensifyGeodesic). Grep labelPoints|"areas|densify w geometry-server/rest-carto/geometry: brak endpointu. Pokrycie 9 z 12 wymienionych nazw (+ areasAndLengths zastepuje areas). Pliki: gp-imapserver-geometry-server/src/main/java/pl/gispartner/imapserver/rest/GeometryServerController.java; gp-imapserver-geometry-server/src/main/java/pl/gispartner/imapserver/rest/GeometryServerLibraryImpl.java Dowód: GeometryServerController (.../geometry/GeometryServer) ma endpointy: buffer, simplify, union, intersect, project, lengths, generalize, convexHull, distance, areasAndLengths oraz difference, cut, relation.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55.2" customHeight="1" s="15">
       <c r="A15" s="5" t="n">
@@ -2893,7 +2941,11 @@
       <c r="AT15" s="5" t="n"/>
       <c r="AU15" s="5" t="n"/>
       <c r="AV15" s="5" t="n"/>
-      <c r="AW15" s="5" t="n"/>
+      <c r="AW15" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: Dosłowna operacja 'checkJobStatus' (status zadania dostepny przez GET {task}/jobs/{job}, bez endpointu o tej nazwie). Tryb sync = execute, async = submitJob potwierdzone w Common.java (container.async). Zbior operacji wykracza poza opis (addProcess, addFacade, queue, jobs/*/cancel itd.). Pliki: gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/Common.java; gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/Services.java; gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/Service.java Dowód: Mapowania REST GP: {task}/execute, {task}/submitJob, {task}/jobs/{job} (status/wyniki), {task}/schedule, scheduler/{idSchedule}/*, addTask, addModel, {task}/privileges, {task}/delete, {task}/count, {task}/reload.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55.2" customHeight="1" s="15">
       <c r="A16" s="5" t="n">
@@ -2950,7 +3002,7 @@
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P16" s="5" t="n"/>
@@ -2986,7 +3038,11 @@
       <c r="AT16" s="5" t="n"/>
       <c r="AU16" s="5" t="n"/>
       <c r="AV16" s="5" t="n"/>
-      <c r="AW16" s="5" t="n"/>
+      <c r="AW16" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Osobny typ usługi klastrowania; Informacja o licznosci klastra (zapisywane jest tylko cid); Agregacja punktow w klastry w locie przy renderowaniu mapy. Dziala tylko na JDBC/PostGIS (st_ClusterDBSCAN) i nie jest w config/default (brak w default/analysis). Grep klaster|cluster|binning|heatmap|featureReduction: inne trafienia to ClusteredChart (wykres), RasterCluster (bloki rastra), Jenks (klasyfikacja) - niezwiazane. AggregateData/Aggregate w carto/gdb to laczenie tabel, nie klastrowanie punktow. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/ClusterIdentification.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Istnieje tylko zadanie GP ClusterIdentification (wejscia eps, minpoints; SQL st_ClusterDBSCAN(...) over () AS cid) zapisujace punkty z identyfikatorem klastra 'cid', zarejestrowane w config/{capap,gus,isok,sipww}/analysis.jgp.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="138" customHeight="1" s="15">
       <c r="A17" s="5" t="n">
@@ -3085,7 +3141,7 @@
       <c r="AV17" s="5" t="n"/>
       <c r="AW17" s="5" t="inlineStr">
         <is>
-          <t>Potwierdzona wyłącznie wersja 1.3.0 (pl.gispartner.imapserver.wms.version, domyślnie 1.3.0 — configuration/configuration/parameters.md:360). Wersja 1.1.1 nie ma potwierdzenia w bazie wiedzy; brak parametru typu acceptVersions. Plik services-type/wms.md jest pusty (0 B). Do potwierdzenia: czy 1.1.1 jest nadal serwowane.</t>
+          <t>Potwierdzona wyłącznie wersja 1.3.0 (pl.gispartner.imapserver.wms.version, domyślnie 1.3.0 — configuration/configuration/parameters.md:360). Wersja 1.1.1 nie ma potwierdzenia w bazie wiedzy; brak parametru typu acceptVersions. Plik services-type/wms.md jest pusty (0 B). Do potwierdzenia: czy 1.1.1 jest nadal serwowane. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Obsluga WMS 1.1.1 rownolegle z 1.3.0. WmsServiceBase.checkVersion wymaga rownosci z jedna skonfigurowana wersja (domyslnie 1.3.0), wiec 1.1.1 dziala tylko po zmianie klucza i wtedy nie dziala 1.3.0. Wyjatki serializowane jako ServiceExceptionReport 1.3.0. GetMap formaty: png, gif, tiff. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ogc/wms/controller/WmsController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ogc/wms/service/WmsServiceBase.java; gp-imapserver-app/src/main/resources/application.properties Dowód: WmsController (/{map}/wms) obsluguje GetCapabilities, GetMap, GetFeatureInfo, GetLegendGraphic (enum RequestWmsMethod); wersja z klucza pl.gispartner.imapserver.wms.version=1.3.0.</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3238,7 @@
       <c r="AV18" s="5" t="n"/>
       <c r="AW18" s="5" t="inlineStr">
         <is>
-          <t>WFS jako usługa serwerowa jest w trakcie implementacji: changelog 5.1.2060 (2026-02-02) "pierwsza postać GetFeatures", 5.1.2098 "Początki generowania Capa", 5.1.2106 (2026-02-26) "GetFeature zamiast GetFeatures" — nazwa operacji zmieniona na ostatnim buildzie. Operacja Transaction i numer wersji protokołu nie mają potwierdzenia (brak parametru wfs.version; sekcja OGC w parameters.md zawiera tylko WMTS, WMS i WPS). WFS jako źródło danych (IMS-5.2.07) pozostaje potwierdzony. Do potwierdzenia: zakres operacji i wersja protokołu w wersji wydanej.</t>
+          <t>WFS jako usługa serwerowa jest w trakcie implementacji: changelog 5.1.2060 (2026-02-02) "pierwsza postać GetFeatures", 5.1.2098 "Początki generowania Capa", 5.1.2106 (2026-02-26) "GetFeature zamiast GetFeatures" — nazwa operacji zmieniona na ostatnim buildzie. Operacja Transaction i numer wersji protokołu nie mają potwierdzenia (brak parametru wfs.version; sekcja OGC w parameters.md zawiera tylko WMTS, WMS i WPS). WFS jako źródło danych (IMS-5.2.07) pozostaje potwierdzony. Do potwierdzenia: zakres operacji i wersja protokołu w wersji wydanej. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Transaction (brak case w WfsController; inne zadanie zwraca 'Unknown WFS request'). Grep Transaction w ogc/wfs: bez wsparcia WFS-T. Zrodlo WFS: WfsDatabase.startTransaction to tylko interfejs gdb. Nie sprawdzalem pelnego zakresu odczytu (filtry) w WfsCursor. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ogc/wfs/WfsController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ogc/wfs/Wfs20.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/wfs/WfsDatabase.java Dowód: WfsController (/{map}/wfs) obsluguje GetCapabilities, DescribeFeatureType, GetFeature (domyslna wersja 2.0.0, Wfs20); gdb/wfs (WfsFactory 'wfs', WfsDatabase, WfsTable, WfsCursor) to zrodlo danych WFS; GP WfsToDBLoader.</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3301,7 @@
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P19" s="5" t="n"/>
@@ -3281,7 +3337,11 @@
       <c r="AT19" s="5" t="n"/>
       <c r="AU19" s="5" t="n"/>
       <c r="AV19" s="5" t="n"/>
-      <c r="AW19" s="5" t="n"/>
+      <c r="AW19" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Model RESTful (brak ResourceURL ani mapowania sciezek WMTS REST; w capabilities tylko KVP). Grep restful|ResourceURL|resourceType w ogc/wmts: bez trafien. Wymaga co najmniej jednego wlaczonego tileInfo w mapie, inaczej CartoException. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ogc/wmts/controller/WmtsController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ogc/wmts/service/WmtsCapabilitiesService.java; gp-imapserver-app/src/main/resources/application.properties Dowód: WmtsController (/{map}/wmts): GetCapabilities, GetTile (oraz GetFeatureInfo, GetLegendGraphic); wmts.version=1.0.0; capabilities deklaruja ograniczenie KVP (createKVPConstraint).</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55.2" customHeight="1" s="15">
       <c r="A20" s="5" t="n">
@@ -3374,7 +3434,11 @@
       <c r="AT20" s="5" t="n"/>
       <c r="AU20" s="5" t="n"/>
       <c r="AV20" s="5" t="n"/>
-      <c r="AW20" s="5" t="n"/>
+      <c r="AW20" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Opis 'dawne WFS 3.0' i INSPIRE poza kodem. Nie weryfikowalem pelnej zgodnosci z conformance classes (poza ogcapi-common-1 conf core/html/json/oas30/landing-page w l.435-439). Pliki: ogc/gp-imapserver-ogc-api-features/src/main/java/pl/gispartner/imapserver/ogc/FeaturesController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/apifeatures/APIFeaturesFactory.java; settings.gradle Dowód: FeaturesController (/{map}/apiFeatures) ma /, /api, /conformance, /collections, /collections/{layer}, /collections/{layer}/items(/{itemId}) (JSON/GeoJSON); gdb/apifeatures (APIFeaturesFactory 'apifeatures', APIFeaturesDatabase, Cursor) to zrodlo danych; modul wlaczony w settings.gradle i zalaczony w gp-imapserver-app/build.gradle.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55.2" customHeight="1" s="15">
       <c r="A21" s="5" t="n">
@@ -3467,7 +3531,11 @@
       <c r="AT21" s="5" t="n"/>
       <c r="AU21" s="5" t="n"/>
       <c r="AV21" s="5" t="n"/>
-      <c r="AW21" s="5" t="n"/>
+      <c r="AW21" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Dodatkowo MapServer.anyContext obsluguje format pdf, eps, svg, jpg/jpeg (komentarz w kodzie: 'eksperymentalne'), czego opis nie wymienia. Tresci serializeExport (pole z linkiem) nie czytano w calosci. 'CRS' realizowany parametrami imageSR/bboxSR. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/MapServer.java Dowód: MapController i MapsController maja 'export' w trzech wariantach produces: text/html, application/json (serializeExport zapisuje plik w output i zwraca odnosnik) oraz image/png; parametry: extent, size, imageSR, format, transparent, mapScale, rotation, lang, time, historicMoment. MapServer.export analogicznie (ags).</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55.2" customHeight="1" s="15">
       <c r="A22" s="5" t="n">
@@ -3560,7 +3628,11 @@
       <c r="AT22" s="5" t="n"/>
       <c r="AU22" s="5" t="n"/>
       <c r="AV22" s="5" t="n"/>
-      <c r="AW22" s="5" t="n"/>
+      <c r="AW22" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Promien = parametr tolerance (IdentifyParameters.tolerance, domyslnie 0). Nie sprawdzano domyslnej wartosci wyboru warstw (czy domyslnie 'all' czy 'top'), wiec 'z wszystkich warstw' wymaga jawnego ustawienia layers/visibility. Istnieje tez inny 'identify' w TableController (FIELD_URL/identify) - to identyfikacja LRS na polu liniowym z M, nie identify mapy. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapController.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/IdentifyType.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/IdentifyParameters.java Dowód: MapController 'identify' (HTML i JSON, linie ~170-244) wola MapComposition.identify z parametrami geometry, sr, visibility (IdentifyLayerVisibility), tolerance, extent, size, returnAttributes/Geometry/Label; IdentifyType ma wartosci top, visible, all.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="69" customHeight="1" s="15">
       <c r="A23" s="5" t="n">
@@ -3617,7 +3689,7 @@
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P23" s="5" t="n"/>
@@ -3653,7 +3725,11 @@
       <c r="AT23" s="5" t="n"/>
       <c r="AU23" s="5" t="n"/>
       <c r="AV23" s="5" t="n"/>
-      <c r="AW23" s="5" t="n"/>
+      <c r="AW23" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: twierdzenie, ze formaty SQLite/GeoPackage/OBJ/GLB sa 'niedostepne przez MapServer/FeatureServer' - kod temu przeczy: FeatureServer.query wola ten sam TableController.serialize(..., f, ...), a GdbUtil.serialize nie warunkuje tych formatow flaga esri. Niezweryfikowany dla 'maps' bezposrednio (LayerController) - zakladam ten sam serialize (nie czytano). Dla obj/glb potrzebna geometria 3D (ObjUtil/GLBUtil). Przy bledzie dla sqlite/pbf/gpkg zwracany jest JSON z bledem. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/mvc/GdbConfig.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java Dowód: GdbUtil.serialize (linie ~353 i ~493-554) obsluguje f=sqlite/gpkg (geopackage+sqlite3), obj (ObjUtil), glb (GLBUtil), pbf, shp, dxf, xlsx, csv; GdbConfig rejestruje media types dla sqlite, gpkg, obj, glb. TableController.query (databases) wywoluje serialize z parametrem f.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55.2" customHeight="1" s="15">
       <c r="A24" s="5" t="n">
@@ -3746,7 +3822,11 @@
       <c r="AT24" s="5" t="n"/>
       <c r="AU24" s="5" t="n"/>
       <c r="AV24" s="5" t="n"/>
-      <c r="AW24" s="5" t="n"/>
+      <c r="AW24" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. dpiFactor i designer i threads maja TYLKO wariant produces=text/html (brak JSON); dpiFactor ustawia container.setDpiFactor globalnie (wymaga admin), a nie per mapa; threads: map.setThreads (admin). designer to tylko strona HTML z assertCanDesigner (domyslnie rola public). Domyslne role: createMapRoles/removeMapRoles/modifyMapRoles=admin (application.properties 289-291). Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java Dowód: MapsController: create (POST, JSON), {map}/modify, {map}/remove, {map}/reload, {map}/state (zmiana MapState), {map}/generateThumbnail, {map}/privileges, designer, dpiFactor, {map}/threads - wszystkie zmapowane (linie 180-1400).</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="69" customHeight="1" s="15">
       <c r="A25" s="5" t="n">
@@ -3803,7 +3883,7 @@
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P25" s="5" t="n"/>
@@ -3839,7 +3919,11 @@
       <c r="AT25" s="5" t="n"/>
       <c r="AU25" s="5" t="n"/>
       <c r="AV25" s="5" t="n"/>
-      <c r="AW25" s="5" t="n"/>
+      <c r="AW25" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: createTile sam NIE inicjuje generowania cache - tworzy tylko definicje kafli (generowanie to oddzielny task GP 'generate' lub kafle on-demand). Zadanie GenerateTiles/DeleteTiles/ExportTiles/ImportTiles rejestrowane programowo w TileGp (nie przez jgp). Uprawnienie: map.assertCanTile(user). Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java; gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/extensions/TileGp.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/tiles/GenerateTiles.java Dowód: MapsController {map}/createTile (POST JSON, linia ~1317) tworzy definicje TileInfo (TileCache: storage, directory, file, version, toLevel; onDemand, enabled) i zapisuje mex; {map}/tile/{tile}/stats i {map}/tile/{tile}/delete (JSON) potwierdzone. Faktyczne generowanie kafli realizuje GP task 'generate' (GenerateTiles) wystawiony przez TileGp pod maps/{map}/tile/{tile}/gp.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55.2" customHeight="1" s="15">
       <c r="A26" s="5" t="n">
@@ -3896,7 +3980,7 @@
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P26" s="5" t="n"/>
@@ -3932,7 +4016,11 @@
       <c r="AT26" s="5" t="n"/>
       <c r="AU26" s="5" t="n"/>
       <c r="AV26" s="5" t="n"/>
-      <c r="AW26" s="5" t="n"/>
+      <c r="AW26" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: osobny endpoint listy /databases/{db}/schemas - brak mapowania; lista schematow jest tylko w tablicy 'schemas' w odpowiedzi database (DatabaseSerializer linia 75) i jako breadcrumb. Dodatkowo istnieja stare sciezki databases/{database}/{schema}/{dataset} (DATASET_OLD). Warunek aktywnosci: TableController ma @ConditionalOnProperty(pl.gispartner.imapserver.gdb.databases=true); w application.properties domyslnie =true (linia 419). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/DatabaseController.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/SchemaController.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java Dowód: Sciezki: databases (DatabaseController.DATABASES), databases/{database}, databases/{database}/schemas/{schema} (SchemaController.SCHEMA), .../{schema}/datasets (SchemaController linia 107), .../datasets/{dataset} (TableController.DATASET), .../fields/{field} (FIELD_URL). Uprawnienia: privileges na poziomie bazy, schematu, tabeli i pola (DatabaseController 884, SchemaController 515, TableController 3265 i 3012).</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55.2" customHeight="1" s="15">
       <c r="A27" s="5" t="n">
@@ -4025,7 +4113,11 @@
       <c r="AT27" s="5" t="n"/>
       <c r="AU27" s="5" t="n"/>
       <c r="AV27" s="5" t="n"/>
-      <c r="AW27" s="5" t="n"/>
+      <c r="AW27" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Domyslne addRoles/updateRoles/deleteRoles=admin. Warunek aktywnosci: TableController ma @ConditionalOnProperty(pl.gispartner.imapserver.gdb.databases=true); w application.properties domyslnie =true (linia 419). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/DatabaseController.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/SchemaController.java Dowód: TableController: applyEdits (POST, linia ~2446), addFeatures (~2497), updateFeatures (~2549), deleteFeatures (~2602), wszystkie JSON. applyEdits(...) wola assertCanAdd/assertCanUpdate/assertCanDelete zaleznie od niepustych adds/updates/deletes (role addRoles/updateRoles/deleteRoles), z transakcja i rollbackOnFailure. Analogiczne applyEdits tez na poziomie schematu i bazy.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55.2" customHeight="1" s="15">
       <c r="A28" s="5" t="n">
@@ -4118,7 +4210,11 @@
       <c r="AT28" s="5" t="n"/>
       <c r="AU28" s="5" t="n"/>
       <c r="AV28" s="5" t="n"/>
-      <c r="AW28" s="5" t="n"/>
+      <c r="AW28" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. current_timestamp nie znaleziono w MsSyntax (moze byc dziedziczone z JdbcSyntax - nie sprawdzono). Wymagane assertCanUpdate. Calculate ma tez wariant HTML. Operatory + - * / sa w JdbcSyntax (addBinary), szczegolow typow nie weryfikowano. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseTable.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/postgre/PgSyntax.java Dowód: TableController 'calculate' (POST, JSON, linia ~3197) czyta calcExpression (JSON tablica {field, sqlExpression|value}) i where, wola Table.calculate -&gt; BaseTable.calculate (linia ~1690) w transakcji; zwraca {success, updatedFeatureCount}. Operatory: JdbcSyntax (AND/OR/NOT, LIKE, IN/NOT IN), Parser obsluguje IS/IS NOT; funkcje UPPER/LOWER (Pg/Ora/Ms Syntax), current_timestamp (Pg/Ora Syntax).</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="41.4" customHeight="1" s="15">
       <c r="A29" s="5" t="n">
@@ -4211,7 +4307,11 @@
       <c r="AT29" s="5" t="n"/>
       <c r="AU29" s="5" t="n"/>
       <c r="AV29" s="5" t="n"/>
-      <c r="AW29" s="5" t="n"/>
+      <c r="AW29" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Faktyczne ALTER TABLE realizuja implementacje JdbcTable/Database (nie czytano). Role: modifyTableRoles/createTableRoles (domyslnie admin). Warunek aktywnosci: TableController ma @ConditionalOnProperty(pl.gispartner.imapserver.gdb.databases=true); w application.properties domyslnie =true (linia 419). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseTable.java Dowód: TableController 'createField' (HTML i JSON, linia ~1951) przyjmuje name, alias, type, length, geometryType, epsg, hasZ, hasM, editable, nullable; po table.assertCanCreateField(user) wola table.createField(...).</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="41.4" customHeight="1" s="15">
       <c r="A30" s="5" t="n">
@@ -4304,7 +4404,11 @@
       <c r="AT30" s="5" t="n"/>
       <c r="AU30" s="5" t="n"/>
       <c r="AV30" s="5" t="n"/>
-      <c r="AW30" s="5" t="n"/>
+      <c r="AW30" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. RYZYKO/ANOMALIA: w TableController i BaseTable.createRelation (linia 1792) parametr outFields jest ignorowany, a w jego miejsce przekazywane jest reverseOutFields (kopiuj-wklej?). Nie ma typu 1:1. Warunek aktywnosci: TableController ma @ConditionalOnProperty(pl.gispartner.imapserver.gdb.databases=true); w application.properties domyslnie =true (linia 419). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseTable.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/RelationType.java Dowód: TableController 'createRelation' (JSON, linia ~2057) z parametrami toSchema,toTable,relation1,type,reverseName,reverseAlias,reverseOutFields,interSchema,interTable,relation2; BaseTable.createRelation (linie 1772-1796) dla type 'manyMany' tworzy dwie relacje przez tabele posrednia, w pozostalych przypadkach relacje z reverseName. RelationType: ManyOne('one'), OneMany('many'), ManyMany('manyMany').</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55.2" customHeight="1" s="15">
       <c r="A31" s="5" t="n">
@@ -4361,7 +4465,7 @@
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P31" s="5" t="n"/>
@@ -4397,7 +4501,11 @@
       <c r="AT31" s="5" t="n"/>
       <c r="AU31" s="5" t="n"/>
       <c r="AV31" s="5" t="n"/>
-      <c r="AW31" s="5" t="n"/>
+      <c r="AW31" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'widoki bazodanowe' - TableView to wpis metadanych iMS (projekcja pol outFields + flaga rrq), a nie widok SQL w bazie; 'widoki moga miec wlasne uprawnienia i filtry' - w createView/updateView/BaseTableView nie ma parametru filtra (where) ani uprawnien. Sprawdzone grepem: TableView.java nie zawiera where/filter/privileg/roles. Uprawnienia: tylko table.assertCanModifyTable. Widok mozna zapytac przez {view}/query i usunac przez {view}/drop (HTML, nie sprawdzono JSON drop). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseTableView.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseTable.java Dowód: TableController 'createView' (JSON, linia ~2105) i {view}/updateView (JSON, ~2321) tworza/aktualizuja TableView: BaseTable.createTableView zapisuje wiersz w tabeli systemowej views (schema, table, name, alias, description, outFields, rrq); BaseTableView.update(alias, description, outFields, rrq).</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55.2" customHeight="1" s="15">
       <c r="A32" s="5" t="n">
@@ -4490,7 +4598,11 @@
       <c r="AT32" s="5" t="n"/>
       <c r="AU32" s="5" t="n"/>
       <c r="AV32" s="5" t="n"/>
-      <c r="AW32" s="5" t="n"/>
+      <c r="AW32" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Opis 'automatyczne sledzenie historii - kazda modyfikacja zapisywana z data' - to czesc opisu biznesowego; w TableController.registerHistory widoczna jest tylko rejestracja pol; zapis wersji przy edycji (BaseRow/JdbcTable) nie byl czytany. Warunek aktywnosci: TableController ma @ConditionalOnProperty(pl.gispartner.imapserver.gdb.databases=true); w application.properties domyslnie =true (linia 419). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/CheckoutTable.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/Filter.java Dowód: TableController 'registerHistory' (JSON, linia ~807) z parametrami from, to; wola table.registerHistory(from, to, TimestampUtil.MAX) (wymaga niepustych from/to) i unregisterHistory. Zarejestrowane pola from/to sa uzywane w Filter.setHistoricMoment i SqlBuilder do zapytan historycznych.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="41.4" customHeight="1" s="15">
       <c r="A33" s="5" t="n">
@@ -4583,7 +4695,11 @@
       <c r="AT33" s="5" t="n"/>
       <c r="AU33" s="5" t="n"/>
       <c r="AV33" s="5" t="n"/>
-      <c r="AW33" s="5" t="n"/>
+      <c r="AW33" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Zalozenie: nazwy uprawnien w opisie (addAttachment itd.) to w kodzie klucze xxxAttachmentRoles; domyslnie gdb.*AttachmentRoles=admin (application.properties 243-246). BaseTable.supportsAttachments wymaga OID, zarejestrowanej tabeli (tid!=0) i ustawionego maxAttBytesCount. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/RowController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/Databases.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseTable.java Dowód: RowController: {oid}/attachments, {oid}/addAttachment, {oid}/updateAttachment, {oid}/deleteAttachments, {oid}/attachments/{id} (JSON). Uprawnienia jako wlasciwosci tabeli: Databases.QUERY_ATT_ROLES='queryAttachmentRoles', ADD_/UPDATE_/DELETE_ATT_ROLES; BaseTable.canQueryAttachment/canAddAttachment/canUpdateAttachment/canDeleteAttachment. Takze FeatureServer {layer}/{oid}/addAttachment itd.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="55.2" customHeight="1" s="15">
       <c r="A34" s="5" t="n">
@@ -4676,7 +4792,11 @@
       <c r="AT34" s="5" t="n"/>
       <c r="AU34" s="5" t="n"/>
       <c r="AV34" s="5" t="n"/>
-      <c r="AW34" s="5" t="n"/>
+      <c r="AW34" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. HTML wariant filtruje pola do typow String/Short/Int/Float/Double. Pozostale: setDomain/detachDomain na polu. Warunek aktywnosci: TableController ma @ConditionalOnProperty(pl.gispartner.imapserver.gdb.databases=true); w application.properties domyslnie =true (linia 419). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseDatabase.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/DatabaseController.java Dowód: TableController 'registerDomain' (JSON, linia ~1017) z name, alias, domainCode, domainValue wola database.registerDomain(name, alias, table, domainCode, domainValue) (BaseDatabase linia ~626); role assertCanRegisterDomain. Dodatkowo DatabaseController: createDomain, domains/{domain}/addValue|changeValue|deleteValue|drop.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="55.2" customHeight="1" s="15">
       <c r="A35" s="5" t="n">
@@ -4733,7 +4853,7 @@
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P35" s="5" t="n"/>
@@ -4769,7 +4889,11 @@
       <c r="AT35" s="5" t="n"/>
       <c r="AU35" s="5" t="n"/>
       <c r="AV35" s="5" t="n"/>
-      <c r="AW35" s="5" t="n"/>
+      <c r="AW35" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: dostep przez API w formie JSON - oba endpointy createIndex maja wylacznie produces=HTML (brak JSON); indeksy przestrzenne dla Oracle i MS SQL - OraDatabase i MsDatabase kopiuja skladnie PostgreSQL ('using gist'), niepoprawna dla tych SZBD. RYZYKO: OraDatabase.dropIndexSql rzuca NotImplementedException; JdbcDatabase.createIndexSql domyslnie NotImplementedException. Sprawdzone: grep 'createIndex' w TableController - tylko HTML. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/postgre/PgDatabase.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/oracle/OraDatabase.java Dowód: TableController: {field}/createIndex (linia ~1971) i createIndex (~1998) wolaja table.createIndex(name, unique, fields); PgDatabase.createIndexSql buduje 'create [unique] index ... using gist' dla pojedynczego pola geometrycznego, a dla innych zwykly indeks.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="55.2" customHeight="1" s="15">
       <c r="A36" s="5" t="n">
@@ -4826,7 +4950,7 @@
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P36" s="5" t="n"/>
@@ -4862,7 +4986,11 @@
       <c r="AT36" s="5" t="n"/>
       <c r="AU36" s="5" t="n"/>
       <c r="AV36" s="5" t="n"/>
-      <c r="AW36" s="5" t="n"/>
+      <c r="AW36" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: blokowanie TABEL - TableController lock/unlock wolaja Table.lock(user, where) i unlock(user, where), ktorych jedyna implementacja to default w Table.java zwracajacy 0 (brak override w repo); zapobieganie konfliktom przy edycji - nie znaleziono sprawdzania wpisu oidlock w sciezce update/store (sprawdzenie jest tylko w prepareLock). BUG: JSON TableController.unlock (linia 3359) wola table.lock(user, where) zamiast unlock. Zastrzezenie: 'nie znalazlem' sprawdzania blokady przy edycji != 'nie istnieje' (nie czytano calej sciezki BaseRow.store/EditData). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/RowController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseRow.java Dowód: Blokowanie wiersza dziala: RowController {oid}/lock i {oid}/unlock (JSON) wolaja BaseRow.lock/unlock (linie 619-639), ktore zapisuja/usuwaja wpis w tabeli systemowej oidlock (uzytkownik, from, to = now + lockTime; domyslnie gdb.lockMsCount=300000 ms), z odmowa 'Row locked already by ...' dla innego uzytkownika.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="55.2" customHeight="1" s="15">
       <c r="A37" s="5" t="n">
@@ -4955,7 +5083,11 @@
       <c r="AT37" s="5" t="n"/>
       <c r="AU37" s="5" t="n"/>
       <c r="AV37" s="5" t="n"/>
-      <c r="AW37" s="5" t="n"/>
+      <c r="AW37" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Nie ma jawnego registerSidSequence/registerCidSequence. 'Rejestracja sekwencji' potwierdzona dla OID i VID. Odwolania do GML/EGiB/EMUiA to opis biznesowy - nie weryfikowane. Warunek aktywnosci: TableController ma @ConditionalOnProperty(pl.gispartner.imapserver.gdb.databases=true); w application.properties domyslnie =true (linia 419). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/CheckoutTable.java Dowód: TableController (JSON): registerOid, registerGid, registerSid, registerCid, registerVid oraz unregister*; sekwencje: registerOidSequence, registerVidSequence (+ unregister), registerOidAutoincrement. W CheckoutTable uzycie oid.registerSequence(schema, 'seq_'+table, true).</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="41.4" customHeight="1" s="15">
       <c r="A38" s="5" t="n">
@@ -5048,7 +5180,11 @@
       <c r="AT38" s="5" t="n"/>
       <c r="AU38" s="5" t="n"/>
       <c r="AV38" s="5" t="n"/>
-      <c r="AW38" s="5" t="n"/>
+      <c r="AW38" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Sprawdzenie database.checkCreateFunction(user). Flaga 'embedded' rozroznia wbudowane i wlasne. Uzycie wlasnych funkcji w zapytaniach (JdbcCustomFunction w syntaxie) - klasa istnieje, szczegolow rejestracji w Syntax nie czytano. Warunek aktywnosci: TableController ma @ConditionalOnProperty(pl.gispartner.imapserver.gdb.databases=true); w application.properties domyslnie =true (linia 419). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/DatabaseController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/syntax/JdbcCustomFunction.java Dowód: DatabaseController: {database}/createFunction (POST JSON, linia ~1020; parametry name, sql, resultType, attributes), {database}/functions (JSON, linia ~954; zwraca embedded=true/false, dla JdbcCustomFunction i admina tez id i sql), {database}/functions/{id}/delete.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="41.4" customHeight="1" s="15">
       <c r="A39" s="5" t="n">
@@ -5141,7 +5277,11 @@
       <c r="AT39" s="5" t="n"/>
       <c r="AU39" s="5" t="n"/>
       <c r="AV39" s="5" t="n"/>
-      <c r="AW39" s="5" t="n"/>
+      <c r="AW39" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. ZASTRZEZENIA: (1) rejestracja tasków GP odbywa sie przez pliki .jgp w profilach konfiguracji (capap, gs, riip, sipww); w config/default nie ma dataManagement.jgp, wiec w konfiguracji domyslnej taski nie sa wystawione. (2) SchemaController.drop ma tylko produces=text/html (brak JSON). (3) new DropSchema/DropTable nigdzie w kodzie Javy - tylko przez jgp. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/SchemaController.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/DropSchema.java Dowód: GP: klasy DropSchema (setName 'dropSchema') i DropTable ('dropTable'), wpisane w config/capap/dataManagement.jgp (linie 37, 39). REST: TableController drop (JSON, linia 195), register/unregister (JSON, linie 223, 252); SchemaController drop.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="41.4" customHeight="1" s="15">
       <c r="A40" s="5" t="n">
@@ -5234,7 +5374,11 @@
       <c r="AT40" s="5" t="n"/>
       <c r="AU40" s="5" t="n"/>
       <c r="AV40" s="5" t="n"/>
-      <c r="AW40" s="5" t="n"/>
+      <c r="AW40" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Zasobu o nazwie 'catalog' nie znaleziono - korzen to RootController (hierarchia zaczyna sie od '/'). Dodatkowe rozszerzenia korzenia: folders, pages, atlases, scenes, security, lang, manager, monitoring, test. Pliki: gp-imapserver-rest/src/main/java/pl/gispartner/imapserver/rest/RootController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/DatabaseController.java Dowód: RootController (@RequestMapping produces text/html i application/json) + root.addExtension(...): 'maps' (MapsController), 'databases' (DatabaseController), 'apps' (AppConroller), 'gp' (Services), 'tiles' (TileSchemaController), plus storages (StorageController @RequestMapping 'storages'). Odpowiedzi JSON przez serializery.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="55.2" customHeight="1" s="15">
       <c r="A41" s="5" t="n">
@@ -5291,7 +5435,7 @@
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P41" s="5" t="n"/>
@@ -5327,7 +5471,11 @@
       <c r="AT41" s="5" t="n"/>
       <c r="AU41" s="5" t="n"/>
       <c r="AV41" s="5" t="n"/>
-      <c r="AW41" s="5" t="n"/>
+      <c r="AW41" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: SUBSTR - brak funkcji o tej nazwie w syntaxach (w PG jest 'first' mapowane na SQL substr(%0,1,%1)); CONCAT poza PostgreSQL - znaleziono tylko w PgSyntax; funkcje dat - znaleziono tylko current_date/current_time/current_timestamp (PG) i current_timestamp, TO_DATE (Oracle); brak funkcji wyciagania czesci daty (year/month/day itp.). Zestaw funkcji zalezy od SZBD (PgSyntax najbogatszy). Fraza sprawdzona: substr, substring, year, month, day, date_trunc, extract, concat w addFunction - brak. Nie przeszukiwano kodu w MemorySyntax szczegolowo (tylko IIF). Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/postgre/PgSyntax.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/oracle/OraSyntax.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/ms/MsSyntax.java Dowód: JdbcSyntax: AND, OR, NOT (BoolAndBool/BoolOrBool/addUnary NOT), operatory arytmetyczne; PgSyntax: concat (2 i 3 argumenty), UPPER, LOWER, length, trim, round, IIF, current_date/time/timestamp, sqrt, cbrt; OraSyntax i MsSyntax: UPPER, LOWER; Ora: current_timestamp, TO_DATE.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="69" customHeight="1" s="15">
       <c r="A42" s="5" t="n">
@@ -5384,7 +5532,7 @@
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P42" s="5" t="n"/>
@@ -5420,7 +5568,11 @@
       <c r="AT42" s="5" t="n"/>
       <c r="AU42" s="5" t="n"/>
       <c r="AV42" s="5" t="n"/>
-      <c r="AW42" s="5" t="n"/>
+      <c r="AW42" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: widok z wlasnym filtrem (where); widok z niezaleznymi uprawnieniami. W warstwie map (carto) warstwy maja wlasne uprawnienia (role warstw {map}/{layer}/privileges) i definicje - to jednak nie 'widoki na zrodla danych'. Nie weryfikowano pola where w definicji warstwy. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseTableView.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/filters/InternalFilter.java Dowód: TableView (createView/updateView/{view}/query) daje nazwany widok z projekcja pol (outFields) i flaga rrq. Osobny mechanizm filtrow wierszowych (InternalFilter: login, role, attribute, value, expression) jest przypisywany do tabel/schematow przez konfiguracje, nie do widoku.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="55.2" customHeight="1" s="15">
       <c r="A43" s="5" t="n">
@@ -5477,7 +5629,7 @@
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P43" s="5" t="n"/>
@@ -5513,7 +5665,11 @@
       <c r="AT43" s="5" t="n"/>
       <c r="AU43" s="5" t="n"/>
       <c r="AV43" s="5" t="n"/>
-      <c r="AW43" s="5" t="n"/>
+      <c r="AW43" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: integracja z Oracle VPD - grep 'vpd', 'DBMS_SESSION', 'set_context', 'sys_context', 'CLIENT_IDENTIFIER' w *.java/kt/properties/xml: 0 trafien. Filtrowanie dziala po stronie iMS (doklejanie warunkow), nie przez VPD. Atrybuty uzytkownika brane z pl.gispartner.imapserver.security.attributes (zapytanie SQL, patrz UserFactoryImpl). Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/filters/InternalFilter.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/filters/LoginFilter.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/filters/RoleFilter.java Dowód: InternalFilter.create obsluguje typy login, role, attribute, value i expression (ExpressionFilter); BaseTable.filters() laduje FilterCfg z bazy po nazwach (getFilterNames), a SqlBuilder/Filter stosuja je do zapytan i edycji (appliesForQuery/appliesForEdit), z mozliwoscia ignorowania dla rol (ignoreFilters, autoIgnoreRoles).</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="41.4" customHeight="1" s="15">
       <c r="A44" s="5" t="n">
@@ -5606,7 +5762,11 @@
       <c r="AT44" s="5" t="n"/>
       <c r="AU44" s="5" t="n"/>
       <c r="AV44" s="5" t="n"/>
-      <c r="AW44" s="5" t="n"/>
+      <c r="AW44" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Zdefiniowane 'funkcje' to wyrazenia (Expression) w konfiguracji pola (cfg autoWhen/autoExpression). Ustawianie przez BaseField.setAuto. Nie sprawdzano endpointu REST do ustawiania auto. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseRow.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseTable.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseField.java Dowód: BaseField ma getAutoWhen() (WhenType: never/create/change...) i getAutoExpression(); BaseTable.getAutoCreate()/getAutoChange(); BaseRow (linie 128-129 i 153-154) przy tworzeniu/zmianie wiersza ustawia wartosc pola z field.getAutoExpression().getValue(row, user).</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="55.2" customHeight="1" s="15">
       <c r="A45" s="5" t="n">
@@ -5699,7 +5859,11 @@
       <c r="AT45" s="5" t="n"/>
       <c r="AU45" s="5" t="n"/>
       <c r="AV45" s="5" t="n"/>
-      <c r="AW45" s="5" t="n"/>
+      <c r="AW45" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Nie sprawdzano limitow rozmiaru (maxAttBytesCount dotyczy zalacznikow). Uprawnienia do kolumn: clobAccess i fieldRoles. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/RowController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/BlobField.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/ClobField.java Dowód: RowController {oid}/fields/{field} (GET z DataType.Blob/Clob, linie ~637-675, kopiuje strumien Blob do odpowiedzi z content-type/nazwa pliku z pol powiazanych; POST do zapisu, linia 677). BlobField/ClobField w gdb; TableController: changeContentType, rejestracja content-type (BlobField.registerContentType).</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="69" customHeight="1" s="15">
       <c r="A46" s="5" t="n">
@@ -5756,7 +5920,7 @@
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P46" s="5" t="n"/>
@@ -5792,7 +5956,11 @@
       <c r="AT46" s="5" t="n"/>
       <c r="AU46" s="5" t="n"/>
       <c r="AV46" s="5" t="n"/>
-      <c r="AW46" s="5" t="n"/>
+      <c r="AW46" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: zwracanie wedlug Accept-Language - grep 'Accept-Language'/getLocale w *.java/kt: 0 trafien; w REST gdb tlumaczenia sa zwracane w calosci w polu 'local', a nie wybierane naglowkiem; tytuly i opisy (description) warstw w wielu jezykach - potwierdzone tylko 'alias' (i unit); inne klucze Local nie byly weryfikowane. Wybor jezyka w kartografii odbywa sie parametrem 'lang' (np. export/legend), nie naglowkiem HTTP. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/json/DatasetSerializer.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/Layer.java Dowód: TableController changeAlias z parametrem lang (field.setAlias(lang, alias) -&gt; getCfg().getLocal().set('alias', lang, alias)) oraz setUnit(lang, unit); Layer.getAlias(Locale) czyta local.get('alias', locale, ...); mapa, warstwa i StandaloneTable maja Local (MexSerializer/LayerSerializer 'local'); DatasetSerializer zwraca 'local' (wszystkie jezyki) dla pol.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="55.2" customHeight="1" s="15">
       <c r="A47" s="5" t="n">
@@ -5885,7 +6053,11 @@
       <c r="AT47" s="5" t="n"/>
       <c r="AU47" s="5" t="n"/>
       <c r="AV47" s="5" t="n"/>
-      <c r="AW47" s="5" t="n"/>
+      <c r="AW47" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Istnieje tez LengthDomain (BaseLengthDomain) - nie wymieniona w opisie. 'Walidacja dopuszczalnych wartosci' - istnieja domeny w gdb; faktycznego wymuszania przy edycji nie czytano. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/json/DomainSerializer.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/json/MapServerItemSerializer.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/json/DatasetSerializer.java Dowód: DomainSerializer.serialize zapisuje type i dla CodedValueDomain tablice codedValues {name, code}, dla RangeDomain zakres (linie 30-54); wolane z DatasetSerializer (pole 'domain') i MapServerItemSerializer (linia 527-528) w metadanych pol.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="55.2" customHeight="1" s="15">
       <c r="A48" s="5" t="n">
@@ -5942,7 +6114,7 @@
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P48" s="5" t="n"/>
@@ -5978,7 +6150,11 @@
       <c r="AT48" s="5" t="n"/>
       <c r="AU48" s="5" t="n"/>
       <c r="AV48" s="5" t="n"/>
-      <c r="AW48" s="5" t="n"/>
+      <c r="AW48" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'OAuth 2.0' - w kodzie nie ma obslugi OAuth (brak flow, endpointow, Bearer); sprawdzono grep oauth/Bearer/Authorization; przekazanie JWT jako nagłówek - token jest czytany z COOKIE o nazwie gp.sec.key (domyslnie 'gpt'), nie z naglowka Authorization; szyfrowanie TLS - w repo brak konfiguracji server.ssl/key-store; TLS zalezy od wdrozenia (Tomcat/Spring Boot/reverse proxy), poza repo. Caveat: @ConditionalOnProperty(usejwt) bez havingValue - aktywne dla kazdej wartosci innej niz 'false'. UserFactoryImpl jest aktywny tylko przy usejwt=false (Java, havingValue=false); wariant JWT dziedziczy po nim i ma fallback do logowania GP (useAlsoGpLogin=true). W Javie nie ma klasy JWT - latwo przeoczyc, kod jest w Kotlinie. Dodatkowo TestingJwtRestController (/settoken/{token}) pod testjwt. Pliki: gp-imapserver-security/src/main/kotlin/pl/gispartner/imapserver/security/jwtUserFactory.kt; gp-imapserver-security/src/main/java/pl/gispartner/imapserver/security/UserFactoryImpl.java; gp-imapserver-app/src/main/resources/application.properties Dowód: Kotlin JwtUserFactoryImpl (Jwts.parser, klucz publiczny RSA z pliku gp.sec.pubKeyFn, walidacja exp, iat, issuer z listy gp.sec.issuers, opcjonalnie lic) buduje GpJwtUser z claimow subject i roles; aktywny przy ustawionym pl.gispartner.imapserver.security.usejwt (domyslnie false, application.properties linia 188; true w config/sipww).</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="55.2" customHeight="1" s="15">
       <c r="A49" s="5" t="n">
@@ -6071,7 +6247,11 @@
       <c r="AT49" s="5" t="n"/>
       <c r="AU49" s="5" t="n"/>
       <c r="AV49" s="5" t="n"/>
-      <c r="AW49" s="5" t="n"/>
+      <c r="AW49" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Przyklad 'Studio Map' potwierdzony (typ studioMap, endpoint studio-map). Slowo 'portale' nie ma odpowiednika w ApplicationType (tylko wizard/dashboard/studioMap) - to interpretacja z opisu. Klasa kontrolera ma literowke w nazwie (AppConroller). Modul gp-imapserver-rest-app jest w settings.gradle i w zaleznosciach gp-imapserver-app. Pliki: gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/AppConroller.java; gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/Application.java; gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/ApplicationType.java Dowód: AppConroller (@Controller, bez warunku, ROOT="apps") ma mapowania: lista (produces HTML/JSON), "create" (GET/JSON), "wizard", "{app}/privileges" oraz "studio-map", "studio-analiz", "print-editor", "page-editor". ApplicationType ma wartosci wizard, dashboard, studioMap.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="55.2" customHeight="1" s="15">
       <c r="A50" s="5" t="n">
@@ -6128,7 +6308,7 @@
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P50" s="5" t="n"/>
@@ -6164,7 +6344,11 @@
       <c r="AT50" s="5" t="n"/>
       <c r="AU50" s="5" t="n"/>
       <c r="AV50" s="5" t="n"/>
-      <c r="AW50" s="5" t="n"/>
+      <c r="AW50" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'edit - edycja przez kreator aplikacji (wizard)' tylko dla typu wizard: dla studioMap edit otwiera widok "studio-map", dla dashboard widok "studio-analiz", a dla innych typow rzuca CodeException 'Can not edit application with type'. modify/remove potwierdzone w pelni. Opis upraszcza: kreator (wizard) jest tylko jednym z trzech edytorow wybieranych wg typu aplikacji (AppConroller.edit, linie ok. 355-401). Edit zwraca HTML (brak wersji JSON). Pliki: gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/AppConroller.java Dowód: AppConroller: "{app}/modify" (HTML i JSON, z MultipartFile file/thumbnail), "{app}/remove" (HTML i JSON), "{app}/edit" i "{app}/edit/index.html" z przelacznikiem po app.getType().</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="55.2" customHeight="1" s="15">
       <c r="A51" s="5" t="n">
@@ -6257,7 +6441,11 @@
       <c r="AT51" s="5" t="n"/>
       <c r="AU51" s="5" t="n"/>
       <c r="AV51" s="5" t="n"/>
-      <c r="AW51" s="5" t="n"/>
+      <c r="AW51" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Uprawnienia sa per aplikacja (APP_PRIVILEGES) oraz per folder aplikacji ("privileges" na poziomie folderu, APPS_PRIVILEGES z createAppRoles, studioMapAppRoles, wizardAppRoles, dashboardAppRoles). Opis biznesowy o 'srodowisku wieloorganizacyjnym' to interpretacja - kod daje tylko role per aplikacja/folder. Pliki: gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/Application.java; gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/AppConroller.java; gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/container/AppFolder.java Dowód: Application.java: stale APP_ROLES="appRoles", MODIFY_APP_ROLES="modifyAppRoles", REMOVE_APP_ROLES="removeAppRoles" w zbiorze APP_PRIVILEGES; uzywane w isAdminOrOwnerOrHasAnyRole (modify/remove). AppConroller ma "{app}/privileges" (JSON i HTML) wywolujace app.setPrivileges(privileges) po app.assertCanPrivileges(user).</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="55.2" customHeight="1" s="15">
       <c r="A52" s="5" t="n">
@@ -6314,7 +6502,7 @@
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P52" s="5" t="n"/>
@@ -6350,7 +6538,11 @@
       <c r="AT52" s="5" t="n"/>
       <c r="AU52" s="5" t="n"/>
       <c r="AV52" s="5" t="n"/>
-      <c r="AW52" s="5" t="n"/>
+      <c r="AW52" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: operacja generateThumbnail dla aplikacji (apps) - nie istnieje; generateThumbnail jest tylko w MapsController dla map ("{map}/generateThumbnail") i MapComposition.generateThumbnail; 'generowanie miniaturki' aplikacji - miniatura aplikacji nie jest generowana, tylko przesylana. Szukane frazy: generateThumbnail (cale repo, *.java/jsp/properties/jgp/py/xml), umbnail w gp-imapserver-rest-app. Zasoby /thumbnail i /def potwierdzone. Prawdopodobnie opis pomylil operacje map z aplikacjami. Pliki: gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/AppConroller.java; gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/Application.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java Dowód: AppConroller ma "{app}/thumbnail" (zwraca app.getThumbnailBytes() jako image/png, 404 gdy brak) oraz "{app}/def". Miniatura aplikacji jest wgrywana jako MultipartFile 'thumbnail' w create/modify, a serializer AppSerializer zwraca pole 'thumbnail' (base64).</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="55.2" customHeight="1" s="15">
       <c r="A53" s="5" t="n">
@@ -6406,12 +6598,12 @@
       <c r="M53" s="5" t="n"/>
       <c r="N53" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P53" s="5" t="n"/>
@@ -6449,7 +6641,7 @@
       <c r="AV53" s="5" t="n"/>
       <c r="AW53" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'Nie podlega limitowi maxRecordCount': w GdbUtil.setupFilter limit queryCount jest pomijany tylko dla returnIdsOnly/returnCountOnly (warunek oidsOnly/countOnly), samo objectIds nie wyłącza limitu (count = min(queryCount, resultRecordCount)).; Dostępność w databases: DatabaseController.query nie ma parametru objectIds (tylko tableDefs, geometry, spatialRel, historicMoment, inSR, outSR, returnGeometry, maxAllowableOffset, returnIdsOnly, returnCountOnly).. Wyjątek od limitu dotyczy returnIdsOnly, nie objectIds. Obok objectIds kod obsługuje też stringIds i globalIds (getMapIds); dla kilku typów naraz setWhere wywoływane w pętli (nie weryfikowano, czy łączy czy nadpisuje). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/MapServer.java Dowód: Parametr objectIds jest odczytywany w TableController.query, LayerController.query, MapServer.query i FeatureServer.query; GdbUtil.getMapIds buduje z niego mapę identyfikatorów, a GdbUtil.setupFilter zamienia ją na warunek '#oid in (...)' i wtedy pomija parametr where (gałąź else po mapIds).</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6671,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Ogranicza zapytanie do obiektów z wcześniej zapisanej selekcji serwerowej (parametr przyjmuje identyfikator selekcji).</t>
+          <t>Parametr selection (Integer): obiekty należące do zapisanej selekcji serwerowej są oznaczane flagą sel (LEFT JOIN na tabelę items); wynik nie jest przez niego ograniczany (ograniczenie do zbioru realizuje setId). Obsługiwany w query tabel, warstw i FeatureServer; MapServer.query go nie ma.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -6507,12 +6699,12 @@
       <c r="M54" s="5" t="n"/>
       <c r="N54" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P54" s="5" t="n"/>
@@ -6550,7 +6742,7 @@
       <c r="AV54" s="5" t="n"/>
       <c r="AW54" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer - | FeatureServer - | databases TAK. Nazwa parametru potwierdzona: api/maps/map.md:99.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer - | FeatureServer - | databases TAK. Nazwa parametru potwierdzona: api/maps/map.md:99. | Weryfikacja kodu 2026-10-16: sprzeczne. Niepotwierdzone w kodzie: 'Ogranicza zapytanie do obiektów z zapisanej selekcji': kod używa LEFT JOIN i tylko oznacza wiersze flagą sel, nie filtruje. Ograniczenie wyniku do zbioru realizuje setId (zwykły JOIN w getJoinSet).. MapServer.query (HTML i JSON) nie ma parametru selection (do createFilter przekazywane null), FeatureServer.query ma. W DatabaseController brak. W EsriCursorSerializer (MapServer/FeatureServer, esri=true) nie widać pola sel w sygnaturze serialize, więc flaga prawdopodobnie nie jest tam zwracana (niepotwierdzone w pełni). Uwagi_obecne mówią FeatureServer '-', a kod ma parametr. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/sql/SqlBuilder.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/json/CursorSerializer.java Dowód: Parametr selection (Integer) jest odczytywany w TableController.query, LayerController.query i FeatureServer.query i trafia do Filter.setSelection. W SqlBuilder.getJoinSelection jest to LEFT JOIN na tabelę items po (set=selection, tid, oid), a w getSelect dodawana jest kolumna ukryta '#sel'; CursorSerializer zapisuje ją jako boolean 'sel' w wierszu. | Opis przed korektą: Ogranicza zapytanie do obiektów z wcześniej zapisanej selekcji serwerowej (parametr przyjmuje identyfikator selekcji).</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6800,7 @@
       <c r="M55" s="5" t="n"/>
       <c r="N55" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O55" s="5" t="inlineStr">
@@ -6651,7 +6843,7 @@
       <c r="AV55" s="5" t="n"/>
       <c r="AW55" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: potwierdzone. Plik OidsSerializer.java wskazany z nazwy w wywołaniu w GdbUtil.serializeContent (nie otwierano go). Przy returnIdsOnly nie obowiązuje limit queryCount (GdbUtil.setupFilter). Gdy jednocześnie returnCountOnly=true, wygrywa count. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/DatabaseController.java Dowód: returnIdsOnly jest parametrem we wszystkich query (Table/Layer/MapServer/FeatureServer/Database). GdbUtil.setupFilter wywołuje Filter.setOidsOnly, a GdbUtil.serializeContent dla getOidsOnly() używa OidsSerializer zamiast serializera wierszy.</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6901,7 @@
       <c r="M56" s="5" t="n"/>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
@@ -6752,7 +6944,7 @@
       <c r="AV56" s="5" t="n"/>
       <c r="AW56" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: potwierdzone. Z returnDistinctValues zapytanie jest obudowywane zapytaniem o liczbę (komentarz w setupFilter). Odpowiednik SQL COUNT zgodny z kodem (statystyka count). Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/json/CountSerializer.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java Dowód: returnCountOnly jest parametrem w Table/Layer/MapServer/FeatureServer/Database. GdbUtil.setupFilter dodaje statystykę count('*') i ustawia setCountOnly; GdbUtil.serializeContent przy returnCountOnly używa CountSerializer (pole count).</t>
         </is>
       </c>
     </row>
@@ -6810,12 +7002,12 @@
       <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P57" s="5" t="n"/>
@@ -6853,7 +7045,7 @@
       <c r="AV57" s="5" t="n"/>
       <c r="AW57" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'bez geometrii i atrybutów obiektów': bez returnCountOnly gałąź setupFilter dodaje outFields i '#shape', a PgField zwraca box2d per wiersz, więc atrybuty nadal są zwracane; zagregowany zasięg (st_extent, kolumna 'extent') powstaje tylko w trybie returnCountOnly.; Dostępność w databases: DatabaseController.query nie ma parametru returnExtentOnly.. Zagregowany zasięg wyniku wymaga kombinacji returnExtentOnly + returnCountOnly (GdbUtil.setupFilter, statistics union 'extent'). Przy returnM PgField rzuca NotImplementedException dla union. Nie sprawdzano wszystkich dialektów (MS SQL: tylko wywołanie isExtentOnly w MsField). Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/postgre/PgField.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/json/CountSerializer.java Dowód: returnExtentOnly jest parametrem w Table/Layer/MapServer/FeatureServer; GdbUtil.setupFilter ustawia Filter.setExtentOnly, a PgField.getSelectSql (i warianty Ora*) przy isExtentOnly zwraca box2d/st_extent. Z returnCountOnly dodawana jest statystyka union 'extent'.</t>
         </is>
       </c>
     </row>
@@ -6907,7 +7099,7 @@
       <c r="M58" s="5" t="n"/>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
@@ -6950,7 +7142,7 @@
       <c r="AV58" s="5" t="n"/>
       <c r="AW58" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru REST niepotwierdzona: nie występuje w pełnym URL operacji query (database.md:287) ani w parametrach export/identify (map.md). Do potwierdzenia w kodzie.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru REST niepotwierdzona: nie występuje w pełnym URL operacji query (database.md:287) ani w parametrach export/identify (map.md). Do potwierdzenia w kodzie. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'zamiast pełnej geometrii': centroid jest zwracany jako dodatkowe pole 'centroid'; pełna geometria jest pomijana tylko gdy returnGeometry=false (domyślnie false w natywnym, true w MapServer/FeatureServer).; Dostępność w databases: DatabaseController/ApplyManyQueriesSerializer przekazują returnCentroid=false na stałe, brak parametru.. Funkcja CENTROID zdefiniowana w PgSyntax (ST_Centroid) i OraSyntax (SDE.ST_Centroid); inne dialekty nie sprawdzane. W GdbUtil.shape centroid wymusza odczyt pola geometrii. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/json/CursorSerializer.java Dowód: Parametr nazywa się returnCentroid (boolean, domyślnie false): TableController.query, LayerController.query, MapServer.query, FeatureServer.query. GdbUtil.setupFilter dodaje wyrażenie '#centroid' = CENTROID (lub MULTIPATCH_CENTROID dla multipatch/tin z Z), a CursorSerializer/EsriCursorSerializer zapisują pole 'centroid'.</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7200,7 @@
       <c r="M59" s="5" t="n"/>
       <c r="N59" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
@@ -7051,7 +7243,7 @@
       <c r="AV59" s="5" t="n"/>
       <c r="AW59" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: potwierdzone. Jednostki: gdy podano outSR, generalizacja jest po projekcji (jednostki układu wyjściowego), bez outSR w jednostkach źródła (PgField, gałęzie epsg==null / != null). Analogiczne wywołania w OraSdoField i OraStField; MS SQL nie weryfikowano. st_simplify odpowiada 'odrzuceniu wierzchołków', co jest interpretacją komentarza kodu. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/postgre/PgField.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java Dowód: maxAllowableOffset (Double) jest parametrem we wszystkich query, w tym DatabaseController; GdbUtil.setupFilter wywołuje Filter.setGeneralization, a PgField.getSelectSql opakowuje geometrię w st_simplify(geom, ?) z tym parametrem (po st_transform, gdy podano outSR).</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7301,7 @@
       <c r="M60" s="5" t="n"/>
       <c r="N60" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O60" s="5" t="inlineStr">
@@ -7152,7 +7344,7 @@
       <c r="AV60" s="5" t="n"/>
       <c r="AW60" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: potwierdzone. Parametr nie działa dla formatów shp/csv/xlsx/kml/gml/dxf/pbf/gpkg/glb/obj (inne gałęzie GdbUtil.serialize) ani w databases (ApplyManyQueriesSerializer przekazuje null). Zaokrąglane są współrzędne zapisywane przez writeCoordinate (używane w GeometrySerializer/VertexSerializer), nie atrybuty. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-common/src/main/java/pl/gispartner/imapserver/util/JsonUtil.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java Dowód: geometryPrecision (Integer) jest parametrem Table/Layer/MapServer/FeatureServer; GdbUtil.serialize tworzy JsonGenerator przez JsonUtil.createGenerator(output, pretty, geometryPrecision) tylko w gałęzi JSON/pjson/geojson. PrecisionGenerator.writeCoordinate zaokrągla współrzędne: Math.round(d*10^precision)/10^precision.</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7402,7 @@
       <c r="M61" s="5" t="n"/>
       <c r="N61" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
@@ -7253,7 +7445,7 @@
       <c r="AV61" s="5" t="n"/>
       <c r="AW61" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny - | MapServer TAK | FeatureServer TAK | databases -. Nazwa parametru potwierdzona: api/maps/map.md:148-149.</t>
+          <t>Dostępność: interfejs natywny - | MapServer TAK | FeatureServer TAK | databases -. Nazwa parametru potwierdzona: api/maps/map.md:148-149. | Weryfikacja kodu 2026-10-16: potwierdzone. TableController.query (natywny, tabela) i DatabaseController nie mają time. Natywny LayerController (warstwa mapy) MA time/timeRelation, więc 'interfejs natywny -' jest nieścisłe. Format time: znaczniki ms epoch rozdzielone przecinkiem (MapItemFilter.setTime/timestamp). Filtr działa tylko gdy warstwa ma pole czasowe (timeInfo start/end) i jest to FeatureLayer; brak timeRelation bierze wartość z map.getTimeInfo().getRelation() (CartoController.createFilter). Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/MapServer.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/FeatureServer.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/LayerController.java Dowód: time i timeRelation są parametrami MapServer.query, FeatureServer.query i LayerController.query; CartoController.createFilter ustawia MapItemFilter.setTime/setTimeRelation, a FeatureLayer.prepareFilter wywołuje MapItemFilter.applyTime(startField, endField) dodając warunki na polach czasowych. TimeRelation: overlaps, overlapsStart, overlapsEnd, within (oraz nazwy esriTimeRelation*).</t>
         </is>
       </c>
     </row>
@@ -7311,7 +7503,7 @@
       <c r="M62" s="5" t="n"/>
       <c r="N62" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
@@ -7354,7 +7546,7 @@
       <c r="AV62" s="5" t="n"/>
       <c r="AW62" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases -. Nazwa parametru potwierdzona: api/maps/map.md:97. W interfejsie natywnym parametr nosi nazwę version (map.md:97). Esri-owa nazwa gdbVersion dla MapServer/FeatureServer nie ma potwierdzenia w bazie wiedzy — do sprawdzenia w kodzie.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases -. Nazwa parametru potwierdzona: api/maps/map.md:97. W interfejsie natywnym parametr nosi nazwę version (map.md:97). Esri-owa nazwa gdbVersion dla MapServer/FeatureServer nie ma potwierdzenia w bazie wiedzy — do sprawdzenia w kodzie. | Weryfikacja kodu 2026-10-16: potwierdzone. Rozstrzyga wątpliwość z uwag: gdbVersion istnieje w kodzie dla MapServer/FeatureServer. W DatabaseController brak parametru. Warunek bid dodawany tylko dla tabel z polem bid (findBid != null). BaseDatabase.getVersion rzuca GdbException 'No version' dla nieznanej wersji. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/LayerController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/MapServer.java Dowód: Nazwa to 'version' w TableController.query i LayerController.query oraz 'gdbVersion' w MapServer.query i FeatureServer.query (przekazywane jako version do createFilter). GdbUtil.setupFilter robi filter.setVersion(database.getVersion(version)), a JdbcTable.applyAll dodaje warunek bid = filter.getVersionId().</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7604,7 @@
       <c r="M63" s="5" t="n"/>
       <c r="N63" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
@@ -7455,7 +7647,7 @@
       <c r="AV63" s="5" t="n"/>
       <c r="AW63" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer - | FeatureServer - | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer - | FeatureServer - | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: Znaczenie '#.pole': w SqlBuilder.findVariable/getVariable prefiks '#.' odsyła do zmiennej builderu nadrzędnego (tabela zewnętrznego zapytania), a pola bez prefiksu należą do tabeli wewnątrz EXISTS/JOIN. Opis 'pole tabeli korelowanej' może to odwracać.; Dostępność 'MapServer -, FeatureServer -': kod nie ogranicza where do interfejsów, where jest przekazywane identycznie w MapServer/FeatureServer.. Parametr techniczny to where (składnia w wyrażeniu). W databases where jest podawane w tableDefs (JSON), przetwarzane tym samym parserem; nie sprawdzano szczegółowo. idSet w EXISTS/JOIN ustawia Filter.setSet tabeli wewnętrznej (getJoinSet). Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/sql/SqlBuilder.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/expression/Expression.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/syntax/JdbcExists.java Dowód: Expression.EXISTS='EXISTS.' i JOIN='JOIN.' (komentarz: &lt;schema&gt;.&lt;table&gt;([&lt;idSet&gt;,]&lt;where&gt;)); SqlBuilder.getFunction akceptuje 1 argument bool lub (long idSet, bool). JdbcExists generuje 'EXISTS(SELECT 1 FROM ... WHERE ...)', JdbcJoin dołącza tabelę do FROM z warunkiem ON i zwraca '1=1'.</t>
         </is>
       </c>
     </row>
@@ -7513,12 +7705,12 @@
       <c r="M64" s="5" t="n"/>
       <c r="N64" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P64" s="5" t="n"/>
@@ -7556,7 +7748,7 @@
       <c r="AV64" s="5" t="n"/>
       <c r="AW64" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'funkcji query' i 'zamiast przesyłania pełnego zestawu parametrów': kod traktuje setId jako zbiór identyfikatorów obiektów (JOIN po oid), nie jako zapisane zapytanie/parametry.; Dostępność w databases: DatabaseController.query nie ma setId.. Zbiory są też listowane/zarządzane w LayerController (endpointy sets, setOperation). Tabela items z kolumnami ITEMS_SET/ITEMS_TID/ITEMS_OID w SystemSchema. Jest też osobny limit SET_QUERY_COUNT (BaseTable.getSetQueryCount), nie sprawdzano jego użycia w zapytaniu. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/sql/SqlBuilder.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java Dowód: setId (Integer) jest parametrem Table/Layer/MapServer/FeatureServer; GdbUtil.setupFilter robi filter.setSet(setId), a SqlBuilder.getJoinSet dodaje JOIN na tabelę items (set=setId, tid, oid), czyli ogranicza wynik do obiektów ze zbioru.</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7806,7 @@
       <c r="M65" s="5" t="n"/>
       <c r="N65" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O65" s="5" t="inlineStr">
@@ -7657,7 +7849,7 @@
       <c r="AV65" s="5" t="n"/>
       <c r="AW65" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer - | FeatureServer - | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer - | FeatureServer - | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: potwierdzone. W MapServer i FeatureServer flatten nie jest parametrem: do createFilter przekazywane na stałe true. DatabaseController: brak. Mechanizm działa na poziomie budowy zapytania/serializacji (też CSV/XLSX), nie tylko JSON. Szczegółów serializacji spłaszczonych rekordów nie czytano. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/LayerController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/sql/SqlBuilder.java Dowód: flatten (boolean, domyślnie false) jest parametrem TableController.query i LayerController.query; GdbUtil.setupFilter robi Filter.setFlatten, a SqlBuilder.getSelect przy getFlatten() dokłada SqlTable.addFlattenFields dla relacji typu many (spłaszczenie, komentarz: serializacja dokonuje spłaszczenia).</t>
         </is>
       </c>
     </row>
@@ -7715,12 +7907,12 @@
       <c r="M66" s="5" t="n"/>
       <c r="N66" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O66" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P66" s="5" t="n"/>
@@ -7758,7 +7950,7 @@
       <c r="AV66" s="5" t="n"/>
       <c r="AW66" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer - | FeatureServer - | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer - | FeatureServer - | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'Tryb zapytań raportowych' i rozwinięcie 'restRelQuery': w kodzie jest tylko format serializacji relacji RRQ (nazwa nie jest rozwinięta); jedyne powiązanie z raportami to użycie RelationSerializeFormat.RRQ w gp/tasks/reports/Ims2.java.; Dostępność w databases: brak parametru w DatabaseController; w LayerController też brak.. MapServer/FeatureServer wywołują serialize z rrq=false na stałe. Co dokładnie zmienia format RRQ w wyniku nie analizowano (ParametrizedCursorSerializer, Util.java gałęzie RRQ). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/json/RelationSerializeFormat.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/json/ParametrizedCursorSerializer.java Dowód: Parametr rrq (boolean) występuje tylko w TableController.query; TableController.serialize przekazuje RelationSerializeFormat.getValue(rrq), co daje RRQ i kieruje serializację do ParametrizedCursorSerializer. Istnieje też flaga rrq widoków tabel (BaseTableView, SystemSchema.VIEWS_RRQ).</t>
         </is>
       </c>
     </row>
@@ -7816,7 +8008,7 @@
       <c r="M67" s="5" t="n"/>
       <c r="N67" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O67" s="5" t="inlineStr">
@@ -7859,7 +8051,7 @@
       <c r="AV67" s="5" t="n"/>
       <c r="AW67" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: potwierdzone. Faktyczny efekt to wybór limitu liczby rekordów (przekazywany jako queryCount do GdbUtil.setupFilter), a nie 'tryb zwracania wyniku' w sensie formatu. W databases brak parametru. TableLayer i StandaloneTable mają analogiczne getQueryCount(resultType). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/QueryResultType.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseTable.java Dowód: resultType typu QueryResultType {none, standard, tile} (domyślnie none) jest parametrem Table/Layer/MapServer/FeatureServer. BaseTable.getQueryCount(resultType) wybiera limit: standard -&gt; STANDARD_QUERY_COUNT, tile -&gt; TILE_QUERY_COUNT, domyślnie QUERY_COUNT.</t>
         </is>
       </c>
     </row>
@@ -7917,12 +8109,12 @@
       <c r="M68" s="5" t="n"/>
       <c r="N68" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P68" s="5" t="n"/>
@@ -7960,7 +8152,7 @@
       <c r="AV68" s="5" t="n"/>
       <c r="AW68" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'daty jako czytelny tekst' w JSON: CursorSerializer przy formatted tłumaczy tylko domeny kodowane, daty zapisuje jak zwykle; formatowanie dat jest w CSV/XLSX.; W MapServer/FeatureServer (esri=true) dla f=json GdbUtil.serializeContent używa EsriCursorSerializer, którego wywołanie nie przyjmuje formatted, więc parametr nie działa dla JSON Esri (działa dla geojson/csv/xlsx).. Dostępność w databases: ApplyManyQueriesSerializer przekazuje stałe, brak parametru w DatabaseController. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/json/CursorSerializer.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/csv/CsvUtil.java Dowód: returnFormattedValues jest parametrem Table/Layer/MapServer/FeatureServer i trafia do GdbUtil.serialize. W CursorSerializer (JSON natywny), GeoJsonCursorSerializer, CsvUtil i XlsUtil kody CodedValueDomain są zamieniane na opisy; w CsvUtil i XlsUtil daty (Timestamp) są wtedy zapisywane jako tekst zamiast ms epoch.</t>
         </is>
       </c>
     </row>
@@ -8018,12 +8210,12 @@
       <c r="M69" s="5" t="n"/>
       <c r="N69" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P69" s="5" t="n"/>
@@ -8061,7 +8253,7 @@
       <c r="AV69" s="5" t="n"/>
       <c r="AW69" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Dla odpowiedzi JSON parametr nie jest przekazywany do serializerów (GdbUtil.serializeContent go nie przyjmuje); aliasy w JSON są zapisywane zawsze w metadanych pól ('alias') niezależnie od parametru.; Dostępność w databases: brak parametru w DatabaseController.. Efekt parametru potwierdzony tylko dla formatów csv i xlsx. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/csv/CsvUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/xls/XlsUtil.java Dowód: returnFieldAliases jest parametrem Table/Layer/MapServer/FeatureServer i w GdbUtil.serialize jest przekazywany tylko do CsvUtil.save i XlsUtil.save (argument aliases), gdzie nagłówki kolumn to field.getAlias() zamiast getName().</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8311,7 @@
       <c r="M70" s="5" t="n"/>
       <c r="N70" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O70" s="5" t="inlineStr">
@@ -8162,7 +8354,7 @@
       <c r="AV70" s="5" t="n"/>
       <c r="AW70" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases TAK. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: Nazwa 'IMS.FILTERS': w SystemSchema jest tabela systemowa 'filters' (SystemSchema.filters), prefiks schematu 'IMS' nie był weryfikowany.. Filtr bez przypisanych ról może zostać zignorowany tylko przez admina. InternalFilter.autoIgnore (autoIgnoreRoles) działa niezależnie od parametru. Typ IgnoreFilterType.all istnieje, ale parametr go nie ustawia. W databases brak parametru. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/filters/InternalFilter.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/JdbcTable.java Dowód: ignoreFilters (Boolean) jest parametrem Table/Layer/MapServer/FeatureServer; GdbUtil.setupFilter ustawia Filter.IgnoreFilterType.ignorable. JdbcTable.applyInternalFilters pomija filtr, gdy InternalFilter.ignores(...) jest prawdziwe, a w trybie ignorable pomija go tylko dla użytkownika admin lub z rolą z konfiguracji filtra (canIgnore).</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8384,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Uwzględnia przedziały skalowe zdefiniowane dla warstwy — zwraca obiekty widoczne na podanej skali.</t>
+          <t>Parametr scale (Double) ustawia Filter.setScale; w operacji query wpływa na wynik tylko przez zmienną wyrażeń $view.scale. Przedziały skalowe warstwy stosowane są przy rysowaniu mapy, nie w query.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -8220,12 +8412,12 @@
       <c r="M71" s="5" t="n"/>
       <c r="N71" s="5" t="inlineStr">
         <is>
-          <t>dokumentacja; baza wiedzy</t>
+          <t>dokumentacja; baza wiedzy; kod</t>
         </is>
       </c>
       <c r="O71" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P71" s="5" t="n"/>
@@ -8263,7 +8455,7 @@
       <c r="AV71" s="5" t="n"/>
       <c r="AW71" s="5" t="inlineStr">
         <is>
-          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases -. Nazwa parametru potwierdzona: api/databases/database.md:287.</t>
+          <t>Dostępność: interfejs natywny TAK | MapServer TAK | FeatureServer TAK | databases -. Nazwa parametru potwierdzona: api/databases/database.md:287. | Weryfikacja kodu 2026-10-16: sprzeczne. Niepotwierdzone w kodzie: 'Uwzględnia przedziały skalowe zdefiniowane dla warstwy - zwraca obiekty widoczne na podanej skali': FeatureLayer.query(Filter) wywołuje query(filter, false, Double.NaN, ...), więc getTableView(scale) nie jest użyte i widoki skalowe warstwy nie są stosowane w zapytaniu REST query; skala służy tylko jako zmienna $view.scale w wyrażeniach.. Skala wpływa na wynik tylko jeśli where/filtr/wyrażenie samo odwołuje się do $view.scale; filtrowanie po przedziałach skalowych działa w rysowaniu (FeatureLayer.prepareDraw, filter.setScale(parameters.scale)), nie w operacji query. W databases brak parametru. Wniosek oparty na ścieżce wywołań widocznej w kodzie (nie uruchamiano). Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/syntax/variable/ScaleVariable.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/FeatureLayer.java Dowód: scale (Double) jest parametrem Table/Layer/MapServer/FeatureServer i GdbUtil.setupFilter robi tylko Filter.setScale. Jedyne zużycie w SQL to zmienna wyrażeń '$view.scale' (ScaleVariable, rejestrowana w JdbcSyntax). | Opis przed korektą: Uwzględnia przedziały skalowe zdefiniowane dla warstwy — zwraca obiekty widoczne na podanej skali.</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8552,7 @@
       <c r="AV72" s="5" t="n"/>
       <c r="AW72" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.1.01 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.01 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.1.01 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.01 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: potwierdzone. Nazwy 'iMS-SQL' nie wyszukiwano w kodzie (nie sprawdzono, czy wystepuje); ocena opiera sie na parserze wyrazen i syntaxach per SZBD. Poza PG/Oracle/MSSQL w gdb sa tez SqlBuildery Maria, SQLite, Duck, Firebird. Dedykowanej klasy MsSqlBuilder nie znaleziono (MsDatabase uzywa bazowego SqlBuilder - niezweryfikowane dalej). Warunek aktywnosci: TableController ma @ConditionalOnProperty(pl.gispartner.imapserver.gdb.databases=true); w application.properties domyslnie =true (linia 419). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/postgre/PgSyntax.java Dowód: TableController.query (JSON, linia ~2821) przyjmuje najwiekszy zestaw parametrow (where, geometry, spatialRel, relationParam, outStatistics, outExpressions, having, outRenderer, historicMoment, quantizationParameters itd.) i buduje Filter przez GdbUtil.createFilter. Wyrazenie where jest parsowane przez gdb.expression.Parser i tlumaczone na SQL przez klasy syntax per SZBD (PgSyntax, OraSyntax, MsSyntax) i SqlBuilder.</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8611,7 @@
       </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P73" s="5" t="n"/>
@@ -8457,7 +8649,7 @@
       <c r="AV73" s="5" t="n"/>
       <c r="AW73" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.3.02 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.3.02 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.3.02 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.3.02 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: geometryType - nie znaleziono nigdzie odczytu parametru 'geometryType' w zapytaniu (grep literalu "geometryType" - tylko serializacja odpowiedzi); typ geometrii jest wnioskowany z obiektu JSON w parametrze geometry (GeometryDeserializer). inSR nie jest argumentem metody, lecz czytany w resolverze. Nazwy zgodne z Esri, ale zachowanie nie byl testowane. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/FeatureServer.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/MapServer.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/mvc/GeometryResolver.java Dowód: FeatureServer {layer}/query (linia ~533) i MapServer query przyjmuja: where, geometry, spatialRel, outSR, outFields, returnGeometry, returnDistinctValues, orderByFields, groupByFieldsForStatistics; inSR czytany jest w GeometryResolver (parametry 'sr' lub 'inSR') razem z geometry.</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8746,7 @@
       <c r="AV74" s="5" t="n"/>
       <c r="AW74" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.2.02 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.2.02 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.2.02 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.2.02 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: potwierdzone. Domyslne pl.gispartner.imapserver.properties.queryRoles=admin i gdb.queryRoles=${...queryRoles} (application.properties 212, 234) - potwierdza 'zazwyczaj tylko administratorzy'. Warunek aktywnosci: TableController ma @ConditionalOnProperty(pl.gispartner.imapserver.gdb.databases=true); w application.properties domyslnie =true (linia 419). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/SchemaController.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/DatabaseController.java Dowód: TableController.query (produces JSON, linia ~2821) pod databases/{database}/schemas/{schema}/datasets/{dataset}/query - ten sam kod i zestaw parametrow co 'natywne query'. SchemaController i DatabaseController maja tez wlasne 'query' (multi-query). table.assertCanQuery(user) sprawdza queryRoles.</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8843,7 @@
       <c r="AV75" s="5" t="n"/>
       <c r="AW75" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.1.02 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.02 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.1.02 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.02 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: potwierdzone. Wszystkie 7 wymienionych elementow znalezione. Nie sprawdzano jakosci implementacji kazdego (np. faktycznej obslugi M/N w kazdej geometrii). Warunek aktywnosci: TableController ma @ConditionalOnProperty(pl.gispartner.imapserver.gdb.databases=true); w application.properties domyslnie =true (linia 419). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/mvc/QuantizationResolver.java Dowód: TableController.query ma parametry shape, returnZ, returnM, returnN, multipatchOption, returnPatches, returnFootprint, quantizationParameters (QuantizationResolver czyta 'quantizationParameters') i geometryOptions (GeometryOptionsResolver). GdbUtil.setupFilter ustawia filter.setReturnZ/M/N, setQuantization, setFootprint(multipatchOption); returnPatches/returnFootprint trafiaja do GeometryOptions.setPatches/setFootprint przy serializacji.</t>
         </is>
       </c>
     </row>
@@ -8748,7 +8940,7 @@
       <c r="AV76" s="5" t="n"/>
       <c r="AW76" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.1.03 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.03 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.1.03 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.03 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: potwierdzone. Oracle: aktywna tylko wersja 'SDE.ST_Relate(...)=1' dla ST_GEOMETRY (OraSyntax linia 94); wariant SDO_GEOMETRY jest zakomentowany (linia 84), wiec dla natywnego SDO_GEOMETRY relate nie jest aktywne. Parametr zapytania nazywa sie relationParam. Nie weryfikowano walidacji formatu maski DE-9IM (np. 'F***T****') po stronie iMS - wzorzec trafia do bazy jako string. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/SpatialRelation.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/JdbcTable.java Dowód: SpatialRelation.fromString mapuje 'relation'/'esriSpatialRelRelation'; GdbUtil.setupFilter ustawia filter.setRelationParam(relationParam); JdbcTable (linia ~276) buduje Expression.RELATE(shape, geometry, relationParam), tlumaczone w PgSyntax na ST_Relate(%0,%1,%2) i w MsSyntax na %0.STRelate(%1,%2)=1.</t>
         </is>
       </c>
     </row>
@@ -8845,7 +9037,7 @@
       <c r="AV77" s="5" t="n"/>
       <c r="AW77" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.1.04 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.04 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.1.04 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.04 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: potwierdzone. Wartosc podawana jest jako liczba ms epoch (Long.parseLong) - zgodne z opisem. Wymaga zarejestrowanej historii (registerHistory, pola from/to) w tabeli. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/Filter.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java Dowód: Filter.setHistoricMoment(String) parsuje 'epoch_ms' (jeden moment, setTime) lub 'od,do' (przedzial, setFrom/setTo), z 'null' jako brak ograniczenia; puste = TimestampUtil.MAX (stan biezacy). GdbUtil.setupFilter wola filter.setHistoricMoment(historicMoment); TableController.query ma parametr historicMoment; SqlBuilder uzywa getFrom/getTo do warunkow na polach from/to.</t>
         </is>
       </c>
     </row>
@@ -8942,7 +9134,7 @@
       <c r="AV78" s="5" t="n"/>
       <c r="AW78" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.1.05 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.05 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.1.05 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.05 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: potwierdzone. Nazwa parametru w HTTP to outExpressions (argument metody w kontrolerze nazywa sie 'expressions'). Dostepny tez w FeatureServer.query i LayerController (ten sam typ argumentu). Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/Filter.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/mvc/ExpressionsResolver.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java Dowód: ExpressionsResolver czyta parametr 'outExpressions' (JSON tablica obiektow {name, expression}) do Filter.Expressions (Filter.java linia ~664); GdbUtil.setupFilter wola filter.setExpressions(expressions); wyrazenia sa dodawane jako dodatkowe pola wyniku bez zmiany schematu.</t>
         </is>
       </c>
     </row>
@@ -9039,7 +9231,7 @@
       <c r="AV79" s="5" t="n"/>
       <c r="AW79" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.1.06 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.06 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.1.06 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.06 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: potwierdzone. CIM tylko po jawnym outRendererType=cim; domyslnie esriPMS (obraz PNG). W odpowiedzi dolaczana jest tez legenda (serializeLegend). Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/FeatureServer.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/mvc/RendererResolver.java Dowód: TableController.query przyjmuje 'outRenderer' (RendererResolver czyta getParameter('outRenderer')) i 'outRendererType'. Dla outRendererType='cim' uzywa prepareCIMRenderer + serializeCIMSymbol; w przeciwnym razie prepareImageRenderer + serializeSymbol, ktore zapisuje symbol typu 'esriPMS' (pole type, imageData PNG base64). Ten sam kod w FeatureServer.query.</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9328,7 @@
       <c r="AV80" s="5" t="n"/>
       <c r="AW80" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.1.07 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.07 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.1.07 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.07 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: potwierdzone. Wszystkie wymienione funkcje (SUM, MIN, MAX, AVG, COUNT, STDDEV) obecne; dodatkowo variance i union. UWAGA: having jest ustawiane tylko w galezi bez mapIds (GdbUtil linia ~217) - przy zapytaniu po objectIds/globalIds/stringIds having jest pomijane. Parametr w HTTP to outStatistics. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/Filter.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/mvc/StatisticsResolver.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java Dowód: Filter.StatisticType = none,count,sum,min,max,avg,stddev,variance,union (fromString: tez 'var'). Filter.Statistics.fromString czyta JSON z parametru 'outStatistics' (statisticType|type, onStatisticField|field, outStatisticFieldName|name, distinct, where). GdbUtil.setupFilter ustawia setStatistics, dodaje groupByFieldsForStatistics do outFields i filter.setHaving(having).</t>
         </is>
       </c>
     </row>
@@ -9195,7 +9387,7 @@
       </c>
       <c r="O81" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P81" s="5" t="n"/>
@@ -9233,7 +9425,7 @@
       <c r="AV81" s="5" t="n"/>
       <c r="AW81" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.1.08 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.08 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.1.08 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.1.08 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: nazwa operacji 'intersect' (w kodzie 'intersection'); nazwa operacji 'minus' (w kodzie 'difference'); 'operacje na wynikach wielu zapytan' - w kodzie to operacje na zapisanym zbiorze (set id) i pojedynczym zapytaniu where/geometry dodawanym do zbioru, nie wielozapytaniowy wrapper. Dziala tylko dla JdbcTable (wymaga OID i zarejestrowanej tabeli, tid!=0). ImsTable, WfsTable i APIFeaturesTable zwracaja z setOperation null (puste implementacje). Jest tez osobny MultiQuery (gp tasks), nie badany jako 'set operation'. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/JdbcTable.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/SetOperation.java Dowód: TableController 'setOperation' (HTML i JSON, linie ~3218-3263) wola Table.setOperation; JdbcTable.setOperation (linia ~1181) obsluguje operation = create, union, intersection, difference na zbiorach OID zapisywanych w tabelach systemowych (sys.getSets()/getItems()), rowniez poprzez GP task SetOperation i FeatureServer {layer}/setOperation.</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9484,7 @@
       </c>
       <c r="O82" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P82" s="5" t="n"/>
@@ -9330,7 +9522,7 @@
       <c r="AV82" s="5" t="n"/>
       <c r="AW82" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.3.03 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.3.03 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.3.03 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.3.03 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'Naglowek exceededTransferLimit' - to NIE naglowek HTTP, tylko pole w ciele JSON odpowiedzi (i pole w PBF FeatureCollection). Limit serwera: wlasciwosc queryCount (gdb.properties.queryCount) ogranicza resultRecordCount (Math.min); pole pojawia sie tylko gdy true. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/json/CursorSerializer.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/json/EsriCursorSerializer.java Dowód: GdbUtil.setupFilter: filter.setOffset(resultOffset), filter.setCount(min(queryCount, resultRecordCount)); CursorSerializer (linia 70) i EsriCursorSerializer (69) dopisuja 'exceededTransferLimit': true, gdy cursor.getExeeded().</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9552,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>queryRelatedRecords – odpytywanie rekordów z powiązanych warstw przez zdefiniowane relacje (1:1, 1:N, N:N).</t>
+          <t>Relacje między warstwami dostępne natywnie (RelationField, parametr rrq, outFields z polami relacji). Osobnej operacji queryRelatedRecords nie znaleziono; pole relationships w FeatureServer jest zawsze pustą tablicą.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -9389,7 +9581,7 @@
       </c>
       <c r="O83" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P83" s="5" t="n"/>
@@ -9427,7 +9619,7 @@
       <c r="AV83" s="5" t="n"/>
       <c r="AW83" s="5" t="inlineStr">
         <is>
-          <t>Przeniesiono z IMS-3.3.05 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.3.05 pozostaje niewykorzystany.</t>
+          <t>Przeniesiono z IMS-3.3.05 przy konsolidacji funkcji query (grupa 3.5). Numer IMS-3.3.05 pozostaje niewykorzystany. | Weryfikacja kodu 2026-10-16: niepotwierdzone. Niepotwierdzone w kodzie: operacja queryRelatedRecords; relacje 1:1 (RelationType ma tylko ManyOne, OneMany, ManyMany). Frazy sprawdzone: 'queryRelated', 'relatedRecords', 'RelatedRecord' (case-insensitive, cale repo poza static) - 0 trafien. Relacje istnieja natywnie (RelationField, createRelation, parametr rrq i outFields z polami relacji w query), ale nie jako osobna operacja queryRelatedRecords. Nie 'nie istnieje' w absolutnym sensie, ale w tym repo brak. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/FeatureServer.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/json/FeatureServerItemSerializer.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/TableController.java Dowód: Nie znaleziono operacji queryRelatedRecords. W FeatureServerItemSerializer pole 'relationships' jest zawsze pustą tablicą (writeArrayFieldStart + writeEndArray, linie 92, 123, 208, 312). | Opis przed korektą: queryRelatedRecords – odpytywanie rekordów z powiązanych warstw przez zdefiniowane relacje (1:1, 1:N, N:N).</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9714,11 @@
       <c r="AT84" s="5" t="n"/>
       <c r="AU84" s="5" t="n"/>
       <c r="AV84" s="5" t="n"/>
-      <c r="AW84" s="5" t="n"/>
+      <c r="AW84" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. SLPK jest zarejestrowane tylko w config/orlen (klienckim), nie w config/default. Pliki .jgp to JSON z lista klas Java (rejestracja zadan), nie osobny mechanizm 'rozszerzen' - rozszerzenia ext/* (emuia, gs, nkwpobierz) tez rejestruja zadania przez .jgp. Aktywna konfiguracja wg application.properties: pl.gispartner.imapserver.config=default. Pliki: gp-imapserver-app/config/default/linearReferenceSystem.jgp; gp-imapserver-app/config/default/vectorTiles.jgp; gp-imapserver-app/config/orlen/package.jgp Dowód: GpFolder ladowanie plikow *.jgp (WildcardFileFilter("*.jgp")); default/linearReferenceSystem.jgp rejestruje 5 zadan LRS (UpdateEvents, CalibrateLinearReference, UpdateLinearReference, ChangeGeometryType, OverlayRouteEvents), default/vectorTiles.jgp rejestruje MapCreatorFromVtpk; orlen/package.jgp rejestruje m.in. MapCreatorFromSlpk i PackageSLPK (wg listy klas w jgp).</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="55.2" customHeight="1" s="15">
       <c r="A85" s="5" t="n">
@@ -9579,7 +9775,7 @@
       </c>
       <c r="O85" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P85" s="5" t="n"/>
@@ -9615,7 +9811,11 @@
       <c r="AT85" s="5" t="n"/>
       <c r="AU85" s="5" t="n"/>
       <c r="AV85" s="5" t="n"/>
-      <c r="AW85" s="5" t="n"/>
+      <c r="AW85" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: modul IMSPy (get/set parametrow, databases(), messenges()) - brak w repo (zadnych plikow .py w repo); wersja Python 3.8 - brak w kodzie (exe="py" to launcher systemowy, wersja nie jest wymuszana); funkcje get/set/databases()/messenges() - po stronie Javy istnieje tylko odpowiedni protokol tekstowy w Cmd.line(), brak nazw tych funkcji. Szukane: IMSPy, imspy, messenges, python/jython/graalpy w *.java/*.gradle/*.properties/*.toml/*.md, Glob **/*.py w repo (0 wynikow). IMSPy prawdopodobnie lezy poza repo (osobna paczka Python). Wpis w python.jgp to przyklad z twardymi sciezkami c:\\py i cwd c:\\warstwy (Windows). Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/cmd/Python.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/cmd/Cmd.java; gp-imapserver-app/config/default/python.jgp Dowód: Python extends Cmd: uruchamia zewnetrzny proces (domyslnie exe="py" + script) przez ProcessBuilder, przekazuje argumenty (user, hash, modulo, parametry name=typ:wartosc) i czyta protokol stdout: 'message:', 'output:', 'count:', 'step', 'status', 'request:'. default/python.jgp rejestruje zadanie Python (name=sum, script c:\\py\\test.py).</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="55.2" customHeight="1" s="15">
       <c r="A86" s="5" t="n">
@@ -9708,7 +9908,11 @@
       <c r="AT86" s="5" t="n"/>
       <c r="AU86" s="5" t="n"/>
       <c r="AV86" s="5" t="n"/>
-      <c r="AW86" s="5" t="n"/>
+      <c r="AW86" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. '/model' to widok/definicja modelu zadania ({task}/model, JSON wymaga task.assertCanModify), a nie osobny endpoint uruchamiania lancucha - uruchamianie idzie przez execute/submitJob zadania typu model. Sa tez wezly warunkowe (CONDITIONAL, IfGpTask), wait i relacje - szerzej niz opis. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/model/Model.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/model/TmpModel.java; gp-imapserver-app/config/default/model.jgp Dowód: Model.java buduje graf wezlow (NodeDef) gdzie input wezla odwoluje sie do wyniku innego wezla (np. "buffer.result", rozbijane po '.'); run(job) wola createInstance(job).run(). Common.java ma "{task}/model" (JSON i HTML; HTML rzuca blad gdy task.getType()!=model). model.jgp i GP_AS.jgp rejestruja modele (TmpModel/Model) np. buffer -&gt; table.count.</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="41.4" customHeight="1" s="15">
       <c r="A87" s="5" t="n">
@@ -9801,7 +10005,11 @@
       <c r="AT87" s="5" t="n"/>
       <c r="AU87" s="5" t="n"/>
       <c r="AV87" s="5" t="n"/>
-      <c r="AW87" s="5" t="n"/>
+      <c r="AW87" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Harmonogram dziala tylko gdy skonfigurowano baze GP: GpContainer.refreshScheduler uruchamia SchedulerStarter tylko gdy getDatabase()!=null, inaczej loguje 'GP scheduler is not enabled'. W application.properties pl.gispartner.imapserver.gp.database jest puste (domyslnie wylaczone). Role domyslnie: create schedule wg scheduleRoles=admin; modify/remove/activate=admin. Endpointy: {task}/schedule (tworzenie) i gp/.../scheduler (lista), nie samo '/schedule'. Pliki: gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/Common.java; gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/scheduler/SchedulerStarter.java; gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/scheduler/DatabaseScheduler.java Dowód: Common.java: "{task}/schedule" (HTML/JSON) tworzy harmonogram (cron, scheduleStart/End, active) przez container.getDatabaseScheduler().createReturnSchedule; DatabaseScheduler waliduje CronSequenceGenerator.isValidExpression; SchedulerStarter (watek) odpala joby wg cron. Services.java: "scheduler" oraz "scheduler/{idSchedule}" (update/delete/activate/deactivate).</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="55.2" customHeight="1" s="15">
       <c r="A88" s="5" t="n">
@@ -9858,7 +10066,7 @@
       </c>
       <c r="O88" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P88" s="5" t="n"/>
@@ -9894,7 +10102,11 @@
       <c r="AT88" s="5" t="n"/>
       <c r="AU88" s="5" t="n"/>
       <c r="AV88" s="5" t="n"/>
-      <c r="AW88" s="5" t="n"/>
+      <c r="AW88" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: operacja o nazwie checkJobStatus - brak w kodzie (grep checkJobStatus: 0 trafien); sprawdzanie statusu odbywa sie przez GET {task}/jobs/{job}. execute i submitJob potwierdzone. 'polled status checking' to polling GET jobs/{job} (nazwa checkJobStatus jest terminologia ArcGIS, nie iMS). Joby asynchroniczne maja kolejke (DatabaseQueue gdy ustawiona baza GP, w repo jest tez MemoryAsyncJob). Pliki: gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/Common.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/impl/MemoryAsyncJob.java; gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/container/GpContainer.java Dowód: Common.java: "{task}/execute" (HTML/JSON) wola task.sync(...) i zwraca job synchronicznie; "{task}/submitJob" (HTML/JSON) wola container.async(...) i zwraca AsyncJob; status/wynik czytane przez "{task}/jobs/{job}", ".../inputs", ".../results", plus cancel/accept/finish.</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="55.2" customHeight="1" s="15">
       <c r="A89" s="5" t="n">
@@ -9951,7 +10163,7 @@
       </c>
       <c r="O89" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P89" s="5" t="n"/>
@@ -9987,7 +10199,11 @@
       <c r="AT89" s="5" t="n"/>
       <c r="AU89" s="5" t="n"/>
       <c r="AV89" s="5" t="n"/>
-      <c r="AW89" s="5" t="n"/>
+      <c r="AW89" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'bufory w roznych jednostkach' - brak parametru jednostek; size jest w jednostkach ukladu wspolrzednych danych (opis w capap/analysis.jgp: 'zalezna od ukladu danych wejsciowych'). Dostepnosc: w config/default (aktywny wg application.properties) analysis.jgp rejestruje tylko Buffer i Union; Centroid i GeometricFeatures sa zarejestrowane dopiero w config/capap, gus, isok, sipww (klienckie). Pole dlugosci nazywa sie 'lenght' (literowka w kodzie). Istnieje tez osobne gp.tasks.geometry.Buffer (zarejestrowane w default/geometry.jgp). Zadania uzywaja funkcji PostGIS (st_*), wymagaja bazy z PostGIS. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Buffer.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Centroid.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/GeometricFeatures.java Dowód: Buffer: name="buffer", input size(double), SQL st_multi(st_buffer(shape,size)); Centroid (task 'centroid'): st_centroid; GeometricFeatures: dodaje pola lenght, area, nPoint, numGeometries, isValid, bxmin/bymin/bxmax/bymax (ST_Length, ST_Area, ST_NPoints, ST_NumGeometries, ST_IsValid, ST_XMin...).</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="41.4" customHeight="1" s="15">
       <c r="A90" s="5" t="n">
@@ -10080,7 +10296,11 @@
       <c r="AT90" s="5" t="n"/>
       <c r="AU90" s="5" t="n"/>
       <c r="AV90" s="5" t="n"/>
-      <c r="AW90" s="5" t="n"/>
+      <c r="AW90" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Segmentize to st_segmentize (dogeszczenie wierzcholkow tak, by segmenty byly nie dluzsze niz parametr) - nie dzieli linii na osobne rowne obiekty, wiec 'podzial linii na rowne odcinki' z opisu biznesowego jest nadinterpretacja. Parametr nazywa sie 'lenght' (literowka). Subdivide dziala na dowolnej geometrii (st_subdivide), nie tylko poligonach. Zarejestrowane w config/capap, gus, isok, sipww; brak w config/default. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Simplify.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Segmentize.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Subdivide.java Dowód: Simplify: name="simplify", input tolerance, st_simplify; Segmentize: name="segmentize", input lenght, st_segmentize(shape,lenght), wynik polyline; Subdivide (task 'subdivide'): input vertices(int), st_multi(st_subdivide(shape,vertices)).</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="41.4" customHeight="1" s="15">
       <c r="A91" s="5" t="n">
@@ -10173,7 +10393,11 @@
       <c r="AT91" s="5" t="n"/>
       <c r="AU91" s="5" t="n"/>
       <c r="AV91" s="5" t="n"/>
-      <c r="AW91" s="5" t="n"/>
+      <c r="AW91" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Nazwa zadania snapToGrid w kodzie to 'snaptogrid' (maly zapis; nazwa z klasy/pola name), a nie 'snapToGrid' jak w opisie - moze miec znaczenie przy wywolaniach REST. Zarejestrowane tylko w config/capap, gus, isok, sipww. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Dump.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/DumpPoints.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/SnapToGrid.java Dowód: Dump: st_multi((st_dump(shape)).geom); DumpPoints: (st_dumppoints(shape)).geom -&gt; pole shape typu point; SnapToGrid: name="snaptogrid", input size, st_snaptogrid(shape,size).</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="55.2" customHeight="1" s="15">
       <c r="A92" s="5" t="n">
@@ -10266,7 +10490,11 @@
       <c r="AT92" s="5" t="n"/>
       <c r="AU92" s="5" t="n"/>
       <c r="AV92" s="5" t="n"/>
-      <c r="AW92" s="5" t="n"/>
+      <c r="AW92" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Affine to transformacja 2D (6 parametrow). Zarejestrowane w config/capap, gus, isok, sipww; brak w default. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/AffineTransformation.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Transform.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/FlipCoordinates.java Dowód: AffineTransformation: name="affineTransformation", inputy a,b,d,e,xoff,yoff, ST_Affine; Transform: input srid(int), st_transform(shape,srid), pole wynikowe w nowym srid; FlipCoordinates: name="flipCoordinates", ST_FlipCoordinates.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="55.2" customHeight="1" s="15">
       <c r="A93" s="5" t="n">
@@ -10359,7 +10587,11 @@
       <c r="AT93" s="5" t="n"/>
       <c r="AU93" s="5" t="n"/>
       <c r="AV93" s="5" t="n"/>
-      <c r="AW93" s="5" t="n"/>
+      <c r="AW93" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. MinimumBoundingCircle liczy jedno kolo dla calego zbioru (ST_Collect), nie per obiekt. generatePoints losuje punkty (st_generatepoints), nie generuje siatki - 'siatki punktow probkowania' z opisu biznesowego nie sa potwierdzone. 'Lista wspolrzednych' = tekst WKT (MULTIPOINT); import z list CSV nie jest tu obslugiwany. RYZYKO: wkt wklejany wprost do SQL (konkatenacja) w GeneratePointFromList - mozliwy SQL injection. Zarejestrowane w capap, gus, isok, sipww. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/MinimumBoundingCircle.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/GeneratePoints.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/GeneratePointFromList.java Dowód: MinimumBoundingCircle: ST_multi(ST_MinimumBoundingCircle(ST_Collect(...))); GeneratePoints: input npoints, (ST_Dump(st_generatepoints(shape,npoints))).geom; GeneratePointFromList: inputy database, wkt, srid, (st_dump(ST_GeomFromText(wkt,srid))).geom.</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="41.4" customHeight="1" s="15">
       <c r="A94" s="5" t="n">
@@ -10452,7 +10684,11 @@
       <c r="AT94" s="5" t="n"/>
       <c r="AU94" s="5" t="n"/>
       <c r="AV94" s="5" t="n"/>
-      <c r="AW94" s="5" t="n"/>
+      <c r="AW94" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wszystkie 5 klas istnieje i jest zarejestrowanych w capap/gus/isok/sipww (nie w default). Difference/SymmetricDifference lacza (ST_Union) caly zbior przed operacja, wynik to geometria, a nie filtr obiektow - przyklad 'ktore dzialki NIE leza w strefie' realizuje raczej noCommonPart (IMS-0075). Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Intersection.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Difference.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/SymmetricDifference.java Dowód: Intersection: st_intersection(T.shape1,T2.shape2); Difference: ST_Difference(ST_Union(zb.1),ST_Union(zb.2)); SymmetricDifference: ST_SymDifference; Clip: st_intersection(shape,(select st_union(input2...))); Split: st_split(shape1, brzeg shape2).</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="55.2" customHeight="1" s="15">
       <c r="A95" s="5" t="n">
@@ -10545,7 +10781,11 @@
       <c r="AT95" s="5" t="n"/>
       <c r="AU95" s="5" t="n"/>
       <c r="AV95" s="5" t="n"/>
-      <c r="AW95" s="5" t="n"/>
+      <c r="AW95" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Dissolve realizowany jest jako jedno ST_Union po obiektach spelniajacych wyrazenie (WHERE), a nie GROUP BY po atrybucie - wynik to jeden obiekt; statystyki liczone tylko dla pol nie-tekstowych i nie-geometrycznych. Istnieje tez CollectOld (nierejestrowany) oraz Union (default). Zarejestrowane w capap/gus/isok/sipww. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Collect.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/GroupingAndCombiningObjects.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Copy.java Dowód: Collect (2 wejscia) wstawia obiekty obu tabel do jednej wyjsciowej (merge); GroupingAndCombiningObjects: ST_Multi(ST_Union(T.shape)) z WHERE wg parametru expression, a BaseAnalyse.copyCalculateFiled dodaje dla pol liczbowych kolumny &lt;pole&gt;SUM/AVG/MIN/MAX; Copy kopiuje tabele do wyjscia.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="55.2" customHeight="1" s="15">
       <c r="A96" s="5" t="n">
@@ -10638,7 +10878,11 @@
       <c r="AT96" s="5" t="n"/>
       <c r="AU96" s="5" t="n"/>
       <c r="AV96" s="5" t="n"/>
-      <c r="AW96" s="5" t="n"/>
+      <c r="AW96" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. RYZYKO/uwaga: RemoveByAtributeSelection i RemoveByIntersection wykonuja DELETE bezposrednio na tabeli wejsciowej (connectedName(tmpName,input)), bez tabeli wyjsciowej; RemoveByAtributeSelection bez parametru expression usuwa WSZYSTKIE wiersze (where=""). W AttributeSelection parametr expression jest zakomentowany (zostal 'where'). Zarejestrowane w capap/gus/isok/sipww. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/AttributeSelection.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/CommonPart.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/NoCommonPart.java Dowód: AttributeSelection (kopiuje wybrane obiekty wg parametru where z BaseAnalyse), CommonPart (st_relate 'T********'), NoCommonPart (st_relate 'FF*FF****'), RemoveRepeatedPoints (st_removerepeatedpoints), RemoveByAtributeSelection (DELETE ... WHERE expression), RemoveByIntersection (DELETE ... USING ... st_relate).</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="55.2" customHeight="1" s="15">
       <c r="A97" s="5" t="n">
@@ -10731,7 +10975,11 @@
       <c r="AT97" s="5" t="n"/>
       <c r="AU97" s="5" t="n"/>
       <c r="AV97" s="5" t="n"/>
-      <c r="AW97" s="5" t="n"/>
+      <c r="AW97" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wariant 'within' to ST_DWithin(...,200) z na stale wpisana odlegloscia 200 (jednostki ukladu), a nie ST_Within; 'all' to OR trzech warunkow. Join zwraca wiersz na kazda pare dopasowan (bez agregacji). Zarejestrowane w capap/gus/isok/sipww. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/AddAttributeBySpatialJoin.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/JoinTabularAndSpatialData.java Dowód: AddAttributeBySpatialJoin: input relationship (all/intersects/contains/within), warunek WHERE z ST_Intersects/ST_Contains/ST_DWithin laczy atrybuty obu tabel; JoinTabularAndSpatialData: inputy field, field2, outputFields, outputFields2, join WHERE T.field1 = T2.field2.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="41.4" customHeight="1" s="15">
       <c r="A98" s="5" t="n">
@@ -10824,7 +11072,11 @@
       <c r="AT98" s="5" t="n"/>
       <c r="AU98" s="5" t="n"/>
       <c r="AV98" s="5" t="n"/>
-      <c r="AW98" s="5" t="n"/>
+      <c r="AW98" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Nazwa zadania z klasy to 'statisticalCalculations' (opis: statisticalCalculation). Parametr stats wstawiany do SQL jako nazwa funkcji bez walidacji (getStat) - mozliwa iniekcja. Zarejestrowane w capap/gus/isok/sipww. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/StatisticalCalculations.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Calculate.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Count.java Dowód: StatisticalCalculations: inputy fields (domyslnie "*"), stats (domyslnie "SUM,MIN,MAX,AVG"), st_relate(poligon, obiekt) i agregaty; Calculate: inputy field i expression (Expression.parse(...).prepare); Count: count(...) obiektow zbioru 1 w poligonach zbioru 2 (st_relate).</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="41.4" customHeight="1" s="15">
       <c r="A99" s="5" t="n">
@@ -10881,7 +11133,7 @@
       </c>
       <c r="O99" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P99" s="5" t="n"/>
@@ -10917,7 +11169,11 @@
       <c r="AT99" s="5" t="n"/>
       <c r="AU99" s="5" t="n"/>
       <c r="AV99" s="5" t="n"/>
-      <c r="AW99" s="5" t="n"/>
+      <c r="AW99" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: findNextObject 'NN z odlegloscia' - tabela wynikowa ma tylko pole shape, brak pola z odlegloscia; nazwa findNextObject - w kodzie klasa/zadanie to FindeNextObject (task 'findeNextObject', literowka). W FindeNextObject warunek 'st_distance(T.shape1, T2.shape1) != 0' uzywa shape1 po obu stronach (prawdopodobny blad), wiec wykluczanie obiektu samego ze soba moze nie dzialac jak zamierzono (niepotwierdzone, tylko odczyt kodu). 'Hot-spots' nie ma osobnego zadania - tylko DBSCAN. Zarejestrowane w capap/gus/isok/sipww. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/DensityMap.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/ClusterIdentification.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/FindeNextObject.java Dowód: DensityMap: count(punkty w poligonie)/st_area*1000000; ClusterIdentification: st_ClusterDBSCAN(shape,eps,minpoints) (pole cid); VoronoiPolygons: ST_VoronoiPolygons(union,tolerance); GeometricMedian: st_geometricmedian; FindeNextObject: najblizszy obiekt zbioru 2 wg ORDER BY st_distance LIMIT 1.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="41.4" customHeight="1" s="15">
       <c r="A100" s="5" t="n">
@@ -10974,7 +11230,7 @@
       </c>
       <c r="O100" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P100" s="5" t="n"/>
@@ -11010,7 +11266,11 @@
       <c r="AT100" s="5" t="n"/>
       <c r="AU100" s="5" t="n"/>
       <c r="AV100" s="5" t="n"/>
-      <c r="AW100" s="5" t="n"/>
+      <c r="AW100" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: geokodowanie odwrotne (wspolrzedne -&gt; adres) - brak w kodzie (Geocode zwraca tylko point z adresu; grep reverse w gp: brak w Geocode*); Nominatim jako aktywny geokoder w config/default - default/geocoding.jgp ustawia type="fts" i url=https://capap.gugik.gov.pl/api/fts/gc/pkt, a wpisy _type=nominatim sa wylaczone (klucze z podkreslnikiem). Nominatim jest implementacja domyslna (gdy type!=fts), ale aktywna konfiguracja default uzywa geokodera FTS (capap.gugik.gov.pl). Kod ma tez klase Fts. Brak obslugi kierunku odwrotnego. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/geocoding/Geocode.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/geocoding/GeocodeTable.java; gp-imapserver-app/config/default/geocoding.jgp Dowód: Geocode: wejscie address/city/county/state/country/zip/epsg, wyjscia result/point/id/rank; wewnetrzna klasa Nominatim buduje zapytanie do domyslnego https://nominatim.openstreetmap.org/search.php (format=jsonv2) i parsuje lon/lat; GeocodeTable robi to dla tabeli.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="41.4" customHeight="1" s="15">
       <c r="A101" s="5" t="n">
@@ -11067,7 +11327,7 @@
       </c>
       <c r="O101" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P101" s="5" t="n"/>
@@ -11103,7 +11363,11 @@
       <c r="AT101" s="5" t="n"/>
       <c r="AU101" s="5" t="n"/>
       <c r="AV101" s="5" t="n"/>
-      <c r="AW101" s="5" t="n"/>
+      <c r="AW101" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: resampleRaster 'z wyborem metody' - brak parametru metody, tylko width i height; clipRaster 'do bbox' - przycinanie tylko do geometrii z drugiej tabeli (brak osobnego parametru bbox). Zadania opieraja sie o funkcje rastrowe PostGIS (ST_*). Zarejestrowane w capap/gus/isok/sipww; brak w default. Istnieje tez ClipRasterV2 (nierejestrowany). Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/HillShadeRaster.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/SlopeRaster.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/ClipRaster.java Dowód: HillShadeRaster: inputy azimuth, altitude, max_bright, scale, ST_HillShade; SlopeRaster: ST_Slope; ClipRaster: ST_Clip(raster, geometria z drugiej tabeli, true); ResampleRaster: inputy width, height, ST_Resample(raster,width,height).</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="41.4" customHeight="1" s="15">
       <c r="A102" s="5" t="n">
@@ -11196,7 +11460,11 @@
       <c r="AT102" s="5" t="n"/>
       <c r="AU102" s="5" t="n"/>
       <c r="AV102" s="5" t="n"/>
-      <c r="AW102" s="5" t="n"/>
+      <c r="AW102" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Nazwa z opisu rasterToPolygon to w kodzie RasterToPolygons (task 'rasterToPolygons'). RasterFromShape ma na stale rozdzielczosc 100x100 (st_asraster(..,100,100)) i buforuje obiekty nie-poligonowe o 10 - ograniczenie. Zarejestrowane w capap/gus/isok/sipww. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterFromShape.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterFromFeatures.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterToPolygons.java Dowód: RasterFromShape: st_asraster(...); RasterFromFeatures: inputy method(SUM), resolution, buffers, weightField; RasterToPolygons: ST_PixelAsPolygons; RasterToPoints: ST_PixelAsCentroids; RasterToIsolines: wlasna implementacja (klasa Square, input levels).</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="41.4" customHeight="1" s="15">
       <c r="A103" s="5" t="n">
@@ -11253,7 +11521,7 @@
       </c>
       <c r="O103" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P103" s="5" t="n"/>
@@ -11289,7 +11557,11 @@
       <c r="AT103" s="5" t="n"/>
       <c r="AU103" s="5" t="n"/>
       <c r="AV103" s="5" t="n"/>
-      <c r="AW103" s="5" t="n"/>
+      <c r="AW103" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: rasterStats/rasterToStats 'std' i 'histogram' - brak (tylko min, max, avg i wartosc w punkcie); coverage 'analiza NoData' - Coverage liczy pokrycie poligonow zbioru 1 obiektami zbioru 2 (coverage_area, coverage_percent + statystyki pol), nie NoData rastra. Zadanie 'rasterStats' i 'rasterToStats' istnieja pod tymi nazwami. Coverage dziala na danych wektorowych (wymaga poligonow w pierwszym wejsciu). Zarejestrowane w capap/gus/isok/sipww (Coverage dodatkowo w isok x3). Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterUnion.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterStats.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterToStats.java Dowód: RasterUnion: st_union(raster,method) domyslnie SUM; RasterStats: ST_SummaryStats -&gt; outputy value,min,max,avg w punkcie x,y; RasterToStats: pola min,max,avg,val; TransformRaster: input srid, ST_Transform(raster,srid).</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="55.2" customHeight="1" s="15">
       <c r="A104" s="5" t="n">
@@ -11346,7 +11618,7 @@
       </c>
       <c r="O104" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P104" s="5" t="n"/>
@@ -11382,7 +11654,11 @@
       <c r="AT104" s="5" t="n"/>
       <c r="AU104" s="5" t="n"/>
       <c r="AV104" s="5" t="n"/>
-      <c r="AW104" s="5" t="n"/>
+      <c r="AW104" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: LoadInputFile z formatem GPKG - brak w createLoaders (GPKG tylko przez CursorLoader zarejestrowany w config/gs; GpkgImporter nie jest zarejestrowany nigdzie); import z GDB (FileGDB) przez loadInputFile - brak; ext/gp-imapserver-fgdb jest sterownikiem dostepu do danych, nie loaderem; wymienione zrodla GUGiK/BDOT/OSM - brak jakiegokolwiek wiazania w kodzie. loadInputFile i analyzeInputFile zarejestrowane tylko w config/capap (nie default). Nazwy zadan to loadInputFile/analyzeInputFile (z klas). Eksport przez API query potwierdzony tylko co do listy formatow wyzej; nie weryfikowano dzialania kazdego formatu. Szukane: gpkg, GpkgImporter, FgdbCursor, createLoaders. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/TaskInputFile.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/AnalyzeInputFile.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/CursorLoader.java Dowód: TaskInputFile.createLoaders: formaty csv, geojson, gml, kml, shp, zipshp, xlsx dla LoadInputFile/AnalyzeInputFile (AnalyzeInputFile ma output tableDef); eksport: GpCursorTask ma wybor formatow geojson, geojsonzip, shp, kml, xlsx, csv, gpkg, a TableController obsluguje f=sqlite/pbf/gpkg.</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="41.4" customHeight="1" s="15">
       <c r="A105" s="5" t="n">
@@ -11439,7 +11715,7 @@
       </c>
       <c r="O105" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P105" s="5" t="n"/>
@@ -11475,7 +11751,11 @@
       <c r="AT105" s="5" t="n"/>
       <c r="AU105" s="5" t="n"/>
       <c r="AV105" s="5" t="n"/>
-      <c r="AW105" s="5" t="n"/>
+      <c r="AW105" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Cursor Loader/Converter 'do wsadowych operacji przez kursory DB' - to kursory plikowe: CursorLoader czyta pliki (shp/esrijson/gpkg/geojson/gpx/kml/kmz/gml) do obiektu Cursor, a CursorConverter konwertuje kursor na plik w wybranym formacie; nie sa to kursory bazodanowe; 'modyfikacja tabel' z opisu biznesowego - brak zadania alter/modyfikacji struktury (jest create, drop). createTable/dropTable/dropSchema nie sa zarejestrowane w config/default (tylko capap). Istnieja tez CreateTableSafe, CopyTable, RegisterTable (CopyTable i RegisterTable nie sa zarejestrowane w zadnym .jgp). Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/CreateTable.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/DropTable.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/DropSchema.java Dowód: CreateTable (BaseCreateTable, tworzy tabele wg TableDef), DropTable (inputy database, schema, table), DropSchema (inputy database, schema) - zarejestrowane w config/capap; CursorLoader (input file -&gt; output cursor) i CursorConverter (input cursor -&gt; plik) - zarejestrowane w config/gs, a CursorConverter takze w riip.</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="41.4" customHeight="1" s="15">
       <c r="A106" s="5" t="n">
@@ -11532,7 +11812,7 @@
       </c>
       <c r="O106" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P106" s="5" t="n"/>
@@ -11568,7 +11848,11 @@
       <c r="AT106" s="5" t="n"/>
       <c r="AU106" s="5" t="n"/>
       <c r="AV106" s="5" t="n"/>
-      <c r="AW106" s="5" t="n"/>
+      <c r="AW106" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: createMosaic jako zadanie GP - klasa CreateMosaic istnieje (inputy table, field, epsg, prefix, bands, pixels), ale nie jest zarejestrowana w zadnym pliku .jgp w repo, wiec nie jest dostepna jako zadanie. Szukane: CreateMosaic/createMosaic w *.jgp i *.java (tylko definicja klasy i metody gdb Table.createMosaic). SLPK tylko w config/orlen; VTPK w default. W sipww/mosaic.jgp ImportMosaic jest dodatkowo zarejestrowany pod nazwa 'import'. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/mosaic/CreateMosaic.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/mosaic/ImportMosaic.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/vectorTiles/MapCreatorFromVtpk.java Dowód: ImportMosaic (inputy table, field, path) zarejestrowane jako 'importMosaic' w config/riip i sipww; MapCreatorFromVtpk (plik VTPK -&gt; mapa) zarejestrowany w default/vectorTiles.jgp; MapCreatorFromSlpk i Package/PackageSLPK/Packer zarejestrowane w config/orlen.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="41.4" customHeight="1" s="15">
       <c r="A107" s="5" t="n">
@@ -11657,7 +11941,11 @@
       <c r="AT107" s="5" t="n"/>
       <c r="AU107" s="5" t="n"/>
       <c r="AV107" s="5" t="n"/>
-      <c r="AW107" s="5" t="n"/>
+      <c r="AW107" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. 'Percentile' z opisu odpowiada PercentClip w kodzie; dodatkowo istnieje HistogramEqualization i None. RasterLayer buduje domyslnie MultipleRasterRenderer (Stretch dla float, Rgb dla 3 pasm, GreyScale jako domyslny). Pliki: gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/drawing/StretchRenderer.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/raster/functions/enums/StretchType.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/json/ims/RendererLoaders.java Dowód: RendererLoaders laduje typy 'stretch', 'rgb', 'greyscale'/'grayscale', 'classify', 'multiple' (klasy StretchRenderer, RgbRenderer, GreyScaleRenderer, ClassifyRenderer, MultipleRasterRenderer); StretchType: none, standardDeviation, histogramEqualization, minMax, percentClip, sigmoid.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="55.2" customHeight="1" s="15">
       <c r="A108" s="5" t="n">
@@ -11710,7 +11998,7 @@
       </c>
       <c r="O108" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P108" s="5" t="n"/>
@@ -11746,7 +12034,11 @@
       <c r="AT108" s="5" t="n"/>
       <c r="AU108" s="5" t="n"/>
       <c r="AV108" s="5" t="n"/>
-      <c r="AW108" s="5" t="n"/>
+      <c r="AW108" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Colorize - brak (grep colorize bez rozrozniania wielkosci liter: 0 trafien w *.java/json/jsp/properties); Reclassify - brak (grep reclassif/remap: 0 trafien); Clip jako funkcja rastrowa - brak w enum RasterFunctionName; Mosaic jako funkcja rastrowa - brak w enum; mozaikowanie istnieje jako warstwa mozaiki (MosaicLayer.getMosaic().mosaic(...) w ImageServer), nie jako nazwana funkcja. Potwierdzone 6 z 10: Hillshade, NDVI, BandArithmetic, Convolution, Colormap, Resample. Dodatkowe w kodzie: Stretch, Identity, Grayscale, ExtractBand, CompositeBand, TestTrimSize (ta ostatnia wyglada na testowa). Pliki: gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/raster/functions/enums/RasterFunctionName.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/raster/functions/NDVIFunction.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/raster/functions/BandArithmeticFunction.java Dowód: Enum RasterFunctionName rejestruje funkcje: Hillshade, Colormap, Stretch, Identity, Resample, Convolution, Grayscale, NDVI, BandArithmetic, ExtractBand, CompositeBand, TestTrimSize (kazda z klasa *Function w pakiecie raster.functions).</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="41.4" customHeight="1" s="15">
       <c r="A109" s="5" t="n">
@@ -11835,7 +12127,11 @@
       <c r="AT109" s="5" t="n"/>
       <c r="AU109" s="5" t="n"/>
       <c r="AV109" s="5" t="n"/>
-      <c r="AW109" s="5" t="n"/>
+      <c r="AW109" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wartosc typu jest czula na wielkosc liter ('compactS3', nie 'compacts3'). Kod obsluguje wiecej niz opis: cassandra, cassandra2, s3, slpk. Przykladowe default/*.stg: lite (default.stg), compact, cassandra(type=cassandra2). Typ 'http' to HttpTileStorage z maska url. Pliki: gp-imapserver-rest/src/main/java/pl/gispartner/imapserver/rest/container/RootFolder.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/tile/TileCache.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/tile/RasterGenerator.java Dowód: RootFolder.storage(File) obsluguje type: file, s3, compactS3, cassandra, cassandra2, cassandra3, lite, compact, slpk, http; TileCache opakowuje FileStorage w FileTileStorageWrapper (typ 'file'); RasterGenerator.Format = unknown/png32/jpg/mix; LercGenerator ("lerc"); VectorGenerator ("pbf").</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="41.4" customHeight="1" s="15">
       <c r="A110" s="5" t="n">
@@ -11888,7 +12184,7 @@
       </c>
       <c r="O110" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P110" s="5" t="n"/>
@@ -11924,7 +12220,11 @@
       <c r="AT110" s="5" t="n"/>
       <c r="AU110" s="5" t="n"/>
       <c r="AV110" s="5" t="n"/>
-      <c r="AW110" s="5" t="n"/>
+      <c r="AW110" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: wersja GDAL 3.3.2 - w repo komentarz w gp-imapserver-gdb/build.gradle mowi 'gdal.jar w wersji 3.4.3' (3.3.2 nie wystepuje nigdzie); wersja natywna wynika z instalacji C:\\GDAL poza repo; obsluga HDF, NetCDF, ECW, MrSID, JPEG2000, ASC, VRT - lista formatow zalezy od natywnej biblioteki GDAL (poza repo), w kodzie brak jawnych odwolan do tych sterownikow; eksport do 'wielu' formatow rastrowych - w kodzie tylko GTiff; 'ponad 200 formatow' - brak w kodzie. Sprzecznosc wersji: opis 3.3.2 vs komentarz 3.4.3 (manifest gdal.jar nie zawiera wersji, rzeczywista wersja widoczna dopiero w logu 'GDAL - &lt;VersionInfo&gt;' w runtime). Szukane: gdal (wszystkie *.gradle/*.properties/*.java), 3.3.2 (gradle/properties/md), nazwy sterownikow. Pliki: gp-imapserver-gdb/build.gradle; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/raster/GdalConfigurator.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/raster/FileRaster.java Dowód: GdalConfigurator.initGdal() wola gdal.AllRegister() i loguje gdal.VersionInfo(); FileRaster odczytuje rastry przez gdal.Open(path, GA_ReadOnly); zapis (FileRaster.write) tylko przez sterownik GTiff (TILED, LZW). application.properties: pl.gispartner.imapserver.native=C:\\GDAL.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="41.4" customHeight="1" s="15">
       <c r="A111" s="5" t="n">
@@ -11977,7 +12277,7 @@
       </c>
       <c r="O111" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P111" s="5" t="n"/>
@@ -12013,7 +12313,11 @@
       <c r="AT111" s="5" t="n"/>
       <c r="AU111" s="5" t="n"/>
       <c r="AV111" s="5" t="n"/>
-      <c r="AW111" s="5" t="n"/>
+      <c r="AW111" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'automatyczne generowanie zagregowanych kafli' - nie znaleziono generowania; agregat to recznie wskazywana tabela (addToAggregate), uzywana przy rysowaniu warstw wektorowych (FeatureLayer), nie kafli rastrowych; powiazanie z danymi rastrowymi (kategoria 'Dane rastrowe') - kod agregatow dotyczy warstw obiektowych (wektorowych). Szukane: aggregat* w gp-imapserver-carto (AggregateData, AggregateInfos, FeatureLayer, RasterLayer: tylko sygnatury draw), brak aggregat w TileCache/RasterGenerator. Nie potwierdzono zaleznosci od skali (AggregateInfos nie zawiera slowa 'scale'). Mechanizm istnieje, ale opis go przypisuje do kafli. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/aggregate/Aggregate.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/AggregateData.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/FeatureLayer.java Dowód: Istnieje mechanizm agregatow: klasa Aggregate (tabela zrodlowa -&gt; docelowa, pole id), TableController 'addToAggregate' (rejestracja tabeli w agregacie), AggregateData i FeatureLayer.draw uzywaja AggregateFeatureCursor przy rysowaniu warstw wektorowych.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="55.2" customHeight="1" s="15">
       <c r="A112" s="5" t="n">
@@ -12102,7 +12406,11 @@
       <c r="AT112" s="5" t="n"/>
       <c r="AU112" s="5" t="n"/>
       <c r="AV112" s="5" t="n"/>
-      <c r="AW112" s="5" t="n"/>
+      <c r="AW112" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Endpoint to /maps/{map}/tile/{tile} (nie /maps/&lt;map&gt;/tile/&lt;tile&gt;/ z dodatkowym poziomem), operacje stats i delete (POST). 'GP na kafelkach': aktywnie zarejestrowane tylko GenerateTiles (capap, isok); klasy DeleteTiles, DeleteMapTiles, ExportTiles, ImportTiles, ScopesTask istnieja, ale nie sa w zadnym .jgp. Monitorowanie = stats; 'odbudowa' = createTile. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/TileStorageController.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/tiles/GenerateTiles.java Dowód: MapsController (root maps): "{map}/tile/{tile}" (HTML/JSON), "{map}/tile/{tile}/stats" (map.assertCanTile; tile.getCache().getStats()), "{map}/tile/{tile}/delete" (POST, deleteTile), "{map}/createTile". TileStorageController: levels/{map}/{tile}/{version}/{level}[/stats|/delete]. GP: GenerateTiles zarejestrowane w config/capap i isok.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="41.4" customHeight="1" s="15">
       <c r="A113" s="5" t="n">
@@ -12155,7 +12463,7 @@
       </c>
       <c r="O113" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P113" s="5" t="n"/>
@@ -12191,7 +12499,11 @@
       <c r="AT113" s="5" t="n"/>
       <c r="AU113" s="5" t="n"/>
       <c r="AV113" s="5" t="n"/>
-      <c r="AW113" s="5" t="n"/>
+      <c r="AW113" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: typ geography (brak w gdb/src/main, grep 'geography' = 0 trafien); replikacja (z opisu biznesowego) - brak kodu. PostGIS/GIST potwierdzone w aktywnym kodzie. Nie sprawdzalem wersji PostGIS (kod jej nie wykrywa). Indeks GIST tylko przy tworzeniu indeksu przez IMS na pojedynczym polu geometrii. 'Pelna obsluga zaawansowanej geometrii, analiz' to marketing - nie weryfikowalne. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/postgre/PgFactory.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/postgre/PgDatabase.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/postgre/PgSyntax.java Dowód: PgDatabase.createIndexSql dodaje ' using gist' dla indeksu na jednym polu GeometryField; PgSyntax mapuje funkcje przestrzenne na ST_Intersects/ST_Contains itd. i operator &amp;&amp; (PostGIS), typ 'geometry'/'st_geometry' (PgDatabase.GEOMETRY, ST_GEOMETRY). Konfiguracje type="postgre" w gp-imapserver-app/config/default/*.gdb.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="41.4" customHeight="1" s="15">
       <c r="A114" s="5" t="n">
@@ -12280,7 +12592,11 @@
       <c r="AT114" s="5" t="n"/>
       <c r="AU114" s="5" t="n"/>
       <c r="AV114" s="5" t="n"/>
-      <c r="AW114" s="5" t="n"/>
+      <c r="AW114" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. W OraSyntax czesc funkcji SDO (Crosses, Within, Relate) jest zakomentowana, wiec zestaw operacji dla SDO jest mniejszy niz dla ST_Geometry. Klucz pl.gispartner.imapserver.oracle.lobPrefetchSize w application.properties dotyczy natywnego ST_GEOMETRY. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/oracle/OraDatabase.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/oracle/OraSyntax.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/oracle/OraSdoField.java Dowód: OraDatabase definiuje stale ST_GEOMETRY i SDO_GEOMETRY i rozpoznaje 'SDE.ST_GEOMETRY' oraz 'MDSYS.SDO_GEOMETRY'; OraSyntax ma osobne zestawy funkcji przestrzennych: SDO_FILTER/SDO_ANYINTERACT/SDO_CONTAINS (SDO) oraz SDE.ST_Intersects/ST_Contains/ST_Crosses (ST). Osobne klasy pol OraSdoField i OraStField.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="41.4" customHeight="1" s="15">
       <c r="A115" s="5" t="n">
@@ -12333,7 +12649,7 @@
       </c>
       <c r="O115" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P115" s="5" t="n"/>
@@ -12369,7 +12685,11 @@
       <c r="AT115" s="5" t="n"/>
       <c r="AU115" s="5" t="n"/>
       <c r="AV115" s="5" t="n"/>
-      <c r="AW115" s="5" t="n"/>
+      <c r="AW115" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: polityki VPD (DBMS_RLS) jako funkcja IMS - brak; dane per gmina jako przyklad - brak w kodzie. Grep 'vpd|dbms_rls|add_policy|set_context|policy_function' w calym repo (java/kt/sql/properties/gdb/xml) = 0 trafien. Samo filtrowanie dzieje sie po stronie Oracle i poza repo (definicje pakietu ctx_dostep i polityk nie sa w repo). IMS tylko przekazuje tozsamosc uzytkownika. Mechanizm jest generyczny (nie tylko Oracle) i dziala tylko gdy ustawiono klucz datasource.user. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/JdbcDatabase.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/JdbcFactory.java; gp-imapserver-app/config/orlen/application.properties Dowód: IMS nie zawiera kodu polityk VPD. Jest ogolny mechanizm: klucz &lt;config&gt;.datasource.user (JdbcFactory.userExpression) to wyrazenie SQL wykonywane na kazdym polaczeniu (JdbcDatabase.getSourceConnection) z parametrami %{login},%{time},%{timeHash}; przyklad w config/orlen/application.properties: 'CALL ROB.ctx_dostep.set_user(...)' - ustawienie kontekstu uzytkownika w bazie.</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="41.4" customHeight="1" s="15">
       <c r="A116" s="5" t="n">
@@ -12422,7 +12742,7 @@
       </c>
       <c r="O116" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P116" s="5" t="n"/>
@@ -12458,7 +12778,11 @@
       <c r="AT116" s="5" t="n"/>
       <c r="AU116" s="5" t="n"/>
       <c r="AV116" s="5" t="n"/>
-      <c r="AW116" s="5" t="n"/>
+      <c r="AW116" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: integracja Active Directory dla logowania uzytkownikow GIS (opis biznesowy) - NTLM jest tylko do polaczenia z baza, nie do logowania uzytkownikow; typ geography - brak. NTLM jest wlasciwoscia polaczenia JDBC (konto serwisowe IMS do SQL Server), a nie logowaniem uzytkownikow systemu. Wartosci w application.properties (domain=Gispartner) to ustawienia domyslne/dev. Uwaga: MsFactory.urlOverride i tak wkleja user/password do URL. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/ms/MsFactory.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/ms/MsDatabase.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/ms/MsSyntax.java Dowód: MsFactory uzywa sterownika com.microsoft.sqlserver.jdbc.SQLServerDriver, MsSyntax uzywa 'geometry::STGeomFromWKB' i .STIntersects. application.properties: db.ms.datasource.integratedSecurity=true, authenticationScheme=NTLM, domain=Gispartner; config/default/guspdsdb02.gdb ma postfix ';integratedSecurity=true;authenticationScheme=NTLM'.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="41.4" customHeight="1" s="15">
       <c r="A117" s="5" t="n">
@@ -12511,7 +12835,7 @@
       </c>
       <c r="O117" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P117" s="5" t="n"/>
@@ -12547,7 +12871,11 @@
       <c r="AT117" s="5" t="n"/>
       <c r="AU117" s="5" t="n"/>
       <c r="AV117" s="5" t="n"/>
-      <c r="AW117" s="5" t="n"/>
+      <c r="AW117" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: tryb offline / dystrybucja w terenie (inspektorzy, tablety) jako funkcja - brak dedykowanego kodu poza eksportem LiteUtil (nie weryfikowalem szczegolow). Ladowanie rozszerzenia mod_spatialite jest ZAKOMENTOWANE (LiteFactory: connectionInitSql 'load_extension(mod_spatialite)'; LiteConnectionCustomizer linia 13). Nie ustalilem, czy wbudowany jar ma SpatiaLite - nie potwierdzone. Config przykladowy gpkg.gdb to GeoPackage, nie SpatiaLite. LiteDatabase.getDbmsGeometryType nie obsluguje wszystkich typow. Brak funkcji przestrzennych (addSpatialFunction) w pakiecie sqlite - filtry przestrzenne dla SQLite nieprzejrzane. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/sqlite/LiteFactory.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/sqlite/LiteDatabase.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/sqlite/SpatialiteGeometryField.java Dowód: LiteFactory (type 'sqlite', driver org.sqlite.JDBC) i LiteDatabase wykrywaja tabele 'geometry_columns' (SpatiaLite) oraz 'gpkg_geometry_columns' (GeoPackage); createDbmsField uzywa AddGeometryColumn dla SpatiaLite, SpatialiteGeometryField istnieje. Sterownik: lokalny jar gdb/lib/sqlite-jdbc-3.34.0.1-SNAPSHOT.jar (build.gradle: compile fileTree lib).</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="41.4" customHeight="1" s="15">
       <c r="A118" s="5" t="n">
@@ -12636,7 +12964,11 @@
       <c r="AT118" s="5" t="n"/>
       <c r="AU118" s="5" t="n"/>
       <c r="AV118" s="5" t="n"/>
-      <c r="AW118" s="5" t="n"/>
+      <c r="AW118" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: 'szybkie zapytania agregujace na duzych zbiorach' - wydajnosc/analityka nie jest cecha weryfikowalna w kodzie. DuckDB dziala jako zrodlo JDBC (w testach uzywany jako baza wbudowana). Nie sprawdzalem, czy IMS ma dedykowana optymalizacje agregacji dla Duck. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/duck/DuckFactory.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/duck/DuckDatabase.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/duck/DuckSqlBuilder.java Dowód: DuckFactory (@Component, getName 'duck', driver org.duckdb.DuckDBDriver, url jdbc:duckdb:&lt;database&gt;) tworzy DuckDatabase; zaleznosc org.duckdb:duckdb_jdbc 1.4.4.0 w gdb/build.gradle; przykladowa konfiguracja config/default/duck.gdb type="duck".</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="55.2" customHeight="1" s="15">
       <c r="A119" s="5" t="n">
@@ -12725,7 +13057,11 @@
       <c r="AT119" s="5" t="n"/>
       <c r="AU119" s="5" t="n"/>
       <c r="AV119" s="5" t="n"/>
-      <c r="AW119" s="5" t="n"/>
+      <c r="AW119" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: konkretne serwisy GUGIK, EMUiA, BDOT jako dostepne - nie sprawdzalem; w config sa m.in. BDL Lasy, CBDG, GIOS, wfsBroker GISPartner. WfsDatabase: supportsExpressions=false, supportsStatistics=false, operacje zapisu (createTable, dropTable) zwracaja null/puste - zrodlo tylko do odczytu. Brak wsparcia statystyk i wyrazen. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/wfs/WfsFactory.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/wfs/WfsDatabase.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/wfs/WfsSchema.java Dowód: WfsFactory (type 'wfs') tworzy WfsDatabase; WfsSchema pobiera GetCapabilities i DescribeFeatureType, WfsTable/WfsCursor pobiera GetFeature VERSION=2.0.0 (TYPENAMES, startIndex, resultType=hits). Konfiguracje type="wfs" z host=URL: wfs-egib.gdb, bdl_lasy.gdb, cbdg_mapa.gdb i inne.</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="41.4" customHeight="1" s="15">
       <c r="A120" s="5" t="n">
@@ -12814,7 +13150,11 @@
       <c r="AT120" s="5" t="n"/>
       <c r="AU120" s="5" t="n"/>
       <c r="AV120" s="5" t="n"/>
-      <c r="AW120" s="5" t="n"/>
+      <c r="AW120" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: przyklad rejestrow INSPIRE - w config jest Copernicus STAC (katalog STAC, nie INSPIRE). Typ zrodla nazywa sie 'apifeatures'. Jak w WFS: supportsExpressions=false, supportsStatistics=false, tylko odczyt. Nie weryfikowalem zgodnosci ze standardem OGC API Features poza sciezkami /collections i /items. Osobny modul ogc-api/gp-imapserver-ogc-api-features to serwer (publikacja), nie zrodlo - nie analizowany. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/apifeatures/APIFeaturesFactory.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/apifeatures/APIFeaturesDatabase.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/apifeatures/APIFeaturesSchema.java Dowód: APIFeaturesFactory (type 'apifeatures') -&gt; APIFeaturesDatabase: datasetUrl = host + '/collections' (APIFeaturesSchema czyta 'collections'), APIFeaturesTable uje '/collections/&lt;nazwa&gt;/items'. Przyklad: config/default/copernicus_stac.gdb.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="41.4" customHeight="1" s="15">
       <c r="A121" s="5" t="n">
@@ -12867,7 +13207,7 @@
       </c>
       <c r="O121" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P121" s="5" t="n"/>
@@ -12903,7 +13243,11 @@
       <c r="AT121" s="5" t="n"/>
       <c r="AU121" s="5" t="n"/>
       <c r="AV121" s="5" t="n"/>
-      <c r="AW121" s="5" t="n"/>
+      <c r="AW121" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: pelne dzialanie jako zrodlo danych wektorowych: FgdbDatabase.startTransaction, createSchema, getSystemSchemaOverride rzucaja NotImplementedException; supportsExpressions=false; supportsStatistics=false; brak przykladowej konfiguracji type="gdb" w config/*.gdb (nie znaleziono w default). Wymaga natywnej biblioteki FileGDB API (JNI), repozytorium Maven jfgdb po HTTP (S3); w build.gradle komentarz odsyla do README. Nie weryfikowalem czy dziala w obecnym buildzie. Odczyt tabel jest zaimplementowany (getAllChildDatasets, openTable), zapis ograniczony. Pliki: ext/gp-imapserver-fgdb/src/main/java/pl/gispartner/imapserver/gdb/fgdb/gdb/GdbFactory.java; ext/gp-imapserver-fgdb/src/main/java/pl/gispartner/imapserver/gdb/fgdb/fgdb/FgdbDatabase.java; ext/gp-imapserver-fgdb/build.gradle Dowód: GdbFactory (@Component, getName 'gdb') tworzy GdbDatabase; FgdbDatabase otwiera plik przez FGDBJNIWrapper.openGeodatabase(params.getDatabase()) (biblioteka org.jfgdb:jfgdb 0.1.4, natywne Esri FileGDB API); modul ext:gp-imapserver-fgdb jest w settings.gradle i w gp-imapserver-app/build.gradle (compile project).</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="41.4" customHeight="1" s="15">
       <c r="A122" s="5" t="n">
@@ -12992,7 +13336,11 @@
       <c r="AT122" s="5" t="n"/>
       <c r="AU122" s="5" t="n"/>
       <c r="AV122" s="5" t="n"/>
-      <c r="AW122" s="5" t="n"/>
+      <c r="AW122" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: przyklady geoportal.gov.pl (mapa zasadnicza, ortofoto) - nie weryfikowane w kodzie. Overload draw(LayerContext,...) rzuca CartoException 'WMS layer can only be drawn on Display'. Format zahardkodowany (png, WMS 1.3.0). Istnieje tez WmtsLayer. Do ustalenia: obsluga w runtime kafli/eksportu poza Display. Pliki: gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/WmsLayer.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/json/ims/LayerLoader.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/MapItemType.java Dowód: WmsLayer (MapItemType.wmsLayer) w draw(Display,...) wywoluje GetCapabilities i GetMap (wms 1.3.0, image/png, transparent=true, crs, bbox z obsluga kolejnosci osi) przez RestTemplate i rysuje obraz na Display; LayerLoader.loadWmsLayer czyta url/layers/styles z definicji mapy.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="41.4" customHeight="1" s="15">
       <c r="A123" s="5" t="n">
@@ -13045,7 +13393,7 @@
       </c>
       <c r="O123" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P123" s="5" t="n"/>
@@ -13081,7 +13429,11 @@
       <c r="AT123" s="5" t="n"/>
       <c r="AU123" s="5" t="n"/>
       <c r="AV123" s="5" t="n"/>
-      <c r="AW123" s="5" t="n"/>
+      <c r="AW123" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: nazwane role 'administrator systemu/bazy, edytor schematu/tabeli/pola' - w kodzie sa tylko klucze xxxRoles i rola admin (security.admin-role=admin), brak takich predefiniowanych rol; 'pelna granulacja' na poziomie pola - jest tylko fieldRoles (dostep do pola) i oznaczenie danych osobowych, brak osobnych uprawnien edycji pola. Dziedziczenie uprawnien factory-&gt;baza-&gt;schemat-&gt;tabela-&gt;pole potwierdzone. Domyslnie wiekszosc kluczy = admin. BaseField.isPublic/getRoles opieraja sie na fieldRoles (domyslnie public). Dla poziomu 'system' sprawdzilem tylko klucz root.manageRoles w properties. Pliki: gp-imapserver-common/src/main/java/pl/gispartner/imapserver/properties/Properties.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/Databases.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/config/SchemaCfg.java Dowód: Properties maja lancuch parent (Properties.property szuka w parent); SchemaCfg ustawia parent=database.getProperties(), TableCfg parent=schema, FieldCfg parent=tableProperties, BaseDatabase parent=factory properties. Klucze rol: root.manageRoles, databaseRoles, schemaRoles, tableRoles, fieldRoles (Databases.java, application.properties l.205-253).</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="41.4" customHeight="1" s="15">
       <c r="A124" s="5" t="n">
@@ -13134,7 +13486,7 @@
       </c>
       <c r="O124" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P124" s="5" t="n"/>
@@ -13170,7 +13522,11 @@
       <c r="AT124" s="5" t="n"/>
       <c r="AU124" s="5" t="n"/>
       <c r="AV124" s="5" t="n"/>
-      <c r="AW124" s="5" t="n"/>
+      <c r="AW124" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: endpoint /generateToken - brak w kodzie (grep 'generateToken' w repo = 0; endpoint to 'login'); mozliwosc skrocenia tokenu - nie znalazlem parametru czasu zycia w zadaniu; uniewaznienie tokenu po stronie serwera - logout czysci tylko cookie i sesje, nie znalazlem listy uniewaznionych tokenow. Domyslna wartosc 720 min potwierdzona. Nazwa endpointu w opisie jest nieprawdziwa dla tego kodu (generateToken to nazewnictwo ArcGIS). W konfiguracjach gplogin.xml jest tokensUrl wskazujacy na arcgis/tokens (zewnetrzny). Nie zbadalem pelnie klasy Authenticator. Pliki: gp-imapserver-rest/src/main/java/pl/gispartner/imapserver/rest/RootController.java; gp-imapserver-app/src/main/resources/application.properties; gp-imapserver-rest/src/main/java/pl/gispartner/imapserver/rest/security/SecurityController.java Dowód: application.properties: pl.gispartner.imapserver.security.token.expiration=720 (minuty); RootController (@Value) przekazuje je do factory.authenticate(...) w endpointach 'login' (POST/GET, odpowiedz JSON: token, bestBefore, expiration); logout kasuje cookie i niewaznia sesje HTTP (SecurityController.logout).</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="41.4" customHeight="1" s="15">
       <c r="A125" s="5" t="n">
@@ -13223,7 +13579,7 @@
       </c>
       <c r="O125" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P125" s="5" t="n"/>
@@ -13259,7 +13615,11 @@
       <c r="AT125" s="5" t="n"/>
       <c r="AU125" s="5" t="n"/>
       <c r="AV125" s="5" t="n"/>
-      <c r="AW125" s="5" t="n"/>
+      <c r="AW125" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: zakresy CIDR - brak: sprawdzenie to String.contains(remoteAddr), czyli dopasowanie podciagu; ograniczenie na poziomie pojedynczej uslugi - brak, filtr jest globalny dla serwera. Blokada realizowana przez celowe dzielenie przez zero (345/zero) w IpFilter, czyli zwraca blad 500 zamiast 403. Dopasowanie przez contains moze dawac falszywe trafienia (np. 10.0.0.1 pasuje do 110.0.0.15). Za reverse proxy getRemoteAddr da adres proxy. Ryzyko bezpieczenstwa. Pliki: gp-imapserver-rest/src/main/java/pl/gispartner/imapserver/rest/IpFilter.java; gp-imapserver-rest/src/main/java/pl/gispartner/imapserver/rest/Root.java; gp-imapserver-app/src/main/resources/application.properties Dowód: Klucz pl.gispartner.imapserver.security.ipwhitelist (domyslnie '*') wstrzykiwany w Root.java:139 do IpFilter rejestrowanego jako FilterRegistrationBean; IpFilter.beforeRequest blokuje zadanie, gdy lista nie zawiera '*' ani request.getRemoteAddr().</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="55.2" customHeight="1" s="15">
       <c r="A126" s="5" t="n">
@@ -13312,7 +13672,7 @@
       </c>
       <c r="O126" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P126" s="5" t="n"/>
@@ -13348,7 +13708,11 @@
       <c r="AT126" s="5" t="n"/>
       <c r="AU126" s="5" t="n"/>
       <c r="AV126" s="5" t="n"/>
-      <c r="AW126" s="5" t="n"/>
+      <c r="AW126" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: niepotwierdzone. Niepotwierdzone w kodzie: uwierzytelnianie Windows (SSO) przez NTLM uzytkownikow IMS; Active Directory jako takie (jest tylko ogolny LDAP w gplogin.xml, bez wzmianki o AD). Frazy: ntlm, kerberos, spnego, negotiate, ldap, active directory w *.java/*.kt/*.gradle/*.properties w calym repo i modulu security. Moze byc realizowane poza repo (reverse proxy z uwierzytelnianiem Windows przekazujacym naglowek uzytkownika - klucze security.attributes.header / org.header istnieja w properties, ale nie potwierdzilem takiego uzycia). LDAP jest mozliwy przez gplogin.xml (ldap://192.168.124.108:389) - to nie NTLM. Pliki: gp-imapserver-security/src/main/resources/gplogin.xml; gp-imapserver-app/src/main/resources/application.properties; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/proto/Smtp.java Dowód: Brak logowania uzytkownikow przez NTLM/SSO. Znalazlem tylko: authenticationScheme=NTLM dla polaczenia z SQL Server (db.ms.datasource.*), 'mail.smtp.auth.ntlm.disable=true' w Smtp.java oraz uwierzytelnianie ldap w gplogin.xml (Authentication type="ldap").</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="55.2" customHeight="1" s="15">
       <c r="A127" s="5" t="n">
@@ -13401,7 +13765,7 @@
       </c>
       <c r="O127" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P127" s="5" t="n"/>
@@ -13437,7 +13801,11 @@
       <c r="AT127" s="5" t="n"/>
       <c r="AU127" s="5" t="n"/>
       <c r="AV127" s="5" t="n"/>
-      <c r="AW127" s="5" t="n"/>
+      <c r="AW127" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: tokeny JWT w modelu OAuth 2.0 - brak: nie ma flow OAuth, tylko walidacja gotowego JWT z cookie; szyfrowanie TLS/HTTPS - brak konfiguracji server.ssl w application.properties (server.port=8080); TLS zapewne na proxy/Tomcat poza repo; zgodnosc z KRI - nie weryfikowalne. Domyslnie usejwt=false. Uwaga: @ConditionalOnProperty bez havingValue - wartosc 'false' jest traktowana jako wylaczona (zachowanie Springa), UserFactoryImpl ma havingValue=false. JwtConfig ma domyslnie issuers test.PZ, test.WK, test.CAS i validateIssuer=true. Tokeny wystawia zewnetrzny system, IMS tylko weryfikuje. Grep: server.ssl, oauth, openid, keystore = 0 w application.properties; w build.gradle rest zakomentowany spring-boot-starter-security. Pliki: gp-imapserver-security/src/main/kotlin/pl/gispartner/imapserver/security/jwtUserFactory.kt; gp-imapserver-security/build.gradle; gp-imapserver-app/src/main/resources/application.properties Dowód: jwtUserFactory.kt: JwtUserFactoryImpl waliduje JWS (jjwt 0.9.1, klucz publiczny RSA z pliku, wymagane exp, iat, issuer z listy) z cookie i buduje GpJwtUser z rolami z claima 'roles'; aktywne tylko przy pl.gispartner.imapserver.security.usejwt (@ConditionalOnProperty).</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="55.2" customHeight="1" s="15">
       <c r="A128" s="5" t="n">
@@ -13490,7 +13858,7 @@
       </c>
       <c r="O128" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P128" s="5" t="n"/>
@@ -13526,7 +13894,11 @@
       <c r="AT128" s="5" t="n"/>
       <c r="AU128" s="5" t="n"/>
       <c r="AV128" s="5" t="n"/>
-      <c r="AW128" s="5" t="n"/>
+      <c r="AW128" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: integracja 'z Oracle VPD' jako nazwana funkcja - brak; eliminacja obejscia filtrow przez bezposredni SQL - wlasciwosc bazy, nie IMS. Duplikat semantyczny IMS-0094. Potwierdzono tylko, ze IMS przekazuje do bazy tozsamosc uzytkownika (login, czas, hash). To, czy po stronie Oracle dziala VPD, nie wynika z repo. Przyklad jest w konfiguracji klienta (orlen, kas), nie w domyslnej. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/JdbcDatabase.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/JdbcFactory.java; gp-imapserver-app/config/orlen/application.properties Dowód: Jak IMS-0094: brak kodu VPD, jest tylko mechanizm datasource.user (wykonanie wyrazenia SQL z atrybutami uzytkownika na kazdym polaczeniu, JdbcDatabase.getSourceConnection) i przyklad 'CALL ROB.ctx_dostep.set_user(%{login},%{time},%{timeHash})' w config/orlen/application.properties (db.orlen i db.ora).</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="41.4" customHeight="1" s="15">
       <c r="A129" s="5" t="n">
@@ -13579,7 +13951,7 @@
       </c>
       <c r="O129" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P129" s="5" t="n"/>
@@ -13615,7 +13987,11 @@
       <c r="AT129" s="5" t="n"/>
       <c r="AU129" s="5" t="n"/>
       <c r="AV129" s="5" t="n"/>
-      <c r="AW129" s="5" t="n"/>
+      <c r="AW129" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: logowanie do NoSQL - brak: loggery to CsvPersonalLogger (domyslnie logType=csv) i LokiPersonalLogger (logType=loki, strumien logow Loki), a nie baza NoSQL; sledzenie kto co zmienil w danych (opis biznesowy) - PersonalLogger rejestruje tylko ODCZYT danych osobowych, nie zmiany; rejestr jako zgodnosc z RODO - interpretacja, kod tylko loguje dostep. Mechanizm jest aktywny tylko gdy Database.getPersonalLogger() != null (ustawiany z DatabaseContainer.personalLogger). Nie sprawdzilem gdzie dokladnie tworzony jest CsvPersonalLogger (domyslny logType=csv). Istnieje tez LoggingFilter ('autr.enabled') - nie analizowany pod katem audytu zmian. Cassandra w repo jest uzywana do skladowania kafli/storage, nie do audytu. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/jdbc/sql/SqlBuilder.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/personal/PersonalCursor.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/ImplPersonalLogger.java Dowód: Pola z PersonalDataType != common sa blokowane (JdbcPersonalField), chyba ze podano reason i user ma queryPersonalRoles (SqlBuilder.addField); wtedy PersonalCursor loguje kazdy wiersz przez PersonalLogger. ImplPersonalLogger.getJsonLog zapisuje: data_dostepu, ip, kontekst(url), nazwa_tabeli, nazwa_uzytkownika, oid, powod, typ='dane_osobowe', json wiersza. Endpointy personalDataStart/Stop w RootController ustawiaja cookie z powodem.</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="41.4" customHeight="1" s="15">
       <c r="A130" s="5" t="n">
@@ -13704,7 +14080,11 @@
       <c r="AT130" s="5" t="n"/>
       <c r="AU130" s="5" t="n"/>
       <c r="AV130" s="5" t="n"/>
-      <c r="AW130" s="5" t="n"/>
+      <c r="AW130" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: 'per uzytkownik lub rola' - sprawdzane sa role i wlasciciel (owner), nie osobne wpisy per uzytkownik. Dodatkowo istnieja createAppRoles, studioMapAppRoles, wizardAppRoles, dashboardAppRoles. Domyslnie appRoles=admin, wiec aplikacje domyslnie niewidoczne dla innych rol. W gplogin.xml jest tez sekcja AppRoles (LDAP path) - nie analizowana. Pliki: gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/Application.java; gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/container/AppFolder.java; gp-imapserver-app/src/main/resources/application.properties Dowód: Application.java: stale APP_ROLES='appRoles', MODIFY_APP_ROLES='modifyAppRoles', REMOVE_APP_ROLES='removeAppRoles' (APP_PRIVILEGES); odczyt rol przez properties.property(Roles.class, APP_ROLES), a modify/remove sprawdzane przez isAdminOrOwnerOrHasAnyRole (l.171, 208). application.properties l.360-366 ustawia pl.gispartner.imapserver.properties.app.* (domyslnie admin).</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="41.4" customHeight="1" s="15">
       <c r="A131" s="5" t="n">
@@ -13757,7 +14137,7 @@
       </c>
       <c r="O131" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P131" s="5" t="n"/>
@@ -13793,7 +14173,11 @@
       <c r="AT131" s="5" t="n"/>
       <c r="AU131" s="5" t="n"/>
       <c r="AV131" s="5" t="n"/>
-      <c r="AW131" s="5" t="n"/>
+      <c r="AW131" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: nazwa 'attachmentRoles' - w kodzie nie ma takiego klucza, sa cztery osobne: query/add/update/deleteAttachmentRoles; ukrywanie pol (PESEL itd.) - SqlBuilder.addField wywoluje field.assertCanAccess(user), czyli dostep do pola ZABRONIONY wyjatkiem, a nie ukrycie; pola danych osobowych maskowane osobno przez JdbcPersonalField. Wszystkie klucze z listy opisu (poza attachmentRoles) potwierdzone. Domyslnie wiekszosc = admin, fieldRoles=public. Potwierdzone w gdb/Field.java:180: assertCanAccess rzuca GdbException 'No privileges to access field'. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/Databases.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseTable.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/base/BaseField.java Dowód: Databases.java definiuje stale tableRoles, queryRoles, addRoles, updateRoles, deleteRoles, modifyTableRoles, dropTableRoles, fieldRoles, queryAttachmentRoles/addAttachmentRoles/updateAttachmentRoles/deleteAttachmentRoles (TABLE_PRIVILEGES); wartosci domyslne w application.properties l.207-253; Table.java i Dataset.java sprawdzaja MODIFY_TABLE_ROLES/DROP_TABLE_ROLES; BaseTable.canQueryAttachments uzywa QUERY_ATT_ROLES.</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="41.4" customHeight="1" s="15">
       <c r="A132" s="5" t="n">
@@ -13846,7 +14230,7 @@
       </c>
       <c r="O132" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P132" s="5" t="n"/>
@@ -13882,7 +14266,11 @@
       <c r="AT132" s="5" t="n"/>
       <c r="AU132" s="5" t="n"/>
       <c r="AV132" s="5" t="n"/>
-      <c r="AW132" s="5" t="n"/>
+      <c r="AW132" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Panel 'zarzadza calym serwerem' - zakres funkcji panelu wynika z frontu (webjar), niewidocznego w repo; 'bez dostepu do powloki' - brak mozliwosci weryfikacji, czy panel pokrywa wszystkie operacje administracyjne. Front Managera to webjar pl.gispartner.webjars:ims-manager (imsmanager_version=1.20.39 w gradle.properties) - jego kodu nie ma w repo, wiec warstwa UI nie jest weryfikowalna; potwierdzona jest tylko strona serwerowa. Strona serwerowa to tylko powloka (JSP + handler zasobow) i konfiguracja supportedAppTypes (domyslnie '*'). Operacje administracyjne realizuja REST-y innych modulow (ocenione w wierszach 0112-0119). Pliki: gp-imapserver-manager/src/main/java/pl/gispartner/imapserver/manager/ManagerController.java; gp-imapserver-manager/src/main/resources/META-INF/resources/WEB-INF/jsp/manager/manager.jsp; gp-imapserver-manager/build.gradle Dowód: ManagerController (@RequestMapping 'manager') serwuje JSP manager.jsp, mapuje /manager/** na zasoby webjara ims-manager, rejestruje rozszerzenie 'Manager' widoczne dla roli manageRoles (w application.properties pl.gispartner.imapserver.properties.root.manageRoles=admin). Modul jest w settings.gradle i w zaleznosciach gp-imapserver-app.</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="41.4" customHeight="1" s="15">
       <c r="A133" s="5" t="n">
@@ -13935,7 +14323,7 @@
       </c>
       <c r="O133" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P133" s="5" t="n"/>
@@ -13971,7 +14359,11 @@
       <c r="AT133" s="5" t="n"/>
       <c r="AU133" s="5" t="n"/>
       <c r="AV133" s="5" t="n"/>
-      <c r="AW133" s="5" t="n"/>
+      <c r="AW133" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Edycja/usuwanie/start/stop 'uslug' innych niz mapy: dla uslug GP znaleziono tylko gp/create (Services.java) i brak endpointow remove/modify/state w rest-gp; Funkcjonalnosc edytora map jako UI Managera (czy designer.jsp jest tym edytorem w Managerze) - front poza repo. Szukane: '/remove','/state','/modify' w gp-imapserver-rest-gp - brak trafien. Stan enabled/disabled to jedyna forma 'uruchamiania/zatrzymywania' potwierdzona w kodzie. Front Managera to webjar pl.gispartner.webjars:ims-manager (imsmanager_version=1.20.39 w gradle.properties) - jego kodu nie ma w repo, wiec warstwa UI nie jest weryfikowalna; potwierdzona jest tylko strona serwerowa. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/MapState.java; gp-imapserver-rest-carto/src/main/resources/META-INF/resources/WEB-INF/jsp/carto/designer.jsp Dowód: MapsController: POST maps/create, {map}/modify, {map}/remove, {map}/state (map.setState(MapState.fromString(state)), MapState = enabled|disabled), GET maps/designer (folder.assertCanDesigner -&gt; jsp carto/designer.jsp). Uruchamianie/zatrzymywanie to przelaczanie stanu enabled/disabled mapy, nie procesu.</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="41.4" customHeight="1" s="15">
       <c r="A134" s="5" t="n">
@@ -14024,7 +14416,7 @@
       </c>
       <c r="O134" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P134" s="5" t="n"/>
@@ -14060,7 +14452,11 @@
       <c r="AT134" s="5" t="n"/>
       <c r="AU134" s="5" t="n"/>
       <c r="AV134" s="5" t="n"/>
-      <c r="AW134" s="5" t="n"/>
+      <c r="AW134" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Osobna operacja 'testowanie' polaczenia - test dzieje sie tylko przy zapisie (create/modify), brak osobnego endpointu; Dodawanie polaczen SQLite/DuckDB/WFS/OGC API przez ten endpoint: createModifyDatabase wymaga niepustych host, port, username, password - dla plikowych/HTTP zrodel nie jest oczywiste, czy to dziala (niezweryfikowane). Typ 'OGC API' = fabryka 'apifeatures' (nazwa potwierdzona, dzialanie nie testowane). Dodatkowe fabryki ponad opis: mysql, maria, firebird, ims, fgdb (ext). Szukane: nazwy fabryk, 'testConnection'. Front Managera to webjar pl.gispartner.webjars:ims-manager (imsmanager_version=1.20.39 w gradle.properties) - jego kodu nie ma w repo, wiec warstwa UI nie jest weryfikowalna; potwierdzona jest tylko strona serwerowa. Pliki: gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/DatabaseController.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/container/DatabaseFactories.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/postgre/PgFactory.java Dowód: DatabaseController: databases/createDatabase, {database}/modify, {database}/remove; createModifyDatabase wola factory.createDatabase(...) i result.testConnection() (blad 'Connection failed'). Fabryki @Component o nazwach: postgre, oracle, mssql, sqlite, duck, wfs, apifeatures (APIFeaturesFactory) - rejestrowane w DatabaseFactories przez wstrzykniecie Factory[].</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="27.6" customHeight="1" s="15">
       <c r="A135" s="5" t="n">
@@ -14113,7 +14509,7 @@
       </c>
       <c r="O135" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P135" s="5" t="n"/>
@@ -14149,7 +14545,11 @@
       <c r="AT135" s="5" t="n"/>
       <c r="AU135" s="5" t="n"/>
       <c r="AV135" s="5" t="n"/>
-      <c r="AW135" s="5" t="n"/>
+      <c r="AW135" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Tworzenie kont uzytkownikow - UserFactory nie ma operacji createUser/addUser (uzytkownicy pochodza z requestu/tokenu/GP Login); Grupy - brak klasy/operacji 'group' w gp-imapserver-security. Potwierdzone tylko zarzadzanie ROLAMI. Szukane: createUser, addUser, deleteUser, createGroup, Group w module security - brak. Opis 'konta, role i grupy' jest wiec zawyzony wzgledem kodu (mozliwe, ze konta zarzadzane zewnetrznie, np. JWT/SSO - niezweryfikowane). UserFactoryImpl ma @ConditionalOnProperty(usejwt=false). SecurityController zawiera tez publiczny endpoint /security/test drukujacy role na stdout. Front Managera to webjar pl.gispartner.webjars:ims-manager (imsmanager_version=1.20.39 w gradle.properties) - jego kodu nie ma w repo, wiec warstwa UI nie jest weryfikowalna; potwierdzona jest tylko strona serwerowa. Pliki: gp-imapserver-rest/src/main/java/pl/gispartner/imapserver/rest/security/SecurityController.java; gp-imapserver-security/src/main/java/pl/gispartner/imapserver/security/UserFactory.java; gp-imapserver-security/src/main/java/pl/gispartner/imapserver/security/UserFactoryImpl.java Dowód: SecurityController: security/addRole (factory.addRole), security/roles/{name}/remove (factory.removeRole), lista rol; UserFactoryImpl przechowuje role w pliku (saveRole). Uprawnienia: endpointy privileges na mapach ({map}/privileges, {map}/{layer}/privileges), bazach ({database}/privileges), folderach, aplikacjach (apps {app}/privileges) i globalnie.</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="41.4" customHeight="1" s="15">
       <c r="A136" s="5" t="n">
@@ -14202,7 +14602,7 @@
       </c>
       <c r="O136" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P136" s="5" t="n"/>
@@ -14238,7 +14638,11 @@
       <c r="AT136" s="5" t="n"/>
       <c r="AU136" s="5" t="n"/>
       <c r="AV136" s="5" t="n"/>
-      <c r="AW136" s="5" t="n"/>
+      <c r="AW136" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Logi zadan (request log) - nie znaleziono endpointu ani mechanizmu w repo; Statystyki uzycia i czas odpowiedzi jako funkcja serwera/Managera - znaleziono tylko metryki Micrometer dla polaczen JDBC i custom_app_gauge_value; ImsMetricAspect w ext/monitoring ma @Aspect zakomentowane (//@Aspect); Wizualizacja w Managerze. Funkcja monitoringu jest opcjonalna i domyslnie wylaczona. Endpoint /monitoring/ims/metrics zwraca wylacznie 'custom_app_gauge_value' (pole ustawiane recznie przez status?customAppGaugeValue=). Szukane: logs, requestlog, AccessLog, statistic, MeterRegistry. Front Managera to webjar pl.gispartner.webjars:ims-manager (imsmanager_version=1.20.39 w gradle.properties) - jego kodu nie ma w repo, wiec warstwa UI nie jest weryfikowalna; potwierdzona jest tylko strona serwerowa. Pliki: ext/gp-imapserver-monitoring/src/main/java/pl/gispartner/imapserver/monitoring/MonitoringController.java; gp-imapserver-app/src/main/resources/application-monitoring.properties; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbMeterRegistry.java Dowód: MonitoringController (monitoring/ims/: status, metrics) jest @ConditionalOnProperty pl.gispartner.imapserver.monitoring-ims=true (domyslnie false w application-monitoring.properties); profil 'monitoring' wlacza Spring Actuator/Prometheus (management.endpoints.web.exposure.include=prometheus,metrics,health,...). JdbcDatabase raportuje do MeterRegistry (connectionOpened/Closed/Error). Stan mapy: {map}/state.</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="179.4" customHeight="1" s="15">
       <c r="A137" s="5" t="n">
@@ -14291,7 +14695,7 @@
       </c>
       <c r="O137" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P137" s="5" t="n"/>
@@ -14327,7 +14731,11 @@
       <c r="AT137" s="5" t="n"/>
       <c r="AU137" s="5" t="n"/>
       <c r="AV137" s="5" t="n"/>
-      <c r="AW137" s="5" t="n"/>
+      <c r="AW137" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'Zmiana magazynu' istniejacego cache - brak endpointu; magazyn ustawiany tylko przy createTile; 'Zmiana formatu' - format = generator ustawiany przy tworzeniu tile info; brak operacji zmiany istniejacego. Generowanie/czyszczenie/statystyki potwierdzone (REST + GP). Zadania GenerateTiles/DeleteTiles sa w config capap/isok tiles.jgp, nie w config/default (nie sprawdzono, czy domyslnie wlaczone). Implementacje magazynow kafli: Compact, Lite(SQLite), S3Compact, Cassandra, Http, File wrapper. Front Managera to webjar pl.gispartner.webjars:ims-manager (imsmanager_version=1.20.39 w gradle.properties) - jego kodu nie ma w repo, wiec warstwa UI nie jest weryfikowalna; potwierdzona jest tylko strona serwerowa. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/TileStorageController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/TileSchemaController.java Dowód: MapsController: {map}/createTile (storage, generator, schema, toLevel), {map}/tile/{tile}/delete, {map}/tile/{tile}/stats; TileStorageController: storages/{storage}/levels, .../stats, .../delete; GP: GenerateTiles, DeleteTiles, DeleteMapTiles, ExportTiles, ImportTiles. Generatory (MapLoader.generator): vector, png32, jpg, mix, lerc.</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="55.2" customHeight="1" s="15">
       <c r="A138" s="5" t="n">
@@ -14416,7 +14824,11 @@
       <c r="AT138" s="5" t="n"/>
       <c r="AU138" s="5" t="n"/>
       <c r="AV138" s="5" t="n"/>
-      <c r="AW138" s="5" t="n"/>
+      <c r="AW138" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. preview.jsp laduje biblioteke ArcGIS JS API 3.20 z CDN (https://js.arcgis.com/3.20/) - podglad wymaga dostepu do internetu; to biblioteka JS, nie aplikacja GIS. Wbudowany podglad jest po stronie serwera, ale to czy Manager osadza go w UI - front poza repo. Front Managera to webjar pl.gispartner.webjars:ims-manager (imsmanager_version=1.20.39 w gradle.properties) - jego kodu nie ma w repo, wiec warstwa UI nie jest weryfikowalna; potwierdzona jest tylko strona serwerowa. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/MapServer.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java; gp-imapserver-rest-carto/src/main/resources/META-INF/resources/WEB-INF/jsp/carto/ags/preview.jsp Dowód: MapServer.mapServer(): f=jsapi -&gt; jsp 'preview', f=jsapid -&gt; 'previewD', f=gpapi -&gt; 'previewGp'; MapsController {map} (HTML) renderuje 'preview'. JSP to wbudowane strony podgladu mapy (Map Preview).</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="55.2" customHeight="1" s="15">
       <c r="A139" s="5" t="n">
@@ -14505,7 +14917,11 @@
       <c r="AT139" s="5" t="n"/>
       <c r="AU139" s="5" t="n"/>
       <c r="AV139" s="5" t="n"/>
-      <c r="AW139" s="5" t="n"/>
+      <c r="AW139" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wszystkie elementy opisu (przegladanie, uruchamianie, harmonogramowanie, monitorowanie) maja pokrycie w REST gp. Aktywnosc: moduly gp-imapserver-rest-gp w settings.gradle i w zaleznosciach app; konkretne zadania zaleza od plikow .jgp. Front Managera to webjar pl.gispartner.webjars:ims-manager (imsmanager_version=1.20.39 w gradle.properties) - jego kodu nie ma w repo, wiec warstwa UI nie jest weryfikowalna; potwierdzona jest tylko strona serwerowa. Pliki: gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/Common.java; gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/Services.java Dowód: Common: {task}/submitJob, {task}/execute, {task}/schedule, {task}/jobs/{job}/cancel|accept|finish|setProgress|changePriority|changeRetryCounter; Services: gp/queue, gp/queue/query (przegladanie kolejki), gp/scheduler oraz scheduler/{id}/update|delete|activate|deactivate (harmonogram).</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="41.4" customHeight="1" s="15">
       <c r="A140" s="5" t="n">
@@ -14558,7 +14974,7 @@
       </c>
       <c r="O140" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P140" s="5" t="n"/>
@@ -14594,7 +15010,11 @@
       <c r="AT140" s="5" t="n"/>
       <c r="AU140" s="5" t="n"/>
       <c r="AV140" s="5" t="n"/>
-      <c r="AW140" s="5" t="n"/>
+      <c r="AW140" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'Kreator (wizard)' jako interfejs tworzenia aplikacji - w kodzie 'wizard' to typ aplikacji (ApplicationType.wizard), sam kreator UI jest poza repo. CRUD i uprawnienia aplikacji potwierdzone po stronie serwera. Front Managera to webjar pl.gispartner.webjars:ims-manager (imsmanager_version=1.20.39 w gradle.properties) - jego kodu nie ma w repo, wiec warstwa UI nie jest weryfikowalna; potwierdzona jest tylko strona serwerowa. Pliki: gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/AppConroller.java; gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/ApplicationType.java; gp-imapserver-rest-app/src/main/java/pl/gispartner/imapserver/rest/app/container/AppContainer.java Dowód: AppConroller (ROOT 'apps'): apps/create, {app}/modify, {app}/remove, {app}/privileges, privileges, {app}/def, {app}/run, {app}/thumbnail. ApplicationType = wizard, dashboard, studioMap; wlaczone typy z pl.gispartner.imapserver.manager.config.supportedAppTypes (domyslnie '*').</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="41.4" customHeight="1" s="15">
       <c r="A141" s="5" t="n">
@@ -14687,7 +15107,11 @@
       <c r="AT141" s="5" t="n"/>
       <c r="AU141" s="5" t="n"/>
       <c r="AV141" s="5" t="n"/>
-      <c r="AW141" s="5" t="n"/>
+      <c r="AW141" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. To weryfikacja topologii grafu (budowa grafu + wykrywanie bledow), bez analiz kosztowych. Nazwy w kodzie angielskie ('Find ...'). Pliki: gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/extensions/NetworkGp.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/network/Build.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/network/Graph.java Dowód: NetworkGp rejestruje zadania GP: Build (network.build), SetDirection, FindUnknownEdges, FindOverlappingLines/Points, FindIntersectingEdgesWithoutNode, FindIsolated*/FindOpen*/FindNotConnected*/FindLoopEdges, FindEdgesByTypeAndByTypeNodes; NetworkController ma addNodes/addEdges/applySchema.</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="41.4" customHeight="1" s="15">
       <c r="A142" s="5" t="n">
@@ -14744,7 +15168,7 @@
       </c>
       <c r="O142" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P142" s="5" t="n"/>
@@ -14780,7 +15204,11 @@
       <c r="AT142" s="5" t="n"/>
       <c r="AU142" s="5" t="n"/>
       <c r="AV142" s="5" t="n"/>
-      <c r="AW142" s="5" t="n"/>
+      <c r="AW142" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: niepotwierdzone. Niepotwierdzone w kodzie: Obszar dostepny w zadanym czasie lub odleglosci od punktu startowego; Izochrony/izochrony (poligon zasiegu). Szukane (cale repo, java/py/jgp/properties/xml/json/jsp): isochron, izochron, izochor, serviceArea, 'service area', dijkstra, shortest, routing, cost, impedance - brak sensownych trafien; Graph.java nie zawiera wag/kosztow (tylko cutEdge z dlugoscia). 'Nie znaleziono' w repo; funkcja moze byc poza repo (np. zewnetrzny silnik), ale w tej bazie kodu nie ma. Nazwa 'izochorony' w macierzy to literowka. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/network/TraceEdges.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/network/FindConnected.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/network/Graph.java Dowód: Brak kodu izochron/obszaru obslugi. Zadania sieciowe (findConnected, traceEdges, traceNodes) to topologiczne sledzenie po atrybutach i miarze krawedzi (parametry: edge, measure, point, type, attributs, endNodes), bez limitu czasu/odleglosci i bez wag.</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="41.4" customHeight="1" s="15">
       <c r="A143" s="5" t="n">
@@ -14837,7 +15265,7 @@
       </c>
       <c r="O143" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P143" s="5" t="n"/>
@@ -14873,7 +15301,11 @@
       <c r="AT143" s="5" t="n"/>
       <c r="AU143" s="5" t="n"/>
       <c r="AV143" s="5" t="n"/>
-      <c r="AW143" s="5" t="n"/>
+      <c r="AW143" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: niepotwierdzone. Niepotwierdzone w kodzie: Optymalna trasa; Uwzglednienie kosztu (czas, odleglosc, impedancja krawedzi). Szukane: routing, route, shortest, dijkstra, cost, impedance, weight (Graph.java, tasks/network, tasks/route). Walk jest tylko w profilu demo (config/demo). Nie wykluczone, ze realizowane poza repo. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/route/Walk.java; gp-imapserver-app/config/demo/route.jgp; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/network/TraceEdges.java Dowód: Nie znaleziono routingu z kosztem. Jedyne zadanie 'route' to Walk (config/demo/route.jgp): wejscia table, shape, oid, route (Geometry), step, interval - przesuwa obiekt wzdluz podanej trasy, nie wyznacza trasy. TraceEdges sledzi krawedzie bez wag.</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="41.4" customHeight="1" s="15">
       <c r="A144" s="5" t="n">
@@ -14966,7 +15398,11 @@
       <c r="AT144" s="5" t="n"/>
       <c r="AU144" s="5" t="n"/>
       <c r="AV144" s="5" t="n"/>
-      <c r="AW144" s="5" t="n"/>
+      <c r="AW144" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: Ogolne wykrywanie 'rozlacznych komponentow' - kod wykrywa elementy nieosiagalne z wezlow typu 'source' (traverse), a nie wylicza komponenty spojne. Interpretacja: 'petle' = krawedzie zamkniete (poczatek = koniec), 'slepe uliczki' = wezly stopnia 1 danego typu (isOpen dodatkowo wymaga tid == tmp), 'rozlaczne' = findNotConnected*/findIsolated*. Semantyka zalezna od typow elementow sieci. Pliki: gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/extensions/NetworkGp.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/network/Graph.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/network/FindLoopEdges.java Dowód: Graph: findLoopEdges (isLoop: pierwszy from == ostatni to), findOpenNodes/findOpenEdges (wezel z 1 krawedzia), findIsolatedNodes/Edges, findNotConnectedNodes/Edges(source,type); wszystkie wystawione jako zadania GP w NetworkGp.</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="41.4" customHeight="1" s="15">
       <c r="A145" s="5" t="n">
@@ -15023,7 +15459,7 @@
       </c>
       <c r="O145" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P145" s="5" t="n"/>
@@ -15059,7 +15495,11 @@
       <c r="AT145" s="5" t="n"/>
       <c r="AU145" s="5" t="n"/>
       <c r="AV145" s="5" t="n"/>
-      <c r="AW145" s="5" t="n"/>
+      <c r="AW145" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Zastosowanie wykresow 'na poligonach' - w ChartRenderer nie sprawdzono umieszczania wykresow dla geometrii poligonowych (brak wzmianek polygon/centroid); Metody klasyfikacji naturalBreaks (Jenks) i geometricalInterval w GenerateRenderer maja komentarz TODO; ClassifyRenderer (z enumem naturalBreaks/geometricalInterval) dotyczy rastrow (bandName, RasterStatsType), nie poligonow. Chloropleta = ClassBreaksRenderer z rampa kolorow (sam renderer jest). Jenks/natural breaks w sciezce wektorowej niepotwierdzone (TODO w javadoc GenerateRenderer, linia ~45). Nie ma pojedynczego 'modulu geostatystycznego' - to ogolne renderery modulu carto. Pliki: gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/drawing/ChartRenderer.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/drawing/symbols/marker/chart/PieChart.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/drawing/symbols/marker/chart/BarChart.java Dowód: ChartRenderer (flaga proportional, minSize, wiele wyrazen) z symbolami PieChart, BarChart (+ClusteredChart, DiamondChart, FlowChart, SegmentChart) zaladowany przez RendererLoaders.loadChartRenderer; ClassBreaksRenderer (field/expression, normalizacja, color ramp) + GenerateRenderer.generateClassBreaksRenderer (equalInterval, quantile, standardDeviation).</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="41.4" customHeight="1" s="15">
       <c r="A146" s="5" t="n">
@@ -15116,7 +15556,7 @@
       </c>
       <c r="O146" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P146" s="5" t="n"/>
@@ -15152,7 +15592,11 @@
       <c r="AT146" s="5" t="n"/>
       <c r="AU146" s="5" t="n"/>
       <c r="AV146" s="5" t="n"/>
-      <c r="AW146" s="5" t="n"/>
+      <c r="AW146" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: niepotwierdzone. Niepotwierdzone w kodzie: Statystyka Morana I; Korelacja atrybutow / autokorelacja przestrzenna; Statystyki opisowe jako zestaw zadan GP (znaleziono tylko agregacje SUM/MIN/MAX/AVG). Szukane (java/py/jgp/json/md): moran, autocorrel, autokorel, spatial stat, getis, correlation, korelac, variance, stddev - brak trafien poza renderowaniem (standardDeviation w klasyfikacji) i RasterStats. Nie ma plikow .py w repo (pliki .jgp = konfiguracja GP; config/default/python.jgp istnieje, nie analizowano jego tresci pod katem skryptow) - funkcja moglaby byc w zewnetrznych skryptach Python. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/StatisticalCalculations.java; gp-imapserver-app/config/capap/analysis.jgp; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterStats.java Dowód: Brak Morana I i korelacji. Najblizsze: StatisticalCalculations (parametr stats domyslnie 'SUM,MIN,MAX,AVG', agregacja pol z tabeli 2 po st_relate wzgledem tabeli 1) oraz RasterStats; zarejestrowane m.in. w config/capap, gus, isok, sipww analysis.jgp (nie w config/default).</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="41.4" customHeight="1" s="15">
       <c r="A147" s="5" t="n">
@@ -15205,7 +15649,7 @@
       </c>
       <c r="O147" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P147" s="5" t="n"/>
@@ -15241,7 +15685,11 @@
       <c r="AT147" s="5" t="n"/>
       <c r="AU147" s="5" t="n"/>
       <c r="AV147" s="5" t="n"/>
-      <c r="AW147" s="5" t="n"/>
+      <c r="AW147" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'Domyslny format REST API' = JSON: Root ustawia defaultContentType(MediaType.TEXT_HTML), a favorParameter('f') i Accept decyduja; JSON wymaga f=json/pjson (lub Accept). Domyslny jest HTML (dla OGC API Features domyslnie JSON/GeoJSON wg opisu parametru f); GeoJSON zgodny z RFC 7946 - w kodzie brak odwolania do RFC; GeoJsonCursorSerializer ma zakomentowany blok 'crs' i nie wymusza WGS84 (wspolrzedne w SR warstwy/outSR). pJSON = tylko pretty-print (to samo co json z wcieciami), potwierdzone. GeoJSON dostepny tez przez ogc/gp-imapserver-ogc-api-features (FeaturesController, application/geo+json) i f=geojsonzip. W zlozonych odpowiedziach domyslnym typem jest HTML, wiec zdanie 'domyslny format' jest sprzeczne z kodem. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/json/GeoJsonCursorSerializer.java; gp-imapserver-rest/src/main/java/pl/gispartner/imapserver/rest/Root.java Dowód: GdbUtil.serialize: f=geojson -&gt; 'application/geo+json' (GeoJsonCursorSerializer: FeatureCollection/Feature), f=json|pjson -&gt; JSON, createGenerator(output, pretty) z pretty = 'pjson'.equals(f). Root.configureContentNegotiation: parametr 'f', mediaType json i pjson -&gt; application/json.</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="41.4" customHeight="1" s="15">
       <c r="A148" s="5" t="n">
@@ -15330,7 +15778,11 @@
       <c r="AT148" s="5" t="n"/>
       <c r="AU148" s="5" t="n"/>
       <c r="AV148" s="5" t="n"/>
-      <c r="AW148" s="5" t="n"/>
+      <c r="AW148" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Dodatkowo eksport mapy do pdf, eps, svg (display()). Kontrola DPI przez View/ImageSize (dpi w parametrach mapy/legendy). Kod aktywny, brak warunkow. Pliki: gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/MapServer.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapController.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/json/ims/MapLoader.java Dowód: MapServer.display(format): 'jpg'/'jpeg' i domyslnie PNG przez ImageDisplay (view.getDpi(), imageWidth/Height, compression); export z parametrami size (ImageSize), format (domyslnie 'png'), transparent. Kafle: MapLoader.generator -&gt; RasterGenerator.Format png32, jpg, mix (+ vector, lerc).</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="41.4" customHeight="1" s="15">
       <c r="A149" s="5" t="n">
@@ -15383,7 +15835,7 @@
       </c>
       <c r="O149" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P149" s="5" t="n"/>
@@ -15419,7 +15871,11 @@
       <c r="AT149" s="5" t="n"/>
       <c r="AU149" s="5" t="n"/>
       <c r="AV149" s="5" t="n"/>
-      <c r="AW149" s="5" t="n"/>
+      <c r="AW149" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Eksport do KMZ (skompresowany KML) - nie znaleziono. Szukane: kmz, KMZ, f=kmz, ZipOutputStream w KmlUtil - eksportu KMZ brak (KMZ tylko import w loaderze GP). 'Dla Google Earth i aplikacji mobilnych' - przeznaczenie, nie weryfikowalne w kodzie. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/kml/KmlUtil.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/cursors/KmlCursor.java Dowód: KML: GdbUtil.serialize f=kml -&gt; KmlUtil.save, content-type application/vnd.google-earth.kml+xml. KMZ w kodzie tylko jako WEJSCIE (KmlCursor.KmzOpener, CursorLoader rozpoznaje '.kmz').</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="41.4" customHeight="1" s="15">
       <c r="A150" s="5" t="n">
@@ -15508,7 +15964,11 @@
       <c r="AT150" s="5" t="n"/>
       <c r="AU150" s="5" t="n"/>
       <c r="AV150" s="5" t="n"/>
-      <c r="AW150" s="5" t="n"/>
+      <c r="AW150" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Geometria jako WKT tylko gdy zapytanie zwraca geometrie (returnGeometry); bez geometrii - same atrybuty (zgodne z opisem 'z WKT lub bez'). Ze toString() geometrii jest WKT potwierdzono dla PointImpl i PolygonImpl (pozostale typy nie sprawdzane). Separator zawsze przecinek. Opcje returnFormattedValues, returnFieldAliases. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/csv/CsvUtil.java Dowód: GdbUtil.serialize f=csv -&gt; CsvUtil.save (text/csv, UTF-8): naglowki z nazw/aliasow pol, a dla FeatureCursor dopisywane pole geometrii (getShape), wartosci przez toString(); Geometry.toString() = WktWriter (PointImpl/PolygonImpl).</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="41.4" customHeight="1" s="15">
       <c r="A151" s="5" t="n">
@@ -15561,7 +16021,7 @@
       </c>
       <c r="O151" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P151" s="5" t="n"/>
@@ -15597,7 +16057,11 @@
       <c r="AT151" s="5" t="n"/>
       <c r="AU151" s="5" t="n"/>
       <c r="AV151" s="5" t="n"/>
-      <c r="AW151" s="5" t="n"/>
+      <c r="AW151" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Dane rastrowe w GeoPackage - eksport tylko cursorow wektorowych/tabelarycznych; tabele gpkg_tile_matrix* pojawiaja sie wylacznie na liscie tabel systemowych. Szukane: raster, tile_matrix, data_type w pakiecie sqlite - brak zapisu rastrow/kafli do GPKG w eksporcie. Content-type 'geopackage+sqlite3' nie jest poprawnym typem MIME (bez 'application/'), uwaga marginalna. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/sqlite/LiteUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/sqlite/LiteDatabase.java Dowód: f=gpkg -&gt; LiteUtil.save(output, cursor, 'gpkg', tmp) (spatialite=false, content-type 'geopackage+sqlite3'); LiteDatabase wpisuje gpkg_contents (data_type, identifier, min/max, srs_id) i obsluguje gpkg_geometry_columns.</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="55.2" customHeight="1" s="15">
       <c r="A152" s="5" t="n">
@@ -15686,7 +16150,11 @@
       <c r="AT152" s="5" t="n"/>
       <c r="AU152" s="5" t="n"/>
       <c r="AV152" s="5" t="n"/>
-      <c r="AW152" s="5" t="n"/>
+      <c r="AW152" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. UWAGA nazewnicza: f=pbf w zapytaniach (GdbUtil -&gt; ProtoUtil.save, 'application/x-protobuf') to INNY format (protobuf FeatureCollection w stylu Esri), nie MVT. Kafle MVT dostepne tylko przez generator 'vector'. 'Client-side rendering' - przeznaczenie. Pliki: gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/tile/VectorGenerator.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/MapsController.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/json/ims/MapLoader.java Dowód: VectorGenerator (nazwa 'vector', format 'pbf', application/x-protobuf) buduje kafle biblioteka com.wdtinc.mapbox_vector_tile (VectorTile.Tile, MvtLayerBuild, MvtLayerParams(512, 4096)); MapsController obsluguje {map}/tile/{tile}/{level}/{row}/{col}.pbf oraz {map}/tile/{tile}/style i fonts/{fonts}/{range} (styl i glify Mapbox).</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="41.4" customHeight="1" s="15">
       <c r="A153" s="5" t="n">
@@ -15775,7 +16243,11 @@
       <c r="AT153" s="5" t="n"/>
       <c r="AU153" s="5" t="n"/>
       <c r="AV153" s="5" t="n"/>
-      <c r="AW153" s="5" t="n"/>
+      <c r="AW153" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Format zwracany z naglowkiem content-disposition (query.sqlite). 'Offline dla aplikacji mobilnych' - przeznaczenie, nie weryfikowalne. f=gpkg uzywa tej samej sciezki z spatialite=false. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/sqlite/LiteUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/sqlite/SpatialiteGeometryField.java Dowód: f=sqlite -&gt; LiteUtil.save z spatialite = 'sqlite'.equals(format) -&gt; newTmpDatabase(file, spatialite=true); klasa SpatialiteGeometryField obsluguje geometrie SpatiaLite.</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="41.4" customHeight="1" s="15">
       <c r="A154" s="5" t="n">
@@ -15864,7 +16336,11 @@
       <c r="AT154" s="5" t="n"/>
       <c r="AU154" s="5" t="n"/>
       <c r="AV154" s="5" t="n"/>
-      <c r="AW154" s="5" t="n"/>
+      <c r="AW154" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wynik to ZIP z plikami shapefile, nie pojedynczy .shp. Dostepne tez przez zapytania na schema/database/table view. Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/shp/ShpUtil.java Dowód: f=shp -&gt; ShpUtil.save do katalogu tymczasowego, calosc pakowana FileUtil.zip (application/zip, plik query.zip); dla wielu warstw osobne SHP z unikalnymi nazwami (tableNameMap).</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="41.4" customHeight="1" s="15">
       <c r="A155" s="5" t="n">
@@ -15953,7 +16429,11 @@
       <c r="AT155" s="5" t="n"/>
       <c r="AU155" s="5" t="n"/>
       <c r="AV155" s="5" t="n"/>
-      <c r="AW155" s="5" t="n"/>
+      <c r="AW155" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Content-type dla glb i obj to 'text/plain' (z komentarzem o model/obj). Wymaga danych 3D (struct3D: multipatch/trojkaty) - zachowanie dla zwyklych geometrii 2D nie sprawdzane. JSP schemaQuery/tableViewQuery nie listuja obj/glb (tylko query.jsp, databaseQuery.jsp). Pliki: gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/GdbUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/struct3D/GLBUtil.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/struct3D/ObjUtil.java Dowód: GdbUtil.serialize: f=glb -&gt; GLBUtil.save (GlTFBuilder + BinaryGlTF), f=obj -&gt; ObjUtil.save; TableController.query przekazuje f do TableController.serialize-&gt;GdbUtil.serialize; ta sama sciezka uzywana przez LayerController i FeatureServer (rest-carto). Lista formatow w JSP query.jsp/databaseQuery.jsp zawiera obj i glb.</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="41.4" customHeight="1" s="15">
       <c r="A156" s="5" t="n">
@@ -16040,7 +16520,7 @@
       <c r="AV156" s="5" t="n"/>
       <c r="AW156" s="5" t="inlineStr">
         <is>
-          <t>Brak potwierdzenia w bazie wiedzy: zero wzmianek o AMF / Action Message Format w gp-knowledgebase (stan 2026-07-28). Udokumentowane wartości parametru f: html, json, pjson; dodatkowo PBF (pl.gispartner.imapserver.ags.pbf). Plik api/getstarted/output_formats.md jest pusty (0 B). Do potwierdzenia w kodzie: czy format jest nadal obsługiwany, czy wycofany.</t>
+          <t>Brak potwierdzenia w bazie wiedzy: zero wzmianek o AMF / Action Message Format w gp-knowledgebase (stan 2026-07-28). Udokumentowane wartości parametru f: html, json, pjson; dodatkowo PBF (pl.gispartner.imapserver.ags.pbf). Plik api/getstarted/output_formats.md jest pusty (0 B). Do potwierdzenia w kodzie: czy format jest nadal obsługiwany, czy wycofany. | Weryfikacja kodu 2026-10-16: niepotwierdzone. Niepotwierdzone w kodzie: Format AMF (Action Message Format) dla klientow Flash/Flex. Szukane (java/gradle/properties/jsp/xml/jgp/py w calym repo): amf, AMF, ActionMessage, flex, blazeds - wylacznie trafienia przypadkowe (brak). Nie istnieje w tym repo; ewentualnie dawna funkcja usunieta. Dlugo martwy Flash/Flex czyni obecnosc malo prawdopodobna. Dowód: Brak implementacji AMF.</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16611,11 @@
       <c r="AT157" s="5" t="n"/>
       <c r="AU157" s="5" t="n"/>
       <c r="AV157" s="5" t="n"/>
-      <c r="AW157" s="5" t="n"/>
+      <c r="AW157" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. HTML jest faktycznym domyslnym typem odpowiedzi (przegladarka bez parametru f). Podglad mapy w JSP korzysta z biblioteki JS z CDN (js.arcgis.com 3.20) - wymaga internetu. Pliki: gp-imapserver-rest/src/main/java/pl/gispartner/imapserver/rest/Root.java; gp-imapserver-rest-gdb/src/main/resources/META-INF/resources/WEB-INF/jsp/gdb/query.jsp; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/MapServer.java Dowód: Root: defaultContentType(MediaType.TEXT_HTML), mediaType('html'); kazdy kontroler ma wariant @RequestMapping(produces = HTML) renderujacy JSP (np. gdb/query.jsp z lista formatow, MapServer f=jsapi -&gt; preview.jsp z mapa).</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="41.4" customHeight="1" s="15">
       <c r="A158" s="5" t="n">
@@ -16187,7 +16671,7 @@
       <c r="M158" s="5" t="n"/>
       <c r="N158" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O158" s="5" t="inlineStr">
@@ -16228,7 +16712,11 @@
       <c r="AT158" s="5" t="n"/>
       <c r="AU158" s="5" t="n"/>
       <c r="AV158" s="5" t="n"/>
-      <c r="AW158" s="5" t="n"/>
+      <c r="AW158" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Parametr 'size' w jednostkach układu danych. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Po wykonaniu updateAreaAndLength na wyniku. Rejestracja GP: default (analysis.jgp, bez aliasu/parametrów), capap, gus, isok, sipww; dodatkowo default/test.jgp Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Buffer.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/BaseSpatialFunctionAnalyse.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Buffer (BaseSpatialFunctionAnalyse), name="buffer", inputy: input(+shape/where/geometry), size (Double), output. INSERT do nowej tabeli st_multi(st_buffer(shape,size)), typ wyniku polygon.</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="41.4" customHeight="1" s="15">
       <c r="A159" s="5" t="n">
@@ -16284,7 +16772,7 @@
       <c r="M159" s="5" t="n"/>
       <c r="N159" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O159" s="5" t="inlineStr">
@@ -16325,7 +16813,11 @@
       <c r="AT159" s="5" t="n"/>
       <c r="AU159" s="5" t="n"/>
       <c r="AV159" s="5" t="n"/>
-      <c r="AW159" s="5" t="n"/>
+      <c r="AW159" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Kod nie ogranicza typu wejścia do poligonów (st_centroid na dowolnej geometrii); opis 'poligonów' to typowe użycie, nie wymóg w kodzie. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Centroid); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Centroid.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/BaseSpatialFunctionAnalyse.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Centroid, name="centroid" (z nazwy klasy), inputy: input(+shape/where/geometry), output. INSERT st_centroid(shape), typ wyniku point, kopiuje atrybuty wejścia.</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="41.4" customHeight="1" s="15">
       <c r="A160" s="5" t="n">
@@ -16381,7 +16873,7 @@
       <c r="M160" s="5" t="n"/>
       <c r="N160" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O160" s="5" t="inlineStr">
@@ -16422,7 +16914,11 @@
       <c r="AT160" s="5" t="n"/>
       <c r="AU160" s="5" t="n"/>
       <c r="AV160" s="5" t="n"/>
-      <c r="AW160" s="5" t="n"/>
+      <c r="AW160" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Opis wymienia 4 cechy; kod liczy też liczbę części i obwiednię. Literówka w nazwie pola 'lenght'. Atrybuty wejścia NIE są kopiowane (brak copyFields), tylko geometria + cechy. nPoint dla typu polygon pomniejszone o 1. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.GeometricFeatures); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/GeometricFeatures.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.GeometricFeatures, name="geometricFeatures", inputy: input(+shape/where/geometry), output. Tworzy tabelę z polami shape, lenght (sic), area, nPoint, numGeometries, isValid, bxmin, bymin, bxmax, bymax (ST_Length, ST_Area, ST_NPoints, ST_NumGeometries, ST_IsValid, ST_XMin...).</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="41.4" customHeight="1" s="15">
       <c r="A161" s="5" t="n">
@@ -16478,7 +16974,7 @@
       <c r="M161" s="5" t="n"/>
       <c r="N161" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O161" s="5" t="inlineStr">
@@ -16519,7 +17015,11 @@
       <c r="AT161" s="5" t="n"/>
       <c r="AU161" s="5" t="n"/>
       <c r="AV161" s="5" t="n"/>
-      <c r="AW161" s="5" t="n"/>
+      <c r="AW161" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Nowy rekord per obiekt, atrybuty kopiowane. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Simplify); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Simplify.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/BaseSpatialFunctionAnalyse.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Simplify, name="simplify", inputy: input(+...), tolerance (Double), output. INSERT st_simplify(shape,tolerance), typ wyniku = typ wejścia.</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="41.4" customHeight="1" s="15">
       <c r="A162" s="5" t="n">
@@ -16575,12 +17075,12 @@
       <c r="M162" s="5" t="n"/>
       <c r="N162" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O162" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P162" s="5" t="n"/>
@@ -16616,7 +17116,11 @@
       <c r="AT162" s="5" t="n"/>
       <c r="AU162" s="5" t="n"/>
       <c r="AV162" s="5" t="n"/>
-      <c r="AW162" s="5" t="n"/>
+      <c r="AW162" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'Podział linii' - kod woła st_segmentize na geometrii, czyli (wg nazwy funkcji PostGIS) dogęszcza wierzchołki; w kodzie IMS nie ma rozbijania na osobne obiekty. Rzeczywiste działanie st_segmentize to wiedza spoza repo - niepotwierdzone w kodzie.. Parametr nazywa się 'lenght'. Typ wyniku zawsze polyline (także gdy wejście inne). Opis jgp mówi o segmentacji na obiekty, ale kod robi jedno wywołanie funkcji na geometrii w jednym wierszu. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Segmentize); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Segmentize.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/BaseSpatialFunctionAnalyse.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Segmentize, name="segmentize", inputy: input(+...), lenght (Double, literówka), output. INSERT st_segmentize(shape,lenght), typ wyniku polyline.</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="41.4" customHeight="1" s="15">
       <c r="A163" s="5" t="n">
@@ -16672,7 +17176,7 @@
       <c r="M163" s="5" t="n"/>
       <c r="N163" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O163" s="5" t="inlineStr">
@@ -16713,7 +17217,11 @@
       <c r="AT163" s="5" t="n"/>
       <c r="AU163" s="5" t="n"/>
       <c r="AV163" s="5" t="n"/>
-      <c r="AW163" s="5" t="n"/>
+      <c r="AW163" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Typ wyniku = typ wejścia. Limity 'min. 8, max. 255' tylko w opisie parametru w jgp, w kodzie Java brak walidacji zakresu. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Subdivide); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Subdivide.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Subdivide, name="subdivide", inputy: input(+...), vertices (Int), output. INSERT st_multi(st_subdivide(shape,vertices)) - zbiór-zwracająca funkcja daje wiele wierszy na obiekt; atrybuty kopiowane.</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="41.4" customHeight="1" s="15">
       <c r="A164" s="5" t="n">
@@ -16769,7 +17277,7 @@
       <c r="M164" s="5" t="n"/>
       <c r="N164" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O164" s="5" t="inlineStr">
@@ -16810,7 +17318,11 @@
       <c r="AT164" s="5" t="n"/>
       <c r="AU164" s="5" t="n"/>
       <c r="AV164" s="5" t="n"/>
-      <c r="AW164" s="5" t="n"/>
+      <c r="AW164" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Każda część opakowana z powrotem w st_multi, więc typ kolumny wynikowej to nadal typ z tabeli (poza multipoint-&gt;point). Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Dump); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Dump.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Dump, name="dump", inputy: input(+...), output. INSERT st_multi((st_dump(shape)).geom) - jeden wiersz na część, atrybuty kopiowane; multipoint -&gt; typ point.</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="41.4" customHeight="1" s="15">
       <c r="A165" s="5" t="n">
@@ -16866,7 +17378,7 @@
       <c r="M165" s="5" t="n"/>
       <c r="N165" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O165" s="5" t="inlineStr">
@@ -16907,7 +17419,11 @@
       <c r="AT165" s="5" t="n"/>
       <c r="AU165" s="5" t="n"/>
       <c r="AV165" s="5" t="n"/>
-      <c r="AW165" s="5" t="n"/>
+      <c r="AW165" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Atrybuty wejścia kopiowane (copyFields) tylko w polach tabeli; w insercie dodawana jest sama geometria - INSERT nie listuje atrybutów (values(null,...)), więc praktycznie tylko geometria; nie ma indeksu ani Area/Length. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.DumpPoints); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/DumpPoints.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.DumpPoints, name="dumpPoints", inputy: input(+...), output. INSERT (st_dumppoints(shape)).geom do tabeli typu point.</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="41.4" customHeight="1" s="15">
       <c r="A166" s="5" t="n">
@@ -16963,7 +17479,7 @@
       <c r="M166" s="5" t="n"/>
       <c r="N166" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O166" s="5" t="inlineStr">
@@ -17004,7 +17520,11 @@
       <c r="AT166" s="5" t="n"/>
       <c r="AU166" s="5" t="n"/>
       <c r="AV166" s="5" t="n"/>
-      <c r="AW166" s="5" t="n"/>
+      <c r="AW166" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Identyfikator techniczny w macierzy 'snapToGrid' różni się wielkością liter od nazwy w kodzie 'snaptogrid' - poprawić w macierzy. Poza profilami config/zip/analizy.gp występuje wpis name="snapToGrid" z klasą CapapDummy (atrapa, nie ta implementacja). Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.SnapToGrid); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/SnapToGrid.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/BaseSpatialFunctionAnalyse.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.SnapToGrid, name="snaptogrid" (ustawione ręcznie w init, małe litery), inputy: input(+...), size (Double), output. INSERT st_snaptogrid(shape,size), typ = typ wejścia.</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="41.4" customHeight="1" s="15">
       <c r="A167" s="5" t="n">
@@ -17060,7 +17580,7 @@
       <c r="M167" s="5" t="n"/>
       <c r="N167" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O167" s="5" t="inlineStr">
@@ -17101,7 +17621,11 @@
       <c r="AT167" s="5" t="n"/>
       <c r="AU167" s="5" t="n"/>
       <c r="AV167" s="5" t="n"/>
-      <c r="AW167" s="5" t="n"/>
+      <c r="AW167" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wzory x'=a*x+b*y+xoff itd. pochodzą z opisu w jgp, w kodzie Java tylko wywołanie ST_Affine z 6 parametrami. Opisy parametrów yoff w jgp błędnie 'względem osi X'. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.AffineTransformation); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/AffineTransformation.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.AffineTransformation, name="affineTransformation", inputy: input(+...), a,b,d,e,xoff,yoff (Double), output. INSERT ST_Affine(shape,a,b,d,e,xoff,yoff).</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="55.2" customHeight="1" s="15">
       <c r="A168" s="5" t="n">
@@ -17157,7 +17681,7 @@
       <c r="M168" s="5" t="n"/>
       <c r="N168" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O168" s="5" t="inlineStr">
@@ -17198,7 +17722,11 @@
       <c r="AT168" s="5" t="n"/>
       <c r="AU168" s="5" t="n"/>
       <c r="AV168" s="5" t="n"/>
-      <c r="AW168" s="5" t="n"/>
+      <c r="AW168" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. srid wstawiany do SQL jako liczba (Int), nie parametr bindowany. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Transform); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Transform.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Transform, name="transform", inputy: input(+...), srid (Int), output. Tworzy tabelę wyjściową z polem w podanym srid, INSERT st_transform(shape,srid).</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="41.4" customHeight="1" s="15">
       <c r="A169" s="5" t="n">
@@ -17254,7 +17782,7 @@
       <c r="M169" s="5" t="n"/>
       <c r="N169" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O169" s="5" t="inlineStr">
@@ -17295,7 +17823,11 @@
       <c r="AT169" s="5" t="n"/>
       <c r="AU169" s="5" t="n"/>
       <c r="AV169" s="5" t="n"/>
-      <c r="AW169" s="5" t="n"/>
+      <c r="AW169" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.FlipCoordinates); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/FlipCoordinates.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/BaseSpatialFunctionAnalyse.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.FlipCoordinates, name="flipCoordinates", inputy: input(+...), output. INSERT ST_FlipCoordinates(shape), typ = typ wejścia.</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="41.4" customHeight="1" s="15">
       <c r="A170" s="5" t="n">
@@ -17351,7 +17883,7 @@
       <c r="M170" s="5" t="n"/>
       <c r="N170" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O170" s="5" t="inlineStr">
@@ -17392,7 +17924,11 @@
       <c r="AT170" s="5" t="n"/>
       <c r="AU170" s="5" t="n"/>
       <c r="AV170" s="5" t="n"/>
-      <c r="AW170" s="5" t="n"/>
+      <c r="AW170" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wynik to jeden obiekt bez atrybutów wejścia, bez Area/Length. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.MinimumBoundingCircle); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/MinimumBoundingCircle.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.MinimumBoundingCircle, name="minimumBoundingCircle", inputy: input(+...), output. Jeden wiersz: ST_multi(ST_MinimumBoundingCircle(ST_Collect(array(select shape ...)))) - jedno koło dla całego (przefiltrowanego) zbioru, typ polygon.</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="55.2" customHeight="1" s="15">
       <c r="A171" s="5" t="n">
@@ -17448,7 +17984,7 @@
       <c r="M171" s="5" t="n"/>
       <c r="N171" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O171" s="5" t="inlineStr">
@@ -17489,7 +18025,11 @@
       <c r="AT171" s="5" t="n"/>
       <c r="AU171" s="5" t="n"/>
       <c r="AV171" s="5" t="n"/>
-      <c r="AW171" s="5" t="n"/>
+      <c r="AW171" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. W jgp opis npoints: 'maksymalna ilość punktów' - w kodzie jedynie przekazanie do st_generatepoints. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.GeneratePoints); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/GeneratePoints.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.GeneratePoints, name="generatePoints", inputy: input(+...), npoints (Int), output. INSERT (ST_Dump(st_generatepoints(shape,npoints))).geom, typ point, kopiuje atrybuty oraz oid_input gdy wejście ma OID.</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="41.4" customHeight="1" s="15">
       <c r="A172" s="5" t="n">
@@ -17545,7 +18085,7 @@
       <c r="M172" s="5" t="n"/>
       <c r="N172" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O172" s="5" t="inlineStr">
@@ -17586,7 +18126,11 @@
       <c r="AT172" s="5" t="n"/>
       <c r="AU172" s="5" t="n"/>
       <c r="AV172" s="5" t="n"/>
-      <c r="AW172" s="5" t="n"/>
+      <c r="AW172" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: Opis '(x,y,CRS)': kod przyjmuje listę w formacie WKT (np. MULTIPOINT) + srid, nie osobne x,y.. wkt jest doklejany do SQL jako literał bez bindowania (ryzyko SQL injection). Zapis do tabeli tymczasowej w bazie 'database'. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.GeneratePointFromList); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/GeneratePointFromList.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.GeneratePointFromList, name="generatePointFromList", inputy: database (String), wkt (String), srid (Int), output (brak tabeli wejściowej). INSERT (st_dump(ST_GeomFromText('&lt;wkt&gt;',&lt;srid&gt;))).geom do nowej tabeli typu point (pole 'shape').</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="41.4" customHeight="1" s="15">
       <c r="A173" s="5" t="n">
@@ -17642,7 +18186,7 @@
       <c r="M173" s="5" t="n"/>
       <c r="N173" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O173" s="5" t="inlineStr">
@@ -17683,7 +18227,11 @@
       <c r="AT173" s="5" t="n"/>
       <c r="AU173" s="5" t="n"/>
       <c r="AV173" s="5" t="n"/>
-      <c r="AW173" s="5" t="n"/>
+      <c r="AW173" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wynik per para obiektów (nie union zbiorów); warunek 'T********' pomija obiekty stykające się tylko brzegiem. Atrybuty wejść nie kopiowane (tylko oid1/oid2). Przy tym samym zbiorze dodatkowo T.oid&gt;T2.oid. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Intersection); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Intersection.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Intersection, name="intersection", inputy: input,input2 (+shape/where/geometry), output. INSERT st_intersection(T.shape,T2.shape) dla par obiektów z st_relate(...,'T********'), pola oid1, oid2, shape.</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="41.4" customHeight="1" s="15">
       <c r="A174" s="5" t="n">
@@ -17739,7 +18287,7 @@
       <c r="M174" s="5" t="n"/>
       <c r="N174" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O174" s="5" t="inlineStr">
@@ -17780,7 +18328,11 @@
       <c r="AT174" s="5" t="n"/>
       <c r="AU174" s="5" t="n"/>
       <c r="AV174" s="5" t="n"/>
-      <c r="AW174" s="5" t="n"/>
+      <c r="AW174" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wynik to jeden zagregowany obiekt (różnica unii zbiorów), bez atrybutów. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Difference); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Difference.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Difference, name="difference", inputy: input,input2 (+...), output. Jeden wiersz: ST_Difference((SELECT ST_Union(shape1)...),(SELECT ST_Union(shape2)...)) z collectionextract/st_multi.</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="41.4" customHeight="1" s="15">
       <c r="A175" s="5" t="n">
@@ -17836,7 +18388,7 @@
       <c r="M175" s="5" t="n"/>
       <c r="N175" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O175" s="5" t="inlineStr">
@@ -17877,7 +18429,11 @@
       <c r="AT175" s="5" t="n"/>
       <c r="AU175" s="5" t="n"/>
       <c r="AV175" s="5" t="n"/>
-      <c r="AW175" s="5" t="n"/>
+      <c r="AW175" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wynik to jeden zagregowany obiekt, nie zbiór oryginalnych obiektów 'wyłącznie z jednego zbioru'. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.SymmetricDifference); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/SymmetricDifference.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Difference.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.SymmetricDifference, name="symmetricDifference", inputy: input,input2 (+...), output. Jeden wiersz: ST_SymDifference(unia zbioru 1, unia zbioru 2) opakowane fixDifference.</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="55.2" customHeight="1" s="15">
       <c r="A176" s="5" t="n">
@@ -17933,7 +18489,7 @@
       <c r="M176" s="5" t="n"/>
       <c r="N176" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O176" s="5" t="inlineStr">
@@ -17974,7 +18530,11 @@
       <c r="AT176" s="5" t="n"/>
       <c r="AU176" s="5" t="n"/>
       <c r="AV176" s="5" t="n"/>
-      <c r="AW176" s="5" t="n"/>
+      <c r="AW176" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Ryzyko: tabela wyjściowa tworzy pole o nazwie geometrii wejścia 1, a potem szuka pola 'shape' (findShape("shape")) - przy innej nazwie pola geometrii wejścia może rzucić wyjątek (nie przetestowane). Atrybuty wejścia nie kopiowane. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Split); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Split.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Split, name="split", inputy: input,input2 (+...), output. INSERT st_split(T.shape1, ostrze z zbioru 2) dla par z st_intersects; dla poligonów ostrzem jest ST_Boundary, dla linii/multipoint st_dump; wynik st_multi((st_Dump(...)).geom).</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="41.4" customHeight="1" s="15">
       <c r="A177" s="5" t="n">
@@ -18030,7 +18590,7 @@
       <c r="M177" s="5" t="n"/>
       <c r="N177" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O177" s="5" t="inlineStr">
@@ -18071,7 +18631,11 @@
       <c r="AT177" s="5" t="n"/>
       <c r="AU177" s="5" t="n"/>
       <c r="AV177" s="5" t="n"/>
-      <c r="AW177" s="5" t="n"/>
+      <c r="AW177" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Obiekty niezachodzące na zasięg dają prawdopodobnie puste geometrie (nie filtrowane w kodzie - nie sprawdzone). Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Clip); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Clip.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/BaseSpatialFunctionAnalyse.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Clip (BaseSpatialFunctionAnalyse + addInput("2")), name="clip", inputy: input,input2 (+...), output. INSERT st_intersection(shape,(select st_union(shape2) ...)) z fixIntersection; atrybuty wejścia 1 kopiowane, typ = typ wejścia 1.</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="41.4" customHeight="1" s="15">
       <c r="A178" s="5" t="n">
@@ -18127,7 +18691,7 @@
       <c r="M178" s="5" t="n"/>
       <c r="N178" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O178" s="5" t="inlineStr">
@@ -18168,7 +18732,11 @@
       <c r="AT178" s="5" t="n"/>
       <c r="AU178" s="5" t="n"/>
       <c r="AV178" s="5" t="n"/>
-      <c r="AW178" s="5" t="n"/>
+      <c r="AW178" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Dokładnie dwa wejścia (input, input2), nie 'wiele zbiorów'. Istnieje też nierejestrowana klasa CollectOld. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Collect); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Collect.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Collect, name="collect", inputy: input,input2 (+...), output. INSERT ... SELECT z T UNION ALL SELECT z T2; wymaga tego samego typu geometrii (inaczej GdbException); atrybuty łączone po nazwie i typie, brak -&gt; NULL.</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="41.4" customHeight="1" s="15">
       <c r="A179" s="5" t="n">
@@ -18224,12 +18792,12 @@
       <c r="M179" s="5" t="n"/>
       <c r="N179" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O179" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P179" s="5" t="n"/>
@@ -18265,7 +18833,11 @@
       <c r="AT179" s="5" t="n"/>
       <c r="AU179" s="5" t="n"/>
       <c r="AV179" s="5" t="n"/>
-      <c r="AW179" s="5" t="n"/>
+      <c r="AW179" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'Dissolve z opcjonalnymi statystykami': statystyki SUM/AVG/MIN/MAX liczone zawsze dla wszystkich pól numerycznych (nie opcjonalne).; Brak GROUP BY: expression jest warunkiem WHERE, całość wyniku to jeden obiekt, a nie dissolve per grupa.. Niezgodność semantyki z nazwą 'Grupowanie'. Opis w jgp też wspomina grupowanie po kryterium, ale kod tego nie robi. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.GroupingAndCombiningObjects); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/GroupingAndCombiningObjects.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/BaseAnalyse.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.GroupingAndCombiningObjects, name="groupingAndCombiningObjects", inputy: input(+...), expression (String, wymagany), output. Jeden wiersz: ST_Multi(ST_Union(shape)) dla obiektów spełniających WHERE expression, plus SUM/AVG/MIN/MAX każdego pola numerycznego.</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="41.4" customHeight="1" s="15">
       <c r="A180" s="5" t="n">
@@ -18321,7 +18893,7 @@
       <c r="M180" s="5" t="n"/>
       <c r="N180" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O180" s="5" t="inlineStr">
@@ -18362,7 +18934,11 @@
       <c r="AT180" s="5" t="n"/>
       <c r="AU180" s="5" t="n"/>
       <c r="AV180" s="5" t="n"/>
-      <c r="AW180" s="5" t="n"/>
+      <c r="AW180" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Filtracja realizowana przez wspólne inputy where/geometry. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.Copy); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Copy.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.Copy, name="copy", inputy: input(+shape/where/geometry), output. INSERT wszystkich pól z wejścia do nowej tabeli z filtrem where/geometry (builder).</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="55.2" customHeight="1" s="15">
       <c r="A181" s="5" t="n">
@@ -18418,7 +18994,7 @@
       <c r="M181" s="5" t="n"/>
       <c r="N181" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O181" s="5" t="inlineStr">
@@ -18459,7 +19035,11 @@
       <c r="AT181" s="5" t="n"/>
       <c r="AU181" s="5" t="n"/>
       <c r="AV181" s="5" t="n"/>
-      <c r="AW181" s="5" t="n"/>
+      <c r="AW181" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Parametr 'expression' jest zakomentowany w kodzie (komentarz MG: do tego służy where) - filtr atrybutowy to input 'where'. Opis w jgp mówi o kryteriach, ale bez parametru expression. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.AttributeSelection); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/AttributeSelection.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.AttributeSelection, name="attributeSelection", inputy: input(+shape/where/geometry), output. INSERT kopii obiektów spełniających where (input where).</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="41.4" customHeight="1" s="15">
       <c r="A182" s="5" t="n">
@@ -18515,7 +19095,7 @@
       <c r="M182" s="5" t="n"/>
       <c r="N182" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O182" s="5" t="inlineStr">
@@ -18556,7 +19136,11 @@
       <c r="AT182" s="5" t="n"/>
       <c r="AU182" s="5" t="n"/>
       <c r="AV182" s="5" t="n"/>
-      <c r="AW182" s="5" t="n"/>
+      <c r="AW182" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wartości INSERT (geometria T.shape i oid) dodawane tylko w gałęzi 'if findOid != null' - dla tabeli bez OID kolumny insertu i values mogą się rozjechać (niezweryfikowane w działaniu). Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.NoCommonPart); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/NoCommonPart.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.NoCommonPart, name="noCommonPart", inputy: input,input2 (+...), output. INSERT obiektów zbioru 1 z WHERE st_relate(shape1, ST_Union(zbiór 2),'FF*FF****') (rozłączne), pola oid1 i shape.</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="27.6" customHeight="1" s="15">
       <c r="A183" s="5" t="n">
@@ -18612,7 +19196,7 @@
       <c r="M183" s="5" t="n"/>
       <c r="N183" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O183" s="5" t="inlineStr">
@@ -18653,7 +19237,11 @@
       <c r="AT183" s="5" t="n"/>
       <c r="AU183" s="5" t="n"/>
       <c r="AV183" s="5" t="n"/>
-      <c r="AW183" s="5" t="n"/>
+      <c r="AW183" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Ta sama uwaga o gałęzi 'if findOid != null' co w NoCommonPart. Brak createIndex na wyniku. Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.CommonPart); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/CommonPart.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.CommonPart, name="commonPart", inputy: input,input2 (+...), output. INSERT obiektów zbioru 1 z WHERE st_relate(shape1, ST_Union(zbiór 2),'T********'); kopiowana jest oryginalna geometria zbioru 1 (nie przecięcie), pola oid1, shape.</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="41.4" customHeight="1" s="15">
       <c r="A184" s="5" t="n">
@@ -18709,7 +19297,7 @@
       <c r="M184" s="5" t="n"/>
       <c r="N184" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O184" s="5" t="inlineStr">
@@ -18750,7 +19338,11 @@
       <c r="AT184" s="5" t="n"/>
       <c r="AU184" s="5" t="n"/>
       <c r="AV184" s="5" t="n"/>
-      <c r="AW184" s="5" t="n"/>
+      <c r="AW184" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Działa na wierzchołkach wewnątrz geometrii (nie usuwa zduplikowanych obiektów, choć opis w jgp wspomina 'i obiektów'). tolerance opcjonalny, ale zawsze przekazywany do funkcji (przy braku wartości trafi NULL - zachowanie niezweryfikowane). Wspólne dla klas z addOutput(): input (tabela) nie jest modyfikowany; wynik zapisywany do tabeli 'output' (opcjonalny) lub tymczasowej; jeśli output już istnieje, wykonywany jest DELETE FROM tabeli output przed INSERT. Filtry opcjonalne where/geometry (inputy where, geometry) stosowane do wejścia przez BaseAnalyse.builder. Nazwa zadania = nazwa klasy z małej litery (GpTask.nameFromClass), jeśli nie ustawiona w init(). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.RemoveRepeatedPoints); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/RemoveRepeatedPoints.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.RemoveRepeatedPoints, name="removeRepeatedPoints", inputy: input(+...), tolerance (Double, opcjonalny), output. INSERT st_removerepeatedpoints(shape,tolerance) do nowej tabeli, atrybuty kopiowane.</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="41.4" customHeight="1" s="15">
       <c r="A185" s="5" t="n">
@@ -18806,7 +19398,7 @@
       <c r="M185" s="5" t="n"/>
       <c r="N185" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O185" s="5" t="inlineStr">
@@ -18847,7 +19439,11 @@
       <c r="AT185" s="5" t="n"/>
       <c r="AU185" s="5" t="n"/>
       <c r="AV185" s="5" t="n"/>
-      <c r="AW185" s="5" t="n"/>
+      <c r="AW185" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. UWAGA: modyfikuje tabelę wejściową (DELETE). Brak expression = usunięcie WSZYSTKICH wierszy. Inputy where/geometry z addInput są ignorowane (SqlBuilder utworzony, ale nie użyty w DELETE). Identyfikator z macierzy ('Atribute') zgodny z kodem. Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.RemoveByAtributeSelection); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/RemoveByAtributeSelection.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.RemoveByAtributeSelection, name="removeByAtributeSelection" (literówka w nazwie klasy i zadania), inputy: input(+...), expression (String, opcjonalny). Wykonuje DELETE FROM &lt;input&gt; [WHERE expression]; brak output.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="41.4" customHeight="1" s="15">
       <c r="A186" s="5" t="n">
@@ -18903,7 +19499,7 @@
       <c r="M186" s="5" t="n"/>
       <c r="N186" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O186" s="5" t="inlineStr">
@@ -18944,7 +19540,11 @@
       <c r="AT186" s="5" t="n"/>
       <c r="AU186" s="5" t="n"/>
       <c r="AV186" s="5" t="n"/>
-      <c r="AW186" s="5" t="n"/>
+      <c r="AW186" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. UWAGA: modyfikuje (DELETE) tabelę wejściową 1. Inputy where/geometry z addInput są ignorowane w DELETE (nie użyto builder). Kryterium to przecięcie wnętrz ('T********'). Rejestracja GP: capap, gus, isok, sipww (config/&lt;profil&gt;/analysis.jgp, wpis z klasą pl.gispartner.imapserver.gp.tasks.analysis.RemoveByIntersection); brak w config/default (default/analysis.jgp rejestruje tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/RemoveByIntersection.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa analysis.RemoveByIntersection, name="removeByIntersection", inputy: input,input2 (+...). Wykonuje DELETE FROM &lt;input&gt; T USING &lt;input2&gt; T2 WHERE st_relate(T.shape,T2.shape,'T********'); brak output.</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="41.4" customHeight="1" s="15">
       <c r="A187" s="5" t="n">
@@ -19000,7 +19600,7 @@
       <c r="M187" s="5" t="n"/>
       <c r="N187" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O187" s="5" t="inlineStr">
@@ -19041,7 +19641,11 @@
       <c r="AT187" s="5" t="n"/>
       <c r="AU187" s="5" t="n"/>
       <c r="AV187" s="5" t="n"/>
-      <c r="AW187" s="5" t="n"/>
+      <c r="AW187" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wartosc 'within' to w kodzie ST_DWithin(...,200) z hardkodowana odlegloscia 200 (nie ST_Within); 'all' = OR trzech warunkow. SQL nie dolacza s1/s2.getWhere() (inaczej niz JoinTabularAndSpatialData), a parametry buildera sa przekazywane. Jesli output istnieje, wykonywany jest DELETE FROM tabeli wynikowej. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/AddAttributeBySpatialJoin.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa AddAttributeBySpatialJoin, nazwa zadania addAttributeBySpatialJoin. Inputy: 2 zbiory (addInput(2)), relationship (all/intersects/contains/within), output. Wstawia do wyniku pola zbioru 1 i atrybuty zbioru 2 dla par spelniajacych ST_Intersects/ST_Contains/ST_DWithin.</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="41.4" customHeight="1" s="15">
       <c r="A188" s="5" t="n">
@@ -19097,7 +19701,7 @@
       <c r="M188" s="5" t="n"/>
       <c r="N188" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O188" s="5" t="inlineStr">
@@ -19138,7 +19742,11 @@
       <c r="AT188" s="5" t="n"/>
       <c r="AU188" s="5" t="n"/>
       <c r="AV188" s="5" t="n"/>
-      <c r="AW188" s="5" t="n"/>
+      <c r="AW188" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Przy istniejacym output: DELETE FROM tabeli wynikowej (lub opoznione czyszczenie przy delayCleaning=true). Gdy brak pola, kod rzuca NullPointerException zamiast GpException (field1.getName() na null). Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/JoinTabularAndSpatialData.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa JoinTabularAndSpatialData, zadanie joinTabularAndSpatialData. Inputy: 2 zbiory, field, field2, outputFields, outputFields2, delayCleaning, output. Wstawia wiersze z warunkiem T.field = T2.field2 (inner join po wspolnym kluczu) i kopiuje pola oraz geometrie zbioru 2.</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="41.4" customHeight="1" s="15">
       <c r="A189" s="5" t="n">
@@ -19166,7 +19774,7 @@
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>Sum/avg/min/max pkt/lin w poligonach.</t>
+          <t>Zadanie GP statisticalCalculations: dwa zbiory, parametry fields (domyślnie '*'), stats (domyślnie SUM,MIN,MAX,AVG), output; agregacja po st_relate między zbiorami. Nazwa zadania w kodzie: statisticalCalculations.</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
@@ -19194,12 +19802,12 @@
       <c r="M189" s="5" t="n"/>
       <c r="N189" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O189" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P189" s="5" t="n"/>
@@ -19235,7 +19843,11 @@
       <c r="AT189" s="5" t="n"/>
       <c r="AU189" s="5" t="n"/>
       <c r="AV189" s="5" t="n"/>
-      <c r="AW189" s="5" t="n"/>
+      <c r="AW189" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: sprzeczne. Niepotwierdzone w kodzie: Statystyki sum/avg/min/max pol obiektow pkt/lin (zbior 2) w poligonach: getStat() w BaseAnalyse.java uzywa prefiksu 'T.', a alias zbioru 2 to 'T2' (builder: "T"+postfix). Wniosek ze statycznej lektury kodu (nie uruchamiano): agregaty odnosza sie do kolumn zbioru 1; gdy zbior 1 nie ma pola o nazwie z zbioru 2 - blad SQL, gdy ma - wynik bledny (agregat atrybutu poligonu). Nazwa w macierzy rozni sie od klasy (liczba mnoga). DELETE na output gdy istnieje. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/StatisticalCalculations.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/BaseAnalyse.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa StatisticalCalculations, zadanie statisticalCalculations (macierz podaje statisticalCalculation). Inputy: 2 zbiory, fields (domyslnie '*'), stats (domyslnie SUM,MIN,MAX,AVG), output; poligony = zbior 1 (st_relate(T2,T,'T*F**F***')), GROUP BY oid zbioru 1. Pola wynikowe tworzone wg pol zbioru 2, ale wartosci liczone jako STAT(T.pole) czyli na aliasie T = zbior 1. | Opis przed korektą: Sum/avg/min/max pkt/lin w poligonach.</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="41.4" customHeight="1" s="15">
       <c r="A190" s="5" t="n">
@@ -19291,7 +19903,7 @@
       <c r="M190" s="5" t="n"/>
       <c r="N190" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O190" s="5" t="inlineStr">
@@ -19332,7 +19944,11 @@
       <c r="AT190" s="5" t="n"/>
       <c r="AU190" s="5" t="n"/>
       <c r="AV190" s="5" t="n"/>
-      <c r="AW190" s="5" t="n"/>
+      <c r="AW190" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Zadanie MODYFIKUJE tabele wejsciowa (UPDATE w miejscu, bez tabeli wynikowej); istniejace pole musi miec typ zgodny z wyrazeniem. Zakres 'wyrazen matematycznych' wynika z silnika Expression - nie weryfikowano jego funkcji. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Calculate.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa Calculate, zadanie calculate. Inputy: 1 zbior, field, expression (brak output). Parsuje Expression.parse(expression), tworzy pole jesli nie istnieje i wykonuje UPDATE tabeli wejsciowej SET pole=wyrazenie.</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="41.4" customHeight="1" s="15">
       <c r="A191" s="5" t="n">
@@ -19388,7 +20004,7 @@
       <c r="M191" s="5" t="n"/>
       <c r="N191" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O191" s="5" t="inlineStr">
@@ -19429,7 +20045,11 @@
       <c r="AT191" s="5" t="n"/>
       <c r="AU191" s="5" t="n"/>
       <c r="AV191" s="5" t="n"/>
-      <c r="AW191" s="5" t="n"/>
+      <c r="AW191" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Mnoznik 1000000 hardkodowany (km2 tylko dla ukladu w metrach); brak parametru. Geometrie zbioru 1 nie sa sprawdzane jako punkty. DELETE na output gdy istnieje. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/DensityMap.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa DensityMap, zadanie densityMap. Inputy: 2 zbiory (1 = punkty, 2 = poligony referencyjne), output. Dla kazdego poligonu zbioru 2 liczy count(ST_Contains) punktow zbioru 1 i zapisuje pole 'density' = count/st_area*1000000.</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="41.4" customHeight="1" s="15">
       <c r="A192" s="5" t="n">
@@ -19485,12 +20105,12 @@
       <c r="M192" s="5" t="n"/>
       <c r="N192" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O192" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P192" s="5" t="n"/>
@@ -19526,7 +20146,11 @@
       <c r="AT192" s="5" t="n"/>
       <c r="AU192" s="5" t="n"/>
       <c r="AV192" s="5" t="n"/>
-      <c r="AW192" s="5" t="n"/>
+      <c r="AW192" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Zwracanie odleglosci: kod nie tworzy ani nie zapisuje pola z odlegloscia (tylko pole 'shape'). Warunek st_distance != 0 pomija obiekty o zerowej odleglosci. W WHERE uzyty T2.&lt;nazwa shape1&gt;, w ORDER BY T2.&lt;nazwa shape2&gt; - wymaga tych samych nazw pol geometrii. Opis w jgp mowi 'najblizszy obiekt zbioru 1 dla kazdego z obiektow zbioru 2', kod iteruje po zbiorze 1 i szuka w zbiorze 2 (odwrotnie). Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/FindeNextObject.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa FindeNextObject, zadanie findeNextObject (literowka; macierz: findNextObject). Inputy: 2 zbiory, output. Dla kazdego wiersza zbioru 1 wybiera z zbioru 2 najblizsza geometrie (ORDER BY st_distance LIMIT 1, z warunkiem st_distance != 0) i zapisuje ja w polu 'shape'.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="41.4" customHeight="1" s="15">
       <c r="A193" s="5" t="n">
@@ -19582,7 +20206,7 @@
       <c r="M193" s="5" t="n"/>
       <c r="N193" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O193" s="5" t="inlineStr">
@@ -19623,7 +20247,11 @@
       <c r="AT193" s="5" t="n"/>
       <c r="AU193" s="5" t="n"/>
       <c r="AV193" s="5" t="n"/>
-      <c r="AW193" s="5" t="n"/>
+      <c r="AW193" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. tolerance czytane przez job.getInt mimo typu Double (ulamki obcinane). Wynik jest wstawiany raz na kazdy wiersz wejscia (INSERT ... FROM wejscie) z cala kolekcja - mozliwe powielanie wyniku; nie testowano. Parametry filtra podzapytania ST_Union nie sa dodawane do params (ryzyko przy where/geometry). Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/VoronoiPolygons.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa VoronoiPolygons, zadanie voronoiPolygons. Inputy: 1 zbior, tolerance (Double), output. SQL: ST_CollectionExtract(ST_VoronoiPolygons((SELECT ST_Union(shape) FROM wejscie), tolerance),3) - poligony Woronoja z wierzcholkow zunifikowanej geometrii.</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="41.4" customHeight="1" s="15">
       <c r="A194" s="5" t="n">
@@ -19679,12 +20307,12 @@
       <c r="M194" s="5" t="n"/>
       <c r="N194" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O194" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P194" s="5" t="n"/>
@@ -19720,7 +20348,11 @@
       <c r="AT194" s="5" t="n"/>
       <c r="AU194" s="5" t="n"/>
       <c r="AV194" s="5" t="n"/>
-      <c r="AW194" s="5" t="n"/>
+      <c r="AW194" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'Mediana wspolrzednych': kod uzywa mediany geometrycznej st_geometricmedian (nie mediany osobno X i Y). Liczona per obiekt wejsciowy (funkcja na geometrii wiersza), nie jeden punkt dla calej warstwy. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/GeometricMedian.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa GeometricMedian, zadanie geometricMedian. Inputy: 1 zbior, output. Dla kazdego wiersza zapisuje punkt = st_geometricmedian(shape) (PostGIS) wraz z oid_input.</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="41.4" customHeight="1" s="15">
       <c r="A195" s="5" t="n">
@@ -19776,7 +20408,7 @@
       <c r="M195" s="5" t="n"/>
       <c r="N195" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O195" s="5" t="inlineStr">
@@ -19817,7 +20449,11 @@
       <c r="AT195" s="5" t="n"/>
       <c r="AU195" s="5" t="n"/>
       <c r="AV195" s="5" t="n"/>
-      <c r="AW195" s="5" t="n"/>
+      <c r="AW195" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wynik typu punktowego (pole shape jako point) - zakladane wejscie punktowe. cid dla szumu bedzie NULL (zachowanie PostGIS, nie weryfikowane w kodzie). Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/ClusterIdentification.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa ClusterIdentification, zadanie clusterIdentification. Inputy: 1 zbior, eps (Double), minpoints (Int), output. Zapisuje punkty z polem cid = st_ClusterDBSCAN(shape,eps,minpoints) OVER ().</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="41.4" customHeight="1" s="15">
       <c r="A196" s="5" t="n">
@@ -19873,7 +20509,7 @@
       <c r="M196" s="5" t="n"/>
       <c r="N196" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O196" s="5" t="inlineStr">
@@ -19914,7 +20550,11 @@
       <c r="AT196" s="5" t="n"/>
       <c r="AU196" s="5" t="n"/>
       <c r="AV196" s="5" t="n"/>
-      <c r="AW196" s="5" t="n"/>
+      <c r="AW196" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Brak sprawdzenia typu geometrii zbioru 1. DELETE na output gdy istnieje. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union); ponadto default/test.jgp (zestaw testowy) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Count.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa Count, zadanie count. Inputy: 2 zbiory (1 = pkt/lin, 2 = poligony), output. Dla kazdego poligonu zbioru 2 zapisuje pole 'count' = liczba obiektow zbioru 1 z st_relate(T2,T,'T*****FF*') (zawieranie).</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="41.4" customHeight="1" s="15">
       <c r="A197" s="5" t="n">
@@ -19970,7 +20610,7 @@
       <c r="M197" s="5" t="n"/>
       <c r="N197" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O197" s="5" t="inlineStr">
@@ -20011,7 +20651,11 @@
       <c r="AT197" s="5" t="n"/>
       <c r="AU197" s="5" t="n"/>
       <c r="AV197" s="5" t="n"/>
-      <c r="AW197" s="5" t="n"/>
+      <c r="AW197" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Uzywa pasma 1; kod nie sprawdza czy raster to DEM. DELETE na output gdy istnieje. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/HillShadeRaster.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa HillShadeRaster, zadanie hillShadeRaster. Inputy: 1 zbior, azimuth, altitude, max_bright, scale (Double), output. SQL: ST_HillShade(raster,1,'32BF',azimuth,altitude,max_bright,scale), wynik raster 32BF.</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="41.4" customHeight="1" s="15">
       <c r="A198" s="5" t="n">
@@ -20067,7 +20711,7 @@
       <c r="M198" s="5" t="n"/>
       <c r="N198" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O198" s="5" t="inlineStr">
@@ -20108,7 +20752,11 @@
       <c r="AT198" s="5" t="n"/>
       <c r="AU198" s="5" t="n"/>
       <c r="AV198" s="5" t="n"/>
-      <c r="AW198" s="5" t="n"/>
+      <c r="AW198" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Brak parametrow (jednostki, pasmo, skala) - domyslne PostGIS; nie sprawdza czy raster to DEM. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/SlopeRaster.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa SlopeRaster, zadanie slopeRaster. Inputy: 1 zbior, output (bez parametrow). SQL: ST_Slope(raster) dla kazdego wiersza.</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="41.4" customHeight="1" s="15">
       <c r="A199" s="5" t="n">
@@ -20164,7 +20812,7 @@
       <c r="M199" s="5" t="n"/>
       <c r="N199" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O199" s="5" t="inlineStr">
@@ -20205,7 +20853,11 @@
       <c r="AT199" s="5" t="n"/>
       <c r="AU199" s="5" t="n"/>
       <c r="AV199" s="5" t="n"/>
-      <c r="AW199" s="5" t="n"/>
+      <c r="AW199" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Brak parametru metody resamplingu (domyslne ST_Transform). Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/TransformRaster.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa TransformRaster, zadanie transformRaster. Inputy: 1 zbior, srid (Int), output. SQL: ST_Transform(raster, srid); tworzy raster wyjsciowy i pole ksztaltu w nowym SRID.</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="41.4" customHeight="1" s="15">
       <c r="A200" s="5" t="n">
@@ -20261,7 +20913,7 @@
       <c r="M200" s="5" t="n"/>
       <c r="N200" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O200" s="5" t="inlineStr">
@@ -20302,7 +20954,11 @@
       <c r="AT200" s="5" t="n"/>
       <c r="AU200" s="5" t="n"/>
       <c r="AV200" s="5" t="n"/>
-      <c r="AW200" s="5" t="n"/>
+      <c r="AW200" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Parametrem jest docelowa liczba pikseli (width/height), nie rozmiar piksela w jednostkach terenu. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/ResampleRaster.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa ResampleRaster, zadanie resampleRaster. Inputy: 1 zbior, width, height (Int - liczba pikseli), output. SQL: ST_Resample(raster,width,height).</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="41.4" customHeight="1" s="15">
       <c r="A201" s="5" t="n">
@@ -20358,12 +21014,12 @@
       <c r="M201" s="5" t="n"/>
       <c r="N201" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O201" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P201" s="5" t="n"/>
@@ -20399,7 +21055,11 @@
       <c r="AT201" s="5" t="n"/>
       <c r="AU201" s="5" t="n"/>
       <c r="AV201" s="5" t="n"/>
-      <c r="AW201" s="5" t="n"/>
+      <c r="AW201" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Przyciecie do bbox: brak parametru bbox; geometria tnaca pochodzi wylacznie z warstwy wejsciowej 2. Jest tez ClipRasterV2 (input clipper typu Geometry, ST_Clip z WKB), ale NIE jest zarejestrowana w zadnym .jgp. ClipRaster to iloczyn kartezjanski rastrow i geometrii. W ClipRaster exists[0] nigdy nie jest ustawiane na false (DELETE na swiezo utworzonej tabeli). Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/ClipRaster.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa ClipRaster, zadanie clipRaster. Inputy: 2 zbiory (1 = raster, 2 = geometrie tnace), output. SQL: ST_Clip(T.raster, T2.shape, true) dla kazdej pary (FROM s1, s2 bez warunku laczacego).</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="41.4" customHeight="1" s="15">
       <c r="A202" s="5" t="n">
@@ -20455,7 +21115,7 @@
       <c r="M202" s="5" t="n"/>
       <c r="N202" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O202" s="5" t="inlineStr">
@@ -20496,7 +21156,11 @@
       <c r="AT202" s="5" t="n"/>
       <c r="AU202" s="5" t="n"/>
       <c r="AV202" s="5" t="n"/>
-      <c r="AW202" s="5" t="n"/>
+      <c r="AW202" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. method to dowolny tekst przekazywany do st_union (walidacja po stronie PostGIS). Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterUnion.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa RasterUnion, zadanie rasterUnion. Inputy: 1 zbior, method (domyslnie SUM), output. SQL: st_union(raster, method) po wszystkich rastrach niepustych - jeden raster wynikowy.</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="55.2" customHeight="1" s="15">
       <c r="A203" s="5" t="n">
@@ -20552,7 +21216,7 @@
       <c r="M203" s="5" t="n"/>
       <c r="N203" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O203" s="5" t="inlineStr">
@@ -20593,7 +21257,11 @@
       <c r="AT203" s="5" t="n"/>
       <c r="AU203" s="5" t="n"/>
       <c r="AV203" s="5" t="n"/>
-      <c r="AW203" s="5" t="n"/>
+      <c r="AW203" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Hardkodowane: raster 100x100 pikseli i bufor 10 jednostek ukladu dla punktow/linii; brak parametrow. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterFromShape.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa RasterFromShape, zadanie rasterFromShape. Inputy: 1 zbior, output. SQL: st_asraster(shape,100,100); geometrie niepoligonowe najpierw st_buffer(shape,10).</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="55.2" customHeight="1" s="15">
       <c r="A204" s="5" t="n">
@@ -20649,7 +21317,7 @@
       <c r="M204" s="5" t="n"/>
       <c r="N204" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O204" s="5" t="inlineStr">
@@ -20690,7 +21358,11 @@
       <c r="AT204" s="5" t="n"/>
       <c r="AU204" s="5" t="n"/>
       <c r="AV204" s="5" t="n"/>
-      <c r="AW204" s="5" t="n"/>
+      <c r="AW204" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Raster wyjsciowy zawsze w EPSG 3857 (stala WEB_MERCATOR); waga z pola/wartosci (mapa ciepla). Tabela wynikowa nie jest czyszczona (brak DELETE). Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterFromFeatures.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa RasterFromFeatures, zadanie rasterFromFeatures. Inputy: 1 zbior (opcjonalny), weightField, weightValue, method (SUM), resolution, buffers (DoubleArray), output. Dla kazdego bufora: st_union(st_asraster(geom,resolution,-resolution,...,waga),method) do rastra w EPSG 3857.</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="55.2" customHeight="1" s="15">
       <c r="A205" s="5" t="n">
@@ -20746,7 +21418,7 @@
       <c r="M205" s="5" t="n"/>
       <c r="N205" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O205" s="5" t="inlineStr">
@@ -20787,7 +21459,11 @@
       <c r="AT205" s="5" t="n"/>
       <c r="AU205" s="5" t="n"/>
       <c r="AV205" s="5" t="n"/>
-      <c r="AW205" s="5" t="n"/>
+      <c r="AW205" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Poligonizacja na poziomie pojedynczych pikseli (bez scalania sasiadow o tej samej wartosci). Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterToPolygons.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa RasterToPolygons, zadanie rasterToPolygons (macierz: rasterToPolygon). Inputy: 1 zbior, output. Zapisuje poligon na piksel: ST_Multi((ST_PixelAsPolygons(raster)).geom) z polem value i org_oid.</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="55.2" customHeight="1" s="15">
       <c r="A206" s="5" t="n">
@@ -20843,7 +21519,7 @@
       <c r="M206" s="5" t="n"/>
       <c r="N206" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O206" s="5" t="inlineStr">
@@ -20884,7 +21560,11 @@
       <c r="AT206" s="5" t="n"/>
       <c r="AU206" s="5" t="n"/>
       <c r="AV206" s="5" t="n"/>
-      <c r="AW206" s="5" t="n"/>
+      <c r="AW206" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Brak pominiecia NoData w kodzie (zachowanie ST_PixelAsCentroids). Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterToPoints.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa RasterToPoints, zadanie rasterToPoints. Inputy: 1 zbior, output. Zapisuje punkt per piksel: (ST_PixelAsCentroids(raster)).geom z polem value i org_oid.</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="55.2" customHeight="1" s="15">
       <c r="A207" s="5" t="n">
@@ -20940,7 +21620,7 @@
       <c r="M207" s="5" t="n"/>
       <c r="N207" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O207" s="5" t="inlineStr">
@@ -20981,7 +21661,11 @@
       <c r="AT207" s="5" t="n"/>
       <c r="AU207" s="5" t="n"/>
       <c r="AV207" s="5" t="n"/>
-      <c r="AW207" s="5" t="n"/>
+      <c r="AW207" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Wlasciwy algorytm w Javie, nie w bazie; levels parsowane Double.parseDouble. Tylko pierwszy blok/pasmo (getBlocks(0,0,0,0,0,1)). Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterToIsolines.java; gp-imapserver-app/config/capap/analysis.jgp Dowód: Klasa RasterToIsolines, zadanie rasterToIsolines. Inputy: 1 zbior, levels (String, lista po przecinku), output. Wlasna implementacja (klasy Squares/Square, marching squares na pasmie 0 bloku) zapisuje polilinie z polem value.</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="55.2" customHeight="1" s="15">
       <c r="A208" s="5" t="n">
@@ -21037,12 +21721,12 @@
       <c r="M208" s="5" t="n"/>
       <c r="N208" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O208" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P208" s="5" t="n"/>
@@ -21078,7 +21762,11 @@
       <c r="AT208" s="5" t="n"/>
       <c r="AU208" s="5" t="n"/>
       <c r="AV208" s="5" t="n"/>
-      <c r="AW208" s="5" t="n"/>
+      <c r="AW208" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Std (odchylenie standardowe) i histogram: brak w obu klasach. Obie klasy liczą min, max, avg (sum/count) i wartosc w punkcie; ST_SummaryStats(...,false). Pliki: RasterStats.java i RasterToStats.java. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; brak w config/default (default/analysis.jgp ma tylko Buffer i Union) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterStats.java; gp-imapserver-app/config/capap/analysis.jgp; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/raster/RasterToStats.java Dowód: Dwa zadania: rasterStats (RasterStats: inputy x, y; outputy value, min, max, avg - ST_SummaryStats + ST_Value w punkcie) i rasterToStats (RasterToStats: input point, output tabela z polami shape, min, max, avg, val).</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="55.2" customHeight="1" s="15">
       <c r="A209" s="5" t="n">
@@ -21106,7 +21794,7 @@
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>Zasięg danych i obszary NoData.</t>
+          <t>Zadanie GP coverage (nie rastrowe): dla poligonów zbioru 1 liczy coverage_area i coverage_percent pokrycia przez zbiór 2 (opcjonalny bufor) oraz statystyki pól zbioru 2.</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
@@ -21134,12 +21822,12 @@
       <c r="M209" s="5" t="n"/>
       <c r="N209" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O209" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P209" s="5" t="n"/>
@@ -21175,7 +21863,11 @@
       <c r="AT209" s="5" t="n"/>
       <c r="AU209" s="5" t="n"/>
       <c r="AV209" s="5" t="n"/>
-      <c r="AW209" s="5" t="n"/>
+      <c r="AW209" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: sprzeczne. Niepotwierdzone w kodzie: Zasieg danych i obszary NoData: kod nie operuje na rastrach ani NoData. Nazwa 'Pokrycie terenu' zgadza sie z kodem tylko w sensie procentu pokrycia poligonu przez warstwe 2. Zadanie nie jest rastrowe. Jesli zbior 2 ma inny EPSG, jest st_transform. DELETE na output gdy istnieje. Rejestracja GP: analysis.jgp w profilach capap, gus, isok, sipww; dodatkowo isok/predefined.jgp (predefined3, predefined4 jako Coverage); brak w config/default Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/analysis/Coverage.java; gp-imapserver-app/config/isok/predefined.jgp Dowód: Klasa Coverage, zadanie coverage. Inputy: 2 zbiory, buffer, fields, stats, output. Wymaga poligonow w zbiorze 1; liczy coverage_area = st_area(st_intersection(poligon, st_union(zbior 2 z buforem))), coverage_percent i statystyki pol zbioru 2. To jest wektorowe pokrycie poligonow, nie raster. | Opis przed korektą: Zasięg danych i obszary NoData.</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="55.2" customHeight="1" s="15">
       <c r="A210" s="5" t="n">
@@ -21231,12 +21923,12 @@
       <c r="M210" s="5" t="n"/>
       <c r="N210" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O210" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P210" s="5" t="n"/>
@@ -21272,7 +21964,11 @@
       <c r="AT210" s="5" t="n"/>
       <c r="AU210" s="5" t="n"/>
       <c r="AV210" s="5" t="n"/>
-      <c r="AW210" s="5" t="n"/>
+      <c r="AW210" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Formaty GPKG i GDB: brak loaderow dla gpkg/gdb w LoadInputFile (createLoaders: csv, geojson, gml, kml, shp, zipshp, xlsx). GPKG obsluguje tylko CursorLoader (GeoPackageCursor) i GpkgImporter (nierejestrowany w .jgp), nie LoadInputFile. Tabela docelowa musi istniec (getTable). Rejestracja GP: dataManagement.jgp w profilu capap (rowniez ReloadInputFile); brak w config/default Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/LoadInputFile.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/TaskInputFile.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/BaseLoadInputFile.java Dowód: Klasa LoadInputFile (BaseLoadInputFile), zadanie loadInputFile. Inputy: file, format, database, schema, table, fieldMapping, charset, inSR, reverse. Loadery w TaskInputFile.createLoaders: csv, geojson, gml, kml, shp, zipshp, xlsx - laduje do istniejacej tabeli wg fieldMapping.</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="55.2" customHeight="1" s="15">
       <c r="A211" s="5" t="n">
@@ -21328,7 +22024,7 @@
       <c r="M211" s="5" t="n"/>
       <c r="N211" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O211" s="5" t="inlineStr">
@@ -21369,7 +22065,11 @@
       <c r="AT211" s="5" t="n"/>
       <c r="AU211" s="5" t="n"/>
       <c r="AV211" s="5" t="n"/>
-      <c r="AW211" s="5" t="n"/>
+      <c r="AW211" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Obslugiwane formaty jak w loaderach (csv, geojson, gml, kml, shp, zipshp, xlsx). Rejestracja GP: dataManagement.jgp w profilu capap; brak w config/default Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/AnalyzeInputFile.java; gp-imapserver-app/config/capap/dataManagement.jgp Dowód: Klasa AnalyzeInputFile, zadanie analyzeInputFile (setName). Inputy: file, format, count (opc.); output tableDef (JSON). Wywoluje loader.analyze(job, plik, count) i zwraca definicje tabeli, po czym kasuje plik lokalny.</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="55.2" customHeight="1" s="15">
       <c r="A212" s="5" t="n">
@@ -21425,7 +22125,7 @@
       <c r="M212" s="5" t="n"/>
       <c r="N212" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O212" s="5" t="inlineStr">
@@ -21466,7 +22166,11 @@
       <c r="AT212" s="5" t="n"/>
       <c r="AU212" s="5" t="n"/>
       <c r="AV212" s="5" t="n"/>
-      <c r="AW212" s="5" t="n"/>
+      <c r="AW212" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Dla istniejacej tabeli wykonuje table.change(tableDef) (modyfikacja struktury), nie tylko tworzenie. Rejestracja GP: dataManagement.jgp w profilu capap (tez wariant CreateTableSafe); brak w config/default Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/CreateTable.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/BaseCreateTable.java; gp-imapserver-app/config/capap/dataManagement.jgp Dowód: Klasa CreateTable (BaseCreateTable), zadanie createTable. Inputy: database, schema, table, alias, sourceId, tableDef (JSON), schemaRoles. Tworzy schemat jesli brak, tworzy tabele wg tableDef (domyslny oid, indeksy geometrii) albo zmienia istniejaca (table.change).</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="55.2" customHeight="1" s="15">
       <c r="A213" s="5" t="n">
@@ -21522,7 +22226,7 @@
       <c r="M213" s="5" t="n"/>
       <c r="N213" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O213" s="5" t="inlineStr">
@@ -21563,7 +22267,11 @@
       <c r="AT213" s="5" t="n"/>
       <c r="AU213" s="5" t="n"/>
       <c r="AV213" s="5" t="n"/>
-      <c r="AW213" s="5" t="n"/>
+      <c r="AW213" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Operacja destrukcyjna z CASCADE (PgDatabase). Dla Oracle dropSchemaSql rzuca NotImplementedException (OraDatabase). Brak schematu = tylko ostrzezenie. Rejestracja GP: dataManagement.jgp w profilu capap; brak w config/default Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/DropSchema.java; gp-imapserver-gdb/src/main/java/pl/gispartner/imapserver/gdb/postgre/PgDatabase.java; gp-imapserver-app/config/capap/dataManagement.jgp Dowód: Klasa DropSchema, zadanie dropSchema (setName). Inputy: database, schema. Wywoluje schema.drop(): usuwa metadane i dla PostgreSQL wykonuje 'drop schema ... cascade'.</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="55.2" customHeight="1" s="15">
       <c r="A214" s="5" t="n">
@@ -21619,7 +22327,7 @@
       <c r="M214" s="5" t="n"/>
       <c r="N214" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O214" s="5" t="inlineStr">
@@ -21660,7 +22368,11 @@
       <c r="AT214" s="5" t="n"/>
       <c r="AU214" s="5" t="n"/>
       <c r="AV214" s="5" t="n"/>
-      <c r="AW214" s="5" t="n"/>
+      <c r="AW214" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Operacja destrukcyjna; semantyki argumentow drop(true,true) nie sprawdzano. Rejestracja GP: dataManagement.jgp w profilu capap; brak w config/default Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/DropTable.java; gp-imapserver-app/config/capap/dataManagement.jgp Dowód: Klasa DropTable, zadanie dropTable (setName). Inputy: database, schema, table. Wykonuje table.drop(true, true); brak schematu lub tabeli to tylko ostrzezenie.</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="55.2" customHeight="1" s="15">
       <c r="A215" s="5" t="n">
@@ -21716,7 +22428,7 @@
       <c r="M215" s="5" t="n"/>
       <c r="N215" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O215" s="5" t="inlineStr">
@@ -21757,7 +22469,11 @@
       <c r="AT215" s="5" t="n"/>
       <c r="AU215" s="5" t="n"/>
       <c r="AV215" s="5" t="n"/>
-      <c r="AW215" s="5" t="n"/>
+      <c r="AW215" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. W riip/sipww zarejestrowane jako 'query' w dataManagement (jawne name). Istnieje tez wariant CursorQuery w default/query.jgp. Rejestracja GP: dataManagement.jgp w profilach capap, gs, riip, sipww; brak w config/default Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/Query.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/BaseQuery.java; gp-imapserver-app/config/capap/dataManagement.jgp Dowód: Klasa Query (BaseQuery/GpCursorTask), zadanie query. Inputy: table, shape, outFields, outExpressions, outStatistics, returnGeometry, where, geometry, spatialRel, orderByFields, outSR i in.; format (json, geojson, shp, kml, gml, dxf, xlsx, csv, sqlite, gpkg, pbf, obj, glb); outputy file, size, count.</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="55.2" customHeight="1" s="15">
       <c r="A216" s="5" t="n">
@@ -21785,7 +22501,7 @@
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>Mozaika z zestawu rastrów.</t>
+          <t>Mozaika z zestawu rastrów: klasa CreateMosaic (wywołuje table.createMosaic), ale zadanie nie jest zarejestrowane w żadnym pliku .jgp (niedostępne przez GP).</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
@@ -21813,12 +22529,12 @@
       <c r="M216" s="5" t="n"/>
       <c r="N216" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O216" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P216" s="5" t="n"/>
@@ -21854,7 +22570,11 @@
       <c r="AT216" s="5" t="n"/>
       <c r="AU216" s="5" t="n"/>
       <c r="AV216" s="5" t="n"/>
-      <c r="AW216" s="5" t="n"/>
+      <c r="AW216" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: nieaktywne. Bez wpisu w .jgp zadanie nie jest dostepne przez GP. Wszystkie pixels[i] dostaja te sama glebokosc z jednego stringa. Funkcje mozaiki w REST (FieldGp) uzywaja innych klas (AddFolder, BuildOverviews, RemoveOverviews, Clip). Rejestracja GP: brak rejestracji w .jgp (wystepuje tylko jako klasa; szukano CreateMosaic/createMosaic w java/kt/jgp/json/xml/properties) Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/mosaic/CreateMosaic.java Dowód: Klasa CreateMosaic, zadanie createMosaic (z nazwy klasy). Inputy: table, field, epsg, prefix, bands, pixels; run wywoluje table.createMosaic(field, epsg, null, prefix, pixels). Kod aktywny, ale zadanie nie jest zarejestrowane. | Opis przed korektą: Mozaika z zestawu rastrów.</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="55.2" customHeight="1" s="15">
       <c r="A217" s="5" t="n">
@@ -21910,7 +22630,7 @@
       <c r="M217" s="5" t="n"/>
       <c r="N217" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O217" s="5" t="inlineStr">
@@ -21951,7 +22671,11 @@
       <c r="AT217" s="5" t="n"/>
       <c r="AU217" s="5" t="n"/>
       <c r="AV217" s="5" t="n"/>
-      <c r="AW217" s="5" t="n"/>
+      <c r="AW217" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Obslugiwane typy pikseli tylko U8 i F32 (inne = GpException). Wymaga plikow props.json/paths.json w podanym katalogu. Rejestracja GP: riip (dataManagement.jgp: importMosaic), sipww (dataManagement.jgp: importMosaic; mosaic.jgp: import); brak w config/default Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/mosaic/ImportMosaic.java; gp-imapserver-app/config/sipww/mosaic.jgp; gp-imapserver-app/config/riip/dataManagement.jgp Dowód: Klasa ImportMosaic, zadanie importMosaic (w sipww/mosaic.jgp pod nazwa 'import'). Inputy: table, field (opc.), path. Czyta props.json (spatialReference, extent, bands, root) i paths.json z katalogu na serwerze, tworzy tabele/pole mozaiki i wpisy (MinPS, MaxPS, Path, shape).</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="55.2" customHeight="1" s="15">
       <c r="A218" s="5" t="n">
@@ -22007,12 +22731,12 @@
       <c r="M218" s="5" t="n"/>
       <c r="N218" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O218" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P218" s="5" t="n"/>
@@ -22048,7 +22772,11 @@
       <c r="AT218" s="5" t="n"/>
       <c r="AU218" s="5" t="n"/>
       <c r="AV218" s="5" t="n"/>
-      <c r="AW218" s="5" t="n"/>
+      <c r="AW218" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Wsadowe ladowanie przez kursory DB: CursorLoader tylko otwiera plik jako kursor (bez zapisu do bazy, bez przetwarzania wsadowego). Zapis do bazy robi inne zadanie (CursorImport w ext/gp-imapserver-gs, rejestracja w gs). Shapefile czytany z kodowaniem ISO_8859_1 (hardkod). Rejestracja GP: dataManagement.jgp w profilu gs; brak w config/default Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/CursorLoader.java; gp-imapserver-app/config/gs/dataManagement.jgp Dowód: Klasa CursorLoader, zadanie cursorLoader. Input file (File), output cursor. Otwiera plik jako kursor wg rozszerzenia: shp, esrijson, gpkg, geojson/json, gpx, kml, kmz, gml.</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="55.2" customHeight="1" s="15">
       <c r="A219" s="5" t="n">
@@ -22104,12 +22832,12 @@
       <c r="M219" s="5" t="n"/>
       <c r="N219" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O219" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P219" s="5" t="n"/>
@@ -22145,7 +22873,11 @@
       <c r="AT219" s="5" t="n"/>
       <c r="AU219" s="5" t="n"/>
       <c r="AV219" s="5" t="n"/>
-      <c r="AW219" s="5" t="n"/>
+      <c r="AW219" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Konwersja 'przez kursory DB': wejsciem jest Cursor z innego zadania (np. CursorLoader), nie kursor bazy danych. W gs/dataManagement.jgp CursorConverter jest zarejestrowany dwukrotnie bez jawnej nazwy (ta sama nazwa cursorConverter - kolizja nazw, zachowanie nieweryfikowane). Rejestracja GP: dataManagement.jgp w profilach gs, riip; brak w config/default Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/CursorConverter.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/dataManagement/GpCursorTask.java; gp-imapserver-app/config/riip/dataManagement.jgp Dowód: Klasa CursorConverter (GpCursorTask), zadanie cursorConverter. Inputy: name (opc.), cursor (Cursor), format (json, pjson, geojson, geojsonzip, shp, kml, gml, dxf, xlsx, csv, sqlite, gpkg, pbf, obj, glb) i opcje serializacji; outputy file, size, count. Serializuje kursor do pliku.</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="55.2" customHeight="1" s="15">
       <c r="A220" s="5" t="n">
@@ -22173,7 +22905,7 @@
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Pakiet kafli wektorowych (.vtpk).</t>
+          <t>Zadanie GP MapCreatorFromVtpk: tworzy mapę z istniejącego pakietu .vtpk (import). Generowania pakietu VTPK nie znaleziono.</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
@@ -22201,12 +22933,12 @@
       <c r="M220" s="5" t="n"/>
       <c r="N220" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O220" s="5" t="inlineStr">
         <is>
-          <t>potwierdzone</t>
+          <t>do weryfikacji</t>
         </is>
       </c>
       <c r="P220" s="5" t="n"/>
@@ -22242,7 +22974,11 @@
       <c r="AT220" s="5" t="n"/>
       <c r="AU220" s="5" t="n"/>
       <c r="AV220" s="5" t="n"/>
-      <c r="AW220" s="5" t="n"/>
+      <c r="AW220" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: sprzeczne. Niepotwierdzone w kodzie: Generowanie pakietu kafli wektorowych .vtpk: nie znaleziono; kod robi odwrotnie (tworzy mape z VTPK). Szukano fraz: vtpk (bez rozrozniania wielkosci liter) w *.java/*.kt - jedyny plik MapCreatorFromVtpk; vtpkCreate. Wniosek: w iMS jest import VTPK, a nie generator; nie wykluczam generatora pod inna nazwa bez frazy 'vtpk'. Rejestracja GP: MapCreatorFromVtpk: default/vectorTiles.jgp (config/default); zadanie generujace VTPK: brak rejestracji w .jgp Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/vectorTiles/MapCreatorFromVtpk.java; gp-imapserver-app/config/default/vectorTiles.jgp Dowód: Jedyna klasa z VTPK to MapCreatorFromVtpk (setName 'MapCreatorFromVtpk'): wejscie file (VTPK), mapName, storage; tworzy mape z istniejacego pakietu .vtpk (import), a nie generuje pakiet. Zadania vtpkCreate w kodzie brak. | Opis przed korektą: Pakiet kafli wektorowych (.vtpk).</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="55.2" customHeight="1" s="15">
       <c r="A221" s="5" t="n">
@@ -22298,7 +23034,7 @@
       <c r="M221" s="5" t="n"/>
       <c r="N221" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O221" s="5" t="inlineStr">
@@ -22339,7 +23075,11 @@
       <c r="AT221" s="5" t="n"/>
       <c r="AU221" s="5" t="n"/>
       <c r="AV221" s="5" t="n"/>
-      <c r="AW221" s="5" t="n"/>
+      <c r="AW221" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Dostepne tylko w profilu orlen. Nazwa zadania ustalona z GpTask.nameFromClass (pierwsza litera malą) - nie widzialem setName w PackageSLPK ani PreparePackage. Rejestracja GP: tylko profil orlen (orlen/package.jgp: Package, PackageFromPointScene, Packer, PackageSLPK, MapCreatorFromSlpk, Repair3DObjects); brak w config/default Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/scenes/PackageSLPK.java; gp-imapserver-app/config/orlen/package.jgp Dowód: Klasa PackageSLPK (PreparePackage), zadanie packageSLPK (nazwa z klasy, bez setName; macierz: slpkCreate). Inputy m.in. sourceScenePath, drawingInfo, dracoGeometry, min/maxQuantizationBits, min/maxCompressionLevel, geometryOptions, resourcesFolder. Buduje package.slpk (zip, SLPKBuilder) ze sceny 3D. Jest tez MapCreatorFromSlpk (import SLPK do mapy).</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="55.2" customHeight="1" s="15">
       <c r="A222" s="5" t="n">
@@ -22395,7 +23135,7 @@
       <c r="M222" s="5" t="n"/>
       <c r="N222" s="5" t="inlineStr">
         <is>
-          <t>kod (rejestr zadań GP)</t>
+          <t>kod (rejestr zadań GP); kod</t>
         </is>
       </c>
       <c r="O222" s="5" t="inlineStr">
@@ -22436,10 +23176,1332 @@
       <c r="AT222" s="5" t="n"/>
       <c r="AU222" s="5" t="n"/>
       <c r="AV222" s="5" t="n"/>
-      <c r="AW222" s="5" t="n"/>
+      <c r="AW222" s="5" t="inlineStr">
+        <is>
+          <t>Weryfikacja kodu 2026-10-16: potwierdzone. Nazwy z macierzy 'lrs*' nie odpowiadaja kodowi. Osobnego zadania 'pomiar' nie ma (miara M jest wyliczana w calibrate/update). BatchGeocode w tym pakiecie nie jest w LRS .jgp (uzywany z REST FieldGp). Rejestracja GP: default/linearReferenceSystem.jgp (config/default) oraz wir/linearReferenceSystem.jgp Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/linearReferenceSystem/CalibrateLinearReference.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/linearReferenceSystem/UpdateEvents.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/linearReferenceSystem/OverlayRouteEvents.java Dowód: Pakiet linearReferenceSystem, 5 zadan z setName: calibrateLinearReference (kalibracja LRS punktami referencyjnymi), updateLinearReference (uzupelnianie NaN M), updateEvents (najblizsza linia, M, offset, angle dla zdarzen punktowych), overlayRouteEvents (przeciecie zdarzen po miarach), changeGeometryType.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>IMS-2.2.05</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>Usługi i standardy</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>Standardy OGC</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>WPS (Web Processing Service)</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>Kontroler WPS (GetCapabilities, DescribeProcess, Execute, GetStatus, GetResult) udostepniajacy zadania GP jako standardowe procesy OGC WPS. Potwierdzone w kodzie: WpsController (gp-imapserver-rest-gp).</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr">
+        <is>
+          <t>Zewnetrzne systemy GIS (QGIS, klienci OGC) moga uruchamiac geoprzetwarzanie iMapServera przez standardowy protokol WPS, bez znajomosci wewnetrznego API.</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>standard OGC</t>
+        </is>
+      </c>
+      <c r="I223" s="5" t="inlineStr">
+        <is>
+          <t>WPS</t>
+        </is>
+      </c>
+      <c r="J223" s="5" t="n"/>
+      <c r="K223" s="5" t="n"/>
+      <c r="L223" s="5" t="n"/>
+      <c r="M223" s="5" t="n"/>
+      <c r="N223" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O223" s="5" t="inlineStr">
+        <is>
+          <t>potwierdzone</t>
+        </is>
+      </c>
+      <c r="P223" s="5" t="n"/>
+      <c r="Q223" s="5" t="n"/>
+      <c r="R223" s="5" t="n"/>
+      <c r="S223" s="5" t="n"/>
+      <c r="T223" s="5" t="n"/>
+      <c r="U223" s="5" t="n"/>
+      <c r="V223" s="5" t="n"/>
+      <c r="W223" s="5" t="n"/>
+      <c r="X223" s="5" t="n"/>
+      <c r="Y223" s="5" t="n"/>
+      <c r="Z223" s="5" t="n"/>
+      <c r="AA223" s="5" t="n"/>
+      <c r="AB223" s="5" t="n"/>
+      <c r="AC223" s="5" t="n"/>
+      <c r="AD223" s="5" t="n"/>
+      <c r="AE223" s="5" t="n"/>
+      <c r="AF223" s="5" t="n"/>
+      <c r="AG223" s="5" t="n"/>
+      <c r="AH223" s="5" t="n"/>
+      <c r="AI223" s="5" t="n"/>
+      <c r="AJ223" s="5" t="n"/>
+      <c r="AK223" s="5" t="n"/>
+      <c r="AL223" s="5" t="n"/>
+      <c r="AM223" s="5" t="n"/>
+      <c r="AN223" s="5" t="n"/>
+      <c r="AO223" s="5" t="n"/>
+      <c r="AP223" s="5" t="n"/>
+      <c r="AQ223" s="5" t="n"/>
+      <c r="AR223" s="5" t="n"/>
+      <c r="AS223" s="5" t="n"/>
+      <c r="AT223" s="5" t="n"/>
+      <c r="AU223" s="5" t="n"/>
+      <c r="AV223" s="5" t="n"/>
+      <c r="AW223" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: potwierdzone. Wszystkie 5 operacji potwierdzone w obu trybach (GET KVP i POST XML). Brak operacji Dismiss. Kod aktywny, bez @Conditional. Pliki: gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/ogc/wps/controller/WpsController.java; gp-imapserver-rest-gp/src/main/java/pl/gispartner/imapserver/rest/gp/ogc/wps/service/WpsXmlService.java; gp-imapserver-app/src/main/resources/application.properties Dowód: WpsController (@RestController, /gp/{serv}/wps i /gp/{serv}/{task}/wps) obsluguje GET i POST XML dla GetCapabilities, DescribeProcess, Execute, GetStatus, GetResult (oraz /results); wersja pl.gispartner.imapserver.wps.version=2.0.0 wymuszana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>IMS-3.3.13</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>API i integracja</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>iMapServer REST API</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>SOAP API (legacy)</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint SOAP /soap/table (gp-imapserver-soap) z sześcioma operacjami na tabelach; nie jest to SOAP-owy dostęp do wszystkich usług serwera.</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="inlineStr">
+        <is>
+          <t>Zachowanie kompatybilnosci ze starszymi integracjami klienckimi, ktore nie zostaly jeszcze zmigrowane na REST/JSON.</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="inlineStr">
+        <is>
+          <t>usługa</t>
+        </is>
+      </c>
+      <c r="I224" s="5" t="inlineStr">
+        <is>
+          <t>SOAP</t>
+        </is>
+      </c>
+      <c r="J224" s="5" t="n"/>
+      <c r="K224" s="5" t="n"/>
+      <c r="L224" s="5" t="n"/>
+      <c r="M224" s="5" t="n"/>
+      <c r="N224" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O224" s="5" t="inlineStr">
+        <is>
+          <t>do weryfikacji</t>
+        </is>
+      </c>
+      <c r="P224" s="5" t="n"/>
+      <c r="Q224" s="5" t="n"/>
+      <c r="R224" s="5" t="n"/>
+      <c r="S224" s="5" t="n"/>
+      <c r="T224" s="5" t="n"/>
+      <c r="U224" s="5" t="n"/>
+      <c r="V224" s="5" t="n"/>
+      <c r="W224" s="5" t="n"/>
+      <c r="X224" s="5" t="n"/>
+      <c r="Y224" s="5" t="n"/>
+      <c r="Z224" s="5" t="n"/>
+      <c r="AA224" s="5" t="n"/>
+      <c r="AB224" s="5" t="n"/>
+      <c r="AC224" s="5" t="n"/>
+      <c r="AD224" s="5" t="n"/>
+      <c r="AE224" s="5" t="n"/>
+      <c r="AF224" s="5" t="n"/>
+      <c r="AG224" s="5" t="n"/>
+      <c r="AH224" s="5" t="n"/>
+      <c r="AI224" s="5" t="n"/>
+      <c r="AJ224" s="5" t="n"/>
+      <c r="AK224" s="5" t="n"/>
+      <c r="AL224" s="5" t="n"/>
+      <c r="AM224" s="5" t="n"/>
+      <c r="AN224" s="5" t="n"/>
+      <c r="AO224" s="5" t="n"/>
+      <c r="AP224" s="5" t="n"/>
+      <c r="AQ224" s="5" t="n"/>
+      <c r="AR224" s="5" t="n"/>
+      <c r="AS224" s="5" t="n"/>
+      <c r="AT224" s="5" t="n"/>
+      <c r="AU224" s="5" t="n"/>
+      <c r="AV224" s="5" t="n"/>
+      <c r="AW224" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: 'dostep do uslug serwera' - SOAP obejmuje tylko operacje na tabelach (jeden endpoint /soap/table), nie mapy/GP/bazy. Dodatkowo AgsCatalogServletTest (test) sugeruje SOAP kompatybilny z ArcGIS Catalog - tylko w testach, nie weryfikowano w main. Moduly ext (gs, gs-int, teryt, nkwpobierz) tez zalezne od excludeAllSoap. Pliki: gp-imapserver-soap/src/main/java/pl/gispartner/imapserver/soap/config/SoapConfig.java; gp-imapserver-soap/src/main/java/pl/gispartner/imapserver/soap/endpoint/TableSoapEndpoint.java; settings.gradle Dowód: SoapConfig rejestruje CXFServlet pod /soap/* i endpoint /table (TableSoapEndpoint) z operacjami GetTableStructure, QueryFeatures, AddFeatures, UpdateFeatures, DeleteFeatures, ApplyEdits; modul wlaczony w buildzie (settings.gradle: if (!excludeAllSoap), gradle.properties excludeAllSoap=false; app/build.gradle compile project(':gp-imapserver-soap')).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>IMS-3.1.14</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>API i integracja</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>Natywne API Map (iMapServer)</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>Etykietowanie (labeling) w kompozycji mapowej</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>Etykiety obiektów definiowane w kompozycji mapowej (.mex), z konfigurowalną liczbą miejsc po przecinku. Locale w etykietach to domyślne locale JVM, nie ustawienie z kompozycji.</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t>Mapa wyswietla czytelne etykiety (np. nazwy, wartosci liczbowe) sformatowane zgodnie z lokalnymi konwencjami - bez dodatkowej konfiguracji po stronie klienta.</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>funkcja silnika</t>
+        </is>
+      </c>
+      <c r="I225" s="5" t="n"/>
+      <c r="J225" s="5" t="n"/>
+      <c r="K225" s="5" t="n"/>
+      <c r="L225" s="5" t="n"/>
+      <c r="M225" s="5" t="n"/>
+      <c r="N225" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O225" s="5" t="inlineStr">
+        <is>
+          <t>do weryfikacji</t>
+        </is>
+      </c>
+      <c r="P225" s="5" t="n"/>
+      <c r="Q225" s="5" t="n"/>
+      <c r="R225" s="5" t="n"/>
+      <c r="S225" s="5" t="n"/>
+      <c r="T225" s="5" t="n"/>
+      <c r="U225" s="5" t="n"/>
+      <c r="V225" s="5" t="n"/>
+      <c r="W225" s="5" t="n"/>
+      <c r="X225" s="5" t="n"/>
+      <c r="Y225" s="5" t="n"/>
+      <c r="Z225" s="5" t="n"/>
+      <c r="AA225" s="5" t="n"/>
+      <c r="AB225" s="5" t="n"/>
+      <c r="AC225" s="5" t="n"/>
+      <c r="AD225" s="5" t="n"/>
+      <c r="AE225" s="5" t="n"/>
+      <c r="AF225" s="5" t="n"/>
+      <c r="AG225" s="5" t="n"/>
+      <c r="AH225" s="5" t="n"/>
+      <c r="AI225" s="5" t="n"/>
+      <c r="AJ225" s="5" t="n"/>
+      <c r="AK225" s="5" t="n"/>
+      <c r="AL225" s="5" t="n"/>
+      <c r="AM225" s="5" t="n"/>
+      <c r="AN225" s="5" t="n"/>
+      <c r="AO225" s="5" t="n"/>
+      <c r="AP225" s="5" t="n"/>
+      <c r="AQ225" s="5" t="n"/>
+      <c r="AR225" s="5" t="n"/>
+      <c r="AS225" s="5" t="n"/>
+      <c r="AT225" s="5" t="n"/>
+      <c r="AU225" s="5" t="n"/>
+      <c r="AV225" s="5" t="n"/>
+      <c r="AW225" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: obsluga ustawien regionalnych (locale) w etykietach - FeatureLayer.formatLabelText uzywa DecimalFormat.getInstance() (domyslne locale JVM), a StringUtil.formatDecimal(decimalPlaces,num) Locale.getDefault(); brak locale zdefiniowanego w kompozycji (.mex). Format .mex potwierdzony tylko posrednio (MexSerializer, endpoint {map}/mex); sam plik z etykietami nie byl czytany. Liczba miejsc po przecinku - potwierdzona. Pliki: gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/drawing/LabelClass.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/FeatureLayer.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/json/def/LayerSerializer.java Dowód: Etykiety: Layer ma labelingInfo/showLabels (ladowane przez LabelingLoaders, serializowane w json/def/LayerSerializer i MexSerializer); LabelClass.getFractionDigitsNumber/defFractionDigitsNumber (z pola 'fractionDigitsNumber' w LabelingLoaders linia 406); FeatureLayer.formatLabelText ustawia min/max fraction digits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>IMS-4.12.04</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>Geoprzetwarzanie</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>Zadania GP – Java GP (LRS/3D)</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="inlineStr">
+        <is>
+          <t>TERYT - pobieranie katalogów SIMC/TERC/ULIC</t>
+        </is>
+      </c>
+      <c r="F226" s="5" t="inlineStr">
+        <is>
+          <t>Zadania GP createSIMC, createTERC, createULIC pobierają katalogi z usługi SOAP TERYT (GUS) i zapisują je do tabeli. Domyślny endpoint w Teryt.java to środowisko testowe (uslugaterytws1test.stat.gov.pl) z użytkownikiem TestPubliczny. Moduł ext/gp-imapserver-teryt; zadania nie są zarejestrowane w żadnym .jgp ani w extensions.ext.</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="inlineStr">
+        <is>
+          <t>Automatyczna aktualizacja podzialu terytorialnego (miejscowosci, gminy, ulice) wprost z rejestru GUS, bez recznego wgrywania plikow TERYT.</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="inlineStr">
+        <is>
+          <t>zadanie GP</t>
+        </is>
+      </c>
+      <c r="I226" s="5" t="n"/>
+      <c r="J226" s="5" t="n"/>
+      <c r="K226" s="5" t="n"/>
+      <c r="L226" s="5" t="n"/>
+      <c r="M226" s="5" t="n"/>
+      <c r="N226" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O226" s="5" t="inlineStr">
+        <is>
+          <t>do weryfikacji</t>
+        </is>
+      </c>
+      <c r="P226" s="5" t="n"/>
+      <c r="Q226" s="5" t="n"/>
+      <c r="R226" s="5" t="n"/>
+      <c r="S226" s="5" t="n"/>
+      <c r="T226" s="5" t="n"/>
+      <c r="U226" s="5" t="n"/>
+      <c r="V226" s="5" t="n"/>
+      <c r="W226" s="5" t="n"/>
+      <c r="X226" s="5" t="n"/>
+      <c r="Y226" s="5" t="n"/>
+      <c r="Z226" s="5" t="n"/>
+      <c r="AA226" s="5" t="n"/>
+      <c r="AB226" s="5" t="n"/>
+      <c r="AC226" s="5" t="n"/>
+      <c r="AD226" s="5" t="n"/>
+      <c r="AE226" s="5" t="n"/>
+      <c r="AF226" s="5" t="n"/>
+      <c r="AG226" s="5" t="n"/>
+      <c r="AH226" s="5" t="n"/>
+      <c r="AI226" s="5" t="n"/>
+      <c r="AJ226" s="5" t="n"/>
+      <c r="AK226" s="5" t="n"/>
+      <c r="AL226" s="5" t="n"/>
+      <c r="AM226" s="5" t="n"/>
+      <c r="AN226" s="5" t="n"/>
+      <c r="AO226" s="5" t="n"/>
+      <c r="AP226" s="5" t="n"/>
+      <c r="AQ226" s="5" t="n"/>
+      <c r="AR226" s="5" t="n"/>
+      <c r="AS226" s="5" t="n"/>
+      <c r="AT226" s="5" t="n"/>
+      <c r="AU226" s="5" t="n"/>
+      <c r="AV226" s="5" t="n"/>
+      <c r="AW226" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: UpdateTeryt 'pobierajace dane z uslugi GUS' - sprzeczne: UpdateTeryt wysyla zmiany do uslugi (metody AktualizujUliceEMUiA i AktualizujPunktAdresowyEMUiA, pola PlacUlica/PunktAdresowy z tabel viewTable/editTable), nie pobiera katalogow; host uslugaterytws1.stat.gov.pl - domyslny soapEndpointUrl w Teryt.java to https://uslugaterytws1test.stat.gov.pl/TerytWs1.svc (srodowisko testowe) z domyslnym uzytkownikiem TestPubliczny; rejestracja zadan (jgp) - zadne z 4 zadan nie jest zarejestrowane w zadnym pliku .jgp w repo; modul nie jest w zaleznosciach gp-imapserver-app ani w config/*/extensions.ext. Modul jest w settings.gradle (warunkowo, !excludeAllSoap) jako osobny jar rozszerzenia - dostepnosc zalezy od wdrozenia poza repo. RYZYKO: SoapUtil wylacza weryfikacje certyfikatow i hostname (TrustingSSLSocketFactory, setHostnameVerifier -&gt; true); domyslne poswiadczenia TestPubliczny/1234abcd w kodzie. W CreateTERC sprawdzenie licznosci jest zakomentowane (recCount=0). Pliki: ext/gp-imapserver-teryt/src/main/java/pl/gispartner/imapserver/teryt/CreateSIMC.java; ext/gp-imapserver-teryt/src/main/java/pl/gispartner/imapserver/teryt/CreateTERC.java; ext/gp-imapserver-teryt/src/main/java/pl/gispartner/imapserver/teryt/CreateULIC.java Dowód: CreateSIMC/CreateTERC/CreateULIC (setName createSIMC/createTERC/createULIC) wolaja SOAP TERYT (PobierzKatalogSIMC/TERC/ULIC, plus LicznoscJednostek) przez SoapUtil i zapisuja wiersze do tabeli (CreateTeryt.prepareTable/call).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>IMS-4.12.05</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>Geoprzetwarzanie</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>Zadania GP – Java GP (LRS/3D)</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="inlineStr">
+        <is>
+          <t>TERYT - wysyłanie zmian (updateTeryt)</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>Zadanie GP updateTeryt wysyła zmiany (ulice, punkty adresowe) do usługi TERYT/GUS (metody AktualizujUliceEMUiA, AktualizujPunktAdresowyEMUiA); nie pobiera katalogów. Moduł ext/gp-imapserver-teryt.</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="inlineStr">
+        <is>
+          <t>Automatyczna aktualizacja podzialu terytorialnego (miejscowosci, gminy, ulice) wprost z rejestru GUS, bez recznego wgrywania plikow TERYT.</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="inlineStr">
+        <is>
+          <t>zadanie GP</t>
+        </is>
+      </c>
+      <c r="I227" s="5" t="n"/>
+      <c r="J227" s="5" t="n"/>
+      <c r="K227" s="5" t="n"/>
+      <c r="L227" s="5" t="n"/>
+      <c r="M227" s="5" t="n"/>
+      <c r="N227" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O227" s="5" t="inlineStr">
+        <is>
+          <t>do weryfikacji</t>
+        </is>
+      </c>
+      <c r="P227" s="5" t="n"/>
+      <c r="Q227" s="5" t="n"/>
+      <c r="R227" s="5" t="n"/>
+      <c r="S227" s="5" t="n"/>
+      <c r="T227" s="5" t="n"/>
+      <c r="U227" s="5" t="n"/>
+      <c r="V227" s="5" t="n"/>
+      <c r="W227" s="5" t="n"/>
+      <c r="X227" s="5" t="n"/>
+      <c r="Y227" s="5" t="n"/>
+      <c r="Z227" s="5" t="n"/>
+      <c r="AA227" s="5" t="n"/>
+      <c r="AB227" s="5" t="n"/>
+      <c r="AC227" s="5" t="n"/>
+      <c r="AD227" s="5" t="n"/>
+      <c r="AE227" s="5" t="n"/>
+      <c r="AF227" s="5" t="n"/>
+      <c r="AG227" s="5" t="n"/>
+      <c r="AH227" s="5" t="n"/>
+      <c r="AI227" s="5" t="n"/>
+      <c r="AJ227" s="5" t="n"/>
+      <c r="AK227" s="5" t="n"/>
+      <c r="AL227" s="5" t="n"/>
+      <c r="AM227" s="5" t="n"/>
+      <c r="AN227" s="5" t="n"/>
+      <c r="AO227" s="5" t="n"/>
+      <c r="AP227" s="5" t="n"/>
+      <c r="AQ227" s="5" t="n"/>
+      <c r="AR227" s="5" t="n"/>
+      <c r="AS227" s="5" t="n"/>
+      <c r="AT227" s="5" t="n"/>
+      <c r="AU227" s="5" t="n"/>
+      <c r="AV227" s="5" t="n"/>
+      <c r="AW227" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: UpdateTeryt 'pobierajace dane z uslugi GUS' - sprzeczne: UpdateTeryt wysyla zmiany do uslugi (metody AktualizujUliceEMUiA i AktualizujPunktAdresowyEMUiA, pola PlacUlica/PunktAdresowy z tabel viewTable/editTable), nie pobiera katalogow; host uslugaterytws1.stat.gov.pl - domyslny soapEndpointUrl w Teryt.java to https://uslugaterytws1test.stat.gov.pl/TerytWs1.svc (srodowisko testowe) z domyslnym uzytkownikiem TestPubliczny; rejestracja zadan (jgp) - zadne z 4 zadan nie jest zarejestrowane w zadnym pliku .jgp w repo; modul nie jest w zaleznosciach gp-imapserver-app ani w config/*/extensions.ext. Modul jest w settings.gradle (warunkowo, !excludeAllSoap) jako osobny jar rozszerzenia - dostepnosc zalezy od wdrozenia poza repo. RYZYKO: SoapUtil wylacza weryfikacje certyfikatow i hostname (TrustingSSLSocketFactory, setHostnameVerifier -&gt; true); domyslne poswiadczenia TestPubliczny/1234abcd w kodzie. W CreateTERC sprawdzenie licznosci jest zakomentowane (recCount=0). Pliki: ext/gp-imapserver-teryt/src/main/java/pl/gispartner/imapserver/teryt/CreateSIMC.java; ext/gp-imapserver-teryt/src/main/java/pl/gispartner/imapserver/teryt/CreateTERC.java; ext/gp-imapserver-teryt/src/main/java/pl/gispartner/imapserver/teryt/CreateULIC.java Dowód: CreateSIMC/CreateTERC/CreateULIC (setName createSIMC/createTERC/createULIC) wolaja SOAP TERYT (PobierzKatalogSIMC/TERC/ULIC, plus LicznoscJednostek) przez SoapUtil i zapisuja wiersze do tabeli (CreateTeryt.prepareTable/call).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" s="5" t="inlineStr">
+        <is>
+          <t>IMS-4.12.06</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t>Geoprzetwarzanie</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>Zadania GP – Java GP (LRS/3D)</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="inlineStr">
+        <is>
+          <t>Pobieranie treści księgi wieczystej (NKW)</t>
+        </is>
+      </c>
+      <c r="F228" s="5" t="inlineStr">
+        <is>
+          <t>Zadanie GP (NkwPobierzTask) pobierajace tresc ksiegi wieczystej (PDF/HTML/XML) po numerze ksiegi z uslugi SOAP GUGiK ZSIN. Potwierdzone w kodzie: modul ext/gp-imapserver-nkwpobierz.</t>
+        </is>
+      </c>
+      <c r="G228" s="5" t="inlineStr">
+        <is>
+          <t>Mozliwosc pobrania tresci ksiegi wieczystej bezposrednio z poziomu iMapServera (np. w powiazaniu z dzialka na mapie), bez przechodzenia do zewnetrznego portalu.</t>
+        </is>
+      </c>
+      <c r="H228" s="5" t="inlineStr">
+        <is>
+          <t>zadanie GP</t>
+        </is>
+      </c>
+      <c r="I228" s="5" t="n"/>
+      <c r="J228" s="5" t="n"/>
+      <c r="K228" s="5" t="n"/>
+      <c r="L228" s="5" t="n"/>
+      <c r="M228" s="5" t="n"/>
+      <c r="N228" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O228" s="5" t="inlineStr">
+        <is>
+          <t>potwierdzone</t>
+        </is>
+      </c>
+      <c r="P228" s="5" t="n"/>
+      <c r="Q228" s="5" t="n"/>
+      <c r="R228" s="5" t="n"/>
+      <c r="S228" s="5" t="n"/>
+      <c r="T228" s="5" t="n"/>
+      <c r="U228" s="5" t="n"/>
+      <c r="V228" s="5" t="n"/>
+      <c r="W228" s="5" t="n"/>
+      <c r="X228" s="5" t="n"/>
+      <c r="Y228" s="5" t="n"/>
+      <c r="Z228" s="5" t="n"/>
+      <c r="AA228" s="5" t="n"/>
+      <c r="AB228" s="5" t="n"/>
+      <c r="AC228" s="5" t="n"/>
+      <c r="AD228" s="5" t="n"/>
+      <c r="AE228" s="5" t="n"/>
+      <c r="AF228" s="5" t="n"/>
+      <c r="AG228" s="5" t="n"/>
+      <c r="AH228" s="5" t="n"/>
+      <c r="AI228" s="5" t="n"/>
+      <c r="AJ228" s="5" t="n"/>
+      <c r="AK228" s="5" t="n"/>
+      <c r="AL228" s="5" t="n"/>
+      <c r="AM228" s="5" t="n"/>
+      <c r="AN228" s="5" t="n"/>
+      <c r="AO228" s="5" t="n"/>
+      <c r="AP228" s="5" t="n"/>
+      <c r="AQ228" s="5" t="n"/>
+      <c r="AR228" s="5" t="n"/>
+      <c r="AS228" s="5" t="n"/>
+      <c r="AT228" s="5" t="n"/>
+      <c r="AU228" s="5" t="n"/>
+      <c r="AV228" s="5" t="n"/>
+      <c r="AW228" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: potwierdzone. Kod dodatkowo obsluguje format JSON (konwersja XML-&gt;JSON lokalnie, XmlMapper), poza opisem. Modul jest zaleznoscia gp-imapserver-app tylko gdy nie ustawiono excludeAllSoap. RYZYKO: w config/default/nkwpobierz.jgp sa na stale wpisane username (KAS_Test) i haslo w postaci jawnej. Brak walidacji formatu null (format.equals). Pliki: ext/gp-imapserver-nkwpobierz/src/main/java/pl/gispartner/imapserver/gs/gp/NkwPobierzTask.java; ext/gp-imapserver-nkwpobierz/src/main/java/pl/gispartner/imapserver/gs/gp/nkwpobierz/NkwPobierzClient.java; ext/gp-imapserver-nkwpobierz/src/main/java/pl/gov/gugik/zsin/nkw/pobierz/NkwFormat.java Dowód: NkwPobierzTask: inputy numerKsiegi i format, output file; dla PDF/HTML/XML wola NkwPobierzClient.pobierzTrescWZadanymFormacie (SOAP INkw/PobierzTrescWZadanymFormacie, NkwFormat HTML/XML/PDF) i zapisuje plik KW.pdf/KW.html/KW.xml; zarejestrowane w default/nkwpobierz.jgp (service https://esb.zsin.gugik.gov.pl/ZSIN/Nkw/service).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>IMS-4.12.07</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>Geoprzetwarzanie</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>Zadania GP – Java GP (LRS/3D)</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="inlineStr">
+        <is>
+          <t>Synchronizacja z EMUiA</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>Zadanie GP Synchronize (EMUIA) ma pustą metodę run(). Faktyczna synchronizacja z PRG działa jako push z handlerów MscHandler, PktHandler, UlcHandler, aktywnych w config/emuia.</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="inlineStr">
+        <is>
+          <t>Docelowo: automatyczna wymiana danych adresowych z krajowa Ewidencja Miejscowosci, Ulic i Adresow bez recznego importu.</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="inlineStr">
+        <is>
+          <t>zadanie GP</t>
+        </is>
+      </c>
+      <c r="I229" s="5" t="n"/>
+      <c r="J229" s="5" t="n"/>
+      <c r="K229" s="5" t="n"/>
+      <c r="L229" s="5" t="n"/>
+      <c r="M229" s="5" t="n"/>
+      <c r="N229" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O229" s="5" t="inlineStr">
+        <is>
+          <t>do weryfikacji</t>
+        </is>
+      </c>
+      <c r="P229" s="5" t="n"/>
+      <c r="Q229" s="5" t="n"/>
+      <c r="R229" s="5" t="n"/>
+      <c r="S229" s="5" t="n"/>
+      <c r="T229" s="5" t="n"/>
+      <c r="U229" s="5" t="n"/>
+      <c r="V229" s="5" t="n"/>
+      <c r="W229" s="5" t="n"/>
+      <c r="X229" s="5" t="n"/>
+      <c r="Y229" s="5" t="n"/>
+      <c r="Z229" s="5" t="n"/>
+      <c r="AA229" s="5" t="n"/>
+      <c r="AB229" s="5" t="n"/>
+      <c r="AC229" s="5" t="n"/>
+      <c r="AD229" s="5" t="n"/>
+      <c r="AE229" s="5" t="n"/>
+      <c r="AF229" s="5" t="n"/>
+      <c r="AG229" s="5" t="n"/>
+      <c r="AH229" s="5" t="n"/>
+      <c r="AI229" s="5" t="n"/>
+      <c r="AJ229" s="5" t="n"/>
+      <c r="AK229" s="5" t="n"/>
+      <c r="AL229" s="5" t="n"/>
+      <c r="AM229" s="5" t="n"/>
+      <c r="AN229" s="5" t="n"/>
+      <c r="AO229" s="5" t="n"/>
+      <c r="AP229" s="5" t="n"/>
+      <c r="AQ229" s="5" t="n"/>
+      <c r="AR229" s="5" t="n"/>
+      <c r="AS229" s="5" t="n"/>
+      <c r="AT229" s="5" t="n"/>
+      <c r="AU229" s="5" t="n"/>
+      <c r="AV229" s="5" t="n"/>
+      <c r="AW229" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: dzialajaca synchronizacja przez zadanie GP Synchronize - zadanie jest puste (nieaktywne); 'komunikaty MSC/PKT/ULC' jako czesc zadania Synchronize - realizowane sa przez handlery zdarzen edycji tabel, niezalezne od Synchronize. Synchronizacja EMUiA/PRG realnie dziala (o ile zaladowano rozszerzenie) jako push przy edycji/commicie, a nie jako zadanie Synchronize. Rozszerzenie aktywne tylko w config/emuia (extensions.ext + application.properties); nie jest w zaleznosciach gp-imapserver-app. RYZYKO: w config/emuia/application.properties sa jawne hasla (prg.pass, emuia.pas) oraz klucze prywatne w katalogu config/emuia. Pliki: ext/gp-imapserver-emuia/src/main/java/pl/gispartner/imapserver/emuia/Synchronize.java; gp-imapserver-app/config/emuia/emuia.jgp; ext/gp-imapserver-emuia/src/main/java/pl/gispartner/imapserver/emuia/MscHandler.java Dowód: Synchronize.run(Job) ma pusta tresc (potwierdza zastrzezenie z opisu); zadanie jest zarejestrowane w config/emuia/emuia.jgp. Natomiast MscHandler/PktHandler/UlcHandler (@Component, TableEditEvents/TableCommitEvents) przy edycji tabel miejscowosci/ulic/punktow (emuia.imap.*) wysylaja operacje ups/del do uslugi PRG przez Prg (RestTemplate, token url, prg.url z application.properties).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>IMS-1.1.06</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>Wdrożenie i licencjonowanie</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>Wdrożenie i licencjonowanie</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="inlineStr">
+        <is>
+          <t>Klastrowanie i propagacja zdarzeń (CAPAP/Kafka)</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>Modul gp-imapserver-capap propaguje zdarzenia zmian zasobow (mapy, uslugi GP, bazy, domeny, pola, aplikacje, media) do zewnetrznego systemu przez Kafka; aktywne tylko gdy skonfigurowany parametr cluster.host. Potwierdzone w kodzie: CapapTaskEvents i pakiet capap.kafka.</t>
+        </is>
+      </c>
+      <c r="G230" s="5" t="inlineStr">
+        <is>
+          <t>W srodowisku wieloinstancyjnym (klaster) zmiany wprowadzone na jednej instancji moga byc automatycznie propagowane do pozostalych, bez recznej synchronizacji konfiguracji.</t>
+        </is>
+      </c>
+      <c r="H230" s="5" t="inlineStr">
+        <is>
+          <t>moduł</t>
+        </is>
+      </c>
+      <c r="I230" s="5" t="n"/>
+      <c r="J230" s="5" t="n"/>
+      <c r="K230" s="5" t="n"/>
+      <c r="L230" s="5" t="n"/>
+      <c r="M230" s="5" t="n"/>
+      <c r="N230" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O230" s="5" t="inlineStr">
+        <is>
+          <t>potwierdzone</t>
+        </is>
+      </c>
+      <c r="P230" s="5" t="n"/>
+      <c r="Q230" s="5" t="n"/>
+      <c r="R230" s="5" t="n"/>
+      <c r="S230" s="5" t="n"/>
+      <c r="T230" s="5" t="n"/>
+      <c r="U230" s="5" t="n"/>
+      <c r="V230" s="5" t="n"/>
+      <c r="W230" s="5" t="n"/>
+      <c r="X230" s="5" t="n"/>
+      <c r="Y230" s="5" t="n"/>
+      <c r="Z230" s="5" t="n"/>
+      <c r="AA230" s="5" t="n"/>
+      <c r="AB230" s="5" t="n"/>
+      <c r="AC230" s="5" t="n"/>
+      <c r="AD230" s="5" t="n"/>
+      <c r="AE230" s="5" t="n"/>
+      <c r="AF230" s="5" t="n"/>
+      <c r="AG230" s="5" t="n"/>
+      <c r="AH230" s="5" t="n"/>
+      <c r="AI230" s="5" t="n"/>
+      <c r="AJ230" s="5" t="n"/>
+      <c r="AK230" s="5" t="n"/>
+      <c r="AL230" s="5" t="n"/>
+      <c r="AM230" s="5" t="n"/>
+      <c r="AN230" s="5" t="n"/>
+      <c r="AO230" s="5" t="n"/>
+      <c r="AP230" s="5" t="n"/>
+      <c r="AQ230" s="5" t="n"/>
+      <c r="AR230" s="5" t="n"/>
+      <c r="AS230" s="5" t="n"/>
+      <c r="AT230" s="5" t="n"/>
+      <c r="AU230" s="5" t="n"/>
+      <c r="AV230" s="5" t="n"/>
+      <c r="AW230" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: potwierdzone. W application.properties cluster.host i cluster.topic sa ZAKOMENTOWANE (l.499-500), wiec domyslnie modul jest nieaktywny - zgodnie z opisem 'tylko gdy skonfigurowany'. Opis mowi 'do zewnetrznego systemu', a AbstractMessageConsumer wskazuje tez konsumpcje (propagacja miedzy instancjami). Nie sprawdzalem szczegolow Messages.send i konfiguracji brokera. Pliki: gp-imapserver-capap/src/main/java/pl/gispartner/imapserver/capap/gp/CapapTaskEvents.java; gp-imapserver-capap/src/main/java/pl/gispartner/imapserver/capap/kafka/Messages.java; gp-imapserver-capap/src/main/java/pl/gispartner/imapserver/capap/carto/CapapMapEvents.java Dowód: Klasy CapapTaskEvents, CapapMapEvents, CapapSceneEvents, AppMapEvents, CapapMediaEvents, ClusterSchedulerEvents oraz kafka/*Message (Database, Domain, Field, GpService, Map, Media, App, Scheduler, Schema, Sequence, Table, Task) maja @ConditionalOnProperty("pl.gispartner.imapserver.cluster.host") i wysylaja/odbieraja komunikaty CREATED/CHANGED/DELETED/REFRESH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>IMS-2.1.10</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>Usługi i standardy</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>Typy usług (Service Types)</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>Atlas - kompozycje wydruku map</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>Modul gp-imapserver-page/rest-page (klasy Atlas, AtlasController, PageController, elementy Grid/Frame/Legend/Map/Marker) - szablonowe kompozycje wydruku z legenda, siatka wspolrzednych, ramkami i elementami graficznymi; eksport do PDF, obrazu i EPS.</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="inlineStr">
+        <is>
+          <t>Uzytkownik moze wygenerowac gotowy do druku wielostronicowy atlas mapowy (np. z siatka ukladu, legenda, ramka) bez recznego skladania w zewnetrznym programie graficznym.</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="inlineStr">
+        <is>
+          <t>usługa</t>
+        </is>
+      </c>
+      <c r="I231" s="5" t="n"/>
+      <c r="J231" s="5" t="n"/>
+      <c r="K231" s="5" t="n"/>
+      <c r="L231" s="5" t="n"/>
+      <c r="M231" s="5" t="n"/>
+      <c r="N231" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O231" s="5" t="inlineStr">
+        <is>
+          <t>potwierdzone</t>
+        </is>
+      </c>
+      <c r="P231" s="5" t="n"/>
+      <c r="Q231" s="5" t="n"/>
+      <c r="R231" s="5" t="n"/>
+      <c r="S231" s="5" t="n"/>
+      <c r="T231" s="5" t="n"/>
+      <c r="U231" s="5" t="n"/>
+      <c r="V231" s="5" t="n"/>
+      <c r="W231" s="5" t="n"/>
+      <c r="X231" s="5" t="n"/>
+      <c r="Y231" s="5" t="n"/>
+      <c r="Z231" s="5" t="n"/>
+      <c r="AA231" s="5" t="n"/>
+      <c r="AB231" s="5" t="n"/>
+      <c r="AC231" s="5" t="n"/>
+      <c r="AD231" s="5" t="n"/>
+      <c r="AE231" s="5" t="n"/>
+      <c r="AF231" s="5" t="n"/>
+      <c r="AG231" s="5" t="n"/>
+      <c r="AH231" s="5" t="n"/>
+      <c r="AI231" s="5" t="n"/>
+      <c r="AJ231" s="5" t="n"/>
+      <c r="AK231" s="5" t="n"/>
+      <c r="AL231" s="5" t="n"/>
+      <c r="AM231" s="5" t="n"/>
+      <c r="AN231" s="5" t="n"/>
+      <c r="AO231" s="5" t="n"/>
+      <c r="AP231" s="5" t="n"/>
+      <c r="AQ231" s="5" t="n"/>
+      <c r="AR231" s="5" t="n"/>
+      <c r="AS231" s="5" t="n"/>
+      <c r="AT231" s="5" t="n"/>
+      <c r="AU231" s="5" t="n"/>
+      <c r="AV231" s="5" t="n"/>
+      <c r="AW231" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: Format obrazu inny niz PNG (gałąź domyślna to ImageDisplay.white, w eksporcie atlasu jawnie "png"). AtlasController i PageController to klasy bazowe bez mapowan (mapowania w AtlasesController/PagesController). Opis wymienia 'rest-page' i klasy poprawnie. Modul page/rest-page nie jest wprost w gp-imapserver-app/build.gradle, tylko tranzytywnie (rest-gp -&gt; rest-page). Pliki: gp-imapserver-page/src/main/java/pl/gispartner/imapserver/page/Atlas.java; gp-imapserver-rest-page/src/main/java/pl/gispartner/imapserver/rest/page/PagesController.java; gp-imapserver-rest-page/src/main/java/pl/gispartner/imapserver/rest/page/AtlasesController.java Dowód: Moduly page i rest-page w settings.gradle (wciagane tranzytywnie przez rest-gp i gp); klasy Atlas, Atlases, elementy Frame, Grid (GridFrame/Label/Tick), LegendElement, MapElement, MarkerElement, ScaleBarElement, TextElement, ImageElement; PagesController.display() tworzy PdfDisplay, EpsDisplay lub ImageDisplay; endpointy pages/{page}/export i atlases/{atlas}/export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
+        <is>
+          <t>IMS-7.1.10</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>Administracja</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>iMapServer Manager (WebGUI)</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="inlineStr">
+        <is>
+          <t>Katalog usług (Service Directory)</t>
+        </is>
+      </c>
+      <c r="F232" s="5" t="inlineStr">
+        <is>
+          <t>Przegladanie hierarchii zasobow i punktow koncowych REST API przez interfejs HTML.</t>
+        </is>
+      </c>
+      <c r="G232" s="5" t="inlineStr">
+        <is>
+          <t>Umozliwia szybkie zorientowanie sie, jakie uslugi i endpointy sa dostepne na serwerze, bez koniecznosci przegladania dokumentacji API.</t>
+        </is>
+      </c>
+      <c r="H232" s="5" t="inlineStr">
+        <is>
+          <t>funkcja administracyjna</t>
+        </is>
+      </c>
+      <c r="I232" s="5" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="J232" s="5" t="n"/>
+      <c r="K232" s="5" t="n"/>
+      <c r="L232" s="5" t="n"/>
+      <c r="M232" s="5" t="n"/>
+      <c r="N232" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O232" s="5" t="inlineStr">
+        <is>
+          <t>potwierdzone</t>
+        </is>
+      </c>
+      <c r="P232" s="5" t="n"/>
+      <c r="Q232" s="5" t="n"/>
+      <c r="R232" s="5" t="n"/>
+      <c r="S232" s="5" t="n"/>
+      <c r="T232" s="5" t="n"/>
+      <c r="U232" s="5" t="n"/>
+      <c r="V232" s="5" t="n"/>
+      <c r="W232" s="5" t="n"/>
+      <c r="X232" s="5" t="n"/>
+      <c r="Y232" s="5" t="n"/>
+      <c r="Z232" s="5" t="n"/>
+      <c r="AA232" s="5" t="n"/>
+      <c r="AB232" s="5" t="n"/>
+      <c r="AC232" s="5" t="n"/>
+      <c r="AD232" s="5" t="n"/>
+      <c r="AE232" s="5" t="n"/>
+      <c r="AF232" s="5" t="n"/>
+      <c r="AG232" s="5" t="n"/>
+      <c r="AH232" s="5" t="n"/>
+      <c r="AI232" s="5" t="n"/>
+      <c r="AJ232" s="5" t="n"/>
+      <c r="AK232" s="5" t="n"/>
+      <c r="AL232" s="5" t="n"/>
+      <c r="AM232" s="5" t="n"/>
+      <c r="AN232" s="5" t="n"/>
+      <c r="AO232" s="5" t="n"/>
+      <c r="AP232" s="5" t="n"/>
+      <c r="AQ232" s="5" t="n"/>
+      <c r="AR232" s="5" t="n"/>
+      <c r="AS232" s="5" t="n"/>
+      <c r="AT232" s="5" t="n"/>
+      <c r="AU232" s="5" t="n"/>
+      <c r="AV232" s="5" t="n"/>
+      <c r="AW232" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: potwierdzone. Nie czytalem plikow JSP; hierarchie wnioskuje z Breadcrumbs w kontrolerach. Nazwa 'Service Directory' nie wystepuje jako klasa. Pliki: gp-imapserver-rest/src/main/java/pl/gispartner/imapserver/rest/RootController.java; gp-imapserver-rest-carto/src/main/java/pl/gispartner/imapserver/rest/carto/ags/MapServer.java Dowód: RootController (produces text/html) zwraca widok 'root' z Breadcrumbs; kazdy kontroler REST ma warianty produces text/html (np. MapServer.java l.173) renderujace JSP z nawigacja hierarchii zasobow; dostepne tez ins, ins/{ins}, debug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>IMS-7.1.11</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>Administracja</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>iMapServer Manager (WebGUI)</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="inlineStr">
+        <is>
+          <t>Zarządzanie plikami i folderami serwera</t>
+        </is>
+      </c>
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>Upload, pobieranie i usuwanie plików na serwerze przez REST (/folders). Powiązania plików z kompozycjami map i konfiguracjami GP nie potwierdzono w kodzie.</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="inlineStr">
+        <is>
+          <t>Administrator moze zarzadzac plikami konfiguracyjnymi serwera bezposrednio przez przegladarke, bez dostepu do systemu plikow serwera.</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="inlineStr">
+        <is>
+          <t>funkcja administracyjna</t>
+        </is>
+      </c>
+      <c r="I233" s="5" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="J233" s="5" t="n"/>
+      <c r="K233" s="5" t="n"/>
+      <c r="L233" s="5" t="n"/>
+      <c r="M233" s="5" t="n"/>
+      <c r="N233" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O233" s="5" t="inlineStr">
+        <is>
+          <t>do weryfikacji</t>
+        </is>
+      </c>
+      <c r="P233" s="5" t="n"/>
+      <c r="Q233" s="5" t="n"/>
+      <c r="R233" s="5" t="n"/>
+      <c r="S233" s="5" t="n"/>
+      <c r="T233" s="5" t="n"/>
+      <c r="U233" s="5" t="n"/>
+      <c r="V233" s="5" t="n"/>
+      <c r="W233" s="5" t="n"/>
+      <c r="X233" s="5" t="n"/>
+      <c r="Y233" s="5" t="n"/>
+      <c r="Z233" s="5" t="n"/>
+      <c r="AA233" s="5" t="n"/>
+      <c r="AB233" s="5" t="n"/>
+      <c r="AC233" s="5" t="n"/>
+      <c r="AD233" s="5" t="n"/>
+      <c r="AE233" s="5" t="n"/>
+      <c r="AF233" s="5" t="n"/>
+      <c r="AG233" s="5" t="n"/>
+      <c r="AH233" s="5" t="n"/>
+      <c r="AI233" s="5" t="n"/>
+      <c r="AJ233" s="5" t="n"/>
+      <c r="AK233" s="5" t="n"/>
+      <c r="AL233" s="5" t="n"/>
+      <c r="AM233" s="5" t="n"/>
+      <c r="AN233" s="5" t="n"/>
+      <c r="AO233" s="5" t="n"/>
+      <c r="AP233" s="5" t="n"/>
+      <c r="AQ233" s="5" t="n"/>
+      <c r="AR233" s="5" t="n"/>
+      <c r="AS233" s="5" t="n"/>
+      <c r="AT233" s="5" t="n"/>
+      <c r="AU233" s="5" t="n"/>
+      <c r="AV233" s="5" t="n"/>
+      <c r="AW233" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Ze to sa 'kompozycje mapowe, konfiguracje GP' - nie znaleziono powiazania FolderController z katalogami config/mapami; folders to ogolny magazyn plikow z konfiguracji FolderConfig (zrodlo definicji nie sprawdzone). Zarzadzanie plikami (upload/download/delete/append) potwierdzone; zakres 'jakie pliki' nie. Front Managera to webjar pl.gispartner.webjars:ims-manager (imsmanager_version=1.20.39 w gradle.properties) - jego kodu nie ma w repo, wiec warstwa UI nie jest weryfikowalna; potwierdzona jest tylko strona serwerowa. Pliki: gp-imapserver-rest-folder/src/main/java/pl/gispartner/imapserver/rest/folder/FolderController.java; gp-imapserver-rest-folder/src/main/java/pl/gispartner/imapserver/rest/folder/Folder.java; gp-imapserver-app/src/main/resources/application.properties Dowód: FolderController (ROOT 'folders'): create, {folder}/addFile, addEmptyFile, append, download, delete, remove, privileges, addFolder; role z application.properties (pl.gispartner.imapserver.properties.folder.{folderRoles,downloadRoles,addFileRoles,addFolderRoles,deleteFolderRoles,deleteFileRoles}=admin).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="B234" s="5" t="inlineStr">
+        <is>
+          <t>IMS-7.1.12</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="inlineStr">
+        <is>
+          <t>Administracja</t>
+        </is>
+      </c>
+      <c r="D234" s="5" t="inlineStr">
+        <is>
+          <t>iMapServer Manager (WebGUI)</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="inlineStr">
+        <is>
+          <t>Biblioteka mediów (symbole, kolory, rampy, fonty)</t>
+        </is>
+      </c>
+      <c r="F234" s="5" t="inlineStr">
+        <is>
+          <t>Moduł gp-imapserver-media to biblioteka symboli, kolorów, ramp i fontów. Zdjęcia i dokumenty powiązane z obiektami obsługuje osobny mechanizm Attachments (gp-imapserver-rest-gdb).</t>
+        </is>
+      </c>
+      <c r="G234" s="5" t="inlineStr">
+        <is>
+          <t>Biblioteka symboli, kolorów i fontów do kompozycji map oraz osobny mechanizm załączników do obiektów.</t>
+        </is>
+      </c>
+      <c r="H234" s="5" t="inlineStr">
+        <is>
+          <t>moduł</t>
+        </is>
+      </c>
+      <c r="I234" s="5" t="n"/>
+      <c r="J234" s="5" t="n"/>
+      <c r="K234" s="5" t="n"/>
+      <c r="L234" s="5" t="n"/>
+      <c r="M234" s="5" t="n"/>
+      <c r="N234" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O234" s="5" t="inlineStr">
+        <is>
+          <t>do weryfikacji</t>
+        </is>
+      </c>
+      <c r="P234" s="5" t="n"/>
+      <c r="Q234" s="5" t="n"/>
+      <c r="R234" s="5" t="n"/>
+      <c r="S234" s="5" t="n"/>
+      <c r="T234" s="5" t="n"/>
+      <c r="U234" s="5" t="n"/>
+      <c r="V234" s="5" t="n"/>
+      <c r="W234" s="5" t="n"/>
+      <c r="X234" s="5" t="n"/>
+      <c r="Y234" s="5" t="n"/>
+      <c r="Z234" s="5" t="n"/>
+      <c r="AA234" s="5" t="n"/>
+      <c r="AB234" s="5" t="n"/>
+      <c r="AC234" s="5" t="n"/>
+      <c r="AD234" s="5" t="n"/>
+      <c r="AE234" s="5" t="n"/>
+      <c r="AF234" s="5" t="n"/>
+      <c r="AG234" s="5" t="n"/>
+      <c r="AH234" s="5" t="n"/>
+      <c r="AI234" s="5" t="n"/>
+      <c r="AJ234" s="5" t="n"/>
+      <c r="AK234" s="5" t="n"/>
+      <c r="AL234" s="5" t="n"/>
+      <c r="AM234" s="5" t="n"/>
+      <c r="AN234" s="5" t="n"/>
+      <c r="AO234" s="5" t="n"/>
+      <c r="AP234" s="5" t="n"/>
+      <c r="AQ234" s="5" t="n"/>
+      <c r="AR234" s="5" t="n"/>
+      <c r="AS234" s="5" t="n"/>
+      <c r="AT234" s="5" t="n"/>
+      <c r="AU234" s="5" t="n"/>
+      <c r="AV234" s="5" t="n"/>
+      <c r="AW234" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: czesciowo. Niepotwierdzone w kodzie: Modul 'media' nie obsluguje zdjec/dokumentow powiazanych z obiektami przestrzennymi - to robi mechanizm attachments w rest-gdb, nie gp-imapserver-media. Opis macierzy myli dwa mechanizmy: 'media' w iMS to symbole/kolory/rampy/fonty. Pliki powiazane z obiektami = Attachments (RowController, Attachment/HistoricAttachment w gdb). Nie sprawdzono usuwania zalacznikow i panelu w Managerze. Front Managera to webjar pl.gispartner.webjars:ims-manager (imsmanager_version=1.20.39 w gradle.properties) - jego kodu nie ma w repo, wiec warstwa UI nie jest weryfikowalna; potwierdzona jest tylko strona serwerowa. Pliki: gp-imapserver-media/src/main/java/pl/gispartner/imapserver/rest/MediaController.java; gp-imapserver-carto/src/main/java/pl/gispartner/imapserver/carto/media/MediaType.java; gp-imapserver-rest-gdb/src/main/java/pl/gispartner/imapserver/rest/gdb/RowController.java Dowód: Modul gp-imapserver-media (MediaController, /media) zarzadza biblioteka zasobow kartograficznych: MediaType = color, ramp, marker, line, fill, text + fonty (media/{type}/add, items/{name}/delete, font/*). Zalaczniki powiazane z obiektami to osobny mechanizm w rest-gdb: RowController {oid}/attachments, addAttachment (MultipartFile), thumbnail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
+        <is>
+          <t>IMS-5.3.12</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="inlineStr">
+        <is>
+          <t>Dane i formaty</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>Formaty wyjściowe</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>Format PDF: eksport mapy (MapServer, formaty pdf/eps/svg) oraz konwersje i raporty GP (PdfTo*, Ims2, Atlas*Export).</t>
+        </is>
+      </c>
+      <c r="G235" s="5" t="inlineStr">
+        <is>
+          <t>Gotowe raporty PDF do wydruku lub przekazania klientowi bez dodatkowej obrobki w innym programie.</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="inlineStr">
+        <is>
+          <t>format</t>
+        </is>
+      </c>
+      <c r="I235" s="5" t="n"/>
+      <c r="J235" s="5" t="n"/>
+      <c r="K235" s="5" t="n"/>
+      <c r="L235" s="5" t="n"/>
+      <c r="M235" s="5" t="n"/>
+      <c r="N235" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O235" s="5" t="inlineStr">
+        <is>
+          <t>potwierdzone</t>
+        </is>
+      </c>
+      <c r="P235" s="5" t="n"/>
+      <c r="Q235" s="5" t="n"/>
+      <c r="R235" s="5" t="n"/>
+      <c r="S235" s="5" t="n"/>
+      <c r="T235" s="5" t="n"/>
+      <c r="U235" s="5" t="n"/>
+      <c r="V235" s="5" t="n"/>
+      <c r="W235" s="5" t="n"/>
+      <c r="X235" s="5" t="n"/>
+      <c r="Y235" s="5" t="n"/>
+      <c r="Z235" s="5" t="n"/>
+      <c r="AA235" s="5" t="n"/>
+      <c r="AB235" s="5" t="n"/>
+      <c r="AC235" s="5" t="n"/>
+      <c r="AD235" s="5" t="n"/>
+      <c r="AE235" s="5" t="n"/>
+      <c r="AF235" s="5" t="n"/>
+      <c r="AG235" s="5" t="n"/>
+      <c r="AH235" s="5" t="n"/>
+      <c r="AI235" s="5" t="n"/>
+      <c r="AJ235" s="5" t="n"/>
+      <c r="AK235" s="5" t="n"/>
+      <c r="AL235" s="5" t="n"/>
+      <c r="AM235" s="5" t="n"/>
+      <c r="AN235" s="5" t="n"/>
+      <c r="AO235" s="5" t="n"/>
+      <c r="AP235" s="5" t="n"/>
+      <c r="AQ235" s="5" t="n"/>
+      <c r="AR235" s="5" t="n"/>
+      <c r="AS235" s="5" t="n"/>
+      <c r="AT235" s="5" t="n"/>
+      <c r="AU235" s="5" t="n"/>
+      <c r="AV235" s="5" t="n"/>
+      <c r="AW235" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: potwierdzone. Niepotwierdzone w kodzie: Raporty (tasks/reports/Ims2) - 'format' jest przekazywany jako dowolny string do zewnetrznej uslugi raportowej (HttpPost na url z konfiguracji, np. config/default/reports.jgp -&gt; localhost:8082/imapserver/report/template/createIms5); PDF jako wynik raportu zalezy od tej zewnetrznej uslugi i nie jest widoczny w kodzie. AtlasExport rejestrowane w config/gdos/createAtlas.jgp (nie w config/default). PdfToX tez konwertuje PDF do obrazow/ps. PDF jest tez formatem wyjsciowym eksportu mapy (nie tylko raportow/atlasow GP) - opis zawezony. Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/atlas/BaseAtlasExport.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/convert/DocToX.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/print/PrintServer.java Dowód: PDF powstaje w GP: BaseAtlasExport (format domyslnie 'pdf', wybory png/pdf/svg/eps), PrintServer (format 'pdf', document.pdf, PDFBox), DocToX (dokument -&gt; pdf/tiff/jpeg/png przez Aspose.Words); poza GP: MapServer.display f=pdf -&gt; PdfDisplay (export mapy) oraz PagesController export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>IMS-5.3.13</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>Dane i formaty</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>Formaty wyjściowe</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="inlineStr">
+        <is>
+          <t>DOCX (Word)</t>
+        </is>
+      </c>
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>Zadanie GP PdfToX ma opcję docx, ale gałąź tworzy pusty obiekt Document i niczego nie zapisuje (stub). Raporty Ims2 delegują do usługi zewnętrznej z dowolnym parametrem format.</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="inlineStr">
+        <is>
+          <t>Brak działającego eksportu do DOCX w kodzie tego repozytorium; funkcja może działać wyłącznie przez usługę zewnętrzną.</t>
+        </is>
+      </c>
+      <c r="H236" s="5" t="inlineStr">
+        <is>
+          <t>format</t>
+        </is>
+      </c>
+      <c r="I236" s="5" t="n"/>
+      <c r="J236" s="5" t="n"/>
+      <c r="K236" s="5" t="n"/>
+      <c r="L236" s="5" t="n"/>
+      <c r="M236" s="5" t="n"/>
+      <c r="N236" s="5" t="inlineStr">
+        <is>
+          <t>kod</t>
+        </is>
+      </c>
+      <c r="O236" s="5" t="inlineStr">
+        <is>
+          <t>do weryfikacji</t>
+        </is>
+      </c>
+      <c r="P236" s="5" t="n"/>
+      <c r="Q236" s="5" t="n"/>
+      <c r="R236" s="5" t="n"/>
+      <c r="S236" s="5" t="n"/>
+      <c r="T236" s="5" t="n"/>
+      <c r="U236" s="5" t="n"/>
+      <c r="V236" s="5" t="n"/>
+      <c r="W236" s="5" t="n"/>
+      <c r="X236" s="5" t="n"/>
+      <c r="Y236" s="5" t="n"/>
+      <c r="Z236" s="5" t="n"/>
+      <c r="AA236" s="5" t="n"/>
+      <c r="AB236" s="5" t="n"/>
+      <c r="AC236" s="5" t="n"/>
+      <c r="AD236" s="5" t="n"/>
+      <c r="AE236" s="5" t="n"/>
+      <c r="AF236" s="5" t="n"/>
+      <c r="AG236" s="5" t="n"/>
+      <c r="AH236" s="5" t="n"/>
+      <c r="AI236" s="5" t="n"/>
+      <c r="AJ236" s="5" t="n"/>
+      <c r="AK236" s="5" t="n"/>
+      <c r="AL236" s="5" t="n"/>
+      <c r="AM236" s="5" t="n"/>
+      <c r="AN236" s="5" t="n"/>
+      <c r="AO236" s="5" t="n"/>
+      <c r="AP236" s="5" t="n"/>
+      <c r="AQ236" s="5" t="n"/>
+      <c r="AR236" s="5" t="n"/>
+      <c r="AS236" s="5" t="n"/>
+      <c r="AT236" s="5" t="n"/>
+      <c r="AU236" s="5" t="n"/>
+      <c r="AV236" s="5" t="n"/>
+      <c r="AW236" s="5" t="inlineStr">
+        <is>
+          <t>Wiersz dodany 2026-10-16 na podstawie analizy kodu. Weryfikacja kodu 2026-10-16: nieaktywne. Niepotwierdzone w kodzie: Wyjscie DOCX dla raportow GP jako dzialajaca funkcja; Edytowalny dokument Word jako wynik raportu - Ims2 przekazuje format do zewnetrznej uslugi, ktorej obslugi docx nie widac w repo. Szukane: docx, wordprocessingml, SaveFormat (poza xlsx/pdf/png/tiff/jpeg w DocUtils/XlsUtil/XlsTemplate) - docx jako wyjscie tylko w stubie PdfToX; mapowanie MIME docx w FileUtil/application.properties to tylko typ pliku. Mozliwe, ze raport DOCX realizuje zewnetrzny serwis raportowy (poza repo). Pliki: gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/convert/PdfToX.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/reports/Ims2.java; gp-imapserver-gp/src/main/java/pl/gispartner/imapserver/gp/tasks/convert/DocToX.java Dowód: PdfToX ma wybor 'docx' (DocX), ale galaz case "docx" tworzy tylko pusty Document i DocumentBuilder (linie 70-76) i nic nie zapisuje - stub; plik wynikowy jest utworzony bez zawartosci. DocToX wejsciowo przyjmuje DOCX, a wyjscie to pdf/tiff/jpeg/png.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AW222"/>
+  <autoFilter ref="A2:AW236"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AW1"/>
   </mergeCells>
